--- a/BOM/GTV3_Board/eSpark_BOM.xlsx
+++ b/BOM/GTV3_Board/eSpark_BOM.xlsx
@@ -1,21 +1,20 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="25427"/>
-  <workbookPr codeName="ThisWorkbook"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
+  <fileVersion appName="xl" lastEdited="6" lowestEdited="6" rupBuild="14420"/>
+  <workbookPr codeName="ThisWorkbook" defaultThemeVersion="153222"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\GitHub\OliverStanton-WaterMonitor\BOM\GTV3_Board\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Faizan\GitHub\OliverStanton-WaterMonitor\BOM\GTV3_Board\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8DD7D7FE-7C6A-41D8-B9BE-2FE2CE9C28F7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="181029"/>
+  <calcPr calcId="162913"/>
   <extLst>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
       <xcalcf:calcFeatures>
@@ -30,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="937" uniqueCount="534">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="945" uniqueCount="540">
   <si>
     <t>Component list</t>
   </si>
@@ -1632,12 +1631,42 @@
   </si>
   <si>
     <t xml:space="preserve"> (GTV3)</t>
+  </si>
+  <si>
+    <t>T491A105K025AT</t>
+  </si>
+  <si>
+    <t>C123716</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Alternate added. </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="9"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Design change needed</t>
+    </r>
+  </si>
+  <si>
+    <t>SMBJ70A/TR13</t>
+  </si>
+  <si>
+    <t>C309982</t>
+  </si>
+  <si>
+    <t>Alternate added. Design change may not be needed. Needs to be confirmed</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
   <numFmts count="3">
     <numFmt numFmtId="164" formatCode="[$-409]h:mm:ss\ AM/PM;@"/>
     <numFmt numFmtId="165" formatCode="&quot;$&quot;#,##0.0000"/>
@@ -2149,7 +2178,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="20" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="101">
+  <cellXfs count="102">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
@@ -2431,6 +2460,9 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="17" fillId="3" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="6" borderId="16" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -2773,32 +2805,32 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet1"/>
   <dimension ref="A1:T104"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="2" max="2" width="3.140625" style="26" customWidth="1"/>
+    <col min="2" max="2" width="3.1796875" style="26" customWidth="1"/>
     <col min="3" max="3" width="18" style="26" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="27.42578125" customWidth="1"/>
-    <col min="5" max="5" width="30.85546875" customWidth="1"/>
-    <col min="6" max="6" width="22.28515625" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="33.42578125" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="21.5703125" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="19.7109375" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="17.5703125" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="10.7109375" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="8.7109375" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="17.28515625" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="19.28515625" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="10.28515625" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="17.7109375" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="18.28515625" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="16.5703125" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="26.85546875" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="27.453125" customWidth="1"/>
+    <col min="5" max="5" width="30.81640625" customWidth="1"/>
+    <col min="6" max="6" width="22.26953125" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="33.453125" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="21.54296875" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="19.7265625" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="17.54296875" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="10.7265625" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="8.7265625" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="17.26953125" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="19.26953125" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="10.26953125" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="17.7265625" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="18.26953125" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="16.54296875" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="26.81640625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:19" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:19" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A1" s="1"/>
       <c r="B1" s="20"/>
       <c r="C1" s="20"/>
@@ -2819,7 +2851,7 @@
       <c r="R1" s="93"/>
       <c r="S1" s="94"/>
     </row>
-    <row r="2" spans="1:19" ht="32.25" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:19" ht="31.5" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A2" s="1"/>
       <c r="B2" s="21"/>
       <c r="C2" s="39"/>
@@ -2844,7 +2876,7 @@
       <c r="R2" s="4"/>
       <c r="S2" s="3"/>
     </row>
-    <row r="3" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A3" s="1"/>
       <c r="B3" s="22"/>
       <c r="C3" s="40"/>
@@ -2869,7 +2901,7 @@
       <c r="R3" s="5"/>
       <c r="S3" s="95"/>
     </row>
-    <row r="4" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A4" s="1"/>
       <c r="B4" s="22"/>
       <c r="C4" s="40"/>
@@ -2894,7 +2926,7 @@
       <c r="R4" s="6"/>
       <c r="S4" s="96"/>
     </row>
-    <row r="5" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A5" s="1"/>
       <c r="B5" s="22"/>
       <c r="C5" s="40"/>
@@ -2919,7 +2951,7 @@
       <c r="R5" s="6"/>
       <c r="S5" s="96"/>
     </row>
-    <row r="6" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A6" s="1"/>
       <c r="B6" s="23"/>
       <c r="C6" s="41"/>
@@ -2940,7 +2972,7 @@
       <c r="R6" s="6"/>
       <c r="S6" s="96"/>
     </row>
-    <row r="7" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A7" s="1"/>
       <c r="B7" s="24"/>
       <c r="C7" s="42"/>
@@ -2961,7 +2993,7 @@
       <c r="R7" s="8"/>
       <c r="S7" s="96"/>
     </row>
-    <row r="8" spans="1:19" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:19" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A8" s="1"/>
       <c r="B8" s="27"/>
       <c r="C8" s="43"/>
@@ -2982,7 +3014,7 @@
       <c r="R8" s="8"/>
       <c r="S8" s="96"/>
     </row>
-    <row r="9" spans="1:19" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:19" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A9" s="1"/>
       <c r="B9" s="30" t="s">
         <v>4</v>
@@ -3039,7 +3071,7 @@
         <v>410</v>
       </c>
     </row>
-    <row r="10" spans="1:19" ht="24.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:19" ht="24.5" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A10" s="1"/>
       <c r="B10" s="38">
         <f t="shared" ref="B10:B41" si="0">ROW(B10) - ROW($B$9)</f>
@@ -3095,7 +3127,7 @@
       <c r="R10" s="48"/>
       <c r="S10" s="49"/>
     </row>
-    <row r="11" spans="1:19" ht="60.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:19" ht="60.5" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A11" s="1"/>
       <c r="B11" s="38">
         <f t="shared" si="0"/>
@@ -3151,7 +3183,7 @@
       <c r="R11" s="52"/>
       <c r="S11" s="53"/>
     </row>
-    <row r="12" spans="1:19" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:19" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A12" s="1"/>
       <c r="B12" s="38">
         <f t="shared" si="0"/>
@@ -3207,7 +3239,7 @@
       <c r="R12" s="48"/>
       <c r="S12" s="48"/>
     </row>
-    <row r="13" spans="1:19" ht="48.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:19" ht="48.5" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A13" s="1"/>
       <c r="B13" s="38">
         <f t="shared" si="0"/>
@@ -3263,7 +3295,7 @@
       <c r="R13" s="52"/>
       <c r="S13" s="52"/>
     </row>
-    <row r="14" spans="1:19" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:19" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A14" s="1"/>
       <c r="B14" s="38">
         <f t="shared" si="0"/>
@@ -3319,7 +3351,7 @@
       <c r="R14" s="48"/>
       <c r="S14" s="48"/>
     </row>
-    <row r="15" spans="1:19" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:19" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A15" s="1"/>
       <c r="B15" s="38">
         <f t="shared" si="0"/>
@@ -3375,7 +3407,7 @@
       <c r="R15" s="52"/>
       <c r="S15" s="52"/>
     </row>
-    <row r="16" spans="1:19" ht="24.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:19" ht="24.5" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A16" s="1"/>
       <c r="B16" s="38">
         <f t="shared" si="0"/>
@@ -3396,11 +3428,15 @@
       <c r="G16" s="76" t="s">
         <v>195</v>
       </c>
-      <c r="H16" s="75"/>
+      <c r="H16" s="75" t="s">
+        <v>534</v>
+      </c>
       <c r="I16" s="75" t="s">
         <v>304</v>
       </c>
-      <c r="J16" s="75"/>
+      <c r="J16" s="75" t="s">
+        <v>535</v>
+      </c>
       <c r="K16" s="75" t="s">
         <v>343</v>
       </c>
@@ -3411,19 +3447,27 @@
         <f t="shared" si="1"/>
         <v>5</v>
       </c>
-      <c r="N16" s="75"/>
-      <c r="O16" s="75"/>
-      <c r="P16" s="77"/>
+      <c r="N16" s="75">
+        <v>10</v>
+      </c>
+      <c r="O16" s="101" t="s">
+        <v>417</v>
+      </c>
+      <c r="P16" s="77">
+        <v>0.187</v>
+      </c>
       <c r="Q16" s="77">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="R16" s="83" t="s">
         <v>527</v>
       </c>
-      <c r="S16" s="78"/>
-    </row>
-    <row r="17" spans="1:19" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="S16" s="78" t="s">
+        <v>536</v>
+      </c>
+    </row>
+    <row r="17" spans="1:19" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A17" s="1"/>
       <c r="B17" s="38">
         <f t="shared" si="0"/>
@@ -3479,7 +3523,7 @@
       <c r="R17" s="52"/>
       <c r="S17" s="52"/>
     </row>
-    <row r="18" spans="1:19" ht="24.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:19" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A18" s="1"/>
       <c r="B18" s="38">
         <f t="shared" si="0"/>
@@ -3535,7 +3579,7 @@
       <c r="R18" s="48"/>
       <c r="S18" s="48"/>
     </row>
-    <row r="19" spans="1:19" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:19" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A19" s="1"/>
       <c r="B19" s="38">
         <f t="shared" si="0"/>
@@ -3591,7 +3635,7 @@
       <c r="R19" s="52"/>
       <c r="S19" s="52"/>
     </row>
-    <row r="20" spans="1:19" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:19" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A20" s="1"/>
       <c r="B20" s="38">
         <f t="shared" si="0"/>
@@ -3647,7 +3691,7 @@
       <c r="R20" s="48"/>
       <c r="S20" s="48"/>
     </row>
-    <row r="21" spans="1:19" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:19" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A21" s="1"/>
       <c r="B21" s="38">
         <f t="shared" si="0"/>
@@ -3703,7 +3747,7 @@
       <c r="R21" s="52"/>
       <c r="S21" s="52"/>
     </row>
-    <row r="22" spans="1:19" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:19" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A22" s="1"/>
       <c r="B22" s="38">
         <f t="shared" si="0"/>
@@ -3759,7 +3803,7 @@
       <c r="R22" s="48"/>
       <c r="S22" s="48"/>
     </row>
-    <row r="23" spans="1:19" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:19" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A23" s="1"/>
       <c r="B23" s="38">
         <f t="shared" si="0"/>
@@ -3815,7 +3859,7 @@
       <c r="R23" s="52"/>
       <c r="S23" s="52"/>
     </row>
-    <row r="24" spans="1:19" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:19" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A24" s="1"/>
       <c r="B24" s="38">
         <f t="shared" si="0"/>
@@ -3871,7 +3915,7 @@
       <c r="R24" s="48"/>
       <c r="S24" s="48"/>
     </row>
-    <row r="25" spans="1:19" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:19" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A25" s="1"/>
       <c r="B25" s="38">
         <f t="shared" si="0"/>
@@ -3927,7 +3971,7 @@
       <c r="R25" s="52"/>
       <c r="S25" s="52"/>
     </row>
-    <row r="26" spans="1:19" ht="24.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:19" ht="24.5" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A26" s="1"/>
       <c r="B26" s="38">
         <f t="shared" si="0"/>
@@ -3983,7 +4027,7 @@
       <c r="R26" s="48"/>
       <c r="S26" s="48"/>
     </row>
-    <row r="27" spans="1:19" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:19" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A27" s="1"/>
       <c r="B27" s="38">
         <f t="shared" si="0"/>
@@ -4039,7 +4083,7 @@
       <c r="R27" s="52"/>
       <c r="S27" s="52"/>
     </row>
-    <row r="28" spans="1:19" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:19" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A28" s="1"/>
       <c r="B28" s="38">
         <f t="shared" si="0"/>
@@ -4093,7 +4137,7 @@
       <c r="R28" s="48"/>
       <c r="S28" s="48"/>
     </row>
-    <row r="29" spans="1:19" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:19" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A29" s="1"/>
       <c r="B29" s="38">
         <f t="shared" si="0"/>
@@ -4149,7 +4193,7 @@
       <c r="R29" s="52"/>
       <c r="S29" s="52"/>
     </row>
-    <row r="30" spans="1:19" ht="36.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:19" ht="24.5" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A30" s="1"/>
       <c r="B30" s="38">
         <f t="shared" si="0"/>
@@ -4170,11 +4214,15 @@
       <c r="G30" s="76" t="s">
         <v>255</v>
       </c>
-      <c r="H30" s="75"/>
+      <c r="H30" s="75" t="s">
+        <v>537</v>
+      </c>
       <c r="I30" s="75" t="s">
         <v>308</v>
       </c>
-      <c r="J30" s="75"/>
+      <c r="J30" s="75" t="s">
+        <v>538</v>
+      </c>
       <c r="K30" s="75" t="s">
         <v>413</v>
       </c>
@@ -4185,19 +4233,27 @@
         <f t="shared" si="1"/>
         <v>5</v>
       </c>
-      <c r="N30" s="75"/>
-      <c r="O30" s="75"/>
-      <c r="P30" s="77"/>
+      <c r="N30" s="75">
+        <v>10</v>
+      </c>
+      <c r="O30" s="101" t="s">
+        <v>417</v>
+      </c>
+      <c r="P30" s="77">
+        <v>6.9000000000000006E-2</v>
+      </c>
       <c r="Q30" s="77">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>0.69000000000000006</v>
       </c>
       <c r="R30" s="83" t="s">
         <v>527</v>
       </c>
-      <c r="S30" s="78"/>
-    </row>
-    <row r="31" spans="1:19" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="S30" s="78" t="s">
+        <v>539</v>
+      </c>
+    </row>
+    <row r="31" spans="1:19" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A31" s="1"/>
       <c r="B31" s="38">
         <f t="shared" si="0"/>
@@ -4253,7 +4309,7 @@
       <c r="R31" s="52"/>
       <c r="S31" s="52"/>
     </row>
-    <row r="32" spans="1:19" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:19" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A32" s="1"/>
       <c r="B32" s="38">
         <f t="shared" si="0"/>
@@ -4299,7 +4355,7 @@
       <c r="R32" s="48"/>
       <c r="S32" s="48"/>
     </row>
-    <row r="33" spans="1:19" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:19" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A33" s="1"/>
       <c r="B33" s="38">
         <f t="shared" si="0"/>
@@ -4355,7 +4411,7 @@
       <c r="R33" s="52"/>
       <c r="S33" s="52"/>
     </row>
-    <row r="34" spans="1:19" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:19" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A34" s="1"/>
       <c r="B34" s="38">
         <f t="shared" si="0"/>
@@ -4411,7 +4467,7 @@
       <c r="R34" s="48"/>
       <c r="S34" s="48"/>
     </row>
-    <row r="35" spans="1:19" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:19" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A35" s="1"/>
       <c r="B35" s="38">
         <f t="shared" si="0"/>
@@ -4467,7 +4523,7 @@
       <c r="R35" s="52"/>
       <c r="S35" s="52"/>
     </row>
-    <row r="36" spans="1:19" ht="36.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:19" ht="36.5" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A36" s="1"/>
       <c r="B36" s="38">
         <f t="shared" si="0"/>
@@ -4523,7 +4579,7 @@
       <c r="R36" s="48"/>
       <c r="S36" s="48"/>
     </row>
-    <row r="37" spans="1:19" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:19" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A37" s="1"/>
       <c r="B37" s="38">
         <f t="shared" si="0"/>
@@ -4579,7 +4635,7 @@
       <c r="R37" s="52"/>
       <c r="S37" s="52"/>
     </row>
-    <row r="38" spans="1:19" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:19" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A38" s="1"/>
       <c r="B38" s="38">
         <f t="shared" si="0"/>
@@ -4635,7 +4691,7 @@
       <c r="R38" s="48"/>
       <c r="S38" s="48"/>
     </row>
-    <row r="39" spans="1:19" ht="24.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:19" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A39" s="1"/>
       <c r="B39" s="38">
         <f t="shared" si="0"/>
@@ -4691,7 +4747,7 @@
       <c r="R39" s="52"/>
       <c r="S39" s="52"/>
     </row>
-    <row r="40" spans="1:19" ht="36.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:19" ht="36.5" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A40" s="1"/>
       <c r="B40" s="38">
         <f t="shared" si="0"/>
@@ -4747,7 +4803,7 @@
       <c r="R40" s="48"/>
       <c r="S40" s="48"/>
     </row>
-    <row r="41" spans="1:19" ht="24.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:19" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A41" s="1"/>
       <c r="B41" s="38">
         <f t="shared" si="0"/>
@@ -4803,7 +4859,7 @@
       <c r="R41" s="52"/>
       <c r="S41" s="52"/>
     </row>
-    <row r="42" spans="1:19" ht="36.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:19" ht="36.5" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A42" s="1"/>
       <c r="B42" s="38">
         <f t="shared" ref="B42:B73" si="3">ROW(B42) - ROW($B$9)</f>
@@ -4859,7 +4915,7 @@
       <c r="R42" s="48"/>
       <c r="S42" s="48"/>
     </row>
-    <row r="43" spans="1:19" ht="24.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="43" spans="1:19" ht="24.5" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A43" s="1"/>
       <c r="B43" s="38">
         <f t="shared" si="3"/>
@@ -4915,7 +4971,7 @@
       <c r="R43" s="52"/>
       <c r="S43" s="52"/>
     </row>
-    <row r="44" spans="1:19" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="44" spans="1:19" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A44" s="1"/>
       <c r="B44" s="38">
         <f t="shared" si="3"/>
@@ -4971,7 +5027,7 @@
       <c r="R44" s="48"/>
       <c r="S44" s="48"/>
     </row>
-    <row r="45" spans="1:19" ht="24.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="45" spans="1:19" ht="24.5" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A45" s="1"/>
       <c r="B45" s="38">
         <f t="shared" si="3"/>
@@ -5027,7 +5083,7 @@
       <c r="R45" s="52"/>
       <c r="S45" s="52"/>
     </row>
-    <row r="46" spans="1:19" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="46" spans="1:19" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A46" s="1"/>
       <c r="B46" s="38">
         <f t="shared" si="3"/>
@@ -5086,7 +5142,7 @@
         <v>413</v>
       </c>
     </row>
-    <row r="47" spans="1:19" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="47" spans="1:19" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A47" s="1"/>
       <c r="B47" s="38">
         <f t="shared" si="3"/>
@@ -5142,7 +5198,7 @@
       <c r="R47" s="52"/>
       <c r="S47" s="52"/>
     </row>
-    <row r="48" spans="1:19" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="48" spans="1:19" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A48" s="1"/>
       <c r="B48" s="38">
         <f t="shared" si="3"/>
@@ -5198,7 +5254,7 @@
       <c r="R48" s="48"/>
       <c r="S48" s="48"/>
     </row>
-    <row r="49" spans="1:19" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="49" spans="1:19" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A49" s="1"/>
       <c r="B49" s="38">
         <f t="shared" si="3"/>
@@ -5254,7 +5310,7 @@
       <c r="R49" s="52"/>
       <c r="S49" s="52"/>
     </row>
-    <row r="50" spans="1:19" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="50" spans="1:19" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A50" s="1"/>
       <c r="B50" s="38">
         <f t="shared" si="3"/>
@@ -5310,7 +5366,7 @@
       <c r="R50" s="48"/>
       <c r="S50" s="48"/>
     </row>
-    <row r="51" spans="1:19" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="51" spans="1:19" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A51" s="1"/>
       <c r="B51" s="38">
         <f t="shared" si="3"/>
@@ -5366,7 +5422,7 @@
       <c r="R51" s="52"/>
       <c r="S51" s="52"/>
     </row>
-    <row r="52" spans="1:19" ht="24.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="52" spans="1:19" ht="24.5" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A52" s="1"/>
       <c r="B52" s="38">
         <f t="shared" si="3"/>
@@ -5422,7 +5478,7 @@
       <c r="R52" s="48"/>
       <c r="S52" s="48"/>
     </row>
-    <row r="53" spans="1:19" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="53" spans="1:19" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A53" s="1"/>
       <c r="B53" s="38">
         <f t="shared" si="3"/>
@@ -5478,7 +5534,7 @@
       <c r="R53" s="52"/>
       <c r="S53" s="52"/>
     </row>
-    <row r="54" spans="1:19" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="54" spans="1:19" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A54" s="1"/>
       <c r="B54" s="38">
         <f t="shared" si="3"/>
@@ -5532,7 +5588,7 @@
       <c r="R54" s="48"/>
       <c r="S54" s="48"/>
     </row>
-    <row r="55" spans="1:19" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="55" spans="1:19" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A55" s="1"/>
       <c r="B55" s="38">
         <f t="shared" si="3"/>
@@ -5588,7 +5644,7 @@
       <c r="R55" s="52"/>
       <c r="S55" s="52"/>
     </row>
-    <row r="56" spans="1:19" ht="24.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="56" spans="1:19" ht="24.5" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A56" s="1"/>
       <c r="B56" s="38">
         <f t="shared" si="3"/>
@@ -5642,7 +5698,7 @@
       <c r="R56" s="48"/>
       <c r="S56" s="48"/>
     </row>
-    <row r="57" spans="1:19" ht="24.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="57" spans="1:19" ht="24.5" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A57" s="1"/>
       <c r="B57" s="38">
         <f t="shared" si="3"/>
@@ -5698,7 +5754,7 @@
       <c r="R57" s="52"/>
       <c r="S57" s="52"/>
     </row>
-    <row r="58" spans="1:19" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="58" spans="1:19" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A58" s="1"/>
       <c r="B58" s="38">
         <f t="shared" si="3"/>
@@ -5754,7 +5810,7 @@
       <c r="R58" s="48"/>
       <c r="S58" s="48"/>
     </row>
-    <row r="59" spans="1:19" ht="36.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="59" spans="1:19" ht="24.5" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A59" s="1"/>
       <c r="B59" s="38">
         <f t="shared" si="3"/>
@@ -5810,7 +5866,7 @@
       <c r="R59" s="52"/>
       <c r="S59" s="52"/>
     </row>
-    <row r="60" spans="1:19" ht="36.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="60" spans="1:19" ht="24.5" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A60" s="1"/>
       <c r="B60" s="38">
         <f t="shared" si="3"/>
@@ -5866,7 +5922,7 @@
       <c r="R60" s="48"/>
       <c r="S60" s="48"/>
     </row>
-    <row r="61" spans="1:19" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="61" spans="1:19" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A61" s="1"/>
       <c r="B61" s="38">
         <f t="shared" si="3"/>
@@ -5920,7 +5976,7 @@
       <c r="R61" s="52"/>
       <c r="S61" s="52"/>
     </row>
-    <row r="62" spans="1:19" ht="36.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="62" spans="1:19" ht="36.5" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A62" s="1"/>
       <c r="B62" s="38">
         <f t="shared" si="3"/>
@@ -5976,7 +6032,7 @@
       <c r="R62" s="48"/>
       <c r="S62" s="48"/>
     </row>
-    <row r="63" spans="1:19" ht="60.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="63" spans="1:19" ht="60.5" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A63" s="1"/>
       <c r="B63" s="38">
         <f t="shared" si="3"/>
@@ -6032,7 +6088,7 @@
       <c r="R63" s="52"/>
       <c r="S63" s="52"/>
     </row>
-    <row r="64" spans="1:19" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="64" spans="1:19" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A64" s="1"/>
       <c r="B64" s="38">
         <f t="shared" si="3"/>
@@ -6088,7 +6144,7 @@
       <c r="R64" s="48"/>
       <c r="S64" s="48"/>
     </row>
-    <row r="65" spans="1:19" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="65" spans="1:19" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A65" s="1"/>
       <c r="B65" s="38">
         <f t="shared" si="3"/>
@@ -6142,7 +6198,7 @@
       <c r="R65" s="52"/>
       <c r="S65" s="52"/>
     </row>
-    <row r="66" spans="1:19" ht="36.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="66" spans="1:19" ht="36.5" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A66" s="1"/>
       <c r="B66" s="38">
         <f t="shared" si="3"/>
@@ -6198,7 +6254,7 @@
       <c r="R66" s="48"/>
       <c r="S66" s="48"/>
     </row>
-    <row r="67" spans="1:19" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="67" spans="1:19" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A67" s="1"/>
       <c r="B67" s="38">
         <f t="shared" si="3"/>
@@ -6254,7 +6310,7 @@
       <c r="R67" s="52"/>
       <c r="S67" s="52"/>
     </row>
-    <row r="68" spans="1:19" ht="24.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="68" spans="1:19" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A68" s="1"/>
       <c r="B68" s="38">
         <f t="shared" si="3"/>
@@ -6310,7 +6366,7 @@
       <c r="R68" s="48"/>
       <c r="S68" s="48"/>
     </row>
-    <row r="69" spans="1:19" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="69" spans="1:19" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A69" s="1"/>
       <c r="B69" s="38">
         <f t="shared" si="3"/>
@@ -6366,7 +6422,7 @@
       <c r="R69" s="52"/>
       <c r="S69" s="52"/>
     </row>
-    <row r="70" spans="1:19" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="70" spans="1:19" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A70" s="1"/>
       <c r="B70" s="38">
         <f t="shared" si="3"/>
@@ -6422,7 +6478,7 @@
       <c r="R70" s="48"/>
       <c r="S70" s="48"/>
     </row>
-    <row r="71" spans="1:19" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="71" spans="1:19" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A71" s="1"/>
       <c r="B71" s="38">
         <f t="shared" si="3"/>
@@ -6478,7 +6534,7 @@
       <c r="R71" s="52"/>
       <c r="S71" s="52"/>
     </row>
-    <row r="72" spans="1:19" ht="24.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="72" spans="1:19" ht="24.5" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A72" s="1"/>
       <c r="B72" s="38">
         <f t="shared" si="3"/>
@@ -6534,7 +6590,7 @@
       <c r="R72" s="48"/>
       <c r="S72" s="48"/>
     </row>
-    <row r="73" spans="1:19" ht="24.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="73" spans="1:19" ht="24.5" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A73" s="1"/>
       <c r="B73" s="38">
         <f t="shared" si="3"/>
@@ -6590,7 +6646,7 @@
       <c r="R73" s="52"/>
       <c r="S73" s="52"/>
     </row>
-    <row r="74" spans="1:19" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="74" spans="1:19" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A74" s="1"/>
       <c r="B74" s="38">
         <f t="shared" ref="B74:B101" si="4">ROW(B74) - ROW($B$9)</f>
@@ -6646,7 +6702,7 @@
       <c r="R74" s="90"/>
       <c r="S74" s="48"/>
     </row>
-    <row r="75" spans="1:19" ht="36.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="75" spans="1:19" ht="36.5" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A75" s="1"/>
       <c r="B75" s="38">
         <f t="shared" si="4"/>
@@ -6702,7 +6758,7 @@
       <c r="R75" s="52"/>
       <c r="S75" s="52"/>
     </row>
-    <row r="76" spans="1:19" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="76" spans="1:19" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A76" s="1"/>
       <c r="B76" s="38">
         <f t="shared" si="4"/>
@@ -6758,7 +6814,7 @@
       <c r="R76" s="48"/>
       <c r="S76" s="48"/>
     </row>
-    <row r="77" spans="1:19" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="77" spans="1:19" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A77" s="1"/>
       <c r="B77" s="38">
         <f t="shared" si="4"/>
@@ -6814,7 +6870,7 @@
       <c r="R77" s="52"/>
       <c r="S77" s="52"/>
     </row>
-    <row r="78" spans="1:19" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="78" spans="1:19" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A78" s="1"/>
       <c r="B78" s="38">
         <f t="shared" si="4"/>
@@ -6870,7 +6926,7 @@
       <c r="R78" s="48"/>
       <c r="S78" s="48"/>
     </row>
-    <row r="79" spans="1:19" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="79" spans="1:19" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A79" s="1"/>
       <c r="B79" s="38">
         <f t="shared" si="4"/>
@@ -6926,7 +6982,7 @@
       <c r="R79" s="52"/>
       <c r="S79" s="52"/>
     </row>
-    <row r="80" spans="1:19" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="80" spans="1:19" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A80" s="1"/>
       <c r="B80" s="38">
         <f t="shared" si="4"/>
@@ -6982,7 +7038,7 @@
       <c r="R80" s="48"/>
       <c r="S80" s="48"/>
     </row>
-    <row r="81" spans="1:20" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="81" spans="1:20" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A81" s="1"/>
       <c r="B81" s="38">
         <f t="shared" si="4"/>
@@ -7038,7 +7094,7 @@
       <c r="R81" s="48"/>
       <c r="S81" s="48"/>
     </row>
-    <row r="82" spans="1:20" ht="24.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="82" spans="1:20" ht="24.5" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A82" s="1"/>
       <c r="B82" s="38">
         <f t="shared" si="4"/>
@@ -7094,7 +7150,7 @@
       <c r="R82" s="52"/>
       <c r="S82" s="52"/>
     </row>
-    <row r="83" spans="1:20" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="83" spans="1:20" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A83" s="1"/>
       <c r="B83" s="38">
         <f t="shared" si="4"/>
@@ -7150,7 +7206,7 @@
       <c r="R83" s="48"/>
       <c r="S83" s="48"/>
     </row>
-    <row r="84" spans="1:20" ht="24.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="84" spans="1:20" ht="24.5" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A84" s="1"/>
       <c r="B84" s="38">
         <f t="shared" si="4"/>
@@ -7206,7 +7262,7 @@
       <c r="R84" s="52"/>
       <c r="S84" s="52"/>
     </row>
-    <row r="85" spans="1:20" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="85" spans="1:20" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A85" s="1"/>
       <c r="B85" s="38">
         <f t="shared" si="4"/>
@@ -7262,7 +7318,7 @@
       <c r="R85" s="48"/>
       <c r="S85" s="48"/>
     </row>
-    <row r="86" spans="1:20" ht="36.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="86" spans="1:20" ht="36.5" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A86" s="1"/>
       <c r="B86" s="38">
         <f t="shared" si="4"/>
@@ -7321,7 +7377,7 @@
         <v>413</v>
       </c>
     </row>
-    <row r="87" spans="1:20" ht="24.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="87" spans="1:20" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A87" s="1"/>
       <c r="B87" s="38">
         <f t="shared" si="4"/>
@@ -7377,7 +7433,7 @@
       <c r="R87" s="48"/>
       <c r="S87" s="48"/>
     </row>
-    <row r="88" spans="1:20" ht="36.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="88" spans="1:20" ht="24.5" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A88" s="1"/>
       <c r="B88" s="38">
         <f t="shared" si="4"/>
@@ -7436,7 +7492,7 @@
       <c r="S88" s="68"/>
       <c r="T88" s="79"/>
     </row>
-    <row r="89" spans="1:20" ht="36.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="89" spans="1:20" ht="36.5" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A89" s="1"/>
       <c r="B89" s="38">
         <f t="shared" si="4"/>
@@ -7492,7 +7548,7 @@
       <c r="R89" s="48"/>
       <c r="S89" s="48"/>
     </row>
-    <row r="90" spans="1:20" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="90" spans="1:20" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A90" s="1"/>
       <c r="B90" s="38">
         <f t="shared" si="4"/>
@@ -7548,7 +7604,7 @@
       <c r="R90" s="52"/>
       <c r="S90" s="52"/>
     </row>
-    <row r="91" spans="1:20" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="91" spans="1:20" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A91" s="1"/>
       <c r="B91" s="38">
         <f t="shared" si="4"/>
@@ -7604,7 +7660,7 @@
       <c r="R91" s="48"/>
       <c r="S91" s="48"/>
     </row>
-    <row r="92" spans="1:20" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="92" spans="1:20" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A92" s="1"/>
       <c r="B92" s="38">
         <f t="shared" si="4"/>
@@ -7654,7 +7710,7 @@
       <c r="R92" s="68"/>
       <c r="S92" s="68"/>
     </row>
-    <row r="93" spans="1:20" ht="24.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="93" spans="1:20" ht="24.5" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A93" s="1"/>
       <c r="B93" s="38">
         <f t="shared" si="4"/>
@@ -7702,7 +7758,7 @@
       <c r="R93" s="78"/>
       <c r="S93" s="78"/>
     </row>
-    <row r="94" spans="1:20" ht="36.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="94" spans="1:20" ht="24.5" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A94" s="1"/>
       <c r="B94" s="38">
         <f t="shared" si="4"/>
@@ -7758,7 +7814,7 @@
       <c r="R94" s="52"/>
       <c r="S94" s="52"/>
     </row>
-    <row r="95" spans="1:20" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="95" spans="1:20" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A95" s="1"/>
       <c r="B95" s="38">
         <f t="shared" si="4"/>
@@ -7814,7 +7870,7 @@
       <c r="R95" s="48"/>
       <c r="S95" s="48"/>
     </row>
-    <row r="96" spans="1:20" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="96" spans="1:20" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A96" s="1"/>
       <c r="B96" s="38">
         <f t="shared" si="4"/>
@@ -7870,7 +7926,7 @@
       <c r="R96" s="52"/>
       <c r="S96" s="52"/>
     </row>
-    <row r="97" spans="1:19" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="97" spans="1:19" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A97" s="1"/>
       <c r="B97" s="38">
         <f t="shared" si="4"/>
@@ -7926,7 +7982,7 @@
       <c r="R97" s="48"/>
       <c r="S97" s="48"/>
     </row>
-    <row r="98" spans="1:19" ht="24.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="98" spans="1:19" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A98" s="1"/>
       <c r="B98" s="38">
         <f t="shared" si="4"/>
@@ -7982,7 +8038,7 @@
       <c r="R98" s="52"/>
       <c r="S98" s="52"/>
     </row>
-    <row r="99" spans="1:19" ht="36.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="99" spans="1:19" ht="36.5" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A99" s="1"/>
       <c r="B99" s="38">
         <f t="shared" si="4"/>
@@ -8028,7 +8084,7 @@
       </c>
       <c r="S99" s="78"/>
     </row>
-    <row r="100" spans="1:19" ht="36.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="100" spans="1:19" ht="36.5" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A100" s="1"/>
       <c r="B100" s="38">
         <f t="shared" si="4"/>
@@ -8084,7 +8140,7 @@
       <c r="R100" s="52"/>
       <c r="S100" s="52"/>
     </row>
-    <row r="101" spans="1:19" ht="36.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="101" spans="1:19" ht="36.5" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A101" s="1"/>
       <c r="B101" s="38">
         <f t="shared" si="4"/>
@@ -8140,7 +8196,7 @@
       <c r="R101" s="48"/>
       <c r="S101" s="48"/>
     </row>
-    <row r="102" spans="1:19" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="102" spans="1:19" ht="19" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A102" s="1"/>
       <c r="B102" s="33"/>
       <c r="C102" s="44"/>
@@ -8161,12 +8217,12 @@
       <c r="P102" s="92"/>
       <c r="Q102" s="80">
         <f>SUM(Q10:Q101)</f>
-        <v>631.50729999999987</v>
+        <v>634.06729999999993</v>
       </c>
       <c r="R102" s="97"/>
       <c r="S102" s="98"/>
     </row>
-    <row r="103" spans="1:19" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="103" spans="1:19" ht="19" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A103" s="1"/>
       <c r="B103" s="25"/>
       <c r="C103" s="45"/>
@@ -8187,12 +8243,12 @@
       <c r="P103" s="92"/>
       <c r="Q103" s="81">
         <f>Q102/5</f>
-        <v>126.30145999999998</v>
+        <v>126.81345999999999</v>
       </c>
       <c r="R103" s="99"/>
       <c r="S103" s="100"/>
     </row>
-    <row r="104" spans="1:19" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="104" spans="1:19" ht="19" thickBot="1" x14ac:dyDescent="0.4">
       <c r="N104" s="91" t="s">
         <v>530</v>
       </c>
@@ -8212,93 +8268,95 @@
     <mergeCell ref="N103:P103"/>
   </mergeCells>
   <hyperlinks>
-    <hyperlink ref="O10" r:id="rId1" xr:uid="{2E7196B7-17EB-4A3A-BBBE-F20142496754}"/>
-    <hyperlink ref="O11" r:id="rId2" xr:uid="{24227A28-30E3-4A7D-ACC9-83A1D87F2814}"/>
-    <hyperlink ref="O12" r:id="rId3" xr:uid="{FE1BDC2E-67C0-4AE9-81C8-6B7625F73009}"/>
-    <hyperlink ref="O13" r:id="rId4" xr:uid="{D8DC4BD8-BB31-4475-87D9-77DFEAD6280B}"/>
-    <hyperlink ref="O14" r:id="rId5" xr:uid="{246E2BF4-9826-45DD-ADA8-DF23CD0CC4F2}"/>
-    <hyperlink ref="O15" r:id="rId6" xr:uid="{D5F16A6B-52BB-43D6-8702-EA0BF946361C}"/>
-    <hyperlink ref="O17" r:id="rId7" xr:uid="{5C3ECBEF-9B20-4C72-85C5-B4210DC008FD}"/>
-    <hyperlink ref="O18" r:id="rId8" xr:uid="{DF660B85-FEA9-4E78-AAB7-56C6430CEBC0}"/>
-    <hyperlink ref="O19" r:id="rId9" xr:uid="{5D833557-62FB-4318-A648-FECDB3290C49}"/>
-    <hyperlink ref="O20" r:id="rId10" xr:uid="{A77EE9E0-3F15-4656-8237-A38358068CB4}"/>
-    <hyperlink ref="O21" r:id="rId11" xr:uid="{F5EBB4F2-5D4F-4F10-9A5D-BE0AC22B0A3F}"/>
-    <hyperlink ref="O22" r:id="rId12" xr:uid="{B9728DA4-DACA-488C-9A7D-342492186C6F}"/>
-    <hyperlink ref="O23" r:id="rId13" xr:uid="{0B123D99-8953-4429-A15F-E310BEC5E7FA}"/>
-    <hyperlink ref="O25" r:id="rId14" xr:uid="{B834ADAC-D117-49B4-AD7D-D27ABB605326}"/>
-    <hyperlink ref="O27" r:id="rId15" xr:uid="{A9100168-CD31-4482-9E96-2622C02A8427}"/>
-    <hyperlink ref="O36" r:id="rId16" xr:uid="{E1F1180A-2EF4-48E2-BF4F-12BEB776CA80}"/>
-    <hyperlink ref="O37" r:id="rId17" xr:uid="{C73A8BCC-86F8-4109-9AA9-B8D7DCE5EDCC}"/>
-    <hyperlink ref="O38" r:id="rId18" xr:uid="{16ECCE03-F673-4B2F-AA89-98A78F1A010A}"/>
-    <hyperlink ref="O40" r:id="rId19" xr:uid="{3D33F6C6-EBE5-436A-B4B0-9AA6044319D4}"/>
-    <hyperlink ref="O41" r:id="rId20" xr:uid="{DB56F5A6-D7AA-4B76-8F79-4DAB313B8056}"/>
-    <hyperlink ref="O42" r:id="rId21" xr:uid="{6EBA3756-8023-4DF9-8FB1-B45C9480F54D}"/>
-    <hyperlink ref="O44" r:id="rId22" xr:uid="{6D9D8028-81E4-4B1C-86B4-78EE5E55E0EB}"/>
-    <hyperlink ref="O45" r:id="rId23" xr:uid="{7D83DD86-CFE0-4253-8E76-35ABC5EA9FF9}"/>
-    <hyperlink ref="O52" r:id="rId24" xr:uid="{24B8AC9E-A4A4-4B9C-95D4-DF0D6051993E}"/>
-    <hyperlink ref="O54" r:id="rId25" xr:uid="{BE8193C0-1672-4B36-84FB-0231DA27A220}"/>
-    <hyperlink ref="O56" r:id="rId26" xr:uid="{85D9A402-8D38-44F2-B1CF-1609D072A63F}"/>
-    <hyperlink ref="O57" r:id="rId27" xr:uid="{40079AA9-5725-4514-9EE1-DE8FE129C438}"/>
-    <hyperlink ref="O58" r:id="rId28" xr:uid="{E2D69BC1-8723-468A-ADB6-F830AADF30C1}"/>
-    <hyperlink ref="O59" r:id="rId29" xr:uid="{CFE6F118-E798-4E0B-A0FA-D24BF1A27CF2}"/>
-    <hyperlink ref="O60" r:id="rId30" xr:uid="{376CDFD1-8D98-4D6F-9D9A-4DE42C6E03FB}"/>
-    <hyperlink ref="O61" r:id="rId31" xr:uid="{9DB40F78-1BDD-431D-95AE-C3066D199D75}"/>
-    <hyperlink ref="O62" r:id="rId32" xr:uid="{E0245546-F21A-4E75-B510-20365CA0EAEB}"/>
-    <hyperlink ref="O63" r:id="rId33" xr:uid="{808035A3-95B3-4248-983D-817557948EFB}"/>
-    <hyperlink ref="O64" r:id="rId34" xr:uid="{8A6D7048-03EF-4773-85D1-8F679B58BDAB}"/>
-    <hyperlink ref="O65" r:id="rId35" xr:uid="{614B8F76-BE4A-44CB-9C26-FF296675C3D7}"/>
-    <hyperlink ref="O66" r:id="rId36" xr:uid="{C518E7DB-4F17-4335-AC87-6250C5BC9693}"/>
-    <hyperlink ref="O68" r:id="rId37" xr:uid="{3043F893-14F3-4F75-A2C8-F9D922DC4D7B}"/>
-    <hyperlink ref="O69" r:id="rId38" xr:uid="{7BB98244-A23C-43F1-A7BD-4270CB605E86}"/>
-    <hyperlink ref="O70" r:id="rId39" xr:uid="{5950984E-7074-45F7-A52C-EDBB04B052A8}"/>
-    <hyperlink ref="O71" r:id="rId40" xr:uid="{D384A66B-1AB5-4A86-B1C5-6C36C800FBA3}"/>
-    <hyperlink ref="O72" r:id="rId41" xr:uid="{D416CA2F-3DBF-4BB5-91E4-50A4CCB83ABC}"/>
-    <hyperlink ref="O73" r:id="rId42" xr:uid="{312B558E-0D5B-4126-B5AB-4B06E093259E}"/>
-    <hyperlink ref="O75" r:id="rId43" xr:uid="{A83E4AFA-DC3C-4F6F-9BA8-8CCB97C53575}"/>
-    <hyperlink ref="O76" r:id="rId44" xr:uid="{5B9E54E0-D624-4CC8-8CBE-30254539C315}"/>
-    <hyperlink ref="O77" r:id="rId45" xr:uid="{6E1A2172-8A3F-4184-B677-FF40B43491AA}"/>
-    <hyperlink ref="O79" r:id="rId46" xr:uid="{93508975-457A-495D-8C37-E21E004DA0FE}"/>
-    <hyperlink ref="O80" r:id="rId47" xr:uid="{5214ED38-8616-4700-926D-3D34D13FEF40}"/>
-    <hyperlink ref="O81" r:id="rId48" xr:uid="{E4237223-8C39-4258-81BA-1615D2399A7B}"/>
-    <hyperlink ref="O82" r:id="rId49" xr:uid="{E11A4332-E6EA-43AB-B359-BCC6F3C401C4}"/>
-    <hyperlink ref="O84" r:id="rId50" xr:uid="{885B123B-5528-4DCE-9DC8-6F335281E245}"/>
-    <hyperlink ref="O87" r:id="rId51" xr:uid="{D2BCBDF9-A74C-4A3A-8625-58A6D16FA728}"/>
-    <hyperlink ref="O90" r:id="rId52" xr:uid="{C1025EBE-2B9B-4F82-8913-94E8D4B70C8C}"/>
-    <hyperlink ref="O91" r:id="rId53" xr:uid="{109E99DF-E179-48CA-A871-3FA35403FA40}"/>
-    <hyperlink ref="O95" r:id="rId54" xr:uid="{63489A4D-1105-4254-8892-B747CA8BE6D3}"/>
-    <hyperlink ref="O96" r:id="rId55" xr:uid="{205C45C9-5385-4B71-82F6-CB22EFEC03BC}"/>
-    <hyperlink ref="O97" r:id="rId56" xr:uid="{A10C0B1A-0547-4AC0-AECA-204CEC50389E}"/>
-    <hyperlink ref="O98" r:id="rId57" xr:uid="{35539995-C6B5-49E5-A00F-C4B539647ACB}"/>
-    <hyperlink ref="O100" r:id="rId58" xr:uid="{7BEA1386-CA7B-4873-84C1-67E96EA97C79}"/>
-    <hyperlink ref="O101" r:id="rId59" xr:uid="{13129D58-7A45-4DD5-AC01-7C42CB68552D}"/>
-    <hyperlink ref="O24" r:id="rId60" xr:uid="{15FF2D2C-F071-49A7-B625-CBE8AA250DF5}"/>
-    <hyperlink ref="O26" r:id="rId61" xr:uid="{296ADE2F-94C6-475B-86AF-821FD35EABB0}"/>
-    <hyperlink ref="O28" r:id="rId62" xr:uid="{F7A2A4B1-F69F-4744-BB3C-5C200EC38EA3}"/>
-    <hyperlink ref="O29" r:id="rId63" xr:uid="{83E2D456-8F59-4B57-A870-65274D6BCFFA}"/>
-    <hyperlink ref="O31" r:id="rId64" xr:uid="{A3BBB744-9B26-4CE1-9889-17E03774FE31}"/>
-    <hyperlink ref="O39" r:id="rId65" xr:uid="{58AEC90B-9C24-4FA1-AA38-1B8769D8BB10}"/>
-    <hyperlink ref="O48" r:id="rId66" xr:uid="{4890ACA3-FED0-4E73-9982-AA6245652B0C}"/>
-    <hyperlink ref="O47" r:id="rId67" xr:uid="{BD6A81E4-6E68-4A59-918A-E9410103558D}"/>
-    <hyperlink ref="O50" r:id="rId68" xr:uid="{9B3EA203-3D3F-4532-9D94-2F69C0008A4C}"/>
-    <hyperlink ref="O51" r:id="rId69" xr:uid="{F590DF7E-371F-4B84-907D-3BC02339C38C}"/>
-    <hyperlink ref="O53" r:id="rId70" xr:uid="{1DDC40AA-C78A-46B5-88ED-BC2B5B1C3144}"/>
-    <hyperlink ref="O55" r:id="rId71" xr:uid="{FDA2E76A-BC42-4AB9-871C-1D222BC8C85D}"/>
-    <hyperlink ref="O67" r:id="rId72" xr:uid="{396F44C7-85C4-4377-9EAB-0335589BB424}"/>
-    <hyperlink ref="O83" r:id="rId73" xr:uid="{7371F9D6-A4BF-4392-8175-E9F1945CB6A6}"/>
-    <hyperlink ref="O85" r:id="rId74" xr:uid="{771D1A85-11B5-407A-BCFB-293D31484E38}"/>
-    <hyperlink ref="O43" r:id="rId75" xr:uid="{430AC511-348E-4F5D-BF43-D38C5AD2ACDB}"/>
-    <hyperlink ref="O49" r:id="rId76" xr:uid="{60D3E071-83F1-4E3E-B99A-CF0DAB7C0848}"/>
-    <hyperlink ref="O74" r:id="rId77" xr:uid="{DDB3781D-CC67-4B9E-8A92-8B0D42E9ADD9}"/>
-    <hyperlink ref="O78" r:id="rId78" xr:uid="{C5625C77-072D-4075-87C6-94DA55FC1A0E}"/>
-    <hyperlink ref="O89" r:id="rId79" xr:uid="{68211B1F-D1FA-4BB4-B9AA-AD1AC06623A0}"/>
-    <hyperlink ref="O94" r:id="rId80" xr:uid="{E93B1DAB-AF05-4E07-8DD3-14AFCDF08ABE}"/>
-    <hyperlink ref="O33" r:id="rId81" xr:uid="{0249B8C0-EAE9-4590-9A86-81848E63EDB2}"/>
-    <hyperlink ref="O34" r:id="rId82" xr:uid="{ED947ABD-8BE1-4E62-8651-5924B800CF3D}"/>
-    <hyperlink ref="O35" r:id="rId83" xr:uid="{8AFB85E6-CCEB-4153-966B-2274E3C5FBE5}"/>
-    <hyperlink ref="O88" r:id="rId84" xr:uid="{508DF2DE-64C1-482F-9133-86D081915FC1}"/>
+    <hyperlink ref="O10" r:id="rId1"/>
+    <hyperlink ref="O11" r:id="rId2"/>
+    <hyperlink ref="O12" r:id="rId3"/>
+    <hyperlink ref="O13" r:id="rId4"/>
+    <hyperlink ref="O14" r:id="rId5"/>
+    <hyperlink ref="O15" r:id="rId6"/>
+    <hyperlink ref="O17" r:id="rId7"/>
+    <hyperlink ref="O18" r:id="rId8"/>
+    <hyperlink ref="O19" r:id="rId9"/>
+    <hyperlink ref="O20" r:id="rId10"/>
+    <hyperlink ref="O21" r:id="rId11"/>
+    <hyperlink ref="O22" r:id="rId12"/>
+    <hyperlink ref="O23" r:id="rId13"/>
+    <hyperlink ref="O25" r:id="rId14"/>
+    <hyperlink ref="O27" r:id="rId15"/>
+    <hyperlink ref="O36" r:id="rId16"/>
+    <hyperlink ref="O37" r:id="rId17"/>
+    <hyperlink ref="O38" r:id="rId18"/>
+    <hyperlink ref="O40" r:id="rId19"/>
+    <hyperlink ref="O41" r:id="rId20"/>
+    <hyperlink ref="O42" r:id="rId21"/>
+    <hyperlink ref="O44" r:id="rId22"/>
+    <hyperlink ref="O45" r:id="rId23"/>
+    <hyperlink ref="O52" r:id="rId24"/>
+    <hyperlink ref="O54" r:id="rId25"/>
+    <hyperlink ref="O56" r:id="rId26"/>
+    <hyperlink ref="O57" r:id="rId27"/>
+    <hyperlink ref="O58" r:id="rId28"/>
+    <hyperlink ref="O59" r:id="rId29"/>
+    <hyperlink ref="O60" r:id="rId30"/>
+    <hyperlink ref="O61" r:id="rId31"/>
+    <hyperlink ref="O62" r:id="rId32"/>
+    <hyperlink ref="O63" r:id="rId33"/>
+    <hyperlink ref="O64" r:id="rId34"/>
+    <hyperlink ref="O65" r:id="rId35"/>
+    <hyperlink ref="O66" r:id="rId36"/>
+    <hyperlink ref="O68" r:id="rId37"/>
+    <hyperlink ref="O69" r:id="rId38"/>
+    <hyperlink ref="O70" r:id="rId39"/>
+    <hyperlink ref="O71" r:id="rId40"/>
+    <hyperlink ref="O72" r:id="rId41"/>
+    <hyperlink ref="O73" r:id="rId42"/>
+    <hyperlink ref="O75" r:id="rId43"/>
+    <hyperlink ref="O76" r:id="rId44"/>
+    <hyperlink ref="O77" r:id="rId45"/>
+    <hyperlink ref="O79" r:id="rId46"/>
+    <hyperlink ref="O80" r:id="rId47"/>
+    <hyperlink ref="O81" r:id="rId48"/>
+    <hyperlink ref="O82" r:id="rId49"/>
+    <hyperlink ref="O84" r:id="rId50"/>
+    <hyperlink ref="O87" r:id="rId51"/>
+    <hyperlink ref="O90" r:id="rId52"/>
+    <hyperlink ref="O91" r:id="rId53"/>
+    <hyperlink ref="O95" r:id="rId54"/>
+    <hyperlink ref="O96" r:id="rId55"/>
+    <hyperlink ref="O97" r:id="rId56"/>
+    <hyperlink ref="O98" r:id="rId57"/>
+    <hyperlink ref="O100" r:id="rId58"/>
+    <hyperlink ref="O101" r:id="rId59"/>
+    <hyperlink ref="O24" r:id="rId60"/>
+    <hyperlink ref="O26" r:id="rId61"/>
+    <hyperlink ref="O28" r:id="rId62"/>
+    <hyperlink ref="O29" r:id="rId63"/>
+    <hyperlink ref="O31" r:id="rId64"/>
+    <hyperlink ref="O39" r:id="rId65"/>
+    <hyperlink ref="O48" r:id="rId66"/>
+    <hyperlink ref="O47" r:id="rId67"/>
+    <hyperlink ref="O50" r:id="rId68"/>
+    <hyperlink ref="O51" r:id="rId69"/>
+    <hyperlink ref="O53" r:id="rId70"/>
+    <hyperlink ref="O55" r:id="rId71"/>
+    <hyperlink ref="O67" r:id="rId72"/>
+    <hyperlink ref="O83" r:id="rId73"/>
+    <hyperlink ref="O85" r:id="rId74"/>
+    <hyperlink ref="O43" r:id="rId75"/>
+    <hyperlink ref="O49" r:id="rId76"/>
+    <hyperlink ref="O74" r:id="rId77"/>
+    <hyperlink ref="O78" r:id="rId78"/>
+    <hyperlink ref="O89" r:id="rId79"/>
+    <hyperlink ref="O94" r:id="rId80"/>
+    <hyperlink ref="O33" r:id="rId81"/>
+    <hyperlink ref="O34" r:id="rId82"/>
+    <hyperlink ref="O35" r:id="rId83"/>
+    <hyperlink ref="O88" r:id="rId84"/>
+    <hyperlink ref="O16" r:id="rId85"/>
+    <hyperlink ref="O30" r:id="rId86"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" r:id="rId85"/>
-  <drawing r:id="rId86"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId87"/>
+  <drawing r:id="rId88"/>
 </worksheet>
 </file>
--- a/BOM/GTV3_Board/eSpark_BOM.xlsx
+++ b/BOM/GTV3_Board/eSpark_BOM.xlsx
@@ -1,20 +1,21 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
-  <fileVersion appName="xl" lastEdited="6" lowestEdited="6" rupBuild="14420"/>
-  <workbookPr codeName="ThisWorkbook" defaultThemeVersion="153222"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="25427"/>
+  <workbookPr codeName="ThisWorkbook"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Faizan\GitHub\OliverStanton-WaterMonitor\BOM\GTV3_Board\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\GitHub\OliverStanton-WaterMonitor\BOM\GTV3_Board\"/>
     </mc:Choice>
   </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C0DE22F8-1DD5-40E7-A536-44D7AFDDDF8C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="162913"/>
+  <calcPr calcId="181029"/>
   <extLst>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
       <xcalcf:calcFeatures>
@@ -29,7 +30,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="945" uniqueCount="540">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="948" uniqueCount="542">
   <si>
     <t>Component list</t>
   </si>
@@ -211,9 +212,6 @@
     <t>R3</t>
   </si>
   <si>
-    <t>R4, R6, R9, R27, R42, R43, R44, R45, R46, R47, R48, R49, R52, R54, R55, R56, R63, R68, R69, R70, R72, R73, R74, R75, R86, R87, R88, R101, R102, R103, R104, R106</t>
-  </si>
-  <si>
     <t>R5, R8, R81, R89, R90, R99, R100</t>
   </si>
   <si>
@@ -592,9 +590,6 @@
     <t>Through Hole Biometric Sensors ROHS</t>
   </si>
   <si>
-    <t>CRYSTAL 8.0000MHZ 18PF SMD</t>
-  </si>
-  <si>
     <t>13.52127MHz SMD Crystal Resonator 20pF 80Ω ±10ppm ±30ppm -40℃~+85℃ SMD3225-4P Crystals ROHS</t>
   </si>
   <si>
@@ -742,9 +737,6 @@
     <t>AS312</t>
   </si>
   <si>
-    <t>9C-8.000MEEJ-T</t>
-  </si>
-  <si>
     <t>SX3B13.52127F2010F30</t>
   </si>
   <si>
@@ -1585,9 +1577,6 @@
     <t xml:space="preserve">RENESAS </t>
   </si>
   <si>
-    <t xml:space="preserve">Ye Part Obsolete ha Design me change hoga </t>
-  </si>
-  <si>
     <t>KF2EDGRC-5.08-2P</t>
   </si>
   <si>
@@ -1610,9 +1599,6 @@
   </si>
   <si>
     <t xml:space="preserve">Is part ki Shipping Cost Add ni ha price me </t>
-  </si>
-  <si>
-    <t xml:space="preserve">Is part ka alternate ni mila mjhe </t>
   </si>
   <si>
     <t xml:space="preserve">Total Component Cost </t>
@@ -1662,11 +1648,32 @@
   <si>
     <t>Alternate added. Design change may not be needed. Needs to be confirmed</t>
   </si>
+  <si>
+    <t>XC32M4-8.000-F18LJDT</t>
+  </si>
+  <si>
+    <t>HCI</t>
+  </si>
+  <si>
+    <t>8MHz</t>
+  </si>
+  <si>
+    <t>8MHz SMD Crystal Resonator 18pF 200Ω ±20ppm ±30ppm -40℃~+85℃ SMD3225-4P Crystals ROHS</t>
+  </si>
+  <si>
+    <t>C2905353</t>
+  </si>
+  <si>
+    <t>R4, R6, R9, R27, R42, R43, R44, R45, R46, R47, R48, R49, R52, R54, R55, R56, R63, R68, R69, R70, R72, R73, R74, R75, R86, R87, R88, R101, R102, R103, R104, R106, R82</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Part added in design </t>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="3">
     <numFmt numFmtId="164" formatCode="[$-409]h:mm:ss\ AM/PM;@"/>
     <numFmt numFmtId="165" formatCode="&quot;$&quot;#,##0.0000"/>
@@ -1902,7 +1909,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="24">
+  <borders count="26">
     <border>
       <left/>
       <right/>
@@ -2139,21 +2146,6 @@
       <right style="medium">
         <color indexed="64"/>
       </right>
-      <top style="medium">
-        <color indexed="64"/>
-      </top>
-      <bottom style="thin">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="medium">
-        <color indexed="64"/>
-      </left>
-      <right style="medium">
-        <color indexed="64"/>
-      </right>
       <top/>
       <bottom style="medium">
         <color indexed="64"/>
@@ -2173,30 +2165,67 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="20" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="102">
+  <cellXfs count="111">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="3" fillId="3" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="3" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="9" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="9" fillId="3" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="10" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="11" fillId="3" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="8" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="9" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="9" fillId="3" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="10" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="11" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="left" vertical="top"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="3" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="12" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="left" vertical="top"/>
       <protection locked="0"/>
     </xf>
@@ -2206,18 +2235,18 @@
     <xf numFmtId="0" fontId="15" fillId="3" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="13" fillId="3" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="13" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="11" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="11" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="13" fillId="3" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="13" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="11" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="13" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="16" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="13" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -2232,7 +2261,7 @@
     <xf numFmtId="0" fontId="6" fillId="3" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="3" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="13" fillId="3" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="top"/>
       <protection locked="0"/>
     </xf>
@@ -2242,8 +2271,8 @@
     <xf numFmtId="0" fontId="5" fillId="3" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="164" fontId="13" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="13" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="164" fontId="13" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="17" fillId="5" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -2255,45 +2284,45 @@
     <xf numFmtId="0" fontId="17" fillId="5" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="3" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="11" fillId="3" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="3" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="11" fillId="3" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment vertical="center"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="3" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="12" fillId="3" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="left" vertical="center"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="11" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="11" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="11" fillId="5" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="3" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="11" fillId="3" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="3" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="13" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="top"/>
       <protection locked="0"/>
     </xf>
@@ -2324,7 +2353,7 @@
     <xf numFmtId="0" fontId="15" fillId="3" borderId="12" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="3" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="11" fillId="3" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="11" fillId="3" borderId="6" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -2334,12 +2363,6 @@
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="18" fillId="2" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="4" borderId="17" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="2" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="20" fillId="2" borderId="16" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -2400,7 +2423,7 @@
     <xf numFmtId="166" fontId="15" fillId="3" borderId="15" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="166" fontId="15" fillId="3" borderId="22" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="166" fontId="15" fillId="3" borderId="21" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="22" fillId="6" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -2430,7 +2453,10 @@
     <xf numFmtId="0" fontId="23" fillId="2" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="24" fillId="3" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="20" fillId="6" borderId="16" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="3" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="top"/>
       <protection locked="0"/>
     </xf>
@@ -2462,7 +2488,37 @@
     <xf numFmtId="0" fontId="17" fillId="3" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="6" borderId="16" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="18" fillId="2" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="2" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="5" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="2" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="4" borderId="25" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="6" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="4" borderId="25" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="6" borderId="25" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="2" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="6" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -2805,32 +2861,38 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <sheetPr codeName="Sheet1"/>
   <dimension ref="A1:T104"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="2" max="2" width="3.1796875" style="26" customWidth="1"/>
+    <col min="2" max="2" width="3.140625" style="26" customWidth="1"/>
     <col min="3" max="3" width="18" style="26" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="27.453125" customWidth="1"/>
-    <col min="5" max="5" width="30.81640625" customWidth="1"/>
-    <col min="6" max="6" width="22.26953125" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="33.453125" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="21.54296875" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="19.7265625" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="17.54296875" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="10.7265625" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="8.7265625" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="17.26953125" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="19.26953125" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="10.26953125" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="17.7265625" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="18.26953125" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="16.54296875" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="26.81640625" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="27.42578125" customWidth="1"/>
+    <col min="5" max="5" width="30.85546875" customWidth="1"/>
+    <col min="6" max="6" width="22.28515625" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="33.42578125" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="21.5703125" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="19.7109375" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="17.5703125" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="10.7109375" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="8.7109375" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="17.28515625" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="19.28515625" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="10.28515625" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="17.7109375" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="18.28515625" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="16.5703125" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="26.85546875" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="25.28515625" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="9.28515625" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="13.28515625" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="10.42578125" bestFit="1" customWidth="1"/>
+    <col min="26" max="26" width="25.140625" bestFit="1" customWidth="1"/>
+    <col min="28" max="28" width="13.140625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:19" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="1" spans="1:19" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A1" s="1"/>
       <c r="B1" s="20"/>
       <c r="C1" s="20"/>
@@ -2841,17 +2903,17 @@
       <c r="H1" s="2"/>
       <c r="I1" s="2"/>
       <c r="J1" s="2"/>
-      <c r="K1" s="93"/>
-      <c r="L1" s="93"/>
-      <c r="M1" s="93"/>
-      <c r="N1" s="93"/>
-      <c r="O1" s="93"/>
-      <c r="P1" s="93"/>
-      <c r="Q1" s="93"/>
-      <c r="R1" s="93"/>
-      <c r="S1" s="94"/>
-    </row>
-    <row r="2" spans="1:19" ht="31.5" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="K1" s="92"/>
+      <c r="L1" s="92"/>
+      <c r="M1" s="92"/>
+      <c r="N1" s="92"/>
+      <c r="O1" s="92"/>
+      <c r="P1" s="92"/>
+      <c r="Q1" s="92"/>
+      <c r="R1" s="92"/>
+      <c r="S1" s="93"/>
+    </row>
+    <row r="2" spans="1:19" ht="32.25" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A2" s="1"/>
       <c r="B2" s="21"/>
       <c r="C2" s="39"/>
@@ -2860,7 +2922,7 @@
       </c>
       <c r="E2" s="11"/>
       <c r="F2" s="54" t="s">
-        <v>532</v>
+        <v>527</v>
       </c>
       <c r="G2" s="12"/>
       <c r="H2" s="12"/>
@@ -2876,7 +2938,7 @@
       <c r="R2" s="4"/>
       <c r="S2" s="3"/>
     </row>
-    <row r="3" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A3" s="1"/>
       <c r="B3" s="22"/>
       <c r="C3" s="40"/>
@@ -2885,7 +2947,7 @@
       </c>
       <c r="E3" s="13"/>
       <c r="F3" s="55" t="s">
-        <v>533</v>
+        <v>528</v>
       </c>
       <c r="G3" s="13"/>
       <c r="H3" s="13"/>
@@ -2899,9 +2961,9 @@
       <c r="P3" s="5"/>
       <c r="Q3" s="5"/>
       <c r="R3" s="5"/>
-      <c r="S3" s="95"/>
-    </row>
-    <row r="4" spans="1:19" x14ac:dyDescent="0.35">
+      <c r="S3" s="94"/>
+    </row>
+    <row r="4" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A4" s="1"/>
       <c r="B4" s="22"/>
       <c r="C4" s="40"/>
@@ -2910,7 +2972,7 @@
       </c>
       <c r="E4" s="13"/>
       <c r="F4" s="56" t="s">
-        <v>533</v>
+        <v>528</v>
       </c>
       <c r="G4" s="14"/>
       <c r="H4" s="14"/>
@@ -2924,9 +2986,9 @@
       <c r="P4" s="6"/>
       <c r="Q4" s="6"/>
       <c r="R4" s="6"/>
-      <c r="S4" s="96"/>
-    </row>
-    <row r="5" spans="1:19" x14ac:dyDescent="0.35">
+      <c r="S4" s="95"/>
+    </row>
+    <row r="5" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A5" s="1"/>
       <c r="B5" s="22"/>
       <c r="C5" s="40"/>
@@ -2949,9 +3011,9 @@
       <c r="P5" s="6"/>
       <c r="Q5" s="6"/>
       <c r="R5" s="6"/>
-      <c r="S5" s="96"/>
-    </row>
-    <row r="6" spans="1:19" x14ac:dyDescent="0.35">
+      <c r="S5" s="95"/>
+    </row>
+    <row r="6" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A6" s="1"/>
       <c r="B6" s="23"/>
       <c r="C6" s="41"/>
@@ -2970,9 +3032,9 @@
       <c r="P6" s="6"/>
       <c r="Q6" s="6"/>
       <c r="R6" s="6"/>
-      <c r="S6" s="96"/>
-    </row>
-    <row r="7" spans="1:19" x14ac:dyDescent="0.35">
+      <c r="S6" s="95"/>
+    </row>
+    <row r="7" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A7" s="1"/>
       <c r="B7" s="24"/>
       <c r="C7" s="42"/>
@@ -2991,9 +3053,9 @@
       <c r="P7" s="8"/>
       <c r="Q7" s="8"/>
       <c r="R7" s="8"/>
-      <c r="S7" s="96"/>
-    </row>
-    <row r="8" spans="1:19" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="S7" s="95"/>
+    </row>
+    <row r="8" spans="1:19" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A8" s="1"/>
       <c r="B8" s="27"/>
       <c r="C8" s="43"/>
@@ -3012,99 +3074,99 @@
       <c r="P8" s="8"/>
       <c r="Q8" s="8"/>
       <c r="R8" s="8"/>
-      <c r="S8" s="96"/>
-    </row>
-    <row r="9" spans="1:19" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="S8" s="95"/>
+    </row>
+    <row r="9" spans="1:19" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A9" s="1"/>
       <c r="B9" s="30" t="s">
         <v>4</v>
       </c>
       <c r="C9" s="30" t="s">
-        <v>401</v>
+        <v>398</v>
       </c>
       <c r="D9" s="30" t="s">
         <v>6</v>
       </c>
       <c r="E9" s="31" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="F9" s="30" t="s">
-        <v>190</v>
+        <v>188</v>
       </c>
       <c r="G9" s="31" t="s">
-        <v>240</v>
+        <v>237</v>
       </c>
       <c r="H9" s="30" t="s">
+        <v>399</v>
+      </c>
+      <c r="I9" s="30" t="s">
+        <v>296</v>
+      </c>
+      <c r="J9" s="30" t="s">
+        <v>400</v>
+      </c>
+      <c r="K9" s="102" t="s">
+        <v>412</v>
+      </c>
+      <c r="L9" s="30" t="s">
+        <v>384</v>
+      </c>
+      <c r="M9" s="30" t="s">
+        <v>401</v>
+      </c>
+      <c r="N9" s="30" t="s">
         <v>402</v>
       </c>
-      <c r="I9" s="30" t="s">
-        <v>299</v>
-      </c>
-      <c r="J9" s="30" t="s">
+      <c r="O9" s="30" t="s">
         <v>403</v>
       </c>
-      <c r="K9" s="30" t="s">
-        <v>415</v>
-      </c>
-      <c r="L9" s="31" t="s">
-        <v>387</v>
-      </c>
-      <c r="M9" s="30" t="s">
+      <c r="P9" s="30" t="s">
         <v>404</v>
       </c>
-      <c r="N9" s="30" t="s">
+      <c r="Q9" s="30" t="s">
         <v>405</v>
       </c>
-      <c r="O9" s="30" t="s">
+      <c r="R9" s="32" t="s">
         <v>406</v>
       </c>
-      <c r="P9" s="30" t="s">
+      <c r="S9" s="32" t="s">
         <v>407</v>
       </c>
-      <c r="Q9" s="30" t="s">
-        <v>408</v>
-      </c>
-      <c r="R9" s="32" t="s">
-        <v>409</v>
-      </c>
-      <c r="S9" s="32" t="s">
-        <v>410</v>
-      </c>
-    </row>
-    <row r="10" spans="1:19" ht="24.5" thickBot="1" x14ac:dyDescent="0.4">
+    </row>
+    <row r="10" spans="1:19" ht="24.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A10" s="1"/>
       <c r="B10" s="38">
         <f t="shared" ref="B10:B41" si="0">ROW(B10) - ROW($B$9)</f>
         <v>1</v>
       </c>
-      <c r="C10" s="84" t="s">
-        <v>388</v>
+      <c r="C10" s="82" t="s">
+        <v>385</v>
       </c>
       <c r="D10" s="46" t="s">
         <v>7</v>
       </c>
       <c r="E10" s="47" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="F10" s="46" t="s">
-        <v>411</v>
+        <v>408</v>
       </c>
       <c r="G10" s="46" t="s">
-        <v>191</v>
+        <v>189</v>
       </c>
       <c r="H10" s="46" t="s">
+        <v>410</v>
+      </c>
+      <c r="I10" s="46" t="s">
+        <v>297</v>
+      </c>
+      <c r="J10" s="46" t="s">
         <v>413</v>
       </c>
-      <c r="I10" s="46" t="s">
-        <v>300</v>
-      </c>
-      <c r="J10" s="46" t="s">
-        <v>416</v>
-      </c>
-      <c r="K10" s="58" t="s">
-        <v>341</v>
-      </c>
-      <c r="L10" s="47">
+      <c r="K10" s="103" t="s">
+        <v>338</v>
+      </c>
+      <c r="L10" s="46">
         <v>13</v>
       </c>
       <c r="M10" s="46">
@@ -3114,53 +3176,53 @@
       <c r="N10" s="46">
         <v>80</v>
       </c>
-      <c r="O10" s="61" t="s">
-        <v>417</v>
-      </c>
-      <c r="P10" s="62">
+      <c r="O10" s="59" t="s">
+        <v>414</v>
+      </c>
+      <c r="P10" s="60">
         <v>2.47E-2</v>
       </c>
-      <c r="Q10" s="62">
+      <c r="Q10" s="60">
         <f>P10*N10</f>
         <v>1.976</v>
       </c>
       <c r="R10" s="48"/>
       <c r="S10" s="49"/>
     </row>
-    <row r="11" spans="1:19" ht="60.5" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="11" spans="1:19" ht="60.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A11" s="1"/>
       <c r="B11" s="38">
         <f t="shared" si="0"/>
         <v>2</v>
       </c>
-      <c r="C11" s="85" t="s">
-        <v>388</v>
+      <c r="C11" s="83" t="s">
+        <v>385</v>
       </c>
       <c r="D11" s="50" t="s">
         <v>8</v>
       </c>
       <c r="E11" s="51" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="F11" s="50" t="s">
-        <v>192</v>
+        <v>190</v>
       </c>
       <c r="G11" s="51" t="s">
-        <v>241</v>
+        <v>238</v>
       </c>
       <c r="H11" s="50" t="s">
-        <v>413</v>
+        <v>410</v>
       </c>
       <c r="I11" s="50" t="s">
-        <v>301</v>
+        <v>298</v>
       </c>
       <c r="J11" s="50" t="s">
-        <v>418</v>
-      </c>
-      <c r="K11" s="50" t="s">
-        <v>342</v>
-      </c>
-      <c r="L11" s="51">
+        <v>415</v>
+      </c>
+      <c r="K11" s="104" t="s">
+        <v>339</v>
+      </c>
+      <c r="L11" s="50">
         <v>36</v>
       </c>
       <c r="M11" s="50">
@@ -3170,53 +3232,53 @@
       <c r="N11" s="50">
         <v>200</v>
       </c>
-      <c r="O11" s="64" t="s">
-        <v>417</v>
-      </c>
-      <c r="P11" s="63">
+      <c r="O11" s="62" t="s">
+        <v>414</v>
+      </c>
+      <c r="P11" s="61">
         <v>3.3999999999999998E-3</v>
       </c>
-      <c r="Q11" s="63">
+      <c r="Q11" s="61">
         <f t="shared" ref="Q11:Q74" si="2">P11*N11</f>
         <v>0.67999999999999994</v>
       </c>
       <c r="R11" s="52"/>
       <c r="S11" s="53"/>
     </row>
-    <row r="12" spans="1:19" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="12" spans="1:19" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A12" s="1"/>
       <c r="B12" s="38">
         <f t="shared" si="0"/>
         <v>3</v>
       </c>
-      <c r="C12" s="84" t="s">
-        <v>388</v>
+      <c r="C12" s="82" t="s">
+        <v>385</v>
       </c>
       <c r="D12" s="46" t="s">
         <v>9</v>
       </c>
       <c r="E12" s="47" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="F12" s="46" t="s">
-        <v>192</v>
+        <v>190</v>
       </c>
       <c r="G12" s="47" t="s">
-        <v>242</v>
+        <v>239</v>
       </c>
       <c r="H12" s="46" t="s">
-        <v>413</v>
+        <v>410</v>
       </c>
       <c r="I12" s="46" t="s">
-        <v>301</v>
+        <v>298</v>
       </c>
       <c r="J12" s="46" t="s">
-        <v>419</v>
-      </c>
-      <c r="K12" s="46" t="s">
-        <v>343</v>
-      </c>
-      <c r="L12" s="47">
+        <v>416</v>
+      </c>
+      <c r="K12" s="105" t="s">
+        <v>340</v>
+      </c>
+      <c r="L12" s="46">
         <v>7</v>
       </c>
       <c r="M12" s="46">
@@ -3226,53 +3288,53 @@
       <c r="N12" s="46">
         <v>50</v>
       </c>
-      <c r="O12" s="61" t="s">
-        <v>417</v>
-      </c>
-      <c r="P12" s="62">
+      <c r="O12" s="59" t="s">
+        <v>414</v>
+      </c>
+      <c r="P12" s="60">
         <v>5.8999999999999999E-3</v>
       </c>
-      <c r="Q12" s="62">
+      <c r="Q12" s="60">
         <f t="shared" si="2"/>
         <v>0.29499999999999998</v>
       </c>
       <c r="R12" s="48"/>
       <c r="S12" s="48"/>
     </row>
-    <row r="13" spans="1:19" ht="48.5" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="13" spans="1:19" ht="48.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A13" s="1"/>
       <c r="B13" s="38">
         <f t="shared" si="0"/>
         <v>4</v>
       </c>
-      <c r="C13" s="85" t="s">
-        <v>388</v>
+      <c r="C13" s="83" t="s">
+        <v>385</v>
       </c>
       <c r="D13" s="50" t="s">
         <v>10</v>
       </c>
       <c r="E13" s="51" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="F13" s="50" t="s">
-        <v>411</v>
+        <v>408</v>
       </c>
       <c r="G13" s="50" t="s">
-        <v>193</v>
+        <v>191</v>
       </c>
       <c r="H13" s="50" t="s">
-        <v>413</v>
+        <v>410</v>
       </c>
       <c r="I13" s="50" t="s">
-        <v>302</v>
+        <v>299</v>
       </c>
       <c r="J13" s="50" t="s">
-        <v>420</v>
-      </c>
-      <c r="K13" s="50" t="s">
-        <v>344</v>
-      </c>
-      <c r="L13" s="51">
+        <v>417</v>
+      </c>
+      <c r="K13" s="104" t="s">
+        <v>341</v>
+      </c>
+      <c r="L13" s="50">
         <v>5</v>
       </c>
       <c r="M13" s="50">
@@ -3282,53 +3344,53 @@
       <c r="N13" s="50">
         <v>27</v>
       </c>
-      <c r="O13" s="64" t="s">
-        <v>417</v>
-      </c>
-      <c r="P13" s="63">
+      <c r="O13" s="62" t="s">
+        <v>414</v>
+      </c>
+      <c r="P13" s="61">
         <v>0.43640000000000001</v>
       </c>
-      <c r="Q13" s="63">
+      <c r="Q13" s="61">
         <f t="shared" si="2"/>
         <v>11.7828</v>
       </c>
       <c r="R13" s="52"/>
       <c r="S13" s="52"/>
     </row>
-    <row r="14" spans="1:19" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="14" spans="1:19" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A14" s="1"/>
       <c r="B14" s="38">
         <f t="shared" si="0"/>
         <v>5</v>
       </c>
-      <c r="C14" s="84" t="s">
-        <v>388</v>
+      <c r="C14" s="82" t="s">
+        <v>385</v>
       </c>
       <c r="D14" s="46" t="s">
         <v>11</v>
       </c>
       <c r="E14" s="47" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="F14" s="46" t="s">
-        <v>411</v>
+        <v>408</v>
       </c>
       <c r="G14" s="47" t="s">
-        <v>194</v>
+        <v>192</v>
       </c>
       <c r="H14" s="46" t="s">
-        <v>413</v>
+        <v>410</v>
       </c>
       <c r="I14" s="46" t="s">
-        <v>303</v>
+        <v>300</v>
       </c>
       <c r="J14" s="46" t="s">
-        <v>421</v>
-      </c>
-      <c r="K14" s="46" t="s">
-        <v>345</v>
-      </c>
-      <c r="L14" s="47">
+        <v>418</v>
+      </c>
+      <c r="K14" s="105" t="s">
+        <v>342</v>
+      </c>
+      <c r="L14" s="46">
         <v>1</v>
       </c>
       <c r="M14" s="46">
@@ -3338,53 +3400,53 @@
       <c r="N14" s="46">
         <v>10</v>
       </c>
-      <c r="O14" s="61" t="s">
-        <v>417</v>
-      </c>
-      <c r="P14" s="62">
+      <c r="O14" s="59" t="s">
+        <v>414</v>
+      </c>
+      <c r="P14" s="60">
         <v>0.1376</v>
       </c>
-      <c r="Q14" s="62">
+      <c r="Q14" s="60">
         <f t="shared" si="2"/>
         <v>1.3759999999999999</v>
       </c>
       <c r="R14" s="48"/>
       <c r="S14" s="48"/>
     </row>
-    <row r="15" spans="1:19" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="15" spans="1:19" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A15" s="1"/>
       <c r="B15" s="38">
         <f t="shared" si="0"/>
         <v>6</v>
       </c>
-      <c r="C15" s="85" t="s">
-        <v>388</v>
+      <c r="C15" s="83" t="s">
+        <v>385</v>
       </c>
       <c r="D15" s="50" t="s">
         <v>12</v>
       </c>
       <c r="E15" s="51" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="F15" s="50" t="s">
-        <v>192</v>
+        <v>190</v>
       </c>
       <c r="G15" s="51" t="s">
-        <v>243</v>
+        <v>240</v>
       </c>
       <c r="H15" s="50" t="s">
-        <v>413</v>
+        <v>410</v>
       </c>
       <c r="I15" s="50" t="s">
-        <v>301</v>
+        <v>298</v>
       </c>
       <c r="J15" s="50" t="s">
-        <v>422</v>
-      </c>
-      <c r="K15" s="50" t="s">
-        <v>346</v>
-      </c>
-      <c r="L15" s="51">
+        <v>419</v>
+      </c>
+      <c r="K15" s="104" t="s">
+        <v>343</v>
+      </c>
+      <c r="L15" s="50">
         <v>1</v>
       </c>
       <c r="M15" s="50">
@@ -3394,113 +3456,113 @@
       <c r="N15" s="50">
         <v>100</v>
       </c>
-      <c r="O15" s="64" t="s">
-        <v>417</v>
-      </c>
-      <c r="P15" s="63">
+      <c r="O15" s="62" t="s">
+        <v>414</v>
+      </c>
+      <c r="P15" s="61">
         <v>3.0999999999999999E-3</v>
       </c>
-      <c r="Q15" s="63">
+      <c r="Q15" s="61">
         <f t="shared" si="2"/>
         <v>0.31</v>
       </c>
       <c r="R15" s="52"/>
       <c r="S15" s="52"/>
     </row>
-    <row r="16" spans="1:19" ht="24.5" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="16" spans="1:19" ht="24.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A16" s="1"/>
       <c r="B16" s="38">
         <f t="shared" si="0"/>
         <v>7</v>
       </c>
-      <c r="C16" s="86" t="s">
-        <v>388</v>
-      </c>
-      <c r="D16" s="75" t="s">
+      <c r="C16" s="84" t="s">
+        <v>385</v>
+      </c>
+      <c r="D16" s="73" t="s">
         <v>13</v>
       </c>
-      <c r="E16" s="76" t="s">
-        <v>106</v>
-      </c>
-      <c r="F16" s="75" t="s">
-        <v>411</v>
-      </c>
-      <c r="G16" s="76" t="s">
-        <v>195</v>
-      </c>
-      <c r="H16" s="75" t="s">
-        <v>534</v>
-      </c>
-      <c r="I16" s="75" t="s">
-        <v>304</v>
-      </c>
-      <c r="J16" s="75" t="s">
-        <v>535</v>
-      </c>
-      <c r="K16" s="75" t="s">
-        <v>343</v>
-      </c>
-      <c r="L16" s="76">
+      <c r="E16" s="74" t="s">
+        <v>105</v>
+      </c>
+      <c r="F16" s="73" t="s">
+        <v>408</v>
+      </c>
+      <c r="G16" s="110" t="s">
+        <v>193</v>
+      </c>
+      <c r="H16" s="73" t="s">
+        <v>529</v>
+      </c>
+      <c r="I16" s="73" t="s">
+        <v>301</v>
+      </c>
+      <c r="J16" s="73" t="s">
+        <v>530</v>
+      </c>
+      <c r="K16" s="106" t="s">
+        <v>340</v>
+      </c>
+      <c r="L16" s="73">
         <v>1</v>
       </c>
-      <c r="M16" s="75">
+      <c r="M16" s="73">
         <f t="shared" si="1"/>
         <v>5</v>
       </c>
-      <c r="N16" s="75">
+      <c r="N16" s="73">
         <v>10</v>
       </c>
-      <c r="O16" s="101" t="s">
-        <v>417</v>
-      </c>
-      <c r="P16" s="77">
+      <c r="O16" s="89" t="s">
+        <v>414</v>
+      </c>
+      <c r="P16" s="75">
         <v>0.187</v>
       </c>
-      <c r="Q16" s="77">
+      <c r="Q16" s="75">
         <f t="shared" si="2"/>
         <v>1.87</v>
       </c>
-      <c r="R16" s="83" t="s">
-        <v>527</v>
-      </c>
-      <c r="S16" s="78" t="s">
-        <v>536</v>
-      </c>
-    </row>
-    <row r="17" spans="1:19" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="R16" s="81" t="s">
+        <v>541</v>
+      </c>
+      <c r="S16" s="76" t="s">
+        <v>531</v>
+      </c>
+    </row>
+    <row r="17" spans="1:19" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A17" s="1"/>
       <c r="B17" s="38">
         <f t="shared" si="0"/>
         <v>8</v>
       </c>
-      <c r="C17" s="85" t="s">
-        <v>388</v>
+      <c r="C17" s="83" t="s">
+        <v>385</v>
       </c>
       <c r="D17" s="50" t="s">
         <v>14</v>
       </c>
       <c r="E17" s="51" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="F17" s="50" t="s">
-        <v>192</v>
+        <v>190</v>
       </c>
       <c r="G17" s="51" t="s">
-        <v>244</v>
+        <v>241</v>
       </c>
       <c r="H17" s="50" t="s">
-        <v>413</v>
+        <v>410</v>
       </c>
       <c r="I17" s="50" t="s">
-        <v>301</v>
+        <v>298</v>
       </c>
       <c r="J17" s="50" t="s">
-        <v>423</v>
-      </c>
-      <c r="K17" s="50" t="s">
-        <v>347</v>
-      </c>
-      <c r="L17" s="51">
+        <v>420</v>
+      </c>
+      <c r="K17" s="104" t="s">
+        <v>344</v>
+      </c>
+      <c r="L17" s="50">
         <v>4</v>
       </c>
       <c r="M17" s="50">
@@ -3510,53 +3572,53 @@
       <c r="N17" s="50">
         <v>100</v>
       </c>
-      <c r="O17" s="64" t="s">
-        <v>417</v>
-      </c>
-      <c r="P17" s="63">
+      <c r="O17" s="62" t="s">
+        <v>414</v>
+      </c>
+      <c r="P17" s="61">
         <v>3.3999999999999998E-3</v>
       </c>
-      <c r="Q17" s="63">
+      <c r="Q17" s="61">
         <f t="shared" si="2"/>
         <v>0.33999999999999997</v>
       </c>
       <c r="R17" s="52"/>
       <c r="S17" s="52"/>
     </row>
-    <row r="18" spans="1:19" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="18" spans="1:19" ht="24.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A18" s="1"/>
       <c r="B18" s="38">
         <f t="shared" si="0"/>
         <v>9</v>
       </c>
-      <c r="C18" s="84" t="s">
-        <v>388</v>
+      <c r="C18" s="82" t="s">
+        <v>385</v>
       </c>
       <c r="D18" s="46" t="s">
         <v>15</v>
       </c>
       <c r="E18" s="47" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="F18" s="46" t="s">
-        <v>192</v>
+        <v>190</v>
       </c>
       <c r="G18" s="47" t="s">
-        <v>245</v>
+        <v>242</v>
       </c>
       <c r="H18" s="46" t="s">
-        <v>413</v>
+        <v>410</v>
       </c>
       <c r="I18" s="46" t="s">
-        <v>301</v>
+        <v>298</v>
       </c>
       <c r="J18" s="46" t="s">
-        <v>424</v>
-      </c>
-      <c r="K18" s="46" t="s">
-        <v>348</v>
-      </c>
-      <c r="L18" s="47">
+        <v>421</v>
+      </c>
+      <c r="K18" s="105" t="s">
+        <v>345</v>
+      </c>
+      <c r="L18" s="46">
         <v>1</v>
       </c>
       <c r="M18" s="46">
@@ -3566,53 +3628,53 @@
       <c r="N18" s="46">
         <v>100</v>
       </c>
-      <c r="O18" s="61" t="s">
-        <v>417</v>
-      </c>
-      <c r="P18" s="62">
+      <c r="O18" s="59" t="s">
+        <v>414</v>
+      </c>
+      <c r="P18" s="60">
         <v>3.3999999999999998E-3</v>
       </c>
-      <c r="Q18" s="62">
+      <c r="Q18" s="60">
         <f t="shared" si="2"/>
         <v>0.33999999999999997</v>
       </c>
       <c r="R18" s="48"/>
       <c r="S18" s="48"/>
     </row>
-    <row r="19" spans="1:19" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="19" spans="1:19" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A19" s="1"/>
       <c r="B19" s="38">
         <f t="shared" si="0"/>
         <v>10</v>
       </c>
-      <c r="C19" s="85" t="s">
-        <v>388</v>
+      <c r="C19" s="83" t="s">
+        <v>385</v>
       </c>
       <c r="D19" s="50" t="s">
         <v>16</v>
       </c>
       <c r="E19" s="51" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="F19" s="50" t="s">
-        <v>192</v>
+        <v>190</v>
       </c>
       <c r="G19" s="51" t="s">
-        <v>246</v>
+        <v>243</v>
       </c>
       <c r="H19" s="50" t="s">
-        <v>413</v>
+        <v>410</v>
       </c>
       <c r="I19" s="50" t="s">
-        <v>301</v>
+        <v>298</v>
       </c>
       <c r="J19" s="50" t="s">
-        <v>425</v>
-      </c>
-      <c r="K19" s="50" t="s">
-        <v>342</v>
-      </c>
-      <c r="L19" s="51">
+        <v>422</v>
+      </c>
+      <c r="K19" s="104" t="s">
+        <v>339</v>
+      </c>
+      <c r="L19" s="50">
         <v>2</v>
       </c>
       <c r="M19" s="50">
@@ -3622,53 +3684,53 @@
       <c r="N19" s="50">
         <v>50</v>
       </c>
-      <c r="O19" s="64" t="s">
-        <v>417</v>
-      </c>
-      <c r="P19" s="63">
+      <c r="O19" s="62" t="s">
+        <v>414</v>
+      </c>
+      <c r="P19" s="61">
         <v>8.0999999999999996E-3</v>
       </c>
-      <c r="Q19" s="63">
+      <c r="Q19" s="61">
         <f t="shared" si="2"/>
         <v>0.40499999999999997</v>
       </c>
       <c r="R19" s="52"/>
       <c r="S19" s="52"/>
     </row>
-    <row r="20" spans="1:19" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="20" spans="1:19" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A20" s="1"/>
       <c r="B20" s="38">
         <f t="shared" si="0"/>
         <v>11</v>
       </c>
-      <c r="C20" s="84" t="s">
-        <v>388</v>
+      <c r="C20" s="82" t="s">
+        <v>385</v>
       </c>
       <c r="D20" s="46" t="s">
         <v>17</v>
       </c>
       <c r="E20" s="47" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="F20" s="46" t="s">
-        <v>192</v>
+        <v>190</v>
       </c>
       <c r="G20" s="47" t="s">
-        <v>247</v>
+        <v>244</v>
       </c>
       <c r="H20" s="46" t="s">
-        <v>413</v>
+        <v>410</v>
       </c>
       <c r="I20" s="46" t="s">
-        <v>301</v>
+        <v>298</v>
       </c>
       <c r="J20" s="46" t="s">
-        <v>426</v>
-      </c>
-      <c r="K20" s="46" t="s">
-        <v>349</v>
-      </c>
-      <c r="L20" s="47">
+        <v>423</v>
+      </c>
+      <c r="K20" s="105" t="s">
+        <v>346</v>
+      </c>
+      <c r="L20" s="46">
         <v>2</v>
       </c>
       <c r="M20" s="46">
@@ -3678,53 +3740,53 @@
       <c r="N20" s="46">
         <v>100</v>
       </c>
-      <c r="O20" s="61" t="s">
-        <v>417</v>
-      </c>
-      <c r="P20" s="62">
+      <c r="O20" s="59" t="s">
+        <v>414</v>
+      </c>
+      <c r="P20" s="60">
         <v>3.5999999999999999E-3</v>
       </c>
-      <c r="Q20" s="62">
+      <c r="Q20" s="60">
         <f t="shared" si="2"/>
         <v>0.36</v>
       </c>
       <c r="R20" s="48"/>
       <c r="S20" s="48"/>
     </row>
-    <row r="21" spans="1:19" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="21" spans="1:19" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A21" s="1"/>
       <c r="B21" s="38">
         <f t="shared" si="0"/>
         <v>12</v>
       </c>
-      <c r="C21" s="85" t="s">
-        <v>388</v>
+      <c r="C21" s="83" t="s">
+        <v>385</v>
       </c>
       <c r="D21" s="50" t="s">
         <v>18</v>
       </c>
       <c r="E21" s="51" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="F21" s="50" t="s">
-        <v>192</v>
+        <v>190</v>
       </c>
       <c r="G21" s="51" t="s">
-        <v>248</v>
+        <v>245</v>
       </c>
       <c r="H21" s="50" t="s">
-        <v>413</v>
+        <v>410</v>
       </c>
       <c r="I21" s="50" t="s">
-        <v>305</v>
+        <v>302</v>
       </c>
       <c r="J21" s="50" t="s">
-        <v>427</v>
-      </c>
-      <c r="K21" s="50" t="s">
-        <v>350</v>
-      </c>
-      <c r="L21" s="51">
+        <v>424</v>
+      </c>
+      <c r="K21" s="104" t="s">
+        <v>347</v>
+      </c>
+      <c r="L21" s="50">
         <v>1</v>
       </c>
       <c r="M21" s="50">
@@ -3734,53 +3796,53 @@
       <c r="N21" s="50">
         <v>50</v>
       </c>
-      <c r="O21" s="64" t="s">
-        <v>417</v>
-      </c>
-      <c r="P21" s="63">
+      <c r="O21" s="62" t="s">
+        <v>414</v>
+      </c>
+      <c r="P21" s="61">
         <v>1.1900000000000001E-2</v>
       </c>
-      <c r="Q21" s="63">
+      <c r="Q21" s="61">
         <f t="shared" si="2"/>
         <v>0.59500000000000008</v>
       </c>
       <c r="R21" s="52"/>
       <c r="S21" s="52"/>
     </row>
-    <row r="22" spans="1:19" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="22" spans="1:19" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A22" s="1"/>
       <c r="B22" s="38">
         <f t="shared" si="0"/>
         <v>13</v>
       </c>
-      <c r="C22" s="84" t="s">
-        <v>388</v>
+      <c r="C22" s="82" t="s">
+        <v>385</v>
       </c>
       <c r="D22" s="46" t="s">
         <v>19</v>
       </c>
       <c r="E22" s="47" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="F22" s="46" t="s">
-        <v>192</v>
+        <v>190</v>
       </c>
       <c r="G22" s="47" t="s">
-        <v>249</v>
+        <v>246</v>
       </c>
       <c r="H22" s="46" t="s">
-        <v>413</v>
+        <v>410</v>
       </c>
       <c r="I22" s="46" t="s">
-        <v>306</v>
+        <v>303</v>
       </c>
       <c r="J22" s="46" t="s">
-        <v>428</v>
-      </c>
-      <c r="K22" s="46" t="s">
-        <v>351</v>
-      </c>
-      <c r="L22" s="47">
+        <v>425</v>
+      </c>
+      <c r="K22" s="105" t="s">
+        <v>348</v>
+      </c>
+      <c r="L22" s="46">
         <v>1</v>
       </c>
       <c r="M22" s="46">
@@ -3790,53 +3852,53 @@
       <c r="N22" s="46">
         <v>20</v>
       </c>
-      <c r="O22" s="61" t="s">
-        <v>417</v>
-      </c>
-      <c r="P22" s="62">
+      <c r="O22" s="59" t="s">
+        <v>414</v>
+      </c>
+      <c r="P22" s="60">
         <v>3.49E-2</v>
       </c>
-      <c r="Q22" s="62">
+      <c r="Q22" s="60">
         <f t="shared" si="2"/>
         <v>0.69799999999999995</v>
       </c>
       <c r="R22" s="48"/>
       <c r="S22" s="48"/>
     </row>
-    <row r="23" spans="1:19" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="23" spans="1:19" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A23" s="1"/>
       <c r="B23" s="38">
         <f t="shared" si="0"/>
         <v>14</v>
       </c>
-      <c r="C23" s="85" t="s">
-        <v>388</v>
+      <c r="C23" s="83" t="s">
+        <v>385</v>
       </c>
       <c r="D23" s="50" t="s">
         <v>20</v>
       </c>
       <c r="E23" s="51" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="F23" s="50" t="s">
-        <v>192</v>
+        <v>190</v>
       </c>
       <c r="G23" s="51" t="s">
-        <v>250</v>
+        <v>247</v>
       </c>
       <c r="H23" s="50" t="s">
-        <v>413</v>
+        <v>410</v>
       </c>
       <c r="I23" s="50" t="s">
-        <v>301</v>
+        <v>298</v>
       </c>
       <c r="J23" s="50" t="s">
-        <v>429</v>
-      </c>
-      <c r="K23" s="50" t="s">
-        <v>352</v>
-      </c>
-      <c r="L23" s="51">
+        <v>426</v>
+      </c>
+      <c r="K23" s="104" t="s">
+        <v>349</v>
+      </c>
+      <c r="L23" s="50">
         <v>1</v>
       </c>
       <c r="M23" s="50">
@@ -3846,53 +3908,53 @@
       <c r="N23" s="50">
         <v>100</v>
       </c>
-      <c r="O23" s="64" t="s">
-        <v>417</v>
-      </c>
-      <c r="P23" s="63">
+      <c r="O23" s="62" t="s">
+        <v>414</v>
+      </c>
+      <c r="P23" s="61">
         <v>3.7000000000000002E-3</v>
       </c>
-      <c r="Q23" s="63">
+      <c r="Q23" s="61">
         <f t="shared" si="2"/>
         <v>0.37</v>
       </c>
       <c r="R23" s="52"/>
       <c r="S23" s="52"/>
     </row>
-    <row r="24" spans="1:19" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="24" spans="1:19" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A24" s="1"/>
       <c r="B24" s="38">
         <f t="shared" si="0"/>
         <v>15</v>
       </c>
-      <c r="C24" s="84" t="s">
-        <v>388</v>
+      <c r="C24" s="82" t="s">
+        <v>385</v>
       </c>
       <c r="D24" s="46" t="s">
         <v>21</v>
       </c>
       <c r="E24" s="47" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="F24" s="46" t="s">
-        <v>192</v>
-      </c>
-      <c r="G24" s="70" t="s">
-        <v>251</v>
+        <v>190</v>
+      </c>
+      <c r="G24" s="68" t="s">
+        <v>248</v>
       </c>
       <c r="H24" s="46" t="s">
-        <v>478</v>
+        <v>475</v>
       </c>
       <c r="I24" s="46" t="s">
-        <v>306</v>
+        <v>303</v>
       </c>
       <c r="J24" s="46" t="s">
-        <v>479</v>
-      </c>
-      <c r="K24" s="46" t="s">
-        <v>353</v>
-      </c>
-      <c r="L24" s="47">
+        <v>476</v>
+      </c>
+      <c r="K24" s="105" t="s">
+        <v>350</v>
+      </c>
+      <c r="L24" s="46">
         <v>1</v>
       </c>
       <c r="M24" s="46">
@@ -3902,53 +3964,53 @@
       <c r="N24" s="46">
         <v>20</v>
       </c>
-      <c r="O24" s="61" t="s">
-        <v>417</v>
-      </c>
-      <c r="P24" s="62">
+      <c r="O24" s="59" t="s">
+        <v>414</v>
+      </c>
+      <c r="P24" s="60">
         <v>3.5999999999999997E-2</v>
       </c>
-      <c r="Q24" s="62">
+      <c r="Q24" s="60">
         <f t="shared" si="2"/>
         <v>0.72</v>
       </c>
       <c r="R24" s="48"/>
       <c r="S24" s="48"/>
     </row>
-    <row r="25" spans="1:19" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="25" spans="1:19" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A25" s="1"/>
       <c r="B25" s="38">
         <f t="shared" si="0"/>
         <v>16</v>
       </c>
-      <c r="C25" s="85" t="s">
-        <v>388</v>
+      <c r="C25" s="83" t="s">
+        <v>385</v>
       </c>
       <c r="D25" s="50" t="s">
         <v>22</v>
       </c>
       <c r="E25" s="51" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="F25" s="50" t="s">
-        <v>192</v>
+        <v>190</v>
       </c>
       <c r="G25" s="51" t="s">
-        <v>252</v>
+        <v>249</v>
       </c>
       <c r="H25" s="50" t="s">
-        <v>413</v>
+        <v>410</v>
       </c>
       <c r="I25" s="50" t="s">
-        <v>301</v>
+        <v>298</v>
       </c>
       <c r="J25" s="50" t="s">
-        <v>430</v>
-      </c>
-      <c r="K25" s="50" t="s">
-        <v>354</v>
-      </c>
-      <c r="L25" s="51">
+        <v>427</v>
+      </c>
+      <c r="K25" s="104" t="s">
+        <v>351</v>
+      </c>
+      <c r="L25" s="50">
         <v>1</v>
       </c>
       <c r="M25" s="50">
@@ -3958,53 +4020,53 @@
       <c r="N25" s="50">
         <v>100</v>
       </c>
-      <c r="O25" s="64" t="s">
-        <v>417</v>
-      </c>
-      <c r="P25" s="63">
+      <c r="O25" s="62" t="s">
+        <v>414</v>
+      </c>
+      <c r="P25" s="61">
         <v>4.0000000000000001E-3</v>
       </c>
-      <c r="Q25" s="63">
+      <c r="Q25" s="61">
         <f t="shared" si="2"/>
         <v>0.4</v>
       </c>
       <c r="R25" s="52"/>
       <c r="S25" s="52"/>
     </row>
-    <row r="26" spans="1:19" ht="24.5" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="26" spans="1:19" ht="24.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A26" s="1"/>
       <c r="B26" s="38">
         <f t="shared" si="0"/>
         <v>17</v>
       </c>
-      <c r="C26" s="84" t="s">
-        <v>389</v>
+      <c r="C26" s="82" t="s">
+        <v>386</v>
       </c>
       <c r="D26" s="46" t="s">
         <v>23</v>
       </c>
       <c r="E26" s="47" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="F26" s="46" t="s">
-        <v>196</v>
+        <v>194</v>
       </c>
       <c r="G26" s="46" t="s">
-        <v>355</v>
+        <v>352</v>
       </c>
       <c r="H26" s="46" t="s">
-        <v>413</v>
+        <v>410</v>
       </c>
       <c r="I26" s="46" t="s">
-        <v>481</v>
+        <v>478</v>
       </c>
       <c r="J26" s="46" t="s">
-        <v>480</v>
-      </c>
-      <c r="K26" s="46" t="s">
-        <v>413</v>
-      </c>
-      <c r="L26" s="47">
+        <v>477</v>
+      </c>
+      <c r="K26" s="105" t="s">
+        <v>410</v>
+      </c>
+      <c r="L26" s="46">
         <v>1</v>
       </c>
       <c r="M26" s="46">
@@ -4014,53 +4076,53 @@
       <c r="N26" s="46">
         <v>20</v>
       </c>
-      <c r="O26" s="61" t="s">
-        <v>417</v>
-      </c>
-      <c r="P26" s="62">
+      <c r="O26" s="59" t="s">
+        <v>414</v>
+      </c>
+      <c r="P26" s="60">
         <v>2.98E-2</v>
       </c>
-      <c r="Q26" s="62">
+      <c r="Q26" s="60">
         <f t="shared" si="2"/>
         <v>0.59599999999999997</v>
       </c>
       <c r="R26" s="48"/>
       <c r="S26" s="48"/>
     </row>
-    <row r="27" spans="1:19" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="27" spans="1:19" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A27" s="1"/>
       <c r="B27" s="38">
         <f t="shared" si="0"/>
         <v>18</v>
       </c>
-      <c r="C27" s="85" t="s">
-        <v>389</v>
+      <c r="C27" s="83" t="s">
+        <v>386</v>
       </c>
       <c r="D27" s="50" t="s">
         <v>24</v>
       </c>
       <c r="E27" s="51" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="F27" s="50" t="s">
-        <v>196</v>
+        <v>194</v>
       </c>
       <c r="G27" s="51" t="s">
-        <v>253</v>
+        <v>250</v>
       </c>
       <c r="H27" s="50" t="s">
-        <v>413</v>
+        <v>410</v>
       </c>
       <c r="I27" s="50" t="s">
-        <v>307</v>
+        <v>304</v>
       </c>
       <c r="J27" s="50" t="s">
-        <v>431</v>
-      </c>
-      <c r="K27" s="50" t="s">
-        <v>413</v>
-      </c>
-      <c r="L27" s="51">
+        <v>428</v>
+      </c>
+      <c r="K27" s="104" t="s">
+        <v>410</v>
+      </c>
+      <c r="L27" s="50">
         <v>1</v>
       </c>
       <c r="M27" s="50">
@@ -4070,51 +4132,51 @@
       <c r="N27" s="50">
         <v>6</v>
       </c>
-      <c r="O27" s="64" t="s">
-        <v>417</v>
-      </c>
-      <c r="P27" s="63">
+      <c r="O27" s="62" t="s">
+        <v>414</v>
+      </c>
+      <c r="P27" s="61">
         <v>0.84399999999999997</v>
       </c>
-      <c r="Q27" s="63">
+      <c r="Q27" s="61">
         <f t="shared" si="2"/>
         <v>5.0640000000000001</v>
       </c>
       <c r="R27" s="52"/>
       <c r="S27" s="52"/>
     </row>
-    <row r="28" spans="1:19" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="28" spans="1:19" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A28" s="1"/>
       <c r="B28" s="38">
         <f t="shared" si="0"/>
         <v>19</v>
       </c>
-      <c r="C28" s="84" t="s">
-        <v>389</v>
+      <c r="C28" s="82" t="s">
+        <v>386</v>
       </c>
       <c r="D28" s="46" t="s">
         <v>25</v>
       </c>
       <c r="E28" s="47" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="F28" s="46" t="s">
-        <v>196</v>
+        <v>194</v>
       </c>
       <c r="G28" s="47" t="s">
-        <v>254</v>
+        <v>251</v>
       </c>
       <c r="H28" s="46"/>
       <c r="I28" s="46" t="s">
-        <v>482</v>
+        <v>479</v>
       </c>
       <c r="J28" s="46" t="s">
-        <v>483</v>
-      </c>
-      <c r="K28" s="46" t="s">
-        <v>413</v>
-      </c>
-      <c r="L28" s="47">
+        <v>480</v>
+      </c>
+      <c r="K28" s="105" t="s">
+        <v>410</v>
+      </c>
+      <c r="L28" s="46">
         <v>1</v>
       </c>
       <c r="M28" s="46">
@@ -4124,53 +4186,53 @@
       <c r="N28" s="46">
         <v>20</v>
       </c>
-      <c r="O28" s="61" t="s">
-        <v>417</v>
-      </c>
-      <c r="P28" s="62">
+      <c r="O28" s="59" t="s">
+        <v>414</v>
+      </c>
+      <c r="P28" s="60">
         <v>3.5000000000000003E-2</v>
       </c>
-      <c r="Q28" s="62">
+      <c r="Q28" s="60">
         <f t="shared" si="2"/>
         <v>0.70000000000000007</v>
       </c>
       <c r="R28" s="48"/>
       <c r="S28" s="48"/>
     </row>
-    <row r="29" spans="1:19" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="29" spans="1:19" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A29" s="1"/>
       <c r="B29" s="38">
         <f t="shared" si="0"/>
         <v>20</v>
       </c>
-      <c r="C29" s="85" t="s">
-        <v>389</v>
+      <c r="C29" s="83" t="s">
+        <v>386</v>
       </c>
       <c r="D29" s="50" t="s">
         <v>26</v>
       </c>
       <c r="E29" s="51" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="F29" s="50" t="s">
-        <v>411</v>
+        <v>408</v>
       </c>
       <c r="G29" s="50" t="s">
-        <v>197</v>
+        <v>195</v>
       </c>
       <c r="H29" s="50" t="s">
-        <v>413</v>
+        <v>410</v>
       </c>
       <c r="I29" s="50" t="s">
-        <v>484</v>
+        <v>481</v>
       </c>
       <c r="J29" s="50" t="s">
-        <v>432</v>
-      </c>
-      <c r="K29" s="50" t="s">
-        <v>413</v>
-      </c>
-      <c r="L29" s="51">
+        <v>429</v>
+      </c>
+      <c r="K29" s="104" t="s">
+        <v>410</v>
+      </c>
+      <c r="L29" s="50">
         <v>2</v>
       </c>
       <c r="M29" s="50">
@@ -4180,113 +4242,113 @@
       <c r="N29" s="50">
         <v>12</v>
       </c>
-      <c r="O29" s="64" t="s">
-        <v>417</v>
-      </c>
-      <c r="P29" s="63">
+      <c r="O29" s="62" t="s">
+        <v>414</v>
+      </c>
+      <c r="P29" s="61">
         <v>0.69610000000000005</v>
       </c>
-      <c r="Q29" s="63">
+      <c r="Q29" s="61">
         <f t="shared" si="2"/>
         <v>8.3532000000000011</v>
       </c>
       <c r="R29" s="52"/>
       <c r="S29" s="52"/>
     </row>
-    <row r="30" spans="1:19" ht="24.5" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="30" spans="1:19" ht="36.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A30" s="1"/>
       <c r="B30" s="38">
         <f t="shared" si="0"/>
         <v>21</v>
       </c>
-      <c r="C30" s="86" t="s">
-        <v>389</v>
-      </c>
-      <c r="D30" s="75" t="s">
+      <c r="C30" s="84" t="s">
+        <v>386</v>
+      </c>
+      <c r="D30" s="73" t="s">
         <v>27</v>
       </c>
-      <c r="E30" s="76" t="s">
-        <v>120</v>
-      </c>
-      <c r="F30" s="75" t="s">
-        <v>198</v>
-      </c>
-      <c r="G30" s="76" t="s">
-        <v>255</v>
-      </c>
-      <c r="H30" s="75" t="s">
-        <v>537</v>
-      </c>
-      <c r="I30" s="75" t="s">
-        <v>308</v>
-      </c>
-      <c r="J30" s="75" t="s">
-        <v>538</v>
-      </c>
-      <c r="K30" s="75" t="s">
-        <v>413</v>
-      </c>
-      <c r="L30" s="76">
+      <c r="E30" s="74" t="s">
+        <v>119</v>
+      </c>
+      <c r="F30" s="73" t="s">
+        <v>196</v>
+      </c>
+      <c r="G30" s="110" t="s">
+        <v>252</v>
+      </c>
+      <c r="H30" s="73" t="s">
+        <v>532</v>
+      </c>
+      <c r="I30" s="73" t="s">
+        <v>305</v>
+      </c>
+      <c r="J30" s="73" t="s">
+        <v>533</v>
+      </c>
+      <c r="K30" s="106" t="s">
+        <v>410</v>
+      </c>
+      <c r="L30" s="73">
         <v>1</v>
       </c>
-      <c r="M30" s="75">
+      <c r="M30" s="73">
         <f t="shared" si="1"/>
         <v>5</v>
       </c>
-      <c r="N30" s="75">
+      <c r="N30" s="73">
         <v>10</v>
       </c>
-      <c r="O30" s="101" t="s">
-        <v>417</v>
-      </c>
-      <c r="P30" s="77">
+      <c r="O30" s="89" t="s">
+        <v>414</v>
+      </c>
+      <c r="P30" s="75">
         <v>6.9000000000000006E-2</v>
       </c>
-      <c r="Q30" s="77">
+      <c r="Q30" s="75">
         <f t="shared" si="2"/>
         <v>0.69000000000000006</v>
       </c>
-      <c r="R30" s="83" t="s">
-        <v>527</v>
-      </c>
-      <c r="S30" s="78" t="s">
-        <v>539</v>
-      </c>
-    </row>
-    <row r="31" spans="1:19" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="R30" s="81" t="s">
+        <v>541</v>
+      </c>
+      <c r="S30" s="76" t="s">
+        <v>534</v>
+      </c>
+    </row>
+    <row r="31" spans="1:19" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A31" s="1"/>
       <c r="B31" s="38">
         <f t="shared" si="0"/>
         <v>22</v>
       </c>
-      <c r="C31" s="85" t="s">
-        <v>389</v>
+      <c r="C31" s="83" t="s">
+        <v>386</v>
       </c>
       <c r="D31" s="50" t="s">
         <v>28</v>
       </c>
       <c r="E31" s="51" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="F31" s="50" t="s">
-        <v>198</v>
+        <v>196</v>
       </c>
       <c r="G31" s="50" t="s">
-        <v>199</v>
+        <v>197</v>
       </c>
       <c r="H31" s="50" t="s">
-        <v>413</v>
+        <v>410</v>
       </c>
       <c r="I31" s="50" t="s">
-        <v>309</v>
+        <v>306</v>
       </c>
       <c r="J31" s="50" t="s">
-        <v>485</v>
-      </c>
-      <c r="K31" s="50" t="s">
-        <v>413</v>
-      </c>
-      <c r="L31" s="51">
+        <v>482</v>
+      </c>
+      <c r="K31" s="104" t="s">
+        <v>410</v>
+      </c>
+      <c r="L31" s="50">
         <v>1</v>
       </c>
       <c r="M31" s="50">
@@ -4296,49 +4358,49 @@
       <c r="N31" s="50">
         <v>10</v>
       </c>
-      <c r="O31" s="64" t="s">
-        <v>417</v>
-      </c>
-      <c r="P31" s="63">
+      <c r="O31" s="62" t="s">
+        <v>414</v>
+      </c>
+      <c r="P31" s="61">
         <v>6.2399999999999997E-2</v>
       </c>
-      <c r="Q31" s="63">
+      <c r="Q31" s="61">
         <f t="shared" si="2"/>
         <v>0.624</v>
       </c>
       <c r="R31" s="52"/>
       <c r="S31" s="52"/>
     </row>
-    <row r="32" spans="1:19" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="32" spans="1:19" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A32" s="1"/>
       <c r="B32" s="38">
         <f t="shared" si="0"/>
         <v>23</v>
       </c>
-      <c r="C32" s="84" t="s">
-        <v>390</v>
+      <c r="C32" s="82" t="s">
+        <v>387</v>
       </c>
       <c r="D32" s="46" t="s">
         <v>29</v>
       </c>
       <c r="E32" s="47" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="F32" s="46" t="s">
-        <v>411</v>
+        <v>408</v>
       </c>
       <c r="G32" s="47" t="s">
-        <v>200</v>
+        <v>198</v>
       </c>
       <c r="H32" s="46"/>
       <c r="I32" s="46" t="s">
-        <v>310</v>
+        <v>307</v>
       </c>
       <c r="J32" s="46"/>
-      <c r="K32" s="46" t="s">
-        <v>413</v>
-      </c>
-      <c r="L32" s="47">
+      <c r="K32" s="105" t="s">
+        <v>410</v>
+      </c>
+      <c r="L32" s="46">
         <v>1</v>
       </c>
       <c r="M32" s="46">
@@ -4347,48 +4409,48 @@
       </c>
       <c r="N32" s="46"/>
       <c r="O32" s="46"/>
-      <c r="P32" s="62"/>
-      <c r="Q32" s="62">
+      <c r="P32" s="60"/>
+      <c r="Q32" s="60">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="R32" s="48"/>
       <c r="S32" s="48"/>
     </row>
-    <row r="33" spans="1:19" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="33" spans="1:19" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A33" s="1"/>
       <c r="B33" s="38">
         <f t="shared" si="0"/>
         <v>24</v>
       </c>
-      <c r="C33" s="85" t="s">
-        <v>391</v>
+      <c r="C33" s="83" t="s">
+        <v>388</v>
       </c>
       <c r="D33" s="50" t="s">
         <v>30</v>
       </c>
       <c r="E33" s="51" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="F33" s="50" t="s">
-        <v>411</v>
-      </c>
-      <c r="G33" s="71" t="s">
-        <v>201</v>
+        <v>408</v>
+      </c>
+      <c r="G33" s="69" t="s">
+        <v>199</v>
       </c>
       <c r="H33" s="50" t="s">
-        <v>519</v>
+        <v>515</v>
       </c>
       <c r="I33" s="50" t="s">
-        <v>311</v>
+        <v>308</v>
       </c>
       <c r="J33" s="50" t="s">
-        <v>520</v>
-      </c>
-      <c r="K33" s="50" t="s">
-        <v>413</v>
-      </c>
-      <c r="L33" s="51">
+        <v>516</v>
+      </c>
+      <c r="K33" s="104" t="s">
+        <v>410</v>
+      </c>
+      <c r="L33" s="50">
         <v>9</v>
       </c>
       <c r="M33" s="50">
@@ -4398,53 +4460,53 @@
       <c r="N33" s="50">
         <v>50</v>
       </c>
-      <c r="O33" s="64" t="s">
-        <v>417</v>
-      </c>
-      <c r="P33" s="63">
+      <c r="O33" s="62" t="s">
+        <v>414</v>
+      </c>
+      <c r="P33" s="61">
         <v>7.0999999999999994E-2</v>
       </c>
-      <c r="Q33" s="63">
+      <c r="Q33" s="61">
         <f t="shared" si="2"/>
         <v>3.55</v>
       </c>
       <c r="R33" s="52"/>
       <c r="S33" s="52"/>
     </row>
-    <row r="34" spans="1:19" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="34" spans="1:19" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A34" s="1"/>
       <c r="B34" s="38">
         <f t="shared" si="0"/>
         <v>25</v>
       </c>
-      <c r="C34" s="84" t="s">
-        <v>391</v>
+      <c r="C34" s="82" t="s">
+        <v>388</v>
       </c>
       <c r="D34" s="46" t="s">
         <v>31</v>
       </c>
       <c r="E34" s="47" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="F34" s="46" t="s">
-        <v>411</v>
-      </c>
-      <c r="G34" s="70" t="s">
-        <v>202</v>
+        <v>408</v>
+      </c>
+      <c r="G34" s="68" t="s">
+        <v>200</v>
       </c>
       <c r="H34" s="46" t="s">
-        <v>521</v>
+        <v>517</v>
       </c>
       <c r="I34" s="46" t="s">
-        <v>311</v>
+        <v>308</v>
       </c>
       <c r="J34" s="46" t="s">
-        <v>522</v>
-      </c>
-      <c r="K34" s="46" t="s">
-        <v>413</v>
-      </c>
-      <c r="L34" s="47">
+        <v>518</v>
+      </c>
+      <c r="K34" s="105" t="s">
+        <v>410</v>
+      </c>
+      <c r="L34" s="46">
         <v>5</v>
       </c>
       <c r="M34" s="46">
@@ -4454,53 +4516,53 @@
       <c r="N34" s="46">
         <v>30</v>
       </c>
-      <c r="O34" s="61" t="s">
-        <v>417</v>
-      </c>
-      <c r="P34" s="62">
+      <c r="O34" s="59" t="s">
+        <v>414</v>
+      </c>
+      <c r="P34" s="60">
         <v>0.1221</v>
       </c>
-      <c r="Q34" s="62">
+      <c r="Q34" s="60">
         <f t="shared" si="2"/>
         <v>3.6629999999999998</v>
       </c>
       <c r="R34" s="48"/>
       <c r="S34" s="48"/>
     </row>
-    <row r="35" spans="1:19" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="35" spans="1:19" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A35" s="1"/>
       <c r="B35" s="38">
         <f t="shared" si="0"/>
         <v>26</v>
       </c>
-      <c r="C35" s="85" t="s">
-        <v>391</v>
+      <c r="C35" s="83" t="s">
+        <v>388</v>
       </c>
       <c r="D35" s="50" t="s">
         <v>32</v>
       </c>
       <c r="E35" s="51" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="F35" s="50" t="s">
+        <v>408</v>
+      </c>
+      <c r="G35" s="69" t="s">
+        <v>201</v>
+      </c>
+      <c r="H35" s="50" t="s">
+        <v>519</v>
+      </c>
+      <c r="I35" s="50" t="s">
+        <v>308</v>
+      </c>
+      <c r="J35" s="50" t="s">
+        <v>520</v>
+      </c>
+      <c r="K35" s="107" t="s">
         <v>411</v>
       </c>
-      <c r="G35" s="71" t="s">
-        <v>203</v>
-      </c>
-      <c r="H35" s="50" t="s">
-        <v>523</v>
-      </c>
-      <c r="I35" s="50" t="s">
-        <v>311</v>
-      </c>
-      <c r="J35" s="50" t="s">
-        <v>524</v>
-      </c>
-      <c r="K35" s="59" t="s">
-        <v>414</v>
-      </c>
-      <c r="L35" s="51">
+      <c r="L35" s="50">
         <v>1</v>
       </c>
       <c r="M35" s="50">
@@ -4510,53 +4572,53 @@
       <c r="N35" s="50">
         <v>10</v>
       </c>
-      <c r="O35" s="64" t="s">
-        <v>417</v>
-      </c>
-      <c r="P35" s="63">
+      <c r="O35" s="62" t="s">
+        <v>414</v>
+      </c>
+      <c r="P35" s="61">
         <v>0.1225</v>
       </c>
-      <c r="Q35" s="63">
+      <c r="Q35" s="61">
         <f t="shared" si="2"/>
         <v>1.2250000000000001</v>
       </c>
       <c r="R35" s="52"/>
       <c r="S35" s="52"/>
     </row>
-    <row r="36" spans="1:19" ht="36.5" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="36" spans="1:19" ht="36.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A36" s="1"/>
       <c r="B36" s="38">
         <f t="shared" si="0"/>
         <v>27</v>
       </c>
-      <c r="C36" s="84" t="s">
-        <v>390</v>
+      <c r="C36" s="82" t="s">
+        <v>387</v>
       </c>
       <c r="D36" s="46" t="s">
         <v>33</v>
       </c>
       <c r="E36" s="47" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="F36" s="46" t="s">
-        <v>411</v>
+        <v>408</v>
       </c>
       <c r="G36" s="47" t="s">
-        <v>204</v>
+        <v>202</v>
       </c>
       <c r="H36" s="46" t="s">
-        <v>413</v>
+        <v>410</v>
       </c>
       <c r="I36" s="46" t="s">
-        <v>312</v>
+        <v>309</v>
       </c>
       <c r="J36" s="46" t="s">
-        <v>433</v>
-      </c>
-      <c r="K36" s="46" t="s">
-        <v>413</v>
-      </c>
-      <c r="L36" s="47">
+        <v>430</v>
+      </c>
+      <c r="K36" s="105" t="s">
+        <v>410</v>
+      </c>
+      <c r="L36" s="46">
         <v>1</v>
       </c>
       <c r="M36" s="46">
@@ -4566,53 +4628,53 @@
       <c r="N36" s="46">
         <v>6</v>
       </c>
-      <c r="O36" s="61" t="s">
-        <v>417</v>
-      </c>
-      <c r="P36" s="62">
+      <c r="O36" s="59" t="s">
+        <v>414</v>
+      </c>
+      <c r="P36" s="60">
         <v>0.83430000000000004</v>
       </c>
-      <c r="Q36" s="62">
+      <c r="Q36" s="60">
         <f t="shared" si="2"/>
         <v>5.0058000000000007</v>
       </c>
       <c r="R36" s="48"/>
       <c r="S36" s="48"/>
     </row>
-    <row r="37" spans="1:19" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="37" spans="1:19" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A37" s="1"/>
       <c r="B37" s="38">
         <f t="shared" si="0"/>
         <v>28</v>
       </c>
-      <c r="C37" s="85" t="s">
-        <v>392</v>
+      <c r="C37" s="83" t="s">
+        <v>389</v>
       </c>
       <c r="D37" s="50" t="s">
         <v>34</v>
       </c>
       <c r="E37" s="51" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="F37" s="50" t="s">
-        <v>411</v>
+        <v>408</v>
       </c>
       <c r="G37" s="50" t="s">
-        <v>205</v>
+        <v>203</v>
       </c>
       <c r="H37" s="50" t="s">
-        <v>413</v>
+        <v>410</v>
       </c>
       <c r="I37" s="50" t="s">
-        <v>313</v>
+        <v>310</v>
       </c>
       <c r="J37" s="50" t="s">
-        <v>434</v>
-      </c>
-      <c r="K37" s="50" t="s">
-        <v>413</v>
-      </c>
-      <c r="L37" s="51">
+        <v>431</v>
+      </c>
+      <c r="K37" s="104" t="s">
+        <v>410</v>
+      </c>
+      <c r="L37" s="50">
         <v>1</v>
       </c>
       <c r="M37" s="50">
@@ -4622,53 +4684,53 @@
       <c r="N37" s="50">
         <v>10</v>
       </c>
-      <c r="O37" s="64" t="s">
-        <v>417</v>
-      </c>
-      <c r="P37" s="63">
+      <c r="O37" s="62" t="s">
+        <v>414</v>
+      </c>
+      <c r="P37" s="61">
         <v>6.7199999999999996E-2</v>
       </c>
-      <c r="Q37" s="63">
+      <c r="Q37" s="61">
         <f t="shared" si="2"/>
         <v>0.67199999999999993</v>
       </c>
       <c r="R37" s="52"/>
       <c r="S37" s="52"/>
     </row>
-    <row r="38" spans="1:19" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="38" spans="1:19" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A38" s="1"/>
       <c r="B38" s="38">
         <f t="shared" si="0"/>
         <v>29</v>
       </c>
-      <c r="C38" s="84" t="s">
-        <v>390</v>
+      <c r="C38" s="82" t="s">
+        <v>387</v>
       </c>
       <c r="D38" s="46" t="s">
         <v>35</v>
       </c>
       <c r="E38" s="47" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="F38" s="46" t="s">
-        <v>411</v>
+        <v>408</v>
       </c>
       <c r="G38" s="47" t="s">
-        <v>206</v>
+        <v>204</v>
       </c>
       <c r="H38" s="46" t="s">
-        <v>413</v>
+        <v>410</v>
       </c>
       <c r="I38" s="46" t="s">
-        <v>314</v>
+        <v>311</v>
       </c>
       <c r="J38" s="46" t="s">
-        <v>435</v>
-      </c>
-      <c r="K38" s="46" t="s">
-        <v>413</v>
-      </c>
-      <c r="L38" s="47">
+        <v>432</v>
+      </c>
+      <c r="K38" s="105" t="s">
+        <v>410</v>
+      </c>
+      <c r="L38" s="46">
         <v>1</v>
       </c>
       <c r="M38" s="46">
@@ -4678,53 +4740,53 @@
       <c r="N38" s="46">
         <v>6</v>
       </c>
-      <c r="O38" s="61" t="s">
-        <v>417</v>
-      </c>
-      <c r="P38" s="62">
+      <c r="O38" s="59" t="s">
+        <v>414</v>
+      </c>
+      <c r="P38" s="60">
         <v>0.2482</v>
       </c>
-      <c r="Q38" s="62">
+      <c r="Q38" s="60">
         <f t="shared" si="2"/>
         <v>1.4892000000000001</v>
       </c>
       <c r="R38" s="48"/>
       <c r="S38" s="48"/>
     </row>
-    <row r="39" spans="1:19" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="39" spans="1:19" ht="24.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A39" s="1"/>
       <c r="B39" s="38">
         <f t="shared" si="0"/>
         <v>30</v>
       </c>
-      <c r="C39" s="85" t="s">
-        <v>393</v>
+      <c r="C39" s="83" t="s">
+        <v>390</v>
       </c>
       <c r="D39" s="50" t="s">
         <v>36</v>
       </c>
       <c r="E39" s="51" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="F39" s="50" t="s">
-        <v>207</v>
+        <v>205</v>
       </c>
       <c r="G39" s="51" t="s">
-        <v>486</v>
+        <v>483</v>
       </c>
       <c r="H39" s="50" t="s">
-        <v>413</v>
+        <v>410</v>
       </c>
       <c r="I39" s="50" t="s">
-        <v>315</v>
+        <v>312</v>
       </c>
       <c r="J39" s="50" t="s">
-        <v>487</v>
-      </c>
-      <c r="K39" s="50" t="s">
-        <v>356</v>
-      </c>
-      <c r="L39" s="51">
+        <v>484</v>
+      </c>
+      <c r="K39" s="104" t="s">
+        <v>353</v>
+      </c>
+      <c r="L39" s="50">
         <v>1</v>
       </c>
       <c r="M39" s="50">
@@ -4734,53 +4796,53 @@
       <c r="N39" s="50">
         <v>10</v>
       </c>
-      <c r="O39" s="64" t="s">
-        <v>417</v>
-      </c>
-      <c r="P39" s="63">
+      <c r="O39" s="62" t="s">
+        <v>414</v>
+      </c>
+      <c r="P39" s="61">
         <v>4.4600000000000001E-2</v>
       </c>
-      <c r="Q39" s="63">
+      <c r="Q39" s="61">
         <f t="shared" si="2"/>
         <v>0.44600000000000001</v>
       </c>
       <c r="R39" s="52"/>
       <c r="S39" s="52"/>
     </row>
-    <row r="40" spans="1:19" ht="36.5" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="40" spans="1:19" ht="36.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A40" s="1"/>
       <c r="B40" s="38">
         <f t="shared" si="0"/>
         <v>31</v>
       </c>
-      <c r="C40" s="84" t="s">
-        <v>393</v>
+      <c r="C40" s="82" t="s">
+        <v>390</v>
       </c>
       <c r="D40" s="46" t="s">
         <v>37</v>
       </c>
       <c r="E40" s="47" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="F40" s="46" t="s">
-        <v>411</v>
+        <v>408</v>
       </c>
       <c r="G40" s="47" t="s">
-        <v>208</v>
+        <v>206</v>
       </c>
       <c r="H40" s="46" t="s">
-        <v>413</v>
+        <v>410</v>
       </c>
       <c r="I40" s="46" t="s">
-        <v>316</v>
+        <v>313</v>
       </c>
       <c r="J40" s="46" t="s">
-        <v>436</v>
-      </c>
-      <c r="K40" s="46" t="s">
-        <v>357</v>
-      </c>
-      <c r="L40" s="47">
+        <v>433</v>
+      </c>
+      <c r="K40" s="105" t="s">
+        <v>354</v>
+      </c>
+      <c r="L40" s="46">
         <v>1</v>
       </c>
       <c r="M40" s="46">
@@ -4790,53 +4852,53 @@
       <c r="N40" s="46">
         <v>6</v>
       </c>
-      <c r="O40" s="61" t="s">
-        <v>417</v>
-      </c>
-      <c r="P40" s="62">
+      <c r="O40" s="59" t="s">
+        <v>414</v>
+      </c>
+      <c r="P40" s="60">
         <v>0.54279999999999995</v>
       </c>
-      <c r="Q40" s="62">
+      <c r="Q40" s="60">
         <f t="shared" si="2"/>
         <v>3.2567999999999997</v>
       </c>
       <c r="R40" s="48"/>
       <c r="S40" s="48"/>
     </row>
-    <row r="41" spans="1:19" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="41" spans="1:19" ht="24.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A41" s="1"/>
       <c r="B41" s="38">
         <f t="shared" si="0"/>
         <v>32</v>
       </c>
-      <c r="C41" s="85" t="s">
-        <v>393</v>
+      <c r="C41" s="83" t="s">
+        <v>390</v>
       </c>
       <c r="D41" s="50" t="s">
         <v>38</v>
       </c>
       <c r="E41" s="51" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="F41" s="50" t="s">
-        <v>209</v>
+        <v>207</v>
       </c>
       <c r="G41" s="51" t="s">
-        <v>256</v>
+        <v>253</v>
       </c>
       <c r="H41" s="50" t="s">
-        <v>413</v>
+        <v>410</v>
       </c>
       <c r="I41" s="50" t="s">
-        <v>317</v>
+        <v>314</v>
       </c>
       <c r="J41" s="50" t="s">
-        <v>437</v>
-      </c>
-      <c r="K41" s="50" t="s">
-        <v>358</v>
-      </c>
-      <c r="L41" s="51">
+        <v>434</v>
+      </c>
+      <c r="K41" s="104" t="s">
+        <v>355</v>
+      </c>
+      <c r="L41" s="50">
         <v>1</v>
       </c>
       <c r="M41" s="50">
@@ -4846,53 +4908,53 @@
       <c r="N41" s="50">
         <v>10</v>
       </c>
-      <c r="O41" s="64" t="s">
-        <v>417</v>
-      </c>
-      <c r="P41" s="63">
+      <c r="O41" s="62" t="s">
+        <v>414</v>
+      </c>
+      <c r="P41" s="61">
         <v>8.9399999999999993E-2</v>
       </c>
-      <c r="Q41" s="63">
+      <c r="Q41" s="61">
         <f t="shared" si="2"/>
         <v>0.89399999999999991</v>
       </c>
       <c r="R41" s="52"/>
       <c r="S41" s="52"/>
     </row>
-    <row r="42" spans="1:19" ht="36.5" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="42" spans="1:19" ht="36.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A42" s="1"/>
       <c r="B42" s="38">
         <f t="shared" ref="B42:B73" si="3">ROW(B42) - ROW($B$9)</f>
         <v>33</v>
       </c>
-      <c r="C42" s="84" t="s">
-        <v>393</v>
+      <c r="C42" s="82" t="s">
+        <v>390</v>
       </c>
       <c r="D42" s="46" t="s">
         <v>39</v>
       </c>
       <c r="E42" s="47" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="F42" s="46" t="s">
-        <v>210</v>
+        <v>208</v>
       </c>
       <c r="G42" s="47" t="s">
-        <v>257</v>
+        <v>254</v>
       </c>
       <c r="H42" s="46" t="s">
-        <v>413</v>
+        <v>410</v>
       </c>
       <c r="I42" s="46" t="s">
-        <v>318</v>
+        <v>315</v>
       </c>
       <c r="J42" s="46" t="s">
-        <v>438</v>
-      </c>
-      <c r="K42" s="46" t="s">
-        <v>359</v>
-      </c>
-      <c r="L42" s="47">
+        <v>435</v>
+      </c>
+      <c r="K42" s="105" t="s">
+        <v>356</v>
+      </c>
+      <c r="L42" s="46">
         <v>1</v>
       </c>
       <c r="M42" s="46">
@@ -4902,53 +4964,53 @@
       <c r="N42" s="46">
         <v>10</v>
       </c>
-      <c r="O42" s="61" t="s">
-        <v>417</v>
-      </c>
-      <c r="P42" s="62">
+      <c r="O42" s="59" t="s">
+        <v>414</v>
+      </c>
+      <c r="P42" s="60">
         <v>1.01E-2</v>
       </c>
-      <c r="Q42" s="62">
+      <c r="Q42" s="60">
         <f t="shared" si="2"/>
         <v>0.10099999999999999</v>
       </c>
       <c r="R42" s="48"/>
       <c r="S42" s="48"/>
     </row>
-    <row r="43" spans="1:19" ht="24.5" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="43" spans="1:19" ht="24.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A43" s="1"/>
       <c r="B43" s="38">
         <f t="shared" si="3"/>
         <v>34</v>
       </c>
-      <c r="C43" s="85" t="s">
-        <v>394</v>
+      <c r="C43" s="83" t="s">
+        <v>391</v>
       </c>
       <c r="D43" s="50" t="s">
         <v>40</v>
       </c>
       <c r="E43" s="51" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="F43" s="50" t="s">
-        <v>211</v>
-      </c>
-      <c r="G43" s="71" t="s">
-        <v>258</v>
+        <v>209</v>
+      </c>
+      <c r="G43" s="69" t="s">
+        <v>255</v>
       </c>
       <c r="H43" s="50" t="s">
-        <v>505</v>
+        <v>502</v>
       </c>
       <c r="I43" s="50" t="s">
-        <v>319</v>
+        <v>316</v>
       </c>
       <c r="J43" s="50" t="s">
-        <v>506</v>
-      </c>
-      <c r="K43" s="50" t="s">
-        <v>413</v>
-      </c>
-      <c r="L43" s="51">
+        <v>503</v>
+      </c>
+      <c r="K43" s="104" t="s">
+        <v>410</v>
+      </c>
+      <c r="L43" s="50">
         <v>7</v>
       </c>
       <c r="M43" s="50">
@@ -4958,53 +5020,53 @@
       <c r="N43" s="50">
         <v>40</v>
       </c>
-      <c r="O43" s="64" t="s">
-        <v>417</v>
-      </c>
-      <c r="P43" s="63">
+      <c r="O43" s="62" t="s">
+        <v>414</v>
+      </c>
+      <c r="P43" s="61">
         <v>3.6799999999999999E-2</v>
       </c>
-      <c r="Q43" s="63">
+      <c r="Q43" s="61">
         <f t="shared" si="2"/>
         <v>1.472</v>
       </c>
       <c r="R43" s="52"/>
       <c r="S43" s="52"/>
     </row>
-    <row r="44" spans="1:19" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="44" spans="1:19" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A44" s="1"/>
       <c r="B44" s="38">
         <f t="shared" si="3"/>
         <v>35</v>
       </c>
-      <c r="C44" s="84" t="s">
-        <v>394</v>
+      <c r="C44" s="82" t="s">
+        <v>391</v>
       </c>
       <c r="D44" s="46" t="s">
         <v>41</v>
       </c>
       <c r="E44" s="47" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="F44" s="46" t="s">
-        <v>411</v>
+        <v>408</v>
       </c>
       <c r="G44" s="47" t="s">
-        <v>259</v>
+        <v>256</v>
       </c>
       <c r="H44" s="46" t="s">
-        <v>413</v>
+        <v>410</v>
       </c>
       <c r="I44" s="46" t="s">
-        <v>320</v>
+        <v>317</v>
       </c>
       <c r="J44" s="46" t="s">
-        <v>439</v>
-      </c>
-      <c r="K44" s="46" t="s">
-        <v>413</v>
-      </c>
-      <c r="L44" s="47">
+        <v>436</v>
+      </c>
+      <c r="K44" s="105" t="s">
+        <v>410</v>
+      </c>
+      <c r="L44" s="46">
         <v>1</v>
       </c>
       <c r="M44" s="46">
@@ -5014,53 +5076,53 @@
       <c r="N44" s="46">
         <v>10</v>
       </c>
-      <c r="O44" s="61" t="s">
-        <v>417</v>
-      </c>
-      <c r="P44" s="62">
+      <c r="O44" s="59" t="s">
+        <v>414</v>
+      </c>
+      <c r="P44" s="60">
         <v>0.1363</v>
       </c>
-      <c r="Q44" s="62">
+      <c r="Q44" s="60">
         <f t="shared" si="2"/>
         <v>1.363</v>
       </c>
       <c r="R44" s="48"/>
       <c r="S44" s="48"/>
     </row>
-    <row r="45" spans="1:19" ht="24.5" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="45" spans="1:19" ht="24.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A45" s="1"/>
       <c r="B45" s="38">
         <f t="shared" si="3"/>
         <v>36</v>
       </c>
-      <c r="C45" s="85" t="s">
-        <v>395</v>
+      <c r="C45" s="83" t="s">
+        <v>392</v>
       </c>
       <c r="D45" s="50" t="s">
         <v>42</v>
       </c>
       <c r="E45" s="51" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="F45" s="50" t="s">
-        <v>411</v>
+        <v>408</v>
       </c>
       <c r="G45" s="50" t="s">
-        <v>212</v>
+        <v>210</v>
       </c>
       <c r="H45" s="50" t="s">
-        <v>413</v>
+        <v>410</v>
       </c>
       <c r="I45" s="50" t="s">
-        <v>321</v>
+        <v>318</v>
       </c>
       <c r="J45" s="50" t="s">
-        <v>440</v>
-      </c>
-      <c r="K45" s="50" t="s">
-        <v>413</v>
-      </c>
-      <c r="L45" s="51">
+        <v>437</v>
+      </c>
+      <c r="K45" s="104" t="s">
+        <v>410</v>
+      </c>
+      <c r="L45" s="50">
         <v>1</v>
       </c>
       <c r="M45" s="50">
@@ -5070,53 +5132,53 @@
       <c r="N45" s="50">
         <v>6</v>
       </c>
-      <c r="O45" s="64" t="s">
-        <v>417</v>
-      </c>
-      <c r="P45" s="63">
+      <c r="O45" s="62" t="s">
+        <v>414</v>
+      </c>
+      <c r="P45" s="61">
         <v>0.46300000000000002</v>
       </c>
-      <c r="Q45" s="63">
+      <c r="Q45" s="61">
         <f t="shared" si="2"/>
         <v>2.778</v>
       </c>
       <c r="R45" s="52"/>
       <c r="S45" s="52"/>
     </row>
-    <row r="46" spans="1:19" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="46" spans="1:19" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A46" s="1"/>
       <c r="B46" s="38">
         <f t="shared" si="3"/>
         <v>37</v>
       </c>
-      <c r="C46" s="84" t="s">
-        <v>360</v>
+      <c r="C46" s="82" t="s">
+        <v>357</v>
       </c>
       <c r="D46" s="46" t="s">
         <v>43</v>
       </c>
       <c r="E46" s="47" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="F46" s="46" t="s">
-        <v>411</v>
+        <v>408</v>
       </c>
       <c r="G46" s="47" t="s">
-        <v>413</v>
+        <v>410</v>
       </c>
       <c r="H46" s="46" t="s">
-        <v>413</v>
+        <v>410</v>
       </c>
       <c r="I46" s="46" t="s">
-        <v>413</v>
+        <v>410</v>
       </c>
       <c r="J46" s="46" t="s">
-        <v>413</v>
-      </c>
-      <c r="K46" s="46" t="s">
-        <v>413</v>
-      </c>
-      <c r="L46" s="47">
+        <v>410</v>
+      </c>
+      <c r="K46" s="105" t="s">
+        <v>410</v>
+      </c>
+      <c r="L46" s="46">
         <v>1</v>
       </c>
       <c r="M46" s="46">
@@ -5124,58 +5186,58 @@
         <v>5</v>
       </c>
       <c r="N46" s="46" t="s">
-        <v>413</v>
+        <v>410</v>
       </c>
       <c r="O46" s="46" t="s">
-        <v>413</v>
-      </c>
-      <c r="P46" s="62" t="s">
-        <v>413</v>
-      </c>
-      <c r="Q46" s="62" t="s">
-        <v>413</v>
-      </c>
-      <c r="R46" s="89" t="s">
-        <v>531</v>
+        <v>410</v>
+      </c>
+      <c r="P46" s="60" t="s">
+        <v>410</v>
+      </c>
+      <c r="Q46" s="60" t="s">
+        <v>410</v>
+      </c>
+      <c r="R46" s="87" t="s">
+        <v>526</v>
       </c>
       <c r="S46" s="48" t="s">
-        <v>413</v>
-      </c>
-    </row>
-    <row r="47" spans="1:19" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+        <v>410</v>
+      </c>
+    </row>
+    <row r="47" spans="1:19" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A47" s="1"/>
       <c r="B47" s="38">
         <f t="shared" si="3"/>
         <v>38</v>
       </c>
-      <c r="C47" s="85" t="s">
-        <v>392</v>
+      <c r="C47" s="83" t="s">
+        <v>389</v>
       </c>
       <c r="D47" s="50" t="s">
         <v>44</v>
       </c>
       <c r="E47" s="51" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="F47" s="50" t="s">
-        <v>213</v>
-      </c>
-      <c r="G47" s="71">
+        <v>211</v>
+      </c>
+      <c r="G47" s="69">
         <v>61300311121</v>
       </c>
       <c r="H47" s="50" t="s">
-        <v>490</v>
+        <v>487</v>
       </c>
       <c r="I47" s="50" t="s">
-        <v>322</v>
+        <v>319</v>
       </c>
       <c r="J47" s="50" t="s">
-        <v>491</v>
-      </c>
-      <c r="K47" s="50" t="s">
-        <v>413</v>
-      </c>
-      <c r="L47" s="51">
+        <v>488</v>
+      </c>
+      <c r="K47" s="104" t="s">
+        <v>410</v>
+      </c>
+      <c r="L47" s="50">
         <v>2</v>
       </c>
       <c r="M47" s="50">
@@ -5185,53 +5247,53 @@
       <c r="N47" s="50">
         <v>20</v>
       </c>
-      <c r="O47" s="64" t="s">
-        <v>417</v>
-      </c>
-      <c r="P47" s="63">
+      <c r="O47" s="62" t="s">
+        <v>414</v>
+      </c>
+      <c r="P47" s="61">
         <v>6.0699999999999997E-2</v>
       </c>
-      <c r="Q47" s="63">
+      <c r="Q47" s="61">
         <f t="shared" si="2"/>
         <v>1.214</v>
       </c>
       <c r="R47" s="52"/>
       <c r="S47" s="52"/>
     </row>
-    <row r="48" spans="1:19" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="48" spans="1:19" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A48" s="1"/>
       <c r="B48" s="38">
         <f t="shared" si="3"/>
         <v>39</v>
       </c>
-      <c r="C48" s="84" t="s">
-        <v>392</v>
+      <c r="C48" s="82" t="s">
+        <v>389</v>
       </c>
       <c r="D48" s="46" t="s">
         <v>45</v>
       </c>
       <c r="E48" s="47" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="F48" s="46" t="s">
-        <v>214</v>
-      </c>
-      <c r="G48" s="70">
+        <v>212</v>
+      </c>
+      <c r="G48" s="68">
         <v>61300611121</v>
       </c>
       <c r="H48" s="46" t="s">
-        <v>488</v>
+        <v>485</v>
       </c>
       <c r="I48" s="46" t="s">
-        <v>322</v>
+        <v>319</v>
       </c>
       <c r="J48" s="46" t="s">
-        <v>489</v>
-      </c>
-      <c r="K48" s="46" t="s">
-        <v>413</v>
-      </c>
-      <c r="L48" s="47">
+        <v>486</v>
+      </c>
+      <c r="K48" s="105" t="s">
+        <v>410</v>
+      </c>
+      <c r="L48" s="46">
         <v>4</v>
       </c>
       <c r="M48" s="46">
@@ -5241,53 +5303,53 @@
       <c r="N48" s="46">
         <v>40</v>
       </c>
-      <c r="O48" s="61" t="s">
-        <v>417</v>
-      </c>
-      <c r="P48" s="62">
+      <c r="O48" s="59" t="s">
+        <v>414</v>
+      </c>
+      <c r="P48" s="60">
         <v>3.5499999999999997E-2</v>
       </c>
-      <c r="Q48" s="62">
+      <c r="Q48" s="60">
         <f t="shared" si="2"/>
         <v>1.42</v>
       </c>
       <c r="R48" s="48"/>
       <c r="S48" s="48"/>
     </row>
-    <row r="49" spans="1:19" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="49" spans="1:19" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A49" s="1"/>
       <c r="B49" s="38">
         <f t="shared" si="3"/>
         <v>40</v>
       </c>
-      <c r="C49" s="85" t="s">
-        <v>392</v>
+      <c r="C49" s="83" t="s">
+        <v>389</v>
       </c>
       <c r="D49" s="50" t="s">
         <v>46</v>
       </c>
       <c r="E49" s="51" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="F49" s="50" t="s">
-        <v>215</v>
-      </c>
-      <c r="G49" s="71" t="s">
-        <v>260</v>
+        <v>213</v>
+      </c>
+      <c r="G49" s="69" t="s">
+        <v>257</v>
       </c>
       <c r="H49" s="50" t="s">
-        <v>507</v>
+        <v>504</v>
       </c>
       <c r="I49" s="50" t="s">
-        <v>508</v>
+        <v>505</v>
       </c>
       <c r="J49" s="50" t="s">
-        <v>507</v>
-      </c>
-      <c r="K49" s="50" t="s">
-        <v>413</v>
-      </c>
-      <c r="L49" s="51">
+        <v>504</v>
+      </c>
+      <c r="K49" s="104" t="s">
+        <v>410</v>
+      </c>
+      <c r="L49" s="50">
         <v>1</v>
       </c>
       <c r="M49" s="50">
@@ -5297,53 +5359,53 @@
       <c r="N49" s="50">
         <v>10</v>
       </c>
-      <c r="O49" s="64" t="s">
-        <v>417</v>
-      </c>
-      <c r="P49" s="63">
+      <c r="O49" s="62" t="s">
+        <v>414</v>
+      </c>
+      <c r="P49" s="61">
         <v>0.12429999999999999</v>
       </c>
-      <c r="Q49" s="63">
+      <c r="Q49" s="61">
         <f t="shared" si="2"/>
         <v>1.2429999999999999</v>
       </c>
       <c r="R49" s="52"/>
       <c r="S49" s="52"/>
     </row>
-    <row r="50" spans="1:19" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="50" spans="1:19" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A50" s="1"/>
       <c r="B50" s="38">
         <f t="shared" si="3"/>
         <v>41</v>
       </c>
-      <c r="C50" s="84" t="s">
-        <v>392</v>
+      <c r="C50" s="82" t="s">
+        <v>389</v>
       </c>
       <c r="D50" s="46" t="s">
         <v>47</v>
       </c>
       <c r="E50" s="47" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="F50" s="46" t="s">
-        <v>216</v>
-      </c>
-      <c r="G50" s="70">
+        <v>214</v>
+      </c>
+      <c r="G50" s="68">
         <v>61300211121</v>
       </c>
       <c r="H50" s="46" t="s">
-        <v>492</v>
+        <v>489</v>
       </c>
       <c r="I50" s="46" t="s">
-        <v>322</v>
+        <v>319</v>
       </c>
       <c r="J50" s="46" t="s">
-        <v>493</v>
-      </c>
-      <c r="K50" s="46" t="s">
-        <v>413</v>
-      </c>
-      <c r="L50" s="47">
+        <v>490</v>
+      </c>
+      <c r="K50" s="105" t="s">
+        <v>410</v>
+      </c>
+      <c r="L50" s="46">
         <v>3</v>
       </c>
       <c r="M50" s="46">
@@ -5353,53 +5415,53 @@
       <c r="N50" s="46">
         <v>50</v>
       </c>
-      <c r="O50" s="61" t="s">
-        <v>417</v>
-      </c>
-      <c r="P50" s="62">
+      <c r="O50" s="59" t="s">
+        <v>414</v>
+      </c>
+      <c r="P50" s="60">
         <v>1.89E-2</v>
       </c>
-      <c r="Q50" s="62">
+      <c r="Q50" s="60">
         <f t="shared" si="2"/>
         <v>0.94500000000000006</v>
       </c>
       <c r="R50" s="48"/>
       <c r="S50" s="48"/>
     </row>
-    <row r="51" spans="1:19" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="51" spans="1:19" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A51" s="1"/>
       <c r="B51" s="38">
         <f t="shared" si="3"/>
         <v>42</v>
       </c>
-      <c r="C51" s="85" t="s">
-        <v>392</v>
+      <c r="C51" s="83" t="s">
+        <v>389</v>
       </c>
       <c r="D51" s="50" t="s">
         <v>48</v>
       </c>
       <c r="E51" s="51" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="F51" s="50" t="s">
-        <v>217</v>
-      </c>
-      <c r="G51" s="71">
+        <v>215</v>
+      </c>
+      <c r="G51" s="69">
         <v>61300411121</v>
       </c>
       <c r="H51" s="50" t="s">
-        <v>494</v>
+        <v>491</v>
       </c>
       <c r="I51" s="50" t="s">
-        <v>322</v>
+        <v>319</v>
       </c>
       <c r="J51" s="50" t="s">
-        <v>495</v>
-      </c>
-      <c r="K51" s="50" t="s">
-        <v>413</v>
-      </c>
-      <c r="L51" s="51">
+        <v>492</v>
+      </c>
+      <c r="K51" s="104" t="s">
+        <v>410</v>
+      </c>
+      <c r="L51" s="50">
         <v>1</v>
       </c>
       <c r="M51" s="50">
@@ -5409,53 +5471,53 @@
       <c r="N51" s="50">
         <v>20</v>
       </c>
-      <c r="O51" s="64" t="s">
-        <v>417</v>
-      </c>
-      <c r="P51" s="63">
+      <c r="O51" s="62" t="s">
+        <v>414</v>
+      </c>
+      <c r="P51" s="61">
         <v>2.29E-2</v>
       </c>
-      <c r="Q51" s="63">
+      <c r="Q51" s="61">
         <f t="shared" si="2"/>
         <v>0.45800000000000002</v>
       </c>
       <c r="R51" s="52"/>
       <c r="S51" s="52"/>
     </row>
-    <row r="52" spans="1:19" ht="24.5" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="52" spans="1:19" ht="24.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A52" s="1"/>
       <c r="B52" s="38">
         <f t="shared" si="3"/>
         <v>43</v>
       </c>
-      <c r="C52" s="84" t="s">
-        <v>396</v>
+      <c r="C52" s="82" t="s">
+        <v>393</v>
       </c>
       <c r="D52" s="46" t="s">
         <v>49</v>
       </c>
       <c r="E52" s="47" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="F52" s="46" t="s">
-        <v>218</v>
+        <v>216</v>
       </c>
       <c r="G52" s="47" t="s">
-        <v>261</v>
+        <v>258</v>
       </c>
       <c r="H52" s="46" t="s">
-        <v>413</v>
+        <v>410</v>
       </c>
       <c r="I52" s="46" t="s">
-        <v>308</v>
+        <v>305</v>
       </c>
       <c r="J52" s="46" t="s">
-        <v>441</v>
-      </c>
-      <c r="K52" s="46" t="s">
-        <v>413</v>
-      </c>
-      <c r="L52" s="47">
+        <v>438</v>
+      </c>
+      <c r="K52" s="105" t="s">
+        <v>410</v>
+      </c>
+      <c r="L52" s="46">
         <v>9</v>
       </c>
       <c r="M52" s="46">
@@ -5465,53 +5527,53 @@
       <c r="N52" s="46">
         <v>48</v>
       </c>
-      <c r="O52" s="61" t="s">
-        <v>417</v>
-      </c>
-      <c r="P52" s="62">
+      <c r="O52" s="59" t="s">
+        <v>414</v>
+      </c>
+      <c r="P52" s="60">
         <v>0.311</v>
       </c>
-      <c r="Q52" s="62">
+      <c r="Q52" s="60">
         <f t="shared" si="2"/>
         <v>14.928000000000001</v>
       </c>
       <c r="R52" s="48"/>
       <c r="S52" s="48"/>
     </row>
-    <row r="53" spans="1:19" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="53" spans="1:19" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A53" s="1"/>
       <c r="B53" s="38">
         <f t="shared" si="3"/>
         <v>44</v>
       </c>
-      <c r="C53" s="85" t="s">
-        <v>396</v>
+      <c r="C53" s="83" t="s">
+        <v>393</v>
       </c>
       <c r="D53" s="50" t="s">
         <v>50</v>
       </c>
       <c r="E53" s="51" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="F53" s="50" t="s">
-        <v>219</v>
+        <v>217</v>
       </c>
       <c r="G53" s="51" t="s">
-        <v>262</v>
+        <v>259</v>
       </c>
       <c r="H53" s="50" t="s">
-        <v>413</v>
+        <v>410</v>
       </c>
       <c r="I53" s="50" t="s">
-        <v>496</v>
+        <v>493</v>
       </c>
       <c r="J53" s="50" t="s">
-        <v>497</v>
-      </c>
-      <c r="K53" s="50" t="s">
-        <v>413</v>
-      </c>
-      <c r="L53" s="51">
+        <v>494</v>
+      </c>
+      <c r="K53" s="104" t="s">
+        <v>410</v>
+      </c>
+      <c r="L53" s="50">
         <v>1</v>
       </c>
       <c r="M53" s="50">
@@ -5521,51 +5583,51 @@
       <c r="N53" s="50">
         <v>10</v>
       </c>
-      <c r="O53" s="64" t="s">
-        <v>417</v>
-      </c>
-      <c r="P53" s="63">
+      <c r="O53" s="62" t="s">
+        <v>414</v>
+      </c>
+      <c r="P53" s="61">
         <v>7.51E-2</v>
       </c>
-      <c r="Q53" s="63">
+      <c r="Q53" s="61">
         <f t="shared" si="2"/>
         <v>0.751</v>
       </c>
       <c r="R53" s="52"/>
       <c r="S53" s="52"/>
     </row>
-    <row r="54" spans="1:19" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="54" spans="1:19" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A54" s="1"/>
       <c r="B54" s="38">
         <f t="shared" si="3"/>
         <v>45</v>
       </c>
-      <c r="C54" s="84" t="s">
-        <v>396</v>
+      <c r="C54" s="82" t="s">
+        <v>393</v>
       </c>
       <c r="D54" s="46" t="s">
         <v>51</v>
       </c>
       <c r="E54" s="47" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="F54" s="46" t="s">
-        <v>220</v>
+        <v>218</v>
       </c>
       <c r="G54" s="47" t="s">
-        <v>263</v>
+        <v>260</v>
       </c>
       <c r="H54" s="46"/>
       <c r="I54" s="46" t="s">
-        <v>323</v>
+        <v>320</v>
       </c>
       <c r="J54" s="46" t="s">
-        <v>442</v>
-      </c>
-      <c r="K54" s="46" t="s">
-        <v>413</v>
-      </c>
-      <c r="L54" s="47">
+        <v>439</v>
+      </c>
+      <c r="K54" s="105" t="s">
+        <v>410</v>
+      </c>
+      <c r="L54" s="46">
         <v>2</v>
       </c>
       <c r="M54" s="46">
@@ -5575,53 +5637,53 @@
       <c r="N54" s="46">
         <v>12</v>
       </c>
-      <c r="O54" s="61" t="s">
-        <v>417</v>
-      </c>
-      <c r="P54" s="62">
+      <c r="O54" s="59" t="s">
+        <v>414</v>
+      </c>
+      <c r="P54" s="60">
         <v>3.6715</v>
       </c>
-      <c r="Q54" s="62">
+      <c r="Q54" s="60">
         <f t="shared" si="2"/>
         <v>44.058</v>
       </c>
       <c r="R54" s="48"/>
       <c r="S54" s="48"/>
     </row>
-    <row r="55" spans="1:19" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="55" spans="1:19" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A55" s="1"/>
       <c r="B55" s="38">
         <f t="shared" si="3"/>
         <v>46</v>
       </c>
-      <c r="C55" s="85" t="s">
-        <v>396</v>
+      <c r="C55" s="83" t="s">
+        <v>393</v>
       </c>
       <c r="D55" s="50" t="s">
         <v>52</v>
       </c>
       <c r="E55" s="51" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="F55" s="50" t="s">
-        <v>219</v>
-      </c>
-      <c r="G55" s="72" t="s">
-        <v>264</v>
+        <v>217</v>
+      </c>
+      <c r="G55" s="70" t="s">
+        <v>261</v>
       </c>
       <c r="H55" s="50" t="s">
-        <v>413</v>
+        <v>410</v>
       </c>
       <c r="I55" s="50" t="s">
-        <v>496</v>
+        <v>493</v>
       </c>
       <c r="J55" s="50" t="s">
-        <v>498</v>
-      </c>
-      <c r="K55" s="50" t="s">
-        <v>413</v>
-      </c>
-      <c r="L55" s="51">
+        <v>495</v>
+      </c>
+      <c r="K55" s="104" t="s">
+        <v>410</v>
+      </c>
+      <c r="L55" s="50">
         <v>2</v>
       </c>
       <c r="M55" s="50">
@@ -5631,51 +5693,51 @@
       <c r="N55" s="50">
         <v>15</v>
       </c>
-      <c r="O55" s="64" t="s">
-        <v>417</v>
-      </c>
-      <c r="P55" s="63">
+      <c r="O55" s="62" t="s">
+        <v>414</v>
+      </c>
+      <c r="P55" s="61">
         <v>7.2599999999999998E-2</v>
       </c>
-      <c r="Q55" s="63">
+      <c r="Q55" s="61">
         <f t="shared" si="2"/>
         <v>1.089</v>
       </c>
       <c r="R55" s="52"/>
       <c r="S55" s="52"/>
     </row>
-    <row r="56" spans="1:19" ht="24.5" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="56" spans="1:19" ht="24.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A56" s="1"/>
       <c r="B56" s="38">
         <f t="shared" si="3"/>
         <v>47</v>
       </c>
-      <c r="C56" s="84" t="s">
-        <v>396</v>
+      <c r="C56" s="82" t="s">
+        <v>393</v>
       </c>
       <c r="D56" s="46" t="s">
         <v>53</v>
       </c>
       <c r="E56" s="47" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="F56" s="46" t="s">
-        <v>219</v>
+        <v>217</v>
       </c>
       <c r="G56" s="47" t="s">
-        <v>265</v>
+        <v>262</v>
       </c>
       <c r="H56" s="46"/>
       <c r="I56" s="46" t="s">
-        <v>324</v>
+        <v>321</v>
       </c>
       <c r="J56" s="46" t="s">
-        <v>443</v>
-      </c>
-      <c r="K56" s="46" t="s">
-        <v>413</v>
-      </c>
-      <c r="L56" s="47">
+        <v>440</v>
+      </c>
+      <c r="K56" s="105" t="s">
+        <v>410</v>
+      </c>
+      <c r="L56" s="46">
         <v>10</v>
       </c>
       <c r="M56" s="46">
@@ -5685,53 +5747,53 @@
       <c r="N56" s="46">
         <v>60</v>
       </c>
-      <c r="O56" s="61" t="s">
-        <v>417</v>
-      </c>
-      <c r="P56" s="62">
+      <c r="O56" s="59" t="s">
+        <v>414</v>
+      </c>
+      <c r="P56" s="60">
         <v>2.1000000000000001E-2</v>
       </c>
-      <c r="Q56" s="62">
+      <c r="Q56" s="60">
         <f t="shared" si="2"/>
         <v>1.26</v>
       </c>
       <c r="R56" s="48"/>
       <c r="S56" s="48"/>
     </row>
-    <row r="57" spans="1:19" ht="24.5" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="57" spans="1:19" ht="24.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A57" s="1"/>
       <c r="B57" s="38">
         <f t="shared" si="3"/>
         <v>48</v>
       </c>
-      <c r="C57" s="85" t="s">
-        <v>396</v>
+      <c r="C57" s="83" t="s">
+        <v>393</v>
       </c>
       <c r="D57" s="50" t="s">
         <v>54</v>
       </c>
       <c r="E57" s="51" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="F57" s="50" t="s">
-        <v>219</v>
+        <v>217</v>
       </c>
       <c r="G57" s="51" t="s">
-        <v>266</v>
+        <v>263</v>
       </c>
       <c r="H57" s="50" t="s">
-        <v>413</v>
+        <v>410</v>
       </c>
       <c r="I57" s="50" t="s">
-        <v>324</v>
+        <v>321</v>
       </c>
       <c r="J57" s="50" t="s">
-        <v>444</v>
-      </c>
-      <c r="K57" s="50" t="s">
-        <v>413</v>
-      </c>
-      <c r="L57" s="51">
+        <v>441</v>
+      </c>
+      <c r="K57" s="104" t="s">
+        <v>410</v>
+      </c>
+      <c r="L57" s="50">
         <v>2</v>
       </c>
       <c r="M57" s="50">
@@ -5741,53 +5803,53 @@
       <c r="N57" s="50">
         <v>20</v>
       </c>
-      <c r="O57" s="64" t="s">
-        <v>417</v>
-      </c>
-      <c r="P57" s="63">
+      <c r="O57" s="62" t="s">
+        <v>414</v>
+      </c>
+      <c r="P57" s="61">
         <v>2.29E-2</v>
       </c>
-      <c r="Q57" s="63">
+      <c r="Q57" s="61">
         <f t="shared" si="2"/>
         <v>0.45800000000000002</v>
       </c>
       <c r="R57" s="52"/>
       <c r="S57" s="52"/>
     </row>
-    <row r="58" spans="1:19" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="58" spans="1:19" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A58" s="1"/>
       <c r="B58" s="38">
         <f t="shared" si="3"/>
         <v>49</v>
       </c>
-      <c r="C58" s="84" t="s">
-        <v>396</v>
+      <c r="C58" s="82" t="s">
+        <v>393</v>
       </c>
       <c r="D58" s="46" t="s">
         <v>55</v>
       </c>
       <c r="E58" s="47" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="F58" s="46" t="s">
-        <v>219</v>
+        <v>217</v>
       </c>
       <c r="G58" s="47" t="s">
-        <v>267</v>
+        <v>264</v>
       </c>
       <c r="H58" s="46" t="s">
-        <v>413</v>
+        <v>410</v>
       </c>
       <c r="I58" s="46" t="s">
-        <v>307</v>
+        <v>304</v>
       </c>
       <c r="J58" s="46" t="s">
-        <v>445</v>
-      </c>
-      <c r="K58" s="46" t="s">
-        <v>413</v>
-      </c>
-      <c r="L58" s="47">
+        <v>442</v>
+      </c>
+      <c r="K58" s="105" t="s">
+        <v>410</v>
+      </c>
+      <c r="L58" s="46">
         <v>1</v>
       </c>
       <c r="M58" s="46">
@@ -5797,53 +5859,53 @@
       <c r="N58" s="46">
         <v>20</v>
       </c>
-      <c r="O58" s="61" t="s">
-        <v>417</v>
-      </c>
-      <c r="P58" s="62">
+      <c r="O58" s="59" t="s">
+        <v>414</v>
+      </c>
+      <c r="P58" s="60">
         <v>3.3399999999999999E-2</v>
       </c>
-      <c r="Q58" s="62">
+      <c r="Q58" s="60">
         <f t="shared" si="2"/>
         <v>0.66799999999999993</v>
       </c>
       <c r="R58" s="48"/>
       <c r="S58" s="48"/>
     </row>
-    <row r="59" spans="1:19" ht="24.5" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="59" spans="1:19" ht="36.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A59" s="1"/>
       <c r="B59" s="38">
         <f t="shared" si="3"/>
         <v>50</v>
       </c>
-      <c r="C59" s="85" t="s">
-        <v>396</v>
+      <c r="C59" s="83" t="s">
+        <v>393</v>
       </c>
       <c r="D59" s="50" t="s">
         <v>56</v>
       </c>
       <c r="E59" s="51" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="F59" s="50" t="s">
-        <v>411</v>
+        <v>408</v>
       </c>
       <c r="G59" s="50" t="s">
-        <v>221</v>
+        <v>219</v>
       </c>
       <c r="H59" s="50" t="s">
-        <v>413</v>
+        <v>410</v>
       </c>
       <c r="I59" s="50" t="s">
-        <v>325</v>
+        <v>322</v>
       </c>
       <c r="J59" s="50" t="s">
-        <v>446</v>
-      </c>
-      <c r="K59" s="50" t="s">
-        <v>413</v>
-      </c>
-      <c r="L59" s="51">
+        <v>443</v>
+      </c>
+      <c r="K59" s="104" t="s">
+        <v>410</v>
+      </c>
+      <c r="L59" s="50">
         <v>1</v>
       </c>
       <c r="M59" s="50">
@@ -5853,53 +5915,53 @@
       <c r="N59" s="50">
         <v>6</v>
       </c>
-      <c r="O59" s="64" t="s">
-        <v>417</v>
-      </c>
-      <c r="P59" s="63">
+      <c r="O59" s="62" t="s">
+        <v>414</v>
+      </c>
+      <c r="P59" s="61">
         <v>0.40760000000000002</v>
       </c>
-      <c r="Q59" s="63">
+      <c r="Q59" s="61">
         <f t="shared" si="2"/>
         <v>2.4456000000000002</v>
       </c>
       <c r="R59" s="52"/>
       <c r="S59" s="52"/>
     </row>
-    <row r="60" spans="1:19" ht="24.5" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="60" spans="1:19" ht="36.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A60" s="1"/>
       <c r="B60" s="38">
         <f t="shared" si="3"/>
         <v>51</v>
       </c>
-      <c r="C60" s="84" t="s">
-        <v>397</v>
+      <c r="C60" s="82" t="s">
+        <v>394</v>
       </c>
       <c r="D60" s="46" t="s">
         <v>57</v>
       </c>
       <c r="E60" s="47" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="F60" s="46" t="s">
-        <v>222</v>
+        <v>220</v>
       </c>
       <c r="G60" s="47" t="s">
-        <v>268</v>
+        <v>265</v>
       </c>
       <c r="H60" s="46" t="s">
-        <v>413</v>
+        <v>410</v>
       </c>
       <c r="I60" s="46" t="s">
-        <v>301</v>
+        <v>298</v>
       </c>
       <c r="J60" s="46" t="s">
-        <v>447</v>
-      </c>
-      <c r="K60" s="46" t="s">
-        <v>361</v>
-      </c>
-      <c r="L60" s="47">
+        <v>444</v>
+      </c>
+      <c r="K60" s="105" t="s">
+        <v>358</v>
+      </c>
+      <c r="L60" s="46">
         <v>1</v>
       </c>
       <c r="M60" s="46">
@@ -5909,51 +5971,51 @@
       <c r="N60" s="46">
         <v>100</v>
       </c>
-      <c r="O60" s="61" t="s">
-        <v>417</v>
-      </c>
-      <c r="P60" s="62">
+      <c r="O60" s="59" t="s">
+        <v>414</v>
+      </c>
+      <c r="P60" s="60">
         <v>2.3999999999999998E-3</v>
       </c>
-      <c r="Q60" s="62">
+      <c r="Q60" s="60">
         <f t="shared" si="2"/>
         <v>0.24</v>
       </c>
       <c r="R60" s="48"/>
       <c r="S60" s="48"/>
     </row>
-    <row r="61" spans="1:19" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="61" spans="1:19" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A61" s="1"/>
       <c r="B61" s="38">
         <f t="shared" si="3"/>
         <v>52</v>
       </c>
-      <c r="C61" s="85" t="s">
-        <v>397</v>
+      <c r="C61" s="83" t="s">
+        <v>394</v>
       </c>
       <c r="D61" s="50" t="s">
         <v>58</v>
       </c>
       <c r="E61" s="51" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="F61" s="50" t="s">
-        <v>222</v>
+        <v>220</v>
       </c>
       <c r="G61" s="51" t="s">
-        <v>269</v>
+        <v>266</v>
       </c>
       <c r="H61" s="50"/>
       <c r="I61" s="50" t="s">
-        <v>301</v>
+        <v>298</v>
       </c>
       <c r="J61" s="50" t="s">
-        <v>448</v>
-      </c>
-      <c r="K61" s="50" t="s">
-        <v>362</v>
-      </c>
-      <c r="L61" s="51">
+        <v>445</v>
+      </c>
+      <c r="K61" s="104" t="s">
+        <v>359</v>
+      </c>
+      <c r="L61" s="50">
         <v>1</v>
       </c>
       <c r="M61" s="50">
@@ -5963,53 +6025,53 @@
       <c r="N61" s="50">
         <v>100</v>
       </c>
-      <c r="O61" s="64" t="s">
-        <v>417</v>
-      </c>
-      <c r="P61" s="63">
+      <c r="O61" s="62" t="s">
+        <v>414</v>
+      </c>
+      <c r="P61" s="61">
         <v>1.2999999999999999E-3</v>
       </c>
-      <c r="Q61" s="63">
+      <c r="Q61" s="61">
         <f t="shared" si="2"/>
         <v>0.13</v>
       </c>
       <c r="R61" s="52"/>
       <c r="S61" s="52"/>
     </row>
-    <row r="62" spans="1:19" ht="36.5" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="62" spans="1:19" ht="36.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A62" s="1"/>
       <c r="B62" s="38">
         <f t="shared" si="3"/>
         <v>53</v>
       </c>
-      <c r="C62" s="84" t="s">
-        <v>397</v>
+      <c r="C62" s="82" t="s">
+        <v>394</v>
       </c>
       <c r="D62" s="46" t="s">
         <v>59</v>
       </c>
       <c r="E62" s="47" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="F62" s="46" t="s">
-        <v>222</v>
+        <v>220</v>
       </c>
       <c r="G62" s="47" t="s">
-        <v>476</v>
+        <v>473</v>
       </c>
       <c r="H62" s="46" t="s">
-        <v>413</v>
+        <v>410</v>
       </c>
       <c r="I62" s="46" t="s">
-        <v>326</v>
+        <v>323</v>
       </c>
       <c r="J62" s="46" t="s">
-        <v>477</v>
-      </c>
-      <c r="K62" s="46" t="s">
-        <v>363</v>
-      </c>
-      <c r="L62" s="47">
+        <v>474</v>
+      </c>
+      <c r="K62" s="105" t="s">
+        <v>360</v>
+      </c>
+      <c r="L62" s="46">
         <v>1</v>
       </c>
       <c r="M62" s="46">
@@ -6019,109 +6081,109 @@
       <c r="N62" s="46">
         <v>50</v>
       </c>
-      <c r="O62" s="61" t="s">
-        <v>417</v>
-      </c>
-      <c r="P62" s="62">
+      <c r="O62" s="59" t="s">
+        <v>414</v>
+      </c>
+      <c r="P62" s="60">
         <v>4.3E-3</v>
       </c>
-      <c r="Q62" s="62">
+      <c r="Q62" s="60">
         <f t="shared" si="2"/>
         <v>0.215</v>
       </c>
       <c r="R62" s="48"/>
       <c r="S62" s="48"/>
     </row>
-    <row r="63" spans="1:19" ht="60.5" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="63" spans="1:19" ht="60.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A63" s="1"/>
       <c r="B63" s="38">
         <f t="shared" si="3"/>
         <v>54</v>
       </c>
-      <c r="C63" s="85" t="s">
-        <v>397</v>
+      <c r="C63" s="83" t="s">
+        <v>394</v>
       </c>
       <c r="D63" s="50" t="s">
-        <v>60</v>
+        <v>540</v>
       </c>
       <c r="E63" s="51" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="F63" s="50" t="s">
-        <v>222</v>
+        <v>220</v>
       </c>
       <c r="G63" s="51" t="s">
-        <v>270</v>
+        <v>267</v>
       </c>
       <c r="H63" s="50" t="s">
-        <v>413</v>
+        <v>410</v>
       </c>
       <c r="I63" s="50" t="s">
-        <v>301</v>
+        <v>298</v>
       </c>
       <c r="J63" s="50" t="s">
-        <v>449</v>
-      </c>
-      <c r="K63" s="50" t="s">
-        <v>364</v>
-      </c>
-      <c r="L63" s="51">
-        <v>32</v>
+        <v>446</v>
+      </c>
+      <c r="K63" s="104" t="s">
+        <v>361</v>
+      </c>
+      <c r="L63" s="50">
+        <v>33</v>
       </c>
       <c r="M63" s="50">
         <f t="shared" si="1"/>
-        <v>160</v>
+        <v>165</v>
       </c>
       <c r="N63" s="50">
         <v>200</v>
       </c>
-      <c r="O63" s="64" t="s">
-        <v>417</v>
-      </c>
-      <c r="P63" s="63">
+      <c r="O63" s="62" t="s">
+        <v>414</v>
+      </c>
+      <c r="P63" s="61">
         <v>2E-3</v>
       </c>
-      <c r="Q63" s="63">
+      <c r="Q63" s="61">
         <f t="shared" si="2"/>
         <v>0.4</v>
       </c>
       <c r="R63" s="52"/>
       <c r="S63" s="52"/>
     </row>
-    <row r="64" spans="1:19" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="64" spans="1:19" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A64" s="1"/>
       <c r="B64" s="38">
         <f t="shared" si="3"/>
         <v>55</v>
       </c>
-      <c r="C64" s="84" t="s">
-        <v>397</v>
+      <c r="C64" s="82" t="s">
+        <v>394</v>
       </c>
       <c r="D64" s="46" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="E64" s="47" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="F64" s="46" t="s">
-        <v>222</v>
+        <v>220</v>
       </c>
       <c r="G64" s="47" t="s">
-        <v>271</v>
+        <v>268</v>
       </c>
       <c r="H64" s="46" t="s">
-        <v>413</v>
+        <v>410</v>
       </c>
       <c r="I64" s="46" t="s">
-        <v>301</v>
+        <v>298</v>
       </c>
       <c r="J64" s="46" t="s">
-        <v>450</v>
-      </c>
-      <c r="K64" s="46" t="s">
-        <v>365</v>
-      </c>
-      <c r="L64" s="47">
+        <v>447</v>
+      </c>
+      <c r="K64" s="105" t="s">
+        <v>362</v>
+      </c>
+      <c r="L64" s="46">
         <v>7</v>
       </c>
       <c r="M64" s="46">
@@ -6131,51 +6193,51 @@
       <c r="N64" s="46">
         <v>100</v>
       </c>
-      <c r="O64" s="61" t="s">
-        <v>417</v>
-      </c>
-      <c r="P64" s="62">
+      <c r="O64" s="59" t="s">
+        <v>414</v>
+      </c>
+      <c r="P64" s="60">
         <v>1.1999999999999999E-3</v>
       </c>
-      <c r="Q64" s="62">
+      <c r="Q64" s="60">
         <f t="shared" si="2"/>
         <v>0.12</v>
       </c>
       <c r="R64" s="48"/>
       <c r="S64" s="48"/>
     </row>
-    <row r="65" spans="1:19" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="65" spans="1:19" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A65" s="1"/>
       <c r="B65" s="38">
         <f t="shared" si="3"/>
         <v>56</v>
       </c>
-      <c r="C65" s="85" t="s">
-        <v>397</v>
+      <c r="C65" s="83" t="s">
+        <v>394</v>
       </c>
       <c r="D65" s="50" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="E65" s="51" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="F65" s="50" t="s">
-        <v>222</v>
+        <v>220</v>
       </c>
       <c r="G65" s="51" t="s">
-        <v>272</v>
+        <v>269</v>
       </c>
       <c r="H65" s="50"/>
       <c r="I65" s="50" t="s">
-        <v>301</v>
+        <v>298</v>
       </c>
       <c r="J65" s="50" t="s">
-        <v>451</v>
-      </c>
-      <c r="K65" s="50" t="s">
-        <v>366</v>
-      </c>
-      <c r="L65" s="51">
+        <v>448</v>
+      </c>
+      <c r="K65" s="104" t="s">
+        <v>363</v>
+      </c>
+      <c r="L65" s="50">
         <v>2</v>
       </c>
       <c r="M65" s="50">
@@ -6185,53 +6247,53 @@
       <c r="N65" s="50">
         <v>100</v>
       </c>
-      <c r="O65" s="64" t="s">
-        <v>417</v>
-      </c>
-      <c r="P65" s="63">
+      <c r="O65" s="62" t="s">
+        <v>414</v>
+      </c>
+      <c r="P65" s="61">
         <v>1.9E-3</v>
       </c>
-      <c r="Q65" s="63">
+      <c r="Q65" s="61">
         <f t="shared" si="2"/>
         <v>0.19</v>
       </c>
       <c r="R65" s="52"/>
       <c r="S65" s="52"/>
     </row>
-    <row r="66" spans="1:19" ht="36.5" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="66" spans="1:19" ht="36.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A66" s="1"/>
       <c r="B66" s="38">
         <f t="shared" si="3"/>
         <v>57</v>
       </c>
-      <c r="C66" s="84" t="s">
-        <v>397</v>
+      <c r="C66" s="82" t="s">
+        <v>394</v>
       </c>
       <c r="D66" s="46" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="E66" s="47" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="F66" s="46" t="s">
-        <v>222</v>
+        <v>220</v>
       </c>
       <c r="G66" s="47" t="s">
-        <v>273</v>
+        <v>270</v>
       </c>
       <c r="H66" s="46" t="s">
-        <v>413</v>
+        <v>410</v>
       </c>
       <c r="I66" s="46" t="s">
-        <v>327</v>
+        <v>324</v>
       </c>
       <c r="J66" s="46" t="s">
-        <v>452</v>
-      </c>
-      <c r="K66" s="46" t="s">
-        <v>367</v>
-      </c>
-      <c r="L66" s="47">
+        <v>449</v>
+      </c>
+      <c r="K66" s="105" t="s">
+        <v>364</v>
+      </c>
+      <c r="L66" s="46">
         <v>1</v>
       </c>
       <c r="M66" s="46">
@@ -6241,53 +6303,53 @@
       <c r="N66" s="46">
         <v>100</v>
       </c>
-      <c r="O66" s="61" t="s">
-        <v>417</v>
-      </c>
-      <c r="P66" s="62">
+      <c r="O66" s="59" t="s">
+        <v>414</v>
+      </c>
+      <c r="P66" s="60">
         <v>1.6999999999999999E-3</v>
       </c>
-      <c r="Q66" s="62">
+      <c r="Q66" s="60">
         <f t="shared" si="2"/>
         <v>0.16999999999999998</v>
       </c>
       <c r="R66" s="48"/>
       <c r="S66" s="48"/>
     </row>
-    <row r="67" spans="1:19" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="67" spans="1:19" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A67" s="1"/>
       <c r="B67" s="38">
         <f t="shared" si="3"/>
         <v>58</v>
       </c>
-      <c r="C67" s="85" t="s">
-        <v>397</v>
+      <c r="C67" s="83" t="s">
+        <v>394</v>
       </c>
       <c r="D67" s="50" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="E67" s="51" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="F67" s="50" t="s">
-        <v>222</v>
-      </c>
-      <c r="G67" s="71" t="s">
-        <v>274</v>
+        <v>220</v>
+      </c>
+      <c r="G67" s="69" t="s">
+        <v>271</v>
       </c>
       <c r="H67" s="50" t="s">
-        <v>499</v>
+        <v>496</v>
       </c>
       <c r="I67" s="50" t="s">
-        <v>328</v>
+        <v>325</v>
       </c>
       <c r="J67" s="50" t="s">
-        <v>500</v>
-      </c>
-      <c r="K67" s="50" t="s">
-        <v>368</v>
-      </c>
-      <c r="L67" s="51">
+        <v>497</v>
+      </c>
+      <c r="K67" s="104" t="s">
+        <v>365</v>
+      </c>
+      <c r="L67" s="50">
         <v>1</v>
       </c>
       <c r="M67" s="50">
@@ -6297,53 +6359,53 @@
       <c r="N67" s="50">
         <v>20</v>
       </c>
-      <c r="O67" s="64" t="s">
-        <v>417</v>
-      </c>
-      <c r="P67" s="63">
+      <c r="O67" s="62" t="s">
+        <v>414</v>
+      </c>
+      <c r="P67" s="61">
         <v>2.93E-2</v>
       </c>
-      <c r="Q67" s="63">
+      <c r="Q67" s="61">
         <f t="shared" si="2"/>
         <v>0.58599999999999997</v>
       </c>
       <c r="R67" s="52"/>
       <c r="S67" s="52"/>
     </row>
-    <row r="68" spans="1:19" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="68" spans="1:19" ht="24.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A68" s="1"/>
       <c r="B68" s="38">
         <f t="shared" si="3"/>
         <v>59</v>
       </c>
-      <c r="C68" s="84" t="s">
-        <v>397</v>
+      <c r="C68" s="82" t="s">
+        <v>394</v>
       </c>
       <c r="D68" s="46" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="E68" s="47" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="F68" s="46" t="s">
-        <v>222</v>
+        <v>220</v>
       </c>
       <c r="G68" s="47" t="s">
-        <v>275</v>
+        <v>272</v>
       </c>
       <c r="H68" s="46" t="s">
-        <v>413</v>
+        <v>410</v>
       </c>
       <c r="I68" s="46" t="s">
-        <v>329</v>
+        <v>326</v>
       </c>
       <c r="J68" s="46" t="s">
-        <v>453</v>
-      </c>
-      <c r="K68" s="46" t="s">
-        <v>369</v>
-      </c>
-      <c r="L68" s="47">
+        <v>450</v>
+      </c>
+      <c r="K68" s="105" t="s">
+        <v>366</v>
+      </c>
+      <c r="L68" s="46">
         <v>8</v>
       </c>
       <c r="M68" s="46">
@@ -6353,53 +6415,53 @@
       <c r="N68" s="46">
         <v>100</v>
       </c>
-      <c r="O68" s="61" t="s">
-        <v>417</v>
-      </c>
-      <c r="P68" s="62">
+      <c r="O68" s="59" t="s">
+        <v>414</v>
+      </c>
+      <c r="P68" s="60">
         <v>1.4E-3</v>
       </c>
-      <c r="Q68" s="62">
+      <c r="Q68" s="60">
         <f t="shared" si="2"/>
         <v>0.13999999999999999</v>
       </c>
       <c r="R68" s="48"/>
       <c r="S68" s="48"/>
     </row>
-    <row r="69" spans="1:19" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="69" spans="1:19" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A69" s="1"/>
       <c r="B69" s="38">
         <f t="shared" si="3"/>
         <v>60</v>
       </c>
-      <c r="C69" s="85" t="s">
-        <v>397</v>
+      <c r="C69" s="83" t="s">
+        <v>394</v>
       </c>
       <c r="D69" s="50" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="E69" s="51" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="F69" s="50" t="s">
-        <v>222</v>
+        <v>220</v>
       </c>
       <c r="G69" s="51" t="s">
-        <v>276</v>
+        <v>273</v>
       </c>
       <c r="H69" s="50" t="s">
-        <v>413</v>
+        <v>410</v>
       </c>
       <c r="I69" s="50" t="s">
-        <v>301</v>
+        <v>298</v>
       </c>
       <c r="J69" s="50" t="s">
-        <v>454</v>
-      </c>
-      <c r="K69" s="50" t="s">
-        <v>370</v>
-      </c>
-      <c r="L69" s="51">
+        <v>451</v>
+      </c>
+      <c r="K69" s="104" t="s">
+        <v>367</v>
+      </c>
+      <c r="L69" s="50">
         <v>3</v>
       </c>
       <c r="M69" s="50">
@@ -6409,53 +6471,53 @@
       <c r="N69" s="50">
         <v>100</v>
       </c>
-      <c r="O69" s="64" t="s">
-        <v>417</v>
-      </c>
-      <c r="P69" s="63">
+      <c r="O69" s="62" t="s">
+        <v>414</v>
+      </c>
+      <c r="P69" s="61">
         <v>1.5E-3</v>
       </c>
-      <c r="Q69" s="63">
+      <c r="Q69" s="61">
         <f t="shared" si="2"/>
         <v>0.15</v>
       </c>
       <c r="R69" s="52"/>
       <c r="S69" s="52"/>
     </row>
-    <row r="70" spans="1:19" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="70" spans="1:19" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A70" s="1"/>
       <c r="B70" s="38">
         <f t="shared" si="3"/>
         <v>61</v>
       </c>
-      <c r="C70" s="84" t="s">
-        <v>397</v>
+      <c r="C70" s="82" t="s">
+        <v>394</v>
       </c>
       <c r="D70" s="46" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="E70" s="47" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="F70" s="46" t="s">
-        <v>222</v>
+        <v>220</v>
       </c>
       <c r="G70" s="47" t="s">
-        <v>277</v>
+        <v>274</v>
       </c>
       <c r="H70" s="46" t="s">
-        <v>413</v>
+        <v>410</v>
       </c>
       <c r="I70" s="46" t="s">
-        <v>329</v>
+        <v>326</v>
       </c>
       <c r="J70" s="46" t="s">
-        <v>455</v>
-      </c>
-      <c r="K70" s="46" t="s">
-        <v>371</v>
-      </c>
-      <c r="L70" s="47">
+        <v>452</v>
+      </c>
+      <c r="K70" s="105" t="s">
+        <v>368</v>
+      </c>
+      <c r="L70" s="46">
         <v>7</v>
       </c>
       <c r="M70" s="46">
@@ -6465,53 +6527,53 @@
       <c r="N70" s="46">
         <v>100</v>
       </c>
-      <c r="O70" s="61" t="s">
-        <v>417</v>
-      </c>
-      <c r="P70" s="62">
+      <c r="O70" s="59" t="s">
+        <v>414</v>
+      </c>
+      <c r="P70" s="60">
         <v>1.4E-3</v>
       </c>
-      <c r="Q70" s="62">
+      <c r="Q70" s="60">
         <f t="shared" si="2"/>
         <v>0.13999999999999999</v>
       </c>
       <c r="R70" s="48"/>
       <c r="S70" s="48"/>
     </row>
-    <row r="71" spans="1:19" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="71" spans="1:19" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A71" s="1"/>
       <c r="B71" s="38">
         <f t="shared" si="3"/>
         <v>62</v>
       </c>
-      <c r="C71" s="85" t="s">
-        <v>397</v>
+      <c r="C71" s="83" t="s">
+        <v>394</v>
       </c>
       <c r="D71" s="50" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="E71" s="51" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="F71" s="50" t="s">
-        <v>222</v>
+        <v>220</v>
       </c>
       <c r="G71" s="51" t="s">
-        <v>278</v>
+        <v>275</v>
       </c>
       <c r="H71" s="50" t="s">
-        <v>413</v>
+        <v>410</v>
       </c>
       <c r="I71" s="50" t="s">
-        <v>301</v>
+        <v>298</v>
       </c>
       <c r="J71" s="50" t="s">
-        <v>456</v>
-      </c>
-      <c r="K71" s="50" t="s">
-        <v>372</v>
-      </c>
-      <c r="L71" s="51">
+        <v>453</v>
+      </c>
+      <c r="K71" s="104" t="s">
+        <v>369</v>
+      </c>
+      <c r="L71" s="50">
         <v>2</v>
       </c>
       <c r="M71" s="50">
@@ -6521,53 +6583,53 @@
       <c r="N71" s="50">
         <v>100</v>
       </c>
-      <c r="O71" s="64" t="s">
-        <v>417</v>
-      </c>
-      <c r="P71" s="63">
+      <c r="O71" s="62" t="s">
+        <v>414</v>
+      </c>
+      <c r="P71" s="61">
         <v>1.2999999999999999E-3</v>
       </c>
-      <c r="Q71" s="63">
+      <c r="Q71" s="61">
         <f t="shared" si="2"/>
         <v>0.13</v>
       </c>
       <c r="R71" s="52"/>
       <c r="S71" s="52"/>
     </row>
-    <row r="72" spans="1:19" ht="24.5" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="72" spans="1:19" ht="24.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A72" s="1"/>
       <c r="B72" s="38">
         <f t="shared" si="3"/>
         <v>63</v>
       </c>
-      <c r="C72" s="84" t="s">
-        <v>397</v>
+      <c r="C72" s="82" t="s">
+        <v>394</v>
       </c>
       <c r="D72" s="46" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="E72" s="47" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="F72" s="46" t="s">
-        <v>222</v>
+        <v>220</v>
       </c>
       <c r="G72" s="47" t="s">
-        <v>279</v>
+        <v>276</v>
       </c>
       <c r="H72" s="46" t="s">
-        <v>413</v>
+        <v>410</v>
       </c>
       <c r="I72" s="46" t="s">
-        <v>301</v>
+        <v>298</v>
       </c>
       <c r="J72" s="46" t="s">
-        <v>457</v>
-      </c>
-      <c r="K72" s="46" t="s">
-        <v>373</v>
-      </c>
-      <c r="L72" s="47">
+        <v>454</v>
+      </c>
+      <c r="K72" s="105" t="s">
+        <v>370</v>
+      </c>
+      <c r="L72" s="46">
         <v>13</v>
       </c>
       <c r="M72" s="46">
@@ -6577,53 +6639,53 @@
       <c r="N72" s="46">
         <v>100</v>
       </c>
-      <c r="O72" s="61" t="s">
-        <v>417</v>
-      </c>
-      <c r="P72" s="62">
+      <c r="O72" s="59" t="s">
+        <v>414</v>
+      </c>
+      <c r="P72" s="60">
         <v>1.1999999999999999E-3</v>
       </c>
-      <c r="Q72" s="62">
+      <c r="Q72" s="60">
         <f t="shared" si="2"/>
         <v>0.12</v>
       </c>
       <c r="R72" s="48"/>
       <c r="S72" s="48"/>
     </row>
-    <row r="73" spans="1:19" ht="24.5" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="73" spans="1:19" ht="24.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A73" s="1"/>
       <c r="B73" s="38">
         <f t="shared" si="3"/>
         <v>64</v>
       </c>
-      <c r="C73" s="85" t="s">
-        <v>397</v>
+      <c r="C73" s="83" t="s">
+        <v>394</v>
       </c>
       <c r="D73" s="50" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="E73" s="51" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="F73" s="50" t="s">
-        <v>222</v>
+        <v>220</v>
       </c>
       <c r="G73" s="51" t="s">
-        <v>280</v>
+        <v>277</v>
       </c>
       <c r="H73" s="50" t="s">
-        <v>413</v>
+        <v>410</v>
       </c>
       <c r="I73" s="50" t="s">
-        <v>330</v>
+        <v>327</v>
       </c>
       <c r="J73" s="50" t="s">
-        <v>458</v>
-      </c>
-      <c r="K73" s="50" t="s">
-        <v>374</v>
-      </c>
-      <c r="L73" s="51">
+        <v>455</v>
+      </c>
+      <c r="K73" s="104" t="s">
+        <v>371</v>
+      </c>
+      <c r="L73" s="50">
         <v>1</v>
       </c>
       <c r="M73" s="50">
@@ -6633,53 +6695,53 @@
       <c r="N73" s="50">
         <v>100</v>
       </c>
-      <c r="O73" s="64" t="s">
-        <v>417</v>
-      </c>
-      <c r="P73" s="63">
+      <c r="O73" s="62" t="s">
+        <v>414</v>
+      </c>
+      <c r="P73" s="61">
         <v>4.0000000000000001E-3</v>
       </c>
-      <c r="Q73" s="63">
+      <c r="Q73" s="61">
         <f t="shared" si="2"/>
         <v>0.4</v>
       </c>
       <c r="R73" s="52"/>
       <c r="S73" s="52"/>
     </row>
-    <row r="74" spans="1:19" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="74" spans="1:19" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A74" s="1"/>
       <c r="B74" s="38">
         <f t="shared" ref="B74:B101" si="4">ROW(B74) - ROW($B$9)</f>
         <v>65</v>
       </c>
-      <c r="C74" s="84" t="s">
-        <v>397</v>
+      <c r="C74" s="82" t="s">
+        <v>394</v>
       </c>
       <c r="D74" s="46" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="E74" s="47" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="F74" s="46" t="s">
-        <v>222</v>
+        <v>220</v>
       </c>
       <c r="G74" s="47" t="s">
-        <v>510</v>
+        <v>507</v>
       </c>
       <c r="H74" s="46" t="s">
-        <v>413</v>
+        <v>410</v>
       </c>
       <c r="I74" s="46" t="s">
-        <v>511</v>
+        <v>508</v>
       </c>
       <c r="J74" s="46" t="s">
-        <v>512</v>
-      </c>
-      <c r="K74" s="46" t="s">
         <v>509</v>
       </c>
-      <c r="L74" s="47">
+      <c r="K74" s="105" t="s">
+        <v>506</v>
+      </c>
+      <c r="L74" s="46">
         <v>1</v>
       </c>
       <c r="M74" s="46">
@@ -6689,53 +6751,53 @@
       <c r="N74" s="46">
         <v>100</v>
       </c>
-      <c r="O74" s="61" t="s">
-        <v>417</v>
-      </c>
-      <c r="P74" s="62">
+      <c r="O74" s="59" t="s">
+        <v>414</v>
+      </c>
+      <c r="P74" s="60">
         <v>1.6000000000000001E-3</v>
       </c>
-      <c r="Q74" s="62">
+      <c r="Q74" s="60">
         <f t="shared" si="2"/>
         <v>0.16</v>
       </c>
-      <c r="R74" s="90"/>
+      <c r="R74" s="88"/>
       <c r="S74" s="48"/>
     </row>
-    <row r="75" spans="1:19" ht="36.5" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="75" spans="1:19" ht="36.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A75" s="1"/>
       <c r="B75" s="38">
         <f t="shared" si="4"/>
         <v>66</v>
       </c>
-      <c r="C75" s="85" t="s">
-        <v>397</v>
+      <c r="C75" s="83" t="s">
+        <v>394</v>
       </c>
       <c r="D75" s="50" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="E75" s="51" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="F75" s="50" t="s">
-        <v>222</v>
+        <v>220</v>
       </c>
       <c r="G75" s="51" t="s">
-        <v>281</v>
+        <v>278</v>
       </c>
       <c r="H75" s="50" t="s">
-        <v>413</v>
+        <v>410</v>
       </c>
       <c r="I75" s="50" t="s">
-        <v>301</v>
+        <v>298</v>
       </c>
       <c r="J75" s="50" t="s">
-        <v>459</v>
-      </c>
-      <c r="K75" s="50" t="s">
-        <v>375</v>
-      </c>
-      <c r="L75" s="51">
+        <v>456</v>
+      </c>
+      <c r="K75" s="104" t="s">
+        <v>372</v>
+      </c>
+      <c r="L75" s="50">
         <v>1</v>
       </c>
       <c r="M75" s="50">
@@ -6745,53 +6807,53 @@
       <c r="N75" s="50">
         <v>100</v>
       </c>
-      <c r="O75" s="64" t="s">
-        <v>417</v>
-      </c>
-      <c r="P75" s="63">
+      <c r="O75" s="62" t="s">
+        <v>414</v>
+      </c>
+      <c r="P75" s="61">
         <v>2.5999999999999999E-3</v>
       </c>
-      <c r="Q75" s="63">
+      <c r="Q75" s="61">
         <f t="shared" ref="Q75:Q101" si="6">P75*N75</f>
         <v>0.26</v>
       </c>
       <c r="R75" s="52"/>
       <c r="S75" s="52"/>
     </row>
-    <row r="76" spans="1:19" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="76" spans="1:19" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A76" s="1"/>
       <c r="B76" s="38">
         <f t="shared" si="4"/>
         <v>67</v>
       </c>
-      <c r="C76" s="84" t="s">
-        <v>397</v>
+      <c r="C76" s="82" t="s">
+        <v>394</v>
       </c>
       <c r="D76" s="46" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="E76" s="47" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="F76" s="46" t="s">
-        <v>222</v>
+        <v>220</v>
       </c>
       <c r="G76" s="47" t="s">
-        <v>282</v>
+        <v>279</v>
       </c>
       <c r="H76" s="46" t="s">
-        <v>413</v>
+        <v>410</v>
       </c>
       <c r="I76" s="46" t="s">
-        <v>301</v>
+        <v>298</v>
       </c>
       <c r="J76" s="46" t="s">
-        <v>460</v>
-      </c>
-      <c r="K76" s="46" t="s">
-        <v>376</v>
-      </c>
-      <c r="L76" s="47">
+        <v>457</v>
+      </c>
+      <c r="K76" s="105" t="s">
+        <v>373</v>
+      </c>
+      <c r="L76" s="46">
         <v>2</v>
       </c>
       <c r="M76" s="46">
@@ -6801,53 +6863,53 @@
       <c r="N76" s="46">
         <v>100</v>
       </c>
-      <c r="O76" s="61" t="s">
-        <v>417</v>
-      </c>
-      <c r="P76" s="62">
+      <c r="O76" s="59" t="s">
+        <v>414</v>
+      </c>
+      <c r="P76" s="60">
         <v>2.2000000000000001E-3</v>
       </c>
-      <c r="Q76" s="62">
+      <c r="Q76" s="60">
         <f t="shared" si="6"/>
         <v>0.22</v>
       </c>
       <c r="R76" s="48"/>
       <c r="S76" s="48"/>
     </row>
-    <row r="77" spans="1:19" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="77" spans="1:19" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A77" s="1"/>
       <c r="B77" s="38">
         <f t="shared" si="4"/>
         <v>68</v>
       </c>
-      <c r="C77" s="85" t="s">
-        <v>397</v>
+      <c r="C77" s="83" t="s">
+        <v>394</v>
       </c>
       <c r="D77" s="50" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="E77" s="51" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="F77" s="50" t="s">
-        <v>222</v>
+        <v>220</v>
       </c>
       <c r="G77" s="51" t="s">
-        <v>283</v>
+        <v>280</v>
       </c>
       <c r="H77" s="50" t="s">
-        <v>413</v>
+        <v>410</v>
       </c>
       <c r="I77" s="50" t="s">
-        <v>301</v>
+        <v>298</v>
       </c>
       <c r="J77" s="50" t="s">
-        <v>461</v>
-      </c>
-      <c r="K77" s="50" t="s">
-        <v>377</v>
-      </c>
-      <c r="L77" s="51">
+        <v>458</v>
+      </c>
+      <c r="K77" s="104" t="s">
+        <v>374</v>
+      </c>
+      <c r="L77" s="50">
         <v>4</v>
       </c>
       <c r="M77" s="50">
@@ -6857,53 +6919,53 @@
       <c r="N77" s="50">
         <v>100</v>
       </c>
-      <c r="O77" s="64" t="s">
-        <v>417</v>
-      </c>
-      <c r="P77" s="63">
+      <c r="O77" s="62" t="s">
+        <v>414</v>
+      </c>
+      <c r="P77" s="61">
         <v>1.5E-3</v>
       </c>
-      <c r="Q77" s="63">
+      <c r="Q77" s="61">
         <f t="shared" si="6"/>
         <v>0.15</v>
       </c>
       <c r="R77" s="52"/>
       <c r="S77" s="52"/>
     </row>
-    <row r="78" spans="1:19" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="78" spans="1:19" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A78" s="1"/>
       <c r="B78" s="38">
         <f t="shared" si="4"/>
         <v>69</v>
       </c>
-      <c r="C78" s="84" t="s">
-        <v>397</v>
+      <c r="C78" s="82" t="s">
+        <v>394</v>
       </c>
       <c r="D78" s="46" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="E78" s="47" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="F78" s="46" t="s">
-        <v>223</v>
-      </c>
-      <c r="G78" s="70" t="s">
-        <v>284</v>
+        <v>221</v>
+      </c>
+      <c r="G78" s="68" t="s">
+        <v>281</v>
       </c>
       <c r="H78" s="46" t="s">
-        <v>513</v>
+        <v>510</v>
       </c>
       <c r="I78" s="46" t="s">
-        <v>328</v>
+        <v>325</v>
       </c>
       <c r="J78" s="46" t="s">
-        <v>514</v>
-      </c>
-      <c r="K78" s="46" t="s">
-        <v>378</v>
-      </c>
-      <c r="L78" s="47">
+        <v>511</v>
+      </c>
+      <c r="K78" s="105" t="s">
+        <v>375</v>
+      </c>
+      <c r="L78" s="46">
         <v>1</v>
       </c>
       <c r="M78" s="46">
@@ -6913,53 +6975,53 @@
       <c r="N78" s="46">
         <v>50</v>
       </c>
-      <c r="O78" s="61" t="s">
-        <v>417</v>
-      </c>
-      <c r="P78" s="62">
+      <c r="O78" s="59" t="s">
+        <v>414</v>
+      </c>
+      <c r="P78" s="60">
         <v>6.4000000000000003E-3</v>
       </c>
-      <c r="Q78" s="62">
+      <c r="Q78" s="60">
         <f t="shared" si="6"/>
         <v>0.32</v>
       </c>
       <c r="R78" s="48"/>
       <c r="S78" s="48"/>
     </row>
-    <row r="79" spans="1:19" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="79" spans="1:19" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A79" s="1"/>
       <c r="B79" s="38">
         <f t="shared" si="4"/>
         <v>70</v>
       </c>
-      <c r="C79" s="85" t="s">
-        <v>397</v>
+      <c r="C79" s="83" t="s">
+        <v>394</v>
       </c>
       <c r="D79" s="50" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="E79" s="51" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="F79" s="50" t="s">
-        <v>222</v>
+        <v>220</v>
       </c>
       <c r="G79" s="51" t="s">
-        <v>285</v>
+        <v>282</v>
       </c>
       <c r="H79" s="50" t="s">
-        <v>413</v>
+        <v>410</v>
       </c>
       <c r="I79" s="50" t="s">
-        <v>301</v>
+        <v>298</v>
       </c>
       <c r="J79" s="50" t="s">
-        <v>462</v>
-      </c>
-      <c r="K79" s="50" t="s">
-        <v>379</v>
-      </c>
-      <c r="L79" s="51">
+        <v>459</v>
+      </c>
+      <c r="K79" s="104" t="s">
+        <v>376</v>
+      </c>
+      <c r="L79" s="50">
         <v>1</v>
       </c>
       <c r="M79" s="50">
@@ -6969,53 +7031,53 @@
       <c r="N79" s="50">
         <v>100</v>
       </c>
-      <c r="O79" s="64" t="s">
-        <v>417</v>
-      </c>
-      <c r="P79" s="63">
+      <c r="O79" s="62" t="s">
+        <v>414</v>
+      </c>
+      <c r="P79" s="61">
         <v>1.4E-3</v>
       </c>
-      <c r="Q79" s="63">
+      <c r="Q79" s="61">
         <f t="shared" si="6"/>
         <v>0.13999999999999999</v>
       </c>
       <c r="R79" s="52"/>
       <c r="S79" s="52"/>
     </row>
-    <row r="80" spans="1:19" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="80" spans="1:19" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A80" s="1"/>
       <c r="B80" s="38">
         <f t="shared" si="4"/>
         <v>71</v>
       </c>
-      <c r="C80" s="84" t="s">
-        <v>397</v>
+      <c r="C80" s="82" t="s">
+        <v>394</v>
       </c>
       <c r="D80" s="46" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="E80" s="47" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="F80" s="46" t="s">
-        <v>222</v>
+        <v>220</v>
       </c>
       <c r="G80" s="47" t="s">
-        <v>286</v>
+        <v>283</v>
       </c>
       <c r="H80" s="46" t="s">
-        <v>413</v>
+        <v>410</v>
       </c>
       <c r="I80" s="46" t="s">
-        <v>301</v>
+        <v>298</v>
       </c>
       <c r="J80" s="46" t="s">
-        <v>463</v>
-      </c>
-      <c r="K80" s="46" t="s">
-        <v>380</v>
-      </c>
-      <c r="L80" s="47">
+        <v>460</v>
+      </c>
+      <c r="K80" s="105" t="s">
+        <v>377</v>
+      </c>
+      <c r="L80" s="46">
         <v>3</v>
       </c>
       <c r="M80" s="46">
@@ -7025,53 +7087,53 @@
       <c r="N80" s="46">
         <v>100</v>
       </c>
-      <c r="O80" s="61" t="s">
-        <v>417</v>
-      </c>
-      <c r="P80" s="62">
+      <c r="O80" s="59" t="s">
+        <v>414</v>
+      </c>
+      <c r="P80" s="60">
         <v>1.5E-3</v>
       </c>
-      <c r="Q80" s="62">
+      <c r="Q80" s="60">
         <f t="shared" si="6"/>
         <v>0.15</v>
       </c>
       <c r="R80" s="48"/>
       <c r="S80" s="48"/>
     </row>
-    <row r="81" spans="1:20" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="81" spans="1:20" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A81" s="1"/>
       <c r="B81" s="38">
         <f t="shared" si="4"/>
         <v>72</v>
       </c>
-      <c r="C81" s="84" t="s">
-        <v>397</v>
+      <c r="C81" s="82" t="s">
+        <v>394</v>
       </c>
       <c r="D81" s="46" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="E81" s="47" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="F81" s="46" t="s">
-        <v>222</v>
+        <v>220</v>
       </c>
       <c r="G81" s="47" t="s">
-        <v>287</v>
+        <v>284</v>
       </c>
       <c r="H81" s="46" t="s">
-        <v>413</v>
+        <v>410</v>
       </c>
       <c r="I81" s="46" t="s">
-        <v>301</v>
+        <v>298</v>
       </c>
       <c r="J81" s="46" t="s">
-        <v>464</v>
-      </c>
-      <c r="K81" s="46" t="s">
-        <v>381</v>
-      </c>
-      <c r="L81" s="47">
+        <v>461</v>
+      </c>
+      <c r="K81" s="105" t="s">
+        <v>378</v>
+      </c>
+      <c r="L81" s="46">
         <v>2</v>
       </c>
       <c r="M81" s="46">
@@ -7081,53 +7143,53 @@
       <c r="N81" s="46">
         <v>100</v>
       </c>
-      <c r="O81" s="61" t="s">
-        <v>417</v>
-      </c>
-      <c r="P81" s="62">
+      <c r="O81" s="59" t="s">
+        <v>414</v>
+      </c>
+      <c r="P81" s="60">
         <v>1.4E-3</v>
       </c>
-      <c r="Q81" s="62">
+      <c r="Q81" s="60">
         <f t="shared" si="6"/>
         <v>0.13999999999999999</v>
       </c>
       <c r="R81" s="48"/>
       <c r="S81" s="48"/>
     </row>
-    <row r="82" spans="1:20" ht="24.5" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="82" spans="1:20" ht="24.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A82" s="1"/>
       <c r="B82" s="38">
         <f t="shared" si="4"/>
         <v>73</v>
       </c>
-      <c r="C82" s="85" t="s">
-        <v>397</v>
+      <c r="C82" s="83" t="s">
+        <v>394</v>
       </c>
       <c r="D82" s="50" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="E82" s="51" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="F82" s="50" t="s">
-        <v>222</v>
+        <v>220</v>
       </c>
       <c r="G82" s="51" t="s">
-        <v>288</v>
+        <v>285</v>
       </c>
       <c r="H82" s="50" t="s">
-        <v>413</v>
+        <v>410</v>
       </c>
       <c r="I82" s="50" t="s">
-        <v>301</v>
+        <v>298</v>
       </c>
       <c r="J82" s="50" t="s">
-        <v>465</v>
-      </c>
-      <c r="K82" s="50" t="s">
-        <v>382</v>
-      </c>
-      <c r="L82" s="51">
+        <v>462</v>
+      </c>
+      <c r="K82" s="104" t="s">
+        <v>379</v>
+      </c>
+      <c r="L82" s="50">
         <v>2</v>
       </c>
       <c r="M82" s="50">
@@ -7137,53 +7199,53 @@
       <c r="N82" s="50">
         <v>100</v>
       </c>
-      <c r="O82" s="64" t="s">
-        <v>417</v>
-      </c>
-      <c r="P82" s="63">
+      <c r="O82" s="62" t="s">
+        <v>414</v>
+      </c>
+      <c r="P82" s="61">
         <v>1.5E-3</v>
       </c>
-      <c r="Q82" s="63">
+      <c r="Q82" s="61">
         <f t="shared" si="6"/>
         <v>0.15</v>
       </c>
       <c r="R82" s="52"/>
       <c r="S82" s="52"/>
     </row>
-    <row r="83" spans="1:20" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="83" spans="1:20" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A83" s="1"/>
       <c r="B83" s="38">
         <f t="shared" si="4"/>
         <v>74</v>
       </c>
-      <c r="C83" s="84" t="s">
-        <v>397</v>
+      <c r="C83" s="82" t="s">
+        <v>394</v>
       </c>
       <c r="D83" s="46" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="E83" s="47" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="F83" s="46" t="s">
-        <v>224</v>
+        <v>222</v>
       </c>
       <c r="G83" s="47" t="s">
-        <v>501</v>
+        <v>498</v>
       </c>
       <c r="H83" s="46" t="s">
-        <v>413</v>
+        <v>410</v>
       </c>
       <c r="I83" s="46" t="s">
-        <v>331</v>
+        <v>328</v>
       </c>
       <c r="J83" s="46" t="s">
-        <v>502</v>
-      </c>
-      <c r="K83" s="46" t="s">
-        <v>383</v>
-      </c>
-      <c r="L83" s="47">
+        <v>499</v>
+      </c>
+      <c r="K83" s="105" t="s">
+        <v>380</v>
+      </c>
+      <c r="L83" s="46">
         <v>2</v>
       </c>
       <c r="M83" s="46">
@@ -7193,53 +7255,53 @@
       <c r="N83" s="46">
         <v>50</v>
       </c>
-      <c r="O83" s="61" t="s">
-        <v>417</v>
-      </c>
-      <c r="P83" s="62">
+      <c r="O83" s="59" t="s">
+        <v>414</v>
+      </c>
+      <c r="P83" s="60">
         <v>1.1299999999999999E-2</v>
       </c>
-      <c r="Q83" s="62">
+      <c r="Q83" s="60">
         <f t="shared" si="6"/>
         <v>0.56499999999999995</v>
       </c>
       <c r="R83" s="48"/>
       <c r="S83" s="48"/>
     </row>
-    <row r="84" spans="1:20" ht="24.5" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="84" spans="1:20" ht="24.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A84" s="1"/>
       <c r="B84" s="38">
         <f t="shared" si="4"/>
         <v>75</v>
       </c>
-      <c r="C84" s="85" t="s">
-        <v>397</v>
+      <c r="C84" s="83" t="s">
+        <v>394</v>
       </c>
       <c r="D84" s="50" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="E84" s="51" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="F84" s="50" t="s">
-        <v>222</v>
+        <v>220</v>
       </c>
       <c r="G84" s="51" t="s">
-        <v>289</v>
+        <v>286</v>
       </c>
       <c r="H84" s="50" t="s">
-        <v>413</v>
+        <v>410</v>
       </c>
       <c r="I84" s="50" t="s">
-        <v>301</v>
+        <v>298</v>
       </c>
       <c r="J84" s="50" t="s">
-        <v>466</v>
-      </c>
-      <c r="K84" s="50" t="s">
-        <v>384</v>
-      </c>
-      <c r="L84" s="51">
+        <v>463</v>
+      </c>
+      <c r="K84" s="104" t="s">
+        <v>381</v>
+      </c>
+      <c r="L84" s="50">
         <v>2</v>
       </c>
       <c r="M84" s="50">
@@ -7249,53 +7311,53 @@
       <c r="N84" s="50">
         <v>100</v>
       </c>
-      <c r="O84" s="64" t="s">
-        <v>417</v>
-      </c>
-      <c r="P84" s="63">
+      <c r="O84" s="62" t="s">
+        <v>414</v>
+      </c>
+      <c r="P84" s="61">
         <v>1.2999999999999999E-3</v>
       </c>
-      <c r="Q84" s="63">
+      <c r="Q84" s="61">
         <f t="shared" si="6"/>
         <v>0.13</v>
       </c>
       <c r="R84" s="52"/>
       <c r="S84" s="52"/>
     </row>
-    <row r="85" spans="1:20" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="85" spans="1:20" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A85" s="1"/>
       <c r="B85" s="38">
         <f t="shared" si="4"/>
         <v>76</v>
       </c>
-      <c r="C85" s="84" t="s">
-        <v>397</v>
+      <c r="C85" s="82" t="s">
+        <v>394</v>
       </c>
       <c r="D85" s="46" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="E85" s="47" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="F85" s="46" t="s">
-        <v>225</v>
-      </c>
-      <c r="G85" s="70" t="s">
-        <v>290</v>
+        <v>223</v>
+      </c>
+      <c r="G85" s="68" t="s">
+        <v>287</v>
       </c>
       <c r="H85" s="46" t="s">
-        <v>503</v>
+        <v>500</v>
       </c>
       <c r="I85" s="46" t="s">
-        <v>332</v>
+        <v>329</v>
       </c>
       <c r="J85" s="46" t="s">
-        <v>504</v>
-      </c>
-      <c r="K85" s="46" t="s">
-        <v>365</v>
-      </c>
-      <c r="L85" s="47">
+        <v>501</v>
+      </c>
+      <c r="K85" s="105" t="s">
+        <v>362</v>
+      </c>
+      <c r="L85" s="46">
         <v>1</v>
       </c>
       <c r="M85" s="46">
@@ -7305,112 +7367,112 @@
       <c r="N85" s="46">
         <v>20</v>
       </c>
-      <c r="O85" s="61" t="s">
-        <v>417</v>
-      </c>
-      <c r="P85" s="62">
+      <c r="O85" s="59" t="s">
+        <v>414</v>
+      </c>
+      <c r="P85" s="60">
         <v>3.2500000000000001E-2</v>
       </c>
-      <c r="Q85" s="62">
+      <c r="Q85" s="60">
         <f t="shared" si="6"/>
         <v>0.65</v>
       </c>
       <c r="R85" s="48"/>
       <c r="S85" s="48"/>
     </row>
-    <row r="86" spans="1:20" ht="36.5" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="86" spans="1:20" ht="36.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A86" s="1"/>
       <c r="B86" s="38">
         <f t="shared" si="4"/>
         <v>77</v>
       </c>
-      <c r="C86" s="85" t="s">
-        <v>226</v>
+      <c r="C86" s="83" t="s">
+        <v>224</v>
       </c>
       <c r="D86" s="50" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="E86" s="51" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="F86" s="50" t="s">
-        <v>411</v>
+        <v>408</v>
       </c>
       <c r="G86" s="51" t="s">
-        <v>413</v>
+        <v>410</v>
       </c>
       <c r="H86" s="50" t="s">
-        <v>413</v>
+        <v>410</v>
       </c>
       <c r="I86" s="51" t="s">
-        <v>413</v>
+        <v>410</v>
       </c>
       <c r="J86" s="50" t="s">
-        <v>413</v>
-      </c>
-      <c r="K86" s="50" t="s">
-        <v>413</v>
-      </c>
-      <c r="L86" s="51">
+        <v>410</v>
+      </c>
+      <c r="K86" s="104" t="s">
+        <v>410</v>
+      </c>
+      <c r="L86" s="50">
         <v>18</v>
       </c>
       <c r="M86" s="50">
         <f t="shared" si="5"/>
         <v>90</v>
       </c>
-      <c r="N86" s="73" t="s">
-        <v>413</v>
-      </c>
-      <c r="O86" s="74" t="s">
-        <v>413</v>
-      </c>
-      <c r="P86" s="73" t="s">
-        <v>413</v>
-      </c>
-      <c r="Q86" s="74" t="s">
-        <v>413</v>
-      </c>
-      <c r="R86" s="88" t="s">
-        <v>531</v>
-      </c>
-      <c r="S86" s="74" t="s">
-        <v>413</v>
-      </c>
-    </row>
-    <row r="87" spans="1:20" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="N86" s="71" t="s">
+        <v>410</v>
+      </c>
+      <c r="O86" s="72" t="s">
+        <v>410</v>
+      </c>
+      <c r="P86" s="71" t="s">
+        <v>410</v>
+      </c>
+      <c r="Q86" s="72" t="s">
+        <v>410</v>
+      </c>
+      <c r="R86" s="86" t="s">
+        <v>526</v>
+      </c>
+      <c r="S86" s="72" t="s">
+        <v>410</v>
+      </c>
+    </row>
+    <row r="87" spans="1:20" ht="24.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A87" s="1"/>
       <c r="B87" s="38">
         <f t="shared" si="4"/>
         <v>78</v>
       </c>
-      <c r="C87" s="84" t="s">
-        <v>398</v>
+      <c r="C87" s="82" t="s">
+        <v>395</v>
       </c>
       <c r="D87" s="46" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="E87" s="47" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="F87" s="46" t="s">
-        <v>411</v>
+        <v>408</v>
       </c>
       <c r="G87" s="47" t="s">
-        <v>227</v>
+        <v>225</v>
       </c>
       <c r="H87" s="46" t="s">
-        <v>413</v>
+        <v>410</v>
       </c>
       <c r="I87" s="46" t="s">
-        <v>333</v>
+        <v>330</v>
       </c>
       <c r="J87" s="46" t="s">
-        <v>467</v>
-      </c>
-      <c r="K87" s="46" t="s">
-        <v>413</v>
-      </c>
-      <c r="L87" s="47">
+        <v>464</v>
+      </c>
+      <c r="K87" s="105" t="s">
+        <v>410</v>
+      </c>
+      <c r="L87" s="46">
         <v>7</v>
       </c>
       <c r="M87" s="46">
@@ -7420,112 +7482,112 @@
       <c r="N87" s="46">
         <v>37</v>
       </c>
-      <c r="O87" s="61" t="s">
-        <v>417</v>
-      </c>
-      <c r="P87" s="62">
+      <c r="O87" s="59" t="s">
+        <v>414</v>
+      </c>
+      <c r="P87" s="60">
         <v>0.74480000000000002</v>
       </c>
-      <c r="Q87" s="62">
+      <c r="Q87" s="60">
         <f t="shared" si="6"/>
         <v>27.557600000000001</v>
       </c>
       <c r="R87" s="48"/>
       <c r="S87" s="48"/>
     </row>
-    <row r="88" spans="1:20" ht="24.5" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="88" spans="1:20" ht="36.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A88" s="1"/>
       <c r="B88" s="38">
         <f t="shared" si="4"/>
         <v>79</v>
       </c>
-      <c r="C88" s="87" t="s">
-        <v>399</v>
-      </c>
-      <c r="D88" s="65" t="s">
-        <v>85</v>
-      </c>
-      <c r="E88" s="66" t="s">
-        <v>176</v>
-      </c>
-      <c r="F88" s="65" t="s">
-        <v>228</v>
-      </c>
-      <c r="G88" s="66" t="s">
-        <v>291</v>
-      </c>
-      <c r="H88" s="65" t="s">
-        <v>413</v>
-      </c>
-      <c r="I88" s="65" t="s">
-        <v>334</v>
-      </c>
-      <c r="J88" s="65" t="s">
-        <v>413</v>
-      </c>
-      <c r="K88" s="65" t="s">
-        <v>413</v>
-      </c>
-      <c r="L88" s="66">
+      <c r="C88" s="85" t="s">
+        <v>396</v>
+      </c>
+      <c r="D88" s="63" t="s">
+        <v>84</v>
+      </c>
+      <c r="E88" s="64" t="s">
+        <v>175</v>
+      </c>
+      <c r="F88" s="63" t="s">
+        <v>226</v>
+      </c>
+      <c r="G88" s="64" t="s">
+        <v>288</v>
+      </c>
+      <c r="H88" s="63" t="s">
+        <v>410</v>
+      </c>
+      <c r="I88" s="63" t="s">
+        <v>331</v>
+      </c>
+      <c r="J88" s="63" t="s">
+        <v>410</v>
+      </c>
+      <c r="K88" s="108" t="s">
+        <v>410</v>
+      </c>
+      <c r="L88" s="63">
         <v>2</v>
       </c>
-      <c r="M88" s="65">
+      <c r="M88" s="63">
         <f t="shared" si="5"/>
         <v>10</v>
       </c>
-      <c r="N88" s="65">
+      <c r="N88" s="63">
         <v>10</v>
       </c>
-      <c r="O88" s="69" t="s">
-        <v>525</v>
-      </c>
-      <c r="P88" s="67">
+      <c r="O88" s="67" t="s">
+        <v>521</v>
+      </c>
+      <c r="P88" s="65">
         <v>8</v>
       </c>
-      <c r="Q88" s="67">
+      <c r="Q88" s="65">
         <f t="shared" si="6"/>
         <v>80</v>
       </c>
-      <c r="R88" s="82" t="s">
-        <v>526</v>
-      </c>
-      <c r="S88" s="68"/>
-      <c r="T88" s="79"/>
-    </row>
-    <row r="89" spans="1:20" ht="36.5" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="R88" s="80" t="s">
+        <v>522</v>
+      </c>
+      <c r="S88" s="66"/>
+      <c r="T88" s="77"/>
+    </row>
+    <row r="89" spans="1:20" ht="36.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A89" s="1"/>
       <c r="B89" s="38">
         <f t="shared" si="4"/>
         <v>80</v>
       </c>
-      <c r="C89" s="84" t="s">
-        <v>399</v>
+      <c r="C89" s="82" t="s">
+        <v>396</v>
       </c>
       <c r="D89" s="46" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="E89" s="47" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="F89" s="46" t="s">
-        <v>228</v>
+        <v>226</v>
       </c>
       <c r="G89" s="47" t="s">
-        <v>292</v>
+        <v>289</v>
       </c>
       <c r="H89" s="46" t="s">
-        <v>413</v>
+        <v>410</v>
       </c>
       <c r="I89" s="46" t="s">
-        <v>335</v>
+        <v>332</v>
       </c>
       <c r="J89" s="46" t="s">
-        <v>515</v>
-      </c>
-      <c r="K89" s="46" t="s">
-        <v>413</v>
-      </c>
-      <c r="L89" s="47">
+        <v>512</v>
+      </c>
+      <c r="K89" s="105" t="s">
+        <v>410</v>
+      </c>
+      <c r="L89" s="46">
         <v>1</v>
       </c>
       <c r="M89" s="46">
@@ -7535,53 +7597,53 @@
       <c r="N89" s="46">
         <v>6</v>
       </c>
-      <c r="O89" s="61" t="s">
-        <v>417</v>
-      </c>
-      <c r="P89" s="62">
+      <c r="O89" s="59" t="s">
+        <v>414</v>
+      </c>
+      <c r="P89" s="60">
         <v>0.47070000000000001</v>
       </c>
-      <c r="Q89" s="62">
+      <c r="Q89" s="60">
         <f t="shared" si="6"/>
         <v>2.8242000000000003</v>
       </c>
       <c r="R89" s="48"/>
       <c r="S89" s="48"/>
     </row>
-    <row r="90" spans="1:20" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="90" spans="1:20" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A90" s="1"/>
       <c r="B90" s="38">
         <f t="shared" si="4"/>
         <v>81</v>
       </c>
-      <c r="C90" s="85" t="s">
-        <v>399</v>
+      <c r="C90" s="83" t="s">
+        <v>396</v>
       </c>
       <c r="D90" s="50" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="E90" s="51" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="F90" s="50" t="s">
-        <v>229</v>
+        <v>227</v>
       </c>
       <c r="G90" s="51" t="s">
-        <v>293</v>
+        <v>290</v>
       </c>
       <c r="H90" s="50" t="s">
-        <v>413</v>
+        <v>410</v>
       </c>
       <c r="I90" s="50" t="s">
-        <v>335</v>
+        <v>332</v>
       </c>
       <c r="J90" s="50" t="s">
-        <v>468</v>
-      </c>
-      <c r="K90" s="50" t="s">
-        <v>413</v>
-      </c>
-      <c r="L90" s="51">
+        <v>465</v>
+      </c>
+      <c r="K90" s="104" t="s">
+        <v>410</v>
+      </c>
+      <c r="L90" s="50">
         <v>1</v>
       </c>
       <c r="M90" s="50">
@@ -7591,53 +7653,53 @@
       <c r="N90" s="50">
         <v>6</v>
       </c>
-      <c r="O90" s="64" t="s">
-        <v>417</v>
-      </c>
-      <c r="P90" s="63">
+      <c r="O90" s="62" t="s">
+        <v>414</v>
+      </c>
+      <c r="P90" s="61">
         <v>1.0368999999999999</v>
       </c>
-      <c r="Q90" s="63">
+      <c r="Q90" s="61">
         <f t="shared" si="6"/>
         <v>6.2213999999999992</v>
       </c>
       <c r="R90" s="52"/>
       <c r="S90" s="52"/>
     </row>
-    <row r="91" spans="1:20" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="91" spans="1:20" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A91" s="1"/>
       <c r="B91" s="38">
         <f t="shared" si="4"/>
         <v>82</v>
       </c>
-      <c r="C91" s="84" t="s">
-        <v>399</v>
+      <c r="C91" s="82" t="s">
+        <v>396</v>
       </c>
       <c r="D91" s="46" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="E91" s="47" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="F91" s="46" t="s">
-        <v>230</v>
+        <v>228</v>
       </c>
       <c r="G91" s="47" t="s">
-        <v>294</v>
+        <v>291</v>
       </c>
       <c r="H91" s="46" t="s">
-        <v>413</v>
+        <v>410</v>
       </c>
       <c r="I91" s="46" t="s">
-        <v>336</v>
+        <v>333</v>
       </c>
       <c r="J91" s="46" t="s">
-        <v>469</v>
-      </c>
-      <c r="K91" s="46" t="s">
-        <v>413</v>
-      </c>
-      <c r="L91" s="47">
+        <v>466</v>
+      </c>
+      <c r="K91" s="105" t="s">
+        <v>410</v>
+      </c>
+      <c r="L91" s="46">
         <v>1</v>
       </c>
       <c r="M91" s="46">
@@ -7647,151 +7709,151 @@
       <c r="N91" s="46">
         <v>6</v>
       </c>
-      <c r="O91" s="61" t="s">
-        <v>417</v>
-      </c>
-      <c r="P91" s="62">
+      <c r="O91" s="59" t="s">
+        <v>414</v>
+      </c>
+      <c r="P91" s="60">
         <v>29.465599999999998</v>
       </c>
-      <c r="Q91" s="62">
+      <c r="Q91" s="60">
         <f t="shared" si="6"/>
         <v>176.7936</v>
       </c>
       <c r="R91" s="48"/>
       <c r="S91" s="48"/>
     </row>
-    <row r="92" spans="1:20" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="92" spans="1:20" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A92" s="1"/>
       <c r="B92" s="38">
         <f t="shared" si="4"/>
         <v>83</v>
       </c>
-      <c r="C92" s="87" t="s">
-        <v>399</v>
-      </c>
-      <c r="D92" s="65" t="s">
-        <v>89</v>
-      </c>
-      <c r="E92" s="66" t="s">
-        <v>180</v>
-      </c>
-      <c r="F92" s="65" t="s">
-        <v>228</v>
-      </c>
-      <c r="G92" s="66" t="s">
-        <v>295</v>
-      </c>
-      <c r="H92" s="65" t="s">
-        <v>413</v>
-      </c>
-      <c r="I92" s="65" t="s">
-        <v>307</v>
-      </c>
-      <c r="J92" s="65"/>
-      <c r="K92" s="65" t="s">
-        <v>413</v>
-      </c>
-      <c r="L92" s="66">
+      <c r="C92" s="85" t="s">
+        <v>396</v>
+      </c>
+      <c r="D92" s="63" t="s">
+        <v>88</v>
+      </c>
+      <c r="E92" s="64" t="s">
+        <v>179</v>
+      </c>
+      <c r="F92" s="63" t="s">
+        <v>226</v>
+      </c>
+      <c r="G92" s="64" t="s">
+        <v>292</v>
+      </c>
+      <c r="H92" s="63" t="s">
+        <v>410</v>
+      </c>
+      <c r="I92" s="63" t="s">
+        <v>304</v>
+      </c>
+      <c r="J92" s="63"/>
+      <c r="K92" s="108" t="s">
+        <v>410</v>
+      </c>
+      <c r="L92" s="63">
         <v>1</v>
       </c>
-      <c r="M92" s="65">
+      <c r="M92" s="63">
         <f t="shared" si="5"/>
         <v>5</v>
       </c>
-      <c r="N92" s="65">
+      <c r="N92" s="63">
         <v>6</v>
       </c>
-      <c r="O92" s="69"/>
-      <c r="P92" s="67"/>
-      <c r="Q92" s="67">
+      <c r="O92" s="67"/>
+      <c r="P92" s="65"/>
+      <c r="Q92" s="65">
         <f t="shared" si="6"/>
         <v>0</v>
       </c>
-      <c r="R92" s="68"/>
-      <c r="S92" s="68"/>
-    </row>
-    <row r="93" spans="1:20" ht="24.5" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="R92" s="66"/>
+      <c r="S92" s="66"/>
+    </row>
+    <row r="93" spans="1:20" ht="24.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A93" s="1"/>
       <c r="B93" s="38">
         <f t="shared" si="4"/>
         <v>84</v>
       </c>
-      <c r="C93" s="86" t="s">
-        <v>399</v>
-      </c>
-      <c r="D93" s="75" t="s">
-        <v>90</v>
-      </c>
-      <c r="E93" s="76" t="s">
-        <v>181</v>
-      </c>
-      <c r="F93" s="75" t="s">
-        <v>412</v>
-      </c>
-      <c r="G93" s="76" t="s">
-        <v>231</v>
-      </c>
-      <c r="H93" s="75" t="s">
-        <v>413</v>
-      </c>
-      <c r="I93" s="75" t="s">
-        <v>337</v>
-      </c>
-      <c r="J93" s="75"/>
-      <c r="K93" s="75" t="s">
-        <v>413</v>
-      </c>
-      <c r="L93" s="76">
+      <c r="C93" s="84" t="s">
+        <v>396</v>
+      </c>
+      <c r="D93" s="73" t="s">
+        <v>89</v>
+      </c>
+      <c r="E93" s="74" t="s">
+        <v>180</v>
+      </c>
+      <c r="F93" s="73" t="s">
+        <v>409</v>
+      </c>
+      <c r="G93" s="74" t="s">
+        <v>229</v>
+      </c>
+      <c r="H93" s="73" t="s">
+        <v>410</v>
+      </c>
+      <c r="I93" s="73" t="s">
+        <v>334</v>
+      </c>
+      <c r="J93" s="73"/>
+      <c r="K93" s="106" t="s">
+        <v>410</v>
+      </c>
+      <c r="L93" s="73">
         <v>1</v>
       </c>
-      <c r="M93" s="75">
+      <c r="M93" s="73">
         <f t="shared" si="5"/>
         <v>5</v>
       </c>
-      <c r="N93" s="75"/>
-      <c r="O93" s="75"/>
-      <c r="P93" s="77"/>
-      <c r="Q93" s="77">
+      <c r="N93" s="73"/>
+      <c r="O93" s="73"/>
+      <c r="P93" s="75"/>
+      <c r="Q93" s="75">
         <f t="shared" si="6"/>
         <v>0</v>
       </c>
-      <c r="R93" s="78"/>
-      <c r="S93" s="78"/>
-    </row>
-    <row r="94" spans="1:20" ht="24.5" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="R93" s="76"/>
+      <c r="S93" s="76"/>
+    </row>
+    <row r="94" spans="1:20" ht="36.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A94" s="1"/>
       <c r="B94" s="38">
         <f t="shared" si="4"/>
         <v>85</v>
       </c>
-      <c r="C94" s="85" t="s">
-        <v>399</v>
+      <c r="C94" s="83" t="s">
+        <v>396</v>
       </c>
       <c r="D94" s="50" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="E94" s="51" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="F94" s="50" t="s">
-        <v>411</v>
+        <v>408</v>
       </c>
       <c r="G94" s="51" t="s">
-        <v>232</v>
+        <v>230</v>
       </c>
       <c r="H94" s="50" t="s">
-        <v>413</v>
+        <v>410</v>
       </c>
       <c r="I94" s="50" t="s">
-        <v>517</v>
+        <v>514</v>
       </c>
       <c r="J94" s="50" t="s">
-        <v>516</v>
-      </c>
-      <c r="K94" s="50" t="s">
-        <v>413</v>
-      </c>
-      <c r="L94" s="51">
+        <v>513</v>
+      </c>
+      <c r="K94" s="104" t="s">
+        <v>410</v>
+      </c>
+      <c r="L94" s="50">
         <v>4</v>
       </c>
       <c r="M94" s="50">
@@ -7801,53 +7863,53 @@
       <c r="N94" s="50">
         <v>22</v>
       </c>
-      <c r="O94" s="64" t="s">
-        <v>417</v>
-      </c>
-      <c r="P94" s="63">
+      <c r="O94" s="62" t="s">
+        <v>414</v>
+      </c>
+      <c r="P94" s="61">
         <v>0.51759999999999995</v>
       </c>
-      <c r="Q94" s="63">
+      <c r="Q94" s="61">
         <f t="shared" si="6"/>
         <v>11.387199999999998</v>
       </c>
       <c r="R94" s="52"/>
       <c r="S94" s="52"/>
     </row>
-    <row r="95" spans="1:20" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="95" spans="1:20" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A95" s="1"/>
       <c r="B95" s="38">
         <f t="shared" si="4"/>
         <v>86</v>
       </c>
-      <c r="C95" s="84" t="s">
-        <v>399</v>
+      <c r="C95" s="82" t="s">
+        <v>396</v>
       </c>
       <c r="D95" s="46" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="E95" s="47" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="F95" s="46" t="s">
-        <v>233</v>
+        <v>231</v>
       </c>
       <c r="G95" s="47" t="s">
-        <v>296</v>
+        <v>293</v>
       </c>
       <c r="H95" s="46" t="s">
-        <v>413</v>
+        <v>410</v>
       </c>
       <c r="I95" s="46" t="s">
-        <v>335</v>
+        <v>332</v>
       </c>
       <c r="J95" s="46" t="s">
-        <v>470</v>
-      </c>
-      <c r="K95" s="46" t="s">
-        <v>413</v>
-      </c>
-      <c r="L95" s="47">
+        <v>467</v>
+      </c>
+      <c r="K95" s="105" t="s">
+        <v>410</v>
+      </c>
+      <c r="L95" s="46">
         <v>3</v>
       </c>
       <c r="M95" s="46">
@@ -7857,53 +7919,53 @@
       <c r="N95" s="46">
         <v>17</v>
       </c>
-      <c r="O95" s="61" t="s">
-        <v>417</v>
-      </c>
-      <c r="P95" s="62">
+      <c r="O95" s="59" t="s">
+        <v>414</v>
+      </c>
+      <c r="P95" s="60">
         <v>0.3337</v>
       </c>
-      <c r="Q95" s="62">
+      <c r="Q95" s="60">
         <f t="shared" si="6"/>
         <v>5.6729000000000003</v>
       </c>
       <c r="R95" s="48"/>
       <c r="S95" s="48"/>
     </row>
-    <row r="96" spans="1:20" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="96" spans="1:20" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A96" s="1"/>
       <c r="B96" s="38">
         <f t="shared" si="4"/>
         <v>87</v>
       </c>
-      <c r="C96" s="85" t="s">
-        <v>399</v>
+      <c r="C96" s="83" t="s">
+        <v>396</v>
       </c>
       <c r="D96" s="50" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="E96" s="51" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="F96" s="50" t="s">
-        <v>234</v>
+        <v>232</v>
       </c>
       <c r="G96" s="51" t="s">
-        <v>297</v>
+        <v>294</v>
       </c>
       <c r="H96" s="50" t="s">
-        <v>413</v>
+        <v>410</v>
       </c>
       <c r="I96" s="50" t="s">
-        <v>335</v>
+        <v>332</v>
       </c>
       <c r="J96" s="50" t="s">
-        <v>471</v>
-      </c>
-      <c r="K96" s="50" t="s">
-        <v>413</v>
-      </c>
-      <c r="L96" s="51">
+        <v>468</v>
+      </c>
+      <c r="K96" s="104" t="s">
+        <v>410</v>
+      </c>
+      <c r="L96" s="50">
         <v>1</v>
       </c>
       <c r="M96" s="50">
@@ -7913,53 +7975,53 @@
       <c r="N96" s="50">
         <v>6</v>
       </c>
-      <c r="O96" s="64" t="s">
-        <v>417</v>
-      </c>
-      <c r="P96" s="63">
+      <c r="O96" s="62" t="s">
+        <v>414</v>
+      </c>
+      <c r="P96" s="61">
         <v>24.546299999999999</v>
       </c>
-      <c r="Q96" s="63">
+      <c r="Q96" s="61">
         <f t="shared" si="6"/>
         <v>147.27779999999998</v>
       </c>
       <c r="R96" s="52"/>
       <c r="S96" s="52"/>
     </row>
-    <row r="97" spans="1:19" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="97" spans="1:19" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A97" s="1"/>
       <c r="B97" s="38">
         <f t="shared" si="4"/>
         <v>88</v>
       </c>
-      <c r="C97" s="84" t="s">
-        <v>399</v>
+      <c r="C97" s="82" t="s">
+        <v>396</v>
       </c>
       <c r="D97" s="46" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="E97" s="47" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="F97" s="46" t="s">
-        <v>235</v>
+        <v>233</v>
       </c>
       <c r="G97" s="47" t="s">
-        <v>298</v>
+        <v>295</v>
       </c>
       <c r="H97" s="46" t="s">
-        <v>413</v>
+        <v>410</v>
       </c>
       <c r="I97" s="46" t="s">
-        <v>338</v>
+        <v>335</v>
       </c>
       <c r="J97" s="46" t="s">
-        <v>472</v>
-      </c>
-      <c r="K97" s="46" t="s">
-        <v>413</v>
-      </c>
-      <c r="L97" s="47">
+        <v>469</v>
+      </c>
+      <c r="K97" s="105" t="s">
+        <v>410</v>
+      </c>
+      <c r="L97" s="46">
         <v>1</v>
       </c>
       <c r="M97" s="46">
@@ -7969,53 +8031,53 @@
       <c r="N97" s="46">
         <v>6</v>
       </c>
-      <c r="O97" s="61" t="s">
-        <v>417</v>
-      </c>
-      <c r="P97" s="62">
+      <c r="O97" s="59" t="s">
+        <v>414</v>
+      </c>
+      <c r="P97" s="60">
         <v>4.1904000000000003</v>
       </c>
-      <c r="Q97" s="62">
+      <c r="Q97" s="60">
         <f t="shared" si="6"/>
         <v>25.142400000000002</v>
       </c>
       <c r="R97" s="48"/>
       <c r="S97" s="48"/>
     </row>
-    <row r="98" spans="1:19" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="98" spans="1:19" ht="24.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A98" s="1"/>
       <c r="B98" s="38">
         <f t="shared" si="4"/>
         <v>89</v>
       </c>
-      <c r="C98" s="85" t="s">
-        <v>399</v>
+      <c r="C98" s="83" t="s">
+        <v>396</v>
       </c>
       <c r="D98" s="50" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="E98" s="51" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="F98" s="50" t="s">
-        <v>411</v>
+        <v>408</v>
       </c>
       <c r="G98" s="51" t="s">
-        <v>236</v>
+        <v>234</v>
       </c>
       <c r="H98" s="50" t="s">
-        <v>413</v>
+        <v>410</v>
       </c>
       <c r="I98" s="50" t="s">
-        <v>339</v>
+        <v>336</v>
       </c>
       <c r="J98" s="50" t="s">
-        <v>473</v>
-      </c>
-      <c r="K98" s="50" t="s">
-        <v>413</v>
-      </c>
-      <c r="L98" s="51">
+        <v>470</v>
+      </c>
+      <c r="K98" s="104" t="s">
+        <v>410</v>
+      </c>
+      <c r="L98" s="50">
         <v>1</v>
       </c>
       <c r="M98" s="50">
@@ -8025,99 +8087,109 @@
       <c r="N98" s="50">
         <v>6</v>
       </c>
-      <c r="O98" s="64" t="s">
-        <v>417</v>
-      </c>
-      <c r="P98" s="63">
+      <c r="O98" s="62" t="s">
+        <v>414</v>
+      </c>
+      <c r="P98" s="61">
         <v>1.1451</v>
       </c>
-      <c r="Q98" s="63">
+      <c r="Q98" s="61">
         <f t="shared" si="6"/>
         <v>6.8705999999999996</v>
       </c>
       <c r="R98" s="52"/>
       <c r="S98" s="52"/>
     </row>
-    <row r="99" spans="1:19" ht="36.5" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="99" spans="1:19" ht="36.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A99" s="1"/>
       <c r="B99" s="38">
         <f t="shared" si="4"/>
         <v>90</v>
       </c>
-      <c r="C99" s="86" t="s">
-        <v>400</v>
-      </c>
-      <c r="D99" s="75" t="s">
-        <v>96</v>
-      </c>
-      <c r="E99" s="76" t="s">
-        <v>187</v>
-      </c>
-      <c r="F99" s="75" t="s">
-        <v>411</v>
-      </c>
-      <c r="G99" s="75" t="s">
-        <v>237</v>
-      </c>
-      <c r="H99" s="75"/>
-      <c r="I99" s="75"/>
-      <c r="J99" s="75"/>
-      <c r="K99" s="75" t="s">
-        <v>413</v>
-      </c>
-      <c r="L99" s="76">
+      <c r="C99" s="82" t="s">
+        <v>397</v>
+      </c>
+      <c r="D99" s="46" t="s">
+        <v>95</v>
+      </c>
+      <c r="E99" s="47" t="s">
+        <v>538</v>
+      </c>
+      <c r="F99" s="46" t="s">
+        <v>408</v>
+      </c>
+      <c r="G99" s="47" t="s">
+        <v>535</v>
+      </c>
+      <c r="H99" s="100" t="s">
+        <v>410</v>
+      </c>
+      <c r="I99" s="46" t="s">
+        <v>536</v>
+      </c>
+      <c r="J99" s="46" t="s">
+        <v>539</v>
+      </c>
+      <c r="K99" s="47" t="s">
+        <v>537</v>
+      </c>
+      <c r="L99" s="46">
         <v>1</v>
       </c>
-      <c r="M99" s="75">
+      <c r="M99" s="46">
         <f t="shared" si="5"/>
         <v>5</v>
       </c>
-      <c r="N99" s="75"/>
-      <c r="O99" s="75"/>
-      <c r="P99" s="77"/>
-      <c r="Q99" s="77">
+      <c r="N99" s="46">
+        <v>6</v>
+      </c>
+      <c r="O99" s="59" t="s">
+        <v>414</v>
+      </c>
+      <c r="P99" s="60">
+        <v>0.21340000000000001</v>
+      </c>
+      <c r="Q99" s="60">
         <f t="shared" si="6"/>
-        <v>0</v>
-      </c>
-      <c r="R99" s="83" t="s">
-        <v>518</v>
-      </c>
-      <c r="S99" s="78"/>
-    </row>
-    <row r="100" spans="1:19" ht="36.5" thickBot="1" x14ac:dyDescent="0.4">
+        <v>1.2804</v>
+      </c>
+      <c r="R99" s="101"/>
+      <c r="S99" s="48"/>
+    </row>
+    <row r="100" spans="1:19" ht="36.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A100" s="1"/>
       <c r="B100" s="38">
         <f t="shared" si="4"/>
         <v>91</v>
       </c>
-      <c r="C100" s="85" t="s">
-        <v>400</v>
+      <c r="C100" s="83" t="s">
+        <v>397</v>
       </c>
       <c r="D100" s="50" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="E100" s="51" t="s">
-        <v>188</v>
+        <v>186</v>
       </c>
       <c r="F100" s="50" t="s">
-        <v>411</v>
+        <v>408</v>
       </c>
       <c r="G100" s="51" t="s">
-        <v>238</v>
+        <v>235</v>
       </c>
       <c r="H100" s="50" t="s">
-        <v>413</v>
+        <v>410</v>
       </c>
       <c r="I100" s="50" t="s">
-        <v>325</v>
+        <v>322</v>
       </c>
       <c r="J100" s="50" t="s">
-        <v>474</v>
-      </c>
-      <c r="K100" s="50" t="s">
-        <v>385</v>
-      </c>
-      <c r="L100" s="51">
+        <v>471</v>
+      </c>
+      <c r="K100" s="104" t="s">
+        <v>382</v>
+      </c>
+      <c r="L100" s="50">
         <v>1</v>
       </c>
       <c r="M100" s="50">
@@ -8127,53 +8199,53 @@
       <c r="N100" s="50">
         <v>6</v>
       </c>
-      <c r="O100" s="64" t="s">
-        <v>417</v>
-      </c>
-      <c r="P100" s="63">
+      <c r="O100" s="62" t="s">
+        <v>414</v>
+      </c>
+      <c r="P100" s="61">
         <v>0.107</v>
       </c>
-      <c r="Q100" s="63">
+      <c r="Q100" s="61">
         <f t="shared" si="6"/>
         <v>0.64200000000000002</v>
       </c>
       <c r="R100" s="52"/>
       <c r="S100" s="52"/>
     </row>
-    <row r="101" spans="1:19" ht="36.5" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="101" spans="1:19" ht="36.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A101" s="1"/>
       <c r="B101" s="38">
         <f t="shared" si="4"/>
         <v>92</v>
       </c>
-      <c r="C101" s="84" t="s">
-        <v>400</v>
+      <c r="C101" s="82" t="s">
+        <v>397</v>
       </c>
       <c r="D101" s="46" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="E101" s="47" t="s">
-        <v>189</v>
+        <v>187</v>
       </c>
       <c r="F101" s="46" t="s">
-        <v>411</v>
+        <v>408</v>
       </c>
       <c r="G101" s="47" t="s">
-        <v>239</v>
+        <v>236</v>
       </c>
       <c r="H101" s="46" t="s">
-        <v>413</v>
+        <v>410</v>
       </c>
       <c r="I101" s="46" t="s">
-        <v>340</v>
+        <v>337</v>
       </c>
       <c r="J101" s="46" t="s">
-        <v>475</v>
-      </c>
-      <c r="K101" s="60" t="s">
-        <v>386</v>
-      </c>
-      <c r="L101" s="47">
+        <v>472</v>
+      </c>
+      <c r="K101" s="109" t="s">
+        <v>383</v>
+      </c>
+      <c r="L101" s="58">
         <v>1</v>
       </c>
       <c r="M101" s="46">
@@ -8183,20 +8255,20 @@
       <c r="N101" s="46">
         <v>6</v>
       </c>
-      <c r="O101" s="61" t="s">
-        <v>417</v>
-      </c>
-      <c r="P101" s="62">
+      <c r="O101" s="59" t="s">
+        <v>414</v>
+      </c>
+      <c r="P101" s="60">
         <v>0.35220000000000001</v>
       </c>
-      <c r="Q101" s="62">
+      <c r="Q101" s="60">
         <f t="shared" si="6"/>
         <v>2.1132</v>
       </c>
       <c r="R101" s="48"/>
       <c r="S101" s="48"/>
     </row>
-    <row r="102" spans="1:19" ht="19" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="102" spans="1:19" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A102" s="1"/>
       <c r="B102" s="33"/>
       <c r="C102" s="44"/>
@@ -8210,19 +8282,19 @@
       <c r="K102" s="37"/>
       <c r="L102" s="37"/>
       <c r="M102" s="37"/>
-      <c r="N102" s="91" t="s">
-        <v>528</v>
-      </c>
-      <c r="O102" s="92"/>
-      <c r="P102" s="92"/>
-      <c r="Q102" s="80">
+      <c r="N102" s="90" t="s">
+        <v>523</v>
+      </c>
+      <c r="O102" s="91"/>
+      <c r="P102" s="91"/>
+      <c r="Q102" s="78">
         <f>SUM(Q10:Q101)</f>
-        <v>634.06729999999993</v>
-      </c>
-      <c r="R102" s="97"/>
-      <c r="S102" s="98"/>
-    </row>
-    <row r="103" spans="1:19" ht="19" thickBot="1" x14ac:dyDescent="0.4">
+        <v>635.34769999999992</v>
+      </c>
+      <c r="R102" s="96"/>
+      <c r="S102" s="97"/>
+    </row>
+    <row r="103" spans="1:19" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A103" s="1"/>
       <c r="B103" s="25"/>
       <c r="C103" s="45"/>
@@ -8236,25 +8308,25 @@
       <c r="K103" s="10"/>
       <c r="L103" s="10"/>
       <c r="M103" s="10"/>
-      <c r="N103" s="91" t="s">
-        <v>529</v>
-      </c>
-      <c r="O103" s="92"/>
-      <c r="P103" s="92"/>
-      <c r="Q103" s="81">
+      <c r="N103" s="90" t="s">
+        <v>524</v>
+      </c>
+      <c r="O103" s="91"/>
+      <c r="P103" s="91"/>
+      <c r="Q103" s="79">
         <f>Q102/5</f>
-        <v>126.81345999999999</v>
-      </c>
-      <c r="R103" s="99"/>
-      <c r="S103" s="100"/>
-    </row>
-    <row r="104" spans="1:19" ht="19" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="N104" s="91" t="s">
-        <v>530</v>
-      </c>
-      <c r="O104" s="92"/>
-      <c r="P104" s="92"/>
-      <c r="Q104" s="81">
+        <v>127.06953999999999</v>
+      </c>
+      <c r="R103" s="98"/>
+      <c r="S103" s="99"/>
+    </row>
+    <row r="104" spans="1:19" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="N104" s="90" t="s">
+        <v>525</v>
+      </c>
+      <c r="O104" s="91"/>
+      <c r="P104" s="91"/>
+      <c r="Q104" s="79">
         <v>4</v>
       </c>
     </row>
@@ -8268,95 +8340,96 @@
     <mergeCell ref="N103:P103"/>
   </mergeCells>
   <hyperlinks>
-    <hyperlink ref="O10" r:id="rId1"/>
-    <hyperlink ref="O11" r:id="rId2"/>
-    <hyperlink ref="O12" r:id="rId3"/>
-    <hyperlink ref="O13" r:id="rId4"/>
-    <hyperlink ref="O14" r:id="rId5"/>
-    <hyperlink ref="O15" r:id="rId6"/>
-    <hyperlink ref="O17" r:id="rId7"/>
-    <hyperlink ref="O18" r:id="rId8"/>
-    <hyperlink ref="O19" r:id="rId9"/>
-    <hyperlink ref="O20" r:id="rId10"/>
-    <hyperlink ref="O21" r:id="rId11"/>
-    <hyperlink ref="O22" r:id="rId12"/>
-    <hyperlink ref="O23" r:id="rId13"/>
-    <hyperlink ref="O25" r:id="rId14"/>
-    <hyperlink ref="O27" r:id="rId15"/>
-    <hyperlink ref="O36" r:id="rId16"/>
-    <hyperlink ref="O37" r:id="rId17"/>
-    <hyperlink ref="O38" r:id="rId18"/>
-    <hyperlink ref="O40" r:id="rId19"/>
-    <hyperlink ref="O41" r:id="rId20"/>
-    <hyperlink ref="O42" r:id="rId21"/>
-    <hyperlink ref="O44" r:id="rId22"/>
-    <hyperlink ref="O45" r:id="rId23"/>
-    <hyperlink ref="O52" r:id="rId24"/>
-    <hyperlink ref="O54" r:id="rId25"/>
-    <hyperlink ref="O56" r:id="rId26"/>
-    <hyperlink ref="O57" r:id="rId27"/>
-    <hyperlink ref="O58" r:id="rId28"/>
-    <hyperlink ref="O59" r:id="rId29"/>
-    <hyperlink ref="O60" r:id="rId30"/>
-    <hyperlink ref="O61" r:id="rId31"/>
-    <hyperlink ref="O62" r:id="rId32"/>
-    <hyperlink ref="O63" r:id="rId33"/>
-    <hyperlink ref="O64" r:id="rId34"/>
-    <hyperlink ref="O65" r:id="rId35"/>
-    <hyperlink ref="O66" r:id="rId36"/>
-    <hyperlink ref="O68" r:id="rId37"/>
-    <hyperlink ref="O69" r:id="rId38"/>
-    <hyperlink ref="O70" r:id="rId39"/>
-    <hyperlink ref="O71" r:id="rId40"/>
-    <hyperlink ref="O72" r:id="rId41"/>
-    <hyperlink ref="O73" r:id="rId42"/>
-    <hyperlink ref="O75" r:id="rId43"/>
-    <hyperlink ref="O76" r:id="rId44"/>
-    <hyperlink ref="O77" r:id="rId45"/>
-    <hyperlink ref="O79" r:id="rId46"/>
-    <hyperlink ref="O80" r:id="rId47"/>
-    <hyperlink ref="O81" r:id="rId48"/>
-    <hyperlink ref="O82" r:id="rId49"/>
-    <hyperlink ref="O84" r:id="rId50"/>
-    <hyperlink ref="O87" r:id="rId51"/>
-    <hyperlink ref="O90" r:id="rId52"/>
-    <hyperlink ref="O91" r:id="rId53"/>
-    <hyperlink ref="O95" r:id="rId54"/>
-    <hyperlink ref="O96" r:id="rId55"/>
-    <hyperlink ref="O97" r:id="rId56"/>
-    <hyperlink ref="O98" r:id="rId57"/>
-    <hyperlink ref="O100" r:id="rId58"/>
-    <hyperlink ref="O101" r:id="rId59"/>
-    <hyperlink ref="O24" r:id="rId60"/>
-    <hyperlink ref="O26" r:id="rId61"/>
-    <hyperlink ref="O28" r:id="rId62"/>
-    <hyperlink ref="O29" r:id="rId63"/>
-    <hyperlink ref="O31" r:id="rId64"/>
-    <hyperlink ref="O39" r:id="rId65"/>
-    <hyperlink ref="O48" r:id="rId66"/>
-    <hyperlink ref="O47" r:id="rId67"/>
-    <hyperlink ref="O50" r:id="rId68"/>
-    <hyperlink ref="O51" r:id="rId69"/>
-    <hyperlink ref="O53" r:id="rId70"/>
-    <hyperlink ref="O55" r:id="rId71"/>
-    <hyperlink ref="O67" r:id="rId72"/>
-    <hyperlink ref="O83" r:id="rId73"/>
-    <hyperlink ref="O85" r:id="rId74"/>
-    <hyperlink ref="O43" r:id="rId75"/>
-    <hyperlink ref="O49" r:id="rId76"/>
-    <hyperlink ref="O74" r:id="rId77"/>
-    <hyperlink ref="O78" r:id="rId78"/>
-    <hyperlink ref="O89" r:id="rId79"/>
-    <hyperlink ref="O94" r:id="rId80"/>
-    <hyperlink ref="O33" r:id="rId81"/>
-    <hyperlink ref="O34" r:id="rId82"/>
-    <hyperlink ref="O35" r:id="rId83"/>
-    <hyperlink ref="O88" r:id="rId84"/>
-    <hyperlink ref="O16" r:id="rId85"/>
-    <hyperlink ref="O30" r:id="rId86"/>
+    <hyperlink ref="O10" r:id="rId1" xr:uid="{00000000-0004-0000-0000-000000000000}"/>
+    <hyperlink ref="O11" r:id="rId2" xr:uid="{00000000-0004-0000-0000-000001000000}"/>
+    <hyperlink ref="O12" r:id="rId3" xr:uid="{00000000-0004-0000-0000-000002000000}"/>
+    <hyperlink ref="O13" r:id="rId4" xr:uid="{00000000-0004-0000-0000-000003000000}"/>
+    <hyperlink ref="O14" r:id="rId5" xr:uid="{00000000-0004-0000-0000-000004000000}"/>
+    <hyperlink ref="O15" r:id="rId6" xr:uid="{00000000-0004-0000-0000-000005000000}"/>
+    <hyperlink ref="O17" r:id="rId7" xr:uid="{00000000-0004-0000-0000-000006000000}"/>
+    <hyperlink ref="O18" r:id="rId8" xr:uid="{00000000-0004-0000-0000-000007000000}"/>
+    <hyperlink ref="O19" r:id="rId9" xr:uid="{00000000-0004-0000-0000-000008000000}"/>
+    <hyperlink ref="O20" r:id="rId10" xr:uid="{00000000-0004-0000-0000-000009000000}"/>
+    <hyperlink ref="O21" r:id="rId11" xr:uid="{00000000-0004-0000-0000-00000A000000}"/>
+    <hyperlink ref="O22" r:id="rId12" xr:uid="{00000000-0004-0000-0000-00000B000000}"/>
+    <hyperlink ref="O23" r:id="rId13" xr:uid="{00000000-0004-0000-0000-00000C000000}"/>
+    <hyperlink ref="O25" r:id="rId14" xr:uid="{00000000-0004-0000-0000-00000D000000}"/>
+    <hyperlink ref="O27" r:id="rId15" xr:uid="{00000000-0004-0000-0000-00000E000000}"/>
+    <hyperlink ref="O36" r:id="rId16" xr:uid="{00000000-0004-0000-0000-00000F000000}"/>
+    <hyperlink ref="O37" r:id="rId17" xr:uid="{00000000-0004-0000-0000-000010000000}"/>
+    <hyperlink ref="O38" r:id="rId18" xr:uid="{00000000-0004-0000-0000-000011000000}"/>
+    <hyperlink ref="O40" r:id="rId19" xr:uid="{00000000-0004-0000-0000-000012000000}"/>
+    <hyperlink ref="O41" r:id="rId20" xr:uid="{00000000-0004-0000-0000-000013000000}"/>
+    <hyperlink ref="O42" r:id="rId21" xr:uid="{00000000-0004-0000-0000-000014000000}"/>
+    <hyperlink ref="O44" r:id="rId22" xr:uid="{00000000-0004-0000-0000-000015000000}"/>
+    <hyperlink ref="O45" r:id="rId23" xr:uid="{00000000-0004-0000-0000-000016000000}"/>
+    <hyperlink ref="O52" r:id="rId24" xr:uid="{00000000-0004-0000-0000-000017000000}"/>
+    <hyperlink ref="O54" r:id="rId25" xr:uid="{00000000-0004-0000-0000-000018000000}"/>
+    <hyperlink ref="O56" r:id="rId26" xr:uid="{00000000-0004-0000-0000-000019000000}"/>
+    <hyperlink ref="O57" r:id="rId27" xr:uid="{00000000-0004-0000-0000-00001A000000}"/>
+    <hyperlink ref="O58" r:id="rId28" xr:uid="{00000000-0004-0000-0000-00001B000000}"/>
+    <hyperlink ref="O59" r:id="rId29" xr:uid="{00000000-0004-0000-0000-00001C000000}"/>
+    <hyperlink ref="O60" r:id="rId30" xr:uid="{00000000-0004-0000-0000-00001D000000}"/>
+    <hyperlink ref="O61" r:id="rId31" xr:uid="{00000000-0004-0000-0000-00001E000000}"/>
+    <hyperlink ref="O62" r:id="rId32" xr:uid="{00000000-0004-0000-0000-00001F000000}"/>
+    <hyperlink ref="O63" r:id="rId33" xr:uid="{00000000-0004-0000-0000-000020000000}"/>
+    <hyperlink ref="O64" r:id="rId34" xr:uid="{00000000-0004-0000-0000-000021000000}"/>
+    <hyperlink ref="O65" r:id="rId35" xr:uid="{00000000-0004-0000-0000-000022000000}"/>
+    <hyperlink ref="O66" r:id="rId36" xr:uid="{00000000-0004-0000-0000-000023000000}"/>
+    <hyperlink ref="O68" r:id="rId37" xr:uid="{00000000-0004-0000-0000-000024000000}"/>
+    <hyperlink ref="O69" r:id="rId38" xr:uid="{00000000-0004-0000-0000-000025000000}"/>
+    <hyperlink ref="O70" r:id="rId39" xr:uid="{00000000-0004-0000-0000-000026000000}"/>
+    <hyperlink ref="O71" r:id="rId40" xr:uid="{00000000-0004-0000-0000-000027000000}"/>
+    <hyperlink ref="O72" r:id="rId41" xr:uid="{00000000-0004-0000-0000-000028000000}"/>
+    <hyperlink ref="O73" r:id="rId42" xr:uid="{00000000-0004-0000-0000-000029000000}"/>
+    <hyperlink ref="O75" r:id="rId43" xr:uid="{00000000-0004-0000-0000-00002A000000}"/>
+    <hyperlink ref="O76" r:id="rId44" xr:uid="{00000000-0004-0000-0000-00002B000000}"/>
+    <hyperlink ref="O77" r:id="rId45" xr:uid="{00000000-0004-0000-0000-00002C000000}"/>
+    <hyperlink ref="O79" r:id="rId46" xr:uid="{00000000-0004-0000-0000-00002D000000}"/>
+    <hyperlink ref="O80" r:id="rId47" xr:uid="{00000000-0004-0000-0000-00002E000000}"/>
+    <hyperlink ref="O81" r:id="rId48" xr:uid="{00000000-0004-0000-0000-00002F000000}"/>
+    <hyperlink ref="O82" r:id="rId49" xr:uid="{00000000-0004-0000-0000-000030000000}"/>
+    <hyperlink ref="O84" r:id="rId50" xr:uid="{00000000-0004-0000-0000-000031000000}"/>
+    <hyperlink ref="O87" r:id="rId51" xr:uid="{00000000-0004-0000-0000-000032000000}"/>
+    <hyperlink ref="O90" r:id="rId52" xr:uid="{00000000-0004-0000-0000-000033000000}"/>
+    <hyperlink ref="O91" r:id="rId53" xr:uid="{00000000-0004-0000-0000-000034000000}"/>
+    <hyperlink ref="O95" r:id="rId54" xr:uid="{00000000-0004-0000-0000-000035000000}"/>
+    <hyperlink ref="O96" r:id="rId55" xr:uid="{00000000-0004-0000-0000-000036000000}"/>
+    <hyperlink ref="O97" r:id="rId56" xr:uid="{00000000-0004-0000-0000-000037000000}"/>
+    <hyperlink ref="O98" r:id="rId57" xr:uid="{00000000-0004-0000-0000-000038000000}"/>
+    <hyperlink ref="O100" r:id="rId58" xr:uid="{00000000-0004-0000-0000-000039000000}"/>
+    <hyperlink ref="O101" r:id="rId59" xr:uid="{00000000-0004-0000-0000-00003A000000}"/>
+    <hyperlink ref="O24" r:id="rId60" xr:uid="{00000000-0004-0000-0000-00003B000000}"/>
+    <hyperlink ref="O26" r:id="rId61" xr:uid="{00000000-0004-0000-0000-00003C000000}"/>
+    <hyperlink ref="O28" r:id="rId62" xr:uid="{00000000-0004-0000-0000-00003D000000}"/>
+    <hyperlink ref="O29" r:id="rId63" xr:uid="{00000000-0004-0000-0000-00003E000000}"/>
+    <hyperlink ref="O31" r:id="rId64" xr:uid="{00000000-0004-0000-0000-00003F000000}"/>
+    <hyperlink ref="O39" r:id="rId65" xr:uid="{00000000-0004-0000-0000-000040000000}"/>
+    <hyperlink ref="O48" r:id="rId66" xr:uid="{00000000-0004-0000-0000-000041000000}"/>
+    <hyperlink ref="O47" r:id="rId67" xr:uid="{00000000-0004-0000-0000-000042000000}"/>
+    <hyperlink ref="O50" r:id="rId68" xr:uid="{00000000-0004-0000-0000-000043000000}"/>
+    <hyperlink ref="O51" r:id="rId69" xr:uid="{00000000-0004-0000-0000-000044000000}"/>
+    <hyperlink ref="O53" r:id="rId70" xr:uid="{00000000-0004-0000-0000-000045000000}"/>
+    <hyperlink ref="O55" r:id="rId71" xr:uid="{00000000-0004-0000-0000-000046000000}"/>
+    <hyperlink ref="O67" r:id="rId72" xr:uid="{00000000-0004-0000-0000-000047000000}"/>
+    <hyperlink ref="O83" r:id="rId73" xr:uid="{00000000-0004-0000-0000-000048000000}"/>
+    <hyperlink ref="O85" r:id="rId74" xr:uid="{00000000-0004-0000-0000-000049000000}"/>
+    <hyperlink ref="O43" r:id="rId75" xr:uid="{00000000-0004-0000-0000-00004A000000}"/>
+    <hyperlink ref="O49" r:id="rId76" xr:uid="{00000000-0004-0000-0000-00004B000000}"/>
+    <hyperlink ref="O74" r:id="rId77" xr:uid="{00000000-0004-0000-0000-00004C000000}"/>
+    <hyperlink ref="O78" r:id="rId78" xr:uid="{00000000-0004-0000-0000-00004D000000}"/>
+    <hyperlink ref="O89" r:id="rId79" xr:uid="{00000000-0004-0000-0000-00004E000000}"/>
+    <hyperlink ref="O94" r:id="rId80" xr:uid="{00000000-0004-0000-0000-00004F000000}"/>
+    <hyperlink ref="O33" r:id="rId81" xr:uid="{00000000-0004-0000-0000-000050000000}"/>
+    <hyperlink ref="O34" r:id="rId82" xr:uid="{00000000-0004-0000-0000-000051000000}"/>
+    <hyperlink ref="O35" r:id="rId83" xr:uid="{00000000-0004-0000-0000-000052000000}"/>
+    <hyperlink ref="O88" r:id="rId84" xr:uid="{00000000-0004-0000-0000-000053000000}"/>
+    <hyperlink ref="O16" r:id="rId85" xr:uid="{00000000-0004-0000-0000-000054000000}"/>
+    <hyperlink ref="O30" r:id="rId86" xr:uid="{00000000-0004-0000-0000-000055000000}"/>
+    <hyperlink ref="O99" r:id="rId87" xr:uid="{41DBDB4E-DF1C-471F-AD20-8FB2CA7D9E5E}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" r:id="rId87"/>
-  <drawing r:id="rId88"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId88"/>
+  <drawing r:id="rId89"/>
 </worksheet>
 </file>
--- a/BOM/GTV3_Board/eSpark_BOM.xlsx
+++ b/BOM/GTV3_Board/eSpark_BOM.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\GitHub\OliverStanton-WaterMonitor\BOM\GTV3_Board\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C0DE22F8-1DD5-40E7-A536-44D7AFDDDF8C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{29721828-455E-4D8A-81C6-4B1D2E0033E3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-5265" yWindow="2205" windowWidth="11790" windowHeight="15360" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -30,7 +30,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="948" uniqueCount="542">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="951" uniqueCount="545">
   <si>
     <t>Component list</t>
   </si>
@@ -1313,9 +1313,6 @@
     <t>C281768</t>
   </si>
   <si>
-    <t>C163551</t>
-  </si>
-  <si>
     <t>C128848</t>
   </si>
   <si>
@@ -1497,12 +1494,6 @@
   </si>
   <si>
     <t>C225478</t>
-  </si>
-  <si>
-    <t>PH-00013</t>
-  </si>
-  <si>
-    <t>C2829889</t>
   </si>
   <si>
     <t>DZ254R-11-04-63</t>
@@ -1668,6 +1659,25 @@
   </si>
   <si>
     <t xml:space="preserve">Part added in design </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Less Stock </t>
+  </si>
+  <si>
+    <t>0603CG1R5C500NT</t>
+  </si>
+  <si>
+    <t>C1639</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PZ254V-11-02P
+</t>
+  </si>
+  <si>
+    <t>C492401</t>
+  </si>
+  <si>
+    <t xml:space="preserve">   </t>
   </si>
 </sst>
 </file>
@@ -2207,7 +2217,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="20" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="111">
+  <cellXfs count="112">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
@@ -2456,6 +2466,39 @@
     <xf numFmtId="0" fontId="20" fillId="6" borderId="16" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="18" fillId="2" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="2" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="5" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="2" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="4" borderId="25" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="6" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="4" borderId="25" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="6" borderId="25" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="2" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="6" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="24" fillId="3" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="top"/>
       <protection locked="0"/>
@@ -2488,38 +2531,8 @@
     <xf numFmtId="0" fontId="17" fillId="3" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="2" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="2" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="5" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="18" fillId="2" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="2" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="4" borderId="25" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="6" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="4" borderId="25" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="6" borderId="25" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="2" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="6" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -2903,15 +2916,15 @@
       <c r="H1" s="2"/>
       <c r="I1" s="2"/>
       <c r="J1" s="2"/>
-      <c r="K1" s="92"/>
-      <c r="L1" s="92"/>
-      <c r="M1" s="92"/>
-      <c r="N1" s="92"/>
-      <c r="O1" s="92"/>
-      <c r="P1" s="92"/>
-      <c r="Q1" s="92"/>
-      <c r="R1" s="92"/>
-      <c r="S1" s="93"/>
+      <c r="K1" s="103"/>
+      <c r="L1" s="103"/>
+      <c r="M1" s="103"/>
+      <c r="N1" s="103"/>
+      <c r="O1" s="103"/>
+      <c r="P1" s="103"/>
+      <c r="Q1" s="103"/>
+      <c r="R1" s="103"/>
+      <c r="S1" s="104"/>
     </row>
     <row r="2" spans="1:19" ht="32.25" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A2" s="1"/>
@@ -2922,7 +2935,7 @@
       </c>
       <c r="E2" s="11"/>
       <c r="F2" s="54" t="s">
-        <v>527</v>
+        <v>524</v>
       </c>
       <c r="G2" s="12"/>
       <c r="H2" s="12"/>
@@ -2947,7 +2960,7 @@
       </c>
       <c r="E3" s="13"/>
       <c r="F3" s="55" t="s">
-        <v>528</v>
+        <v>525</v>
       </c>
       <c r="G3" s="13"/>
       <c r="H3" s="13"/>
@@ -2961,7 +2974,7 @@
       <c r="P3" s="5"/>
       <c r="Q3" s="5"/>
       <c r="R3" s="5"/>
-      <c r="S3" s="94"/>
+      <c r="S3" s="105"/>
     </row>
     <row r="4" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A4" s="1"/>
@@ -2972,7 +2985,7 @@
       </c>
       <c r="E4" s="13"/>
       <c r="F4" s="56" t="s">
-        <v>528</v>
+        <v>525</v>
       </c>
       <c r="G4" s="14"/>
       <c r="H4" s="14"/>
@@ -2986,7 +2999,7 @@
       <c r="P4" s="6"/>
       <c r="Q4" s="6"/>
       <c r="R4" s="6"/>
-      <c r="S4" s="95"/>
+      <c r="S4" s="106"/>
     </row>
     <row r="5" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A5" s="1"/>
@@ -3011,7 +3024,7 @@
       <c r="P5" s="6"/>
       <c r="Q5" s="6"/>
       <c r="R5" s="6"/>
-      <c r="S5" s="95"/>
+      <c r="S5" s="106"/>
     </row>
     <row r="6" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A6" s="1"/>
@@ -3032,7 +3045,7 @@
       <c r="P6" s="6"/>
       <c r="Q6" s="6"/>
       <c r="R6" s="6"/>
-      <c r="S6" s="95"/>
+      <c r="S6" s="106"/>
     </row>
     <row r="7" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A7" s="1"/>
@@ -3053,7 +3066,7 @@
       <c r="P7" s="8"/>
       <c r="Q7" s="8"/>
       <c r="R7" s="8"/>
-      <c r="S7" s="95"/>
+      <c r="S7" s="106"/>
     </row>
     <row r="8" spans="1:19" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A8" s="1"/>
@@ -3074,7 +3087,7 @@
       <c r="P8" s="8"/>
       <c r="Q8" s="8"/>
       <c r="R8" s="8"/>
-      <c r="S8" s="95"/>
+      <c r="S8" s="106"/>
     </row>
     <row r="9" spans="1:19" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A9" s="1"/>
@@ -3105,7 +3118,7 @@
       <c r="J9" s="30" t="s">
         <v>400</v>
       </c>
-      <c r="K9" s="102" t="s">
+      <c r="K9" s="92" t="s">
         <v>412</v>
       </c>
       <c r="L9" s="30" t="s">
@@ -3163,7 +3176,7 @@
       <c r="J10" s="46" t="s">
         <v>413</v>
       </c>
-      <c r="K10" s="103" t="s">
+      <c r="K10" s="93" t="s">
         <v>338</v>
       </c>
       <c r="L10" s="46">
@@ -3219,7 +3232,7 @@
       <c r="J11" s="50" t="s">
         <v>415</v>
       </c>
-      <c r="K11" s="104" t="s">
+      <c r="K11" s="94" t="s">
         <v>339</v>
       </c>
       <c r="L11" s="50">
@@ -3275,7 +3288,7 @@
       <c r="J12" s="46" t="s">
         <v>416</v>
       </c>
-      <c r="K12" s="105" t="s">
+      <c r="K12" s="95" t="s">
         <v>340</v>
       </c>
       <c r="L12" s="46">
@@ -3331,7 +3344,7 @@
       <c r="J13" s="50" t="s">
         <v>417</v>
       </c>
-      <c r="K13" s="104" t="s">
+      <c r="K13" s="94" t="s">
         <v>341</v>
       </c>
       <c r="L13" s="50">
@@ -3387,7 +3400,7 @@
       <c r="J14" s="46" t="s">
         <v>418</v>
       </c>
-      <c r="K14" s="105" t="s">
+      <c r="K14" s="95" t="s">
         <v>342</v>
       </c>
       <c r="L14" s="46">
@@ -3410,7 +3423,9 @@
         <f t="shared" si="2"/>
         <v>1.3759999999999999</v>
       </c>
-      <c r="R14" s="48"/>
+      <c r="R14" s="81" t="s">
+        <v>539</v>
+      </c>
       <c r="S14" s="48"/>
     </row>
     <row r="15" spans="1:19" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
@@ -3443,7 +3458,7 @@
       <c r="J15" s="50" t="s">
         <v>419</v>
       </c>
-      <c r="K15" s="104" t="s">
+      <c r="K15" s="94" t="s">
         <v>343</v>
       </c>
       <c r="L15" s="50">
@@ -3487,19 +3502,19 @@
       <c r="F16" s="73" t="s">
         <v>408</v>
       </c>
-      <c r="G16" s="110" t="s">
+      <c r="G16" s="100" t="s">
         <v>193</v>
       </c>
       <c r="H16" s="73" t="s">
-        <v>529</v>
+        <v>526</v>
       </c>
       <c r="I16" s="73" t="s">
         <v>301</v>
       </c>
       <c r="J16" s="73" t="s">
-        <v>530</v>
-      </c>
-      <c r="K16" s="106" t="s">
+        <v>527</v>
+      </c>
+      <c r="K16" s="96" t="s">
         <v>340</v>
       </c>
       <c r="L16" s="73">
@@ -3523,10 +3538,10 @@
         <v>1.87</v>
       </c>
       <c r="R16" s="81" t="s">
-        <v>541</v>
+        <v>538</v>
       </c>
       <c r="S16" s="76" t="s">
-        <v>531</v>
+        <v>528</v>
       </c>
     </row>
     <row r="17" spans="1:19" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
@@ -3559,7 +3574,7 @@
       <c r="J17" s="50" t="s">
         <v>420</v>
       </c>
-      <c r="K17" s="104" t="s">
+      <c r="K17" s="94" t="s">
         <v>344</v>
       </c>
       <c r="L17" s="50">
@@ -3615,7 +3630,7 @@
       <c r="J18" s="46" t="s">
         <v>421</v>
       </c>
-      <c r="K18" s="105" t="s">
+      <c r="K18" s="95" t="s">
         <v>345</v>
       </c>
       <c r="L18" s="46">
@@ -3671,7 +3686,7 @@
       <c r="J19" s="50" t="s">
         <v>422</v>
       </c>
-      <c r="K19" s="104" t="s">
+      <c r="K19" s="94" t="s">
         <v>339</v>
       </c>
       <c r="L19" s="50">
@@ -3727,7 +3742,7 @@
       <c r="J20" s="46" t="s">
         <v>423</v>
       </c>
-      <c r="K20" s="105" t="s">
+      <c r="K20" s="95" t="s">
         <v>346</v>
       </c>
       <c r="L20" s="46">
@@ -3783,7 +3798,7 @@
       <c r="J21" s="50" t="s">
         <v>424</v>
       </c>
-      <c r="K21" s="104" t="s">
+      <c r="K21" s="94" t="s">
         <v>347</v>
       </c>
       <c r="L21" s="50">
@@ -3839,7 +3854,7 @@
       <c r="J22" s="46" t="s">
         <v>425</v>
       </c>
-      <c r="K22" s="105" t="s">
+      <c r="K22" s="95" t="s">
         <v>348</v>
       </c>
       <c r="L22" s="46">
@@ -3895,7 +3910,7 @@
       <c r="J23" s="50" t="s">
         <v>426</v>
       </c>
-      <c r="K23" s="104" t="s">
+      <c r="K23" s="94" t="s">
         <v>349</v>
       </c>
       <c r="L23" s="50">
@@ -3943,15 +3958,15 @@
         <v>248</v>
       </c>
       <c r="H24" s="46" t="s">
-        <v>475</v>
+        <v>474</v>
       </c>
       <c r="I24" s="46" t="s">
         <v>303</v>
       </c>
       <c r="J24" s="46" t="s">
-        <v>476</v>
-      </c>
-      <c r="K24" s="105" t="s">
+        <v>475</v>
+      </c>
+      <c r="K24" s="95" t="s">
         <v>350</v>
       </c>
       <c r="L24" s="46">
@@ -3995,19 +4010,19 @@
       <c r="F25" s="50" t="s">
         <v>190</v>
       </c>
-      <c r="G25" s="51" t="s">
+      <c r="G25" s="69" t="s">
         <v>249</v>
       </c>
       <c r="H25" s="50" t="s">
-        <v>410</v>
+        <v>540</v>
       </c>
       <c r="I25" s="50" t="s">
         <v>298</v>
       </c>
       <c r="J25" s="50" t="s">
-        <v>427</v>
-      </c>
-      <c r="K25" s="104" t="s">
+        <v>541</v>
+      </c>
+      <c r="K25" s="94" t="s">
         <v>351</v>
       </c>
       <c r="L25" s="50">
@@ -4024,11 +4039,11 @@
         <v>414</v>
       </c>
       <c r="P25" s="61">
-        <v>4.0000000000000001E-3</v>
+        <v>3.5000000000000001E-3</v>
       </c>
       <c r="Q25" s="61">
         <f t="shared" si="2"/>
-        <v>0.4</v>
+        <v>0.35000000000000003</v>
       </c>
       <c r="R25" s="52"/>
       <c r="S25" s="52"/>
@@ -4058,12 +4073,12 @@
         <v>410</v>
       </c>
       <c r="I26" s="46" t="s">
-        <v>478</v>
+        <v>477</v>
       </c>
       <c r="J26" s="46" t="s">
-        <v>477</v>
-      </c>
-      <c r="K26" s="105" t="s">
+        <v>476</v>
+      </c>
+      <c r="K26" s="95" t="s">
         <v>410</v>
       </c>
       <c r="L26" s="46">
@@ -4117,9 +4132,9 @@
         <v>304</v>
       </c>
       <c r="J27" s="50" t="s">
-        <v>428</v>
-      </c>
-      <c r="K27" s="104" t="s">
+        <v>427</v>
+      </c>
+      <c r="K27" s="94" t="s">
         <v>410</v>
       </c>
       <c r="L27" s="50">
@@ -4166,14 +4181,16 @@
       <c r="G28" s="47" t="s">
         <v>251</v>
       </c>
-      <c r="H28" s="46"/>
+      <c r="H28" s="46" t="s">
+        <v>410</v>
+      </c>
       <c r="I28" s="46" t="s">
+        <v>478</v>
+      </c>
+      <c r="J28" s="46" t="s">
         <v>479</v>
       </c>
-      <c r="J28" s="46" t="s">
-        <v>480</v>
-      </c>
-      <c r="K28" s="105" t="s">
+      <c r="K28" s="95" t="s">
         <v>410</v>
       </c>
       <c r="L28" s="46">
@@ -4224,12 +4241,12 @@
         <v>410</v>
       </c>
       <c r="I29" s="50" t="s">
-        <v>481</v>
+        <v>480</v>
       </c>
       <c r="J29" s="50" t="s">
-        <v>429</v>
-      </c>
-      <c r="K29" s="104" t="s">
+        <v>428</v>
+      </c>
+      <c r="K29" s="94" t="s">
         <v>410</v>
       </c>
       <c r="L29" s="50">
@@ -4273,19 +4290,19 @@
       <c r="F30" s="73" t="s">
         <v>196</v>
       </c>
-      <c r="G30" s="110" t="s">
+      <c r="G30" s="100" t="s">
         <v>252</v>
       </c>
       <c r="H30" s="73" t="s">
-        <v>532</v>
+        <v>529</v>
       </c>
       <c r="I30" s="73" t="s">
         <v>305</v>
       </c>
       <c r="J30" s="73" t="s">
-        <v>533</v>
-      </c>
-      <c r="K30" s="106" t="s">
+        <v>530</v>
+      </c>
+      <c r="K30" s="96" t="s">
         <v>410</v>
       </c>
       <c r="L30" s="73">
@@ -4309,10 +4326,10 @@
         <v>0.69000000000000006</v>
       </c>
       <c r="R30" s="81" t="s">
-        <v>541</v>
+        <v>538</v>
       </c>
       <c r="S30" s="76" t="s">
-        <v>534</v>
+        <v>531</v>
       </c>
     </row>
     <row r="31" spans="1:19" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
@@ -4343,9 +4360,9 @@
         <v>306</v>
       </c>
       <c r="J31" s="50" t="s">
-        <v>482</v>
-      </c>
-      <c r="K31" s="104" t="s">
+        <v>481</v>
+      </c>
+      <c r="K31" s="94" t="s">
         <v>410</v>
       </c>
       <c r="L31" s="50">
@@ -4397,7 +4414,7 @@
         <v>307</v>
       </c>
       <c r="J32" s="46"/>
-      <c r="K32" s="105" t="s">
+      <c r="K32" s="95" t="s">
         <v>410</v>
       </c>
       <c r="L32" s="46">
@@ -4439,15 +4456,15 @@
         <v>199</v>
       </c>
       <c r="H33" s="50" t="s">
-        <v>515</v>
+        <v>512</v>
       </c>
       <c r="I33" s="50" t="s">
         <v>308</v>
       </c>
       <c r="J33" s="50" t="s">
-        <v>516</v>
-      </c>
-      <c r="K33" s="104" t="s">
+        <v>513</v>
+      </c>
+      <c r="K33" s="94" t="s">
         <v>410</v>
       </c>
       <c r="L33" s="50">
@@ -4495,15 +4512,15 @@
         <v>200</v>
       </c>
       <c r="H34" s="46" t="s">
-        <v>517</v>
+        <v>514</v>
       </c>
       <c r="I34" s="46" t="s">
         <v>308</v>
       </c>
       <c r="J34" s="46" t="s">
-        <v>518</v>
-      </c>
-      <c r="K34" s="105" t="s">
+        <v>515</v>
+      </c>
+      <c r="K34" s="95" t="s">
         <v>410</v>
       </c>
       <c r="L34" s="46">
@@ -4551,15 +4568,15 @@
         <v>201</v>
       </c>
       <c r="H35" s="50" t="s">
-        <v>519</v>
+        <v>516</v>
       </c>
       <c r="I35" s="50" t="s">
         <v>308</v>
       </c>
       <c r="J35" s="50" t="s">
-        <v>520</v>
-      </c>
-      <c r="K35" s="107" t="s">
+        <v>517</v>
+      </c>
+      <c r="K35" s="97" t="s">
         <v>411</v>
       </c>
       <c r="L35" s="50">
@@ -4613,9 +4630,9 @@
         <v>309</v>
       </c>
       <c r="J36" s="46" t="s">
-        <v>430</v>
-      </c>
-      <c r="K36" s="105" t="s">
+        <v>429</v>
+      </c>
+      <c r="K36" s="95" t="s">
         <v>410</v>
       </c>
       <c r="L36" s="46">
@@ -4669,9 +4686,9 @@
         <v>310</v>
       </c>
       <c r="J37" s="50" t="s">
-        <v>431</v>
-      </c>
-      <c r="K37" s="104" t="s">
+        <v>430</v>
+      </c>
+      <c r="K37" s="94" t="s">
         <v>410</v>
       </c>
       <c r="L37" s="50">
@@ -4725,9 +4742,9 @@
         <v>311</v>
       </c>
       <c r="J38" s="46" t="s">
-        <v>432</v>
-      </c>
-      <c r="K38" s="105" t="s">
+        <v>431</v>
+      </c>
+      <c r="K38" s="95" t="s">
         <v>410</v>
       </c>
       <c r="L38" s="46">
@@ -4772,7 +4789,7 @@
         <v>205</v>
       </c>
       <c r="G39" s="51" t="s">
-        <v>483</v>
+        <v>482</v>
       </c>
       <c r="H39" s="50" t="s">
         <v>410</v>
@@ -4781,9 +4798,9 @@
         <v>312</v>
       </c>
       <c r="J39" s="50" t="s">
-        <v>484</v>
-      </c>
-      <c r="K39" s="104" t="s">
+        <v>483</v>
+      </c>
+      <c r="K39" s="94" t="s">
         <v>353</v>
       </c>
       <c r="L39" s="50">
@@ -4837,9 +4854,9 @@
         <v>313</v>
       </c>
       <c r="J40" s="46" t="s">
-        <v>433</v>
-      </c>
-      <c r="K40" s="105" t="s">
+        <v>432</v>
+      </c>
+      <c r="K40" s="95" t="s">
         <v>354</v>
       </c>
       <c r="L40" s="46">
@@ -4893,9 +4910,9 @@
         <v>314</v>
       </c>
       <c r="J41" s="50" t="s">
-        <v>434</v>
-      </c>
-      <c r="K41" s="104" t="s">
+        <v>433</v>
+      </c>
+      <c r="K41" s="94" t="s">
         <v>355</v>
       </c>
       <c r="L41" s="50">
@@ -4949,9 +4966,9 @@
         <v>315</v>
       </c>
       <c r="J42" s="46" t="s">
-        <v>435</v>
-      </c>
-      <c r="K42" s="105" t="s">
+        <v>434</v>
+      </c>
+      <c r="K42" s="95" t="s">
         <v>356</v>
       </c>
       <c r="L42" s="46">
@@ -4999,15 +5016,15 @@
         <v>255</v>
       </c>
       <c r="H43" s="50" t="s">
-        <v>502</v>
+        <v>499</v>
       </c>
       <c r="I43" s="50" t="s">
         <v>316</v>
       </c>
       <c r="J43" s="50" t="s">
-        <v>503</v>
-      </c>
-      <c r="K43" s="104" t="s">
+        <v>500</v>
+      </c>
+      <c r="K43" s="94" t="s">
         <v>410</v>
       </c>
       <c r="L43" s="50">
@@ -5061,9 +5078,9 @@
         <v>317</v>
       </c>
       <c r="J44" s="46" t="s">
-        <v>436</v>
-      </c>
-      <c r="K44" s="105" t="s">
+        <v>435</v>
+      </c>
+      <c r="K44" s="95" t="s">
         <v>410</v>
       </c>
       <c r="L44" s="46">
@@ -5117,9 +5134,9 @@
         <v>318</v>
       </c>
       <c r="J45" s="50" t="s">
-        <v>437</v>
-      </c>
-      <c r="K45" s="104" t="s">
+        <v>436</v>
+      </c>
+      <c r="K45" s="94" t="s">
         <v>410</v>
       </c>
       <c r="L45" s="50">
@@ -5175,7 +5192,7 @@
       <c r="J46" s="46" t="s">
         <v>410</v>
       </c>
-      <c r="K46" s="105" t="s">
+      <c r="K46" s="95" t="s">
         <v>410</v>
       </c>
       <c r="L46" s="46">
@@ -5198,7 +5215,7 @@
         <v>410</v>
       </c>
       <c r="R46" s="87" t="s">
-        <v>526</v>
+        <v>523</v>
       </c>
       <c r="S46" s="48" t="s">
         <v>410</v>
@@ -5226,15 +5243,15 @@
         <v>61300311121</v>
       </c>
       <c r="H47" s="50" t="s">
-        <v>487</v>
+        <v>486</v>
       </c>
       <c r="I47" s="50" t="s">
         <v>319</v>
       </c>
       <c r="J47" s="50" t="s">
-        <v>488</v>
-      </c>
-      <c r="K47" s="104" t="s">
+        <v>487</v>
+      </c>
+      <c r="K47" s="94" t="s">
         <v>410</v>
       </c>
       <c r="L47" s="50">
@@ -5282,15 +5299,15 @@
         <v>61300611121</v>
       </c>
       <c r="H48" s="46" t="s">
-        <v>485</v>
+        <v>484</v>
       </c>
       <c r="I48" s="46" t="s">
         <v>319</v>
       </c>
       <c r="J48" s="46" t="s">
-        <v>486</v>
-      </c>
-      <c r="K48" s="105" t="s">
+        <v>485</v>
+      </c>
+      <c r="K48" s="95" t="s">
         <v>410</v>
       </c>
       <c r="L48" s="46">
@@ -5338,15 +5355,15 @@
         <v>257</v>
       </c>
       <c r="H49" s="50" t="s">
-        <v>504</v>
+        <v>501</v>
       </c>
       <c r="I49" s="50" t="s">
-        <v>505</v>
+        <v>502</v>
       </c>
       <c r="J49" s="50" t="s">
-        <v>504</v>
-      </c>
-      <c r="K49" s="104" t="s">
+        <v>501</v>
+      </c>
+      <c r="K49" s="94" t="s">
         <v>410</v>
       </c>
       <c r="L49" s="50">
@@ -5393,16 +5410,16 @@
       <c r="G50" s="68">
         <v>61300211121</v>
       </c>
-      <c r="H50" s="46" t="s">
-        <v>489</v>
+      <c r="H50" s="111" t="s">
+        <v>542</v>
       </c>
       <c r="I50" s="46" t="s">
         <v>319</v>
       </c>
       <c r="J50" s="46" t="s">
-        <v>490</v>
-      </c>
-      <c r="K50" s="105" t="s">
+        <v>543</v>
+      </c>
+      <c r="K50" s="95" t="s">
         <v>410</v>
       </c>
       <c r="L50" s="46">
@@ -5419,11 +5436,11 @@
         <v>414</v>
       </c>
       <c r="P50" s="60">
-        <v>1.89E-2</v>
+        <v>1.2E-2</v>
       </c>
       <c r="Q50" s="60">
         <f t="shared" si="2"/>
-        <v>0.94500000000000006</v>
+        <v>0.6</v>
       </c>
       <c r="R50" s="48"/>
       <c r="S50" s="48"/>
@@ -5450,15 +5467,15 @@
         <v>61300411121</v>
       </c>
       <c r="H51" s="50" t="s">
-        <v>491</v>
+        <v>488</v>
       </c>
       <c r="I51" s="50" t="s">
         <v>319</v>
       </c>
       <c r="J51" s="50" t="s">
-        <v>492</v>
-      </c>
-      <c r="K51" s="104" t="s">
+        <v>489</v>
+      </c>
+      <c r="K51" s="94" t="s">
         <v>410</v>
       </c>
       <c r="L51" s="50">
@@ -5512,9 +5529,9 @@
         <v>305</v>
       </c>
       <c r="J52" s="46" t="s">
-        <v>438</v>
-      </c>
-      <c r="K52" s="105" t="s">
+        <v>437</v>
+      </c>
+      <c r="K52" s="95" t="s">
         <v>410</v>
       </c>
       <c r="L52" s="46">
@@ -5565,12 +5582,12 @@
         <v>410</v>
       </c>
       <c r="I53" s="50" t="s">
-        <v>493</v>
+        <v>490</v>
       </c>
       <c r="J53" s="50" t="s">
-        <v>494</v>
-      </c>
-      <c r="K53" s="104" t="s">
+        <v>491</v>
+      </c>
+      <c r="K53" s="94" t="s">
         <v>410</v>
       </c>
       <c r="L53" s="50">
@@ -5617,14 +5634,16 @@
       <c r="G54" s="47" t="s">
         <v>260</v>
       </c>
-      <c r="H54" s="46"/>
+      <c r="H54" s="46" t="s">
+        <v>410</v>
+      </c>
       <c r="I54" s="46" t="s">
         <v>320</v>
       </c>
       <c r="J54" s="46" t="s">
-        <v>439</v>
-      </c>
-      <c r="K54" s="105" t="s">
+        <v>438</v>
+      </c>
+      <c r="K54" s="95" t="s">
         <v>410</v>
       </c>
       <c r="L54" s="46">
@@ -5675,12 +5694,12 @@
         <v>410</v>
       </c>
       <c r="I55" s="50" t="s">
-        <v>493</v>
+        <v>490</v>
       </c>
       <c r="J55" s="50" t="s">
-        <v>495</v>
-      </c>
-      <c r="K55" s="104" t="s">
+        <v>492</v>
+      </c>
+      <c r="K55" s="94" t="s">
         <v>410</v>
       </c>
       <c r="L55" s="50">
@@ -5732,9 +5751,9 @@
         <v>321</v>
       </c>
       <c r="J56" s="46" t="s">
-        <v>440</v>
-      </c>
-      <c r="K56" s="105" t="s">
+        <v>439</v>
+      </c>
+      <c r="K56" s="95" t="s">
         <v>410</v>
       </c>
       <c r="L56" s="46">
@@ -5788,9 +5807,9 @@
         <v>321</v>
       </c>
       <c r="J57" s="50" t="s">
-        <v>441</v>
-      </c>
-      <c r="K57" s="104" t="s">
+        <v>440</v>
+      </c>
+      <c r="K57" s="94" t="s">
         <v>410</v>
       </c>
       <c r="L57" s="50">
@@ -5844,9 +5863,9 @@
         <v>304</v>
       </c>
       <c r="J58" s="46" t="s">
-        <v>442</v>
-      </c>
-      <c r="K58" s="105" t="s">
+        <v>441</v>
+      </c>
+      <c r="K58" s="95" t="s">
         <v>410</v>
       </c>
       <c r="L58" s="46">
@@ -5900,9 +5919,9 @@
         <v>322</v>
       </c>
       <c r="J59" s="50" t="s">
-        <v>443</v>
-      </c>
-      <c r="K59" s="104" t="s">
+        <v>442</v>
+      </c>
+      <c r="K59" s="94" t="s">
         <v>410</v>
       </c>
       <c r="L59" s="50">
@@ -5944,7 +5963,7 @@
         <v>147</v>
       </c>
       <c r="F60" s="46" t="s">
-        <v>220</v>
+        <v>544</v>
       </c>
       <c r="G60" s="47" t="s">
         <v>265</v>
@@ -5956,9 +5975,9 @@
         <v>298</v>
       </c>
       <c r="J60" s="46" t="s">
-        <v>444</v>
-      </c>
-      <c r="K60" s="105" t="s">
+        <v>443</v>
+      </c>
+      <c r="K60" s="95" t="s">
         <v>358</v>
       </c>
       <c r="L60" s="46">
@@ -6010,9 +6029,9 @@
         <v>298</v>
       </c>
       <c r="J61" s="50" t="s">
-        <v>445</v>
-      </c>
-      <c r="K61" s="104" t="s">
+        <v>444</v>
+      </c>
+      <c r="K61" s="94" t="s">
         <v>359</v>
       </c>
       <c r="L61" s="50">
@@ -6057,7 +6076,7 @@
         <v>220</v>
       </c>
       <c r="G62" s="47" t="s">
-        <v>473</v>
+        <v>472</v>
       </c>
       <c r="H62" s="46" t="s">
         <v>410</v>
@@ -6066,9 +6085,9 @@
         <v>323</v>
       </c>
       <c r="J62" s="46" t="s">
-        <v>474</v>
-      </c>
-      <c r="K62" s="105" t="s">
+        <v>473</v>
+      </c>
+      <c r="K62" s="95" t="s">
         <v>360</v>
       </c>
       <c r="L62" s="46">
@@ -6104,7 +6123,7 @@
         <v>394</v>
       </c>
       <c r="D63" s="50" t="s">
-        <v>540</v>
+        <v>537</v>
       </c>
       <c r="E63" s="51" t="s">
         <v>150</v>
@@ -6122,9 +6141,9 @@
         <v>298</v>
       </c>
       <c r="J63" s="50" t="s">
-        <v>446</v>
-      </c>
-      <c r="K63" s="104" t="s">
+        <v>445</v>
+      </c>
+      <c r="K63" s="94" t="s">
         <v>361</v>
       </c>
       <c r="L63" s="50">
@@ -6178,9 +6197,9 @@
         <v>298</v>
       </c>
       <c r="J64" s="46" t="s">
-        <v>447</v>
-      </c>
-      <c r="K64" s="105" t="s">
+        <v>446</v>
+      </c>
+      <c r="K64" s="95" t="s">
         <v>362</v>
       </c>
       <c r="L64" s="46">
@@ -6232,9 +6251,9 @@
         <v>298</v>
       </c>
       <c r="J65" s="50" t="s">
-        <v>448</v>
-      </c>
-      <c r="K65" s="104" t="s">
+        <v>447</v>
+      </c>
+      <c r="K65" s="94" t="s">
         <v>363</v>
       </c>
       <c r="L65" s="50">
@@ -6288,9 +6307,9 @@
         <v>324</v>
       </c>
       <c r="J66" s="46" t="s">
-        <v>449</v>
-      </c>
-      <c r="K66" s="105" t="s">
+        <v>448</v>
+      </c>
+      <c r="K66" s="95" t="s">
         <v>364</v>
       </c>
       <c r="L66" s="46">
@@ -6338,15 +6357,15 @@
         <v>271</v>
       </c>
       <c r="H67" s="50" t="s">
-        <v>496</v>
+        <v>493</v>
       </c>
       <c r="I67" s="50" t="s">
         <v>325</v>
       </c>
       <c r="J67" s="50" t="s">
-        <v>497</v>
-      </c>
-      <c r="K67" s="104" t="s">
+        <v>494</v>
+      </c>
+      <c r="K67" s="94" t="s">
         <v>365</v>
       </c>
       <c r="L67" s="50">
@@ -6400,9 +6419,9 @@
         <v>326</v>
       </c>
       <c r="J68" s="46" t="s">
-        <v>450</v>
-      </c>
-      <c r="K68" s="105" t="s">
+        <v>449</v>
+      </c>
+      <c r="K68" s="95" t="s">
         <v>366</v>
       </c>
       <c r="L68" s="46">
@@ -6456,9 +6475,9 @@
         <v>298</v>
       </c>
       <c r="J69" s="50" t="s">
-        <v>451</v>
-      </c>
-      <c r="K69" s="104" t="s">
+        <v>450</v>
+      </c>
+      <c r="K69" s="94" t="s">
         <v>367</v>
       </c>
       <c r="L69" s="50">
@@ -6512,9 +6531,9 @@
         <v>326</v>
       </c>
       <c r="J70" s="46" t="s">
-        <v>452</v>
-      </c>
-      <c r="K70" s="105" t="s">
+        <v>451</v>
+      </c>
+      <c r="K70" s="95" t="s">
         <v>368</v>
       </c>
       <c r="L70" s="46">
@@ -6568,9 +6587,9 @@
         <v>298</v>
       </c>
       <c r="J71" s="50" t="s">
-        <v>453</v>
-      </c>
-      <c r="K71" s="104" t="s">
+        <v>452</v>
+      </c>
+      <c r="K71" s="94" t="s">
         <v>369</v>
       </c>
       <c r="L71" s="50">
@@ -6624,9 +6643,9 @@
         <v>298</v>
       </c>
       <c r="J72" s="46" t="s">
-        <v>454</v>
-      </c>
-      <c r="K72" s="105" t="s">
+        <v>453</v>
+      </c>
+      <c r="K72" s="95" t="s">
         <v>370</v>
       </c>
       <c r="L72" s="46">
@@ -6680,9 +6699,9 @@
         <v>327</v>
       </c>
       <c r="J73" s="50" t="s">
-        <v>455</v>
-      </c>
-      <c r="K73" s="104" t="s">
+        <v>454</v>
+      </c>
+      <c r="K73" s="94" t="s">
         <v>371</v>
       </c>
       <c r="L73" s="50">
@@ -6727,19 +6746,19 @@
         <v>220</v>
       </c>
       <c r="G74" s="47" t="s">
-        <v>507</v>
+        <v>504</v>
       </c>
       <c r="H74" s="46" t="s">
         <v>410</v>
       </c>
       <c r="I74" s="46" t="s">
-        <v>508</v>
+        <v>505</v>
       </c>
       <c r="J74" s="46" t="s">
-        <v>509</v>
-      </c>
-      <c r="K74" s="105" t="s">
         <v>506</v>
+      </c>
+      <c r="K74" s="95" t="s">
+        <v>503</v>
       </c>
       <c r="L74" s="46">
         <v>1</v>
@@ -6792,9 +6811,9 @@
         <v>298</v>
       </c>
       <c r="J75" s="50" t="s">
-        <v>456</v>
-      </c>
-      <c r="K75" s="104" t="s">
+        <v>455</v>
+      </c>
+      <c r="K75" s="94" t="s">
         <v>372</v>
       </c>
       <c r="L75" s="50">
@@ -6848,9 +6867,9 @@
         <v>298</v>
       </c>
       <c r="J76" s="46" t="s">
-        <v>457</v>
-      </c>
-      <c r="K76" s="105" t="s">
+        <v>456</v>
+      </c>
+      <c r="K76" s="95" t="s">
         <v>373</v>
       </c>
       <c r="L76" s="46">
@@ -6904,9 +6923,9 @@
         <v>298</v>
       </c>
       <c r="J77" s="50" t="s">
-        <v>458</v>
-      </c>
-      <c r="K77" s="104" t="s">
+        <v>457</v>
+      </c>
+      <c r="K77" s="94" t="s">
         <v>374</v>
       </c>
       <c r="L77" s="50">
@@ -6954,15 +6973,15 @@
         <v>281</v>
       </c>
       <c r="H78" s="46" t="s">
-        <v>510</v>
+        <v>507</v>
       </c>
       <c r="I78" s="46" t="s">
         <v>325</v>
       </c>
       <c r="J78" s="46" t="s">
-        <v>511</v>
-      </c>
-      <c r="K78" s="105" t="s">
+        <v>508</v>
+      </c>
+      <c r="K78" s="95" t="s">
         <v>375</v>
       </c>
       <c r="L78" s="46">
@@ -7016,9 +7035,9 @@
         <v>298</v>
       </c>
       <c r="J79" s="50" t="s">
-        <v>459</v>
-      </c>
-      <c r="K79" s="104" t="s">
+        <v>458</v>
+      </c>
+      <c r="K79" s="94" t="s">
         <v>376</v>
       </c>
       <c r="L79" s="50">
@@ -7072,9 +7091,9 @@
         <v>298</v>
       </c>
       <c r="J80" s="46" t="s">
-        <v>460</v>
-      </c>
-      <c r="K80" s="105" t="s">
+        <v>459</v>
+      </c>
+      <c r="K80" s="95" t="s">
         <v>377</v>
       </c>
       <c r="L80" s="46">
@@ -7128,9 +7147,9 @@
         <v>298</v>
       </c>
       <c r="J81" s="46" t="s">
-        <v>461</v>
-      </c>
-      <c r="K81" s="105" t="s">
+        <v>460</v>
+      </c>
+      <c r="K81" s="95" t="s">
         <v>378</v>
       </c>
       <c r="L81" s="46">
@@ -7184,9 +7203,9 @@
         <v>298</v>
       </c>
       <c r="J82" s="50" t="s">
-        <v>462</v>
-      </c>
-      <c r="K82" s="104" t="s">
+        <v>461</v>
+      </c>
+      <c r="K82" s="94" t="s">
         <v>379</v>
       </c>
       <c r="L82" s="50">
@@ -7231,7 +7250,7 @@
         <v>222</v>
       </c>
       <c r="G83" s="47" t="s">
-        <v>498</v>
+        <v>495</v>
       </c>
       <c r="H83" s="46" t="s">
         <v>410</v>
@@ -7240,9 +7259,9 @@
         <v>328</v>
       </c>
       <c r="J83" s="46" t="s">
-        <v>499</v>
-      </c>
-      <c r="K83" s="105" t="s">
+        <v>496</v>
+      </c>
+      <c r="K83" s="95" t="s">
         <v>380</v>
       </c>
       <c r="L83" s="46">
@@ -7296,9 +7315,9 @@
         <v>298</v>
       </c>
       <c r="J84" s="50" t="s">
-        <v>463</v>
-      </c>
-      <c r="K84" s="104" t="s">
+        <v>462</v>
+      </c>
+      <c r="K84" s="94" t="s">
         <v>381</v>
       </c>
       <c r="L84" s="50">
@@ -7346,15 +7365,15 @@
         <v>287</v>
       </c>
       <c r="H85" s="46" t="s">
-        <v>500</v>
+        <v>497</v>
       </c>
       <c r="I85" s="46" t="s">
         <v>329</v>
       </c>
       <c r="J85" s="46" t="s">
-        <v>501</v>
-      </c>
-      <c r="K85" s="105" t="s">
+        <v>498</v>
+      </c>
+      <c r="K85" s="95" t="s">
         <v>362</v>
       </c>
       <c r="L85" s="46">
@@ -7410,7 +7429,7 @@
       <c r="J86" s="50" t="s">
         <v>410</v>
       </c>
-      <c r="K86" s="104" t="s">
+      <c r="K86" s="94" t="s">
         <v>410</v>
       </c>
       <c r="L86" s="50">
@@ -7433,7 +7452,7 @@
         <v>410</v>
       </c>
       <c r="R86" s="86" t="s">
-        <v>526</v>
+        <v>523</v>
       </c>
       <c r="S86" s="72" t="s">
         <v>410</v>
@@ -7467,9 +7486,9 @@
         <v>330</v>
       </c>
       <c r="J87" s="46" t="s">
-        <v>464</v>
-      </c>
-      <c r="K87" s="105" t="s">
+        <v>463</v>
+      </c>
+      <c r="K87" s="95" t="s">
         <v>410</v>
       </c>
       <c r="L87" s="46">
@@ -7525,7 +7544,7 @@
       <c r="J88" s="63" t="s">
         <v>410</v>
       </c>
-      <c r="K88" s="108" t="s">
+      <c r="K88" s="98" t="s">
         <v>410</v>
       </c>
       <c r="L88" s="63">
@@ -7539,7 +7558,7 @@
         <v>10</v>
       </c>
       <c r="O88" s="67" t="s">
-        <v>521</v>
+        <v>518</v>
       </c>
       <c r="P88" s="65">
         <v>8</v>
@@ -7549,7 +7568,7 @@
         <v>80</v>
       </c>
       <c r="R88" s="80" t="s">
-        <v>522</v>
+        <v>519</v>
       </c>
       <c r="S88" s="66"/>
       <c r="T88" s="77"/>
@@ -7582,9 +7601,9 @@
         <v>332</v>
       </c>
       <c r="J89" s="46" t="s">
-        <v>512</v>
-      </c>
-      <c r="K89" s="105" t="s">
+        <v>509</v>
+      </c>
+      <c r="K89" s="95" t="s">
         <v>410</v>
       </c>
       <c r="L89" s="46">
@@ -7638,9 +7657,9 @@
         <v>332</v>
       </c>
       <c r="J90" s="50" t="s">
-        <v>465</v>
-      </c>
-      <c r="K90" s="104" t="s">
+        <v>464</v>
+      </c>
+      <c r="K90" s="94" t="s">
         <v>410</v>
       </c>
       <c r="L90" s="50">
@@ -7694,9 +7713,9 @@
         <v>333</v>
       </c>
       <c r="J91" s="46" t="s">
-        <v>466</v>
-      </c>
-      <c r="K91" s="105" t="s">
+        <v>465</v>
+      </c>
+      <c r="K91" s="95" t="s">
         <v>410</v>
       </c>
       <c r="L91" s="46">
@@ -7750,7 +7769,7 @@
         <v>304</v>
       </c>
       <c r="J92" s="63"/>
-      <c r="K92" s="108" t="s">
+      <c r="K92" s="98" t="s">
         <v>410</v>
       </c>
       <c r="L92" s="63">
@@ -7800,7 +7819,7 @@
         <v>334</v>
       </c>
       <c r="J93" s="73"/>
-      <c r="K93" s="106" t="s">
+      <c r="K93" s="96" t="s">
         <v>410</v>
       </c>
       <c r="L93" s="73">
@@ -7845,12 +7864,12 @@
         <v>410</v>
       </c>
       <c r="I94" s="50" t="s">
-        <v>514</v>
+        <v>511</v>
       </c>
       <c r="J94" s="50" t="s">
-        <v>513</v>
-      </c>
-      <c r="K94" s="104" t="s">
+        <v>510</v>
+      </c>
+      <c r="K94" s="94" t="s">
         <v>410</v>
       </c>
       <c r="L94" s="50">
@@ -7904,9 +7923,9 @@
         <v>332</v>
       </c>
       <c r="J95" s="46" t="s">
-        <v>467</v>
-      </c>
-      <c r="K95" s="105" t="s">
+        <v>466</v>
+      </c>
+      <c r="K95" s="95" t="s">
         <v>410</v>
       </c>
       <c r="L95" s="46">
@@ -7960,9 +7979,9 @@
         <v>332</v>
       </c>
       <c r="J96" s="50" t="s">
-        <v>468</v>
-      </c>
-      <c r="K96" s="104" t="s">
+        <v>467</v>
+      </c>
+      <c r="K96" s="94" t="s">
         <v>410</v>
       </c>
       <c r="L96" s="50">
@@ -8016,9 +8035,9 @@
         <v>335</v>
       </c>
       <c r="J97" s="46" t="s">
-        <v>469</v>
-      </c>
-      <c r="K97" s="105" t="s">
+        <v>468</v>
+      </c>
+      <c r="K97" s="95" t="s">
         <v>410</v>
       </c>
       <c r="L97" s="46">
@@ -8072,9 +8091,9 @@
         <v>336</v>
       </c>
       <c r="J98" s="50" t="s">
-        <v>470</v>
-      </c>
-      <c r="K98" s="104" t="s">
+        <v>469</v>
+      </c>
+      <c r="K98" s="94" t="s">
         <v>410</v>
       </c>
       <c r="L98" s="50">
@@ -8113,25 +8132,25 @@
         <v>95</v>
       </c>
       <c r="E99" s="47" t="s">
-        <v>538</v>
+        <v>535</v>
       </c>
       <c r="F99" s="46" t="s">
         <v>408</v>
       </c>
       <c r="G99" s="47" t="s">
-        <v>535</v>
-      </c>
-      <c r="H99" s="100" t="s">
+        <v>532</v>
+      </c>
+      <c r="H99" s="90" t="s">
         <v>410</v>
       </c>
       <c r="I99" s="46" t="s">
+        <v>533</v>
+      </c>
+      <c r="J99" s="46" t="s">
         <v>536</v>
       </c>
-      <c r="J99" s="46" t="s">
-        <v>539</v>
-      </c>
       <c r="K99" s="47" t="s">
-        <v>537</v>
+        <v>534</v>
       </c>
       <c r="L99" s="46">
         <v>1</v>
@@ -8153,7 +8172,7 @@
         <f t="shared" si="6"/>
         <v>1.2804</v>
       </c>
-      <c r="R99" s="101"/>
+      <c r="R99" s="91"/>
       <c r="S99" s="48"/>
     </row>
     <row r="100" spans="1:19" ht="36.75" thickBot="1" x14ac:dyDescent="0.3">
@@ -8184,9 +8203,9 @@
         <v>322</v>
       </c>
       <c r="J100" s="50" t="s">
-        <v>471</v>
-      </c>
-      <c r="K100" s="104" t="s">
+        <v>470</v>
+      </c>
+      <c r="K100" s="94" t="s">
         <v>382</v>
       </c>
       <c r="L100" s="50">
@@ -8240,9 +8259,9 @@
         <v>337</v>
       </c>
       <c r="J101" s="46" t="s">
-        <v>472</v>
-      </c>
-      <c r="K101" s="109" t="s">
+        <v>471</v>
+      </c>
+      <c r="K101" s="99" t="s">
         <v>383</v>
       </c>
       <c r="L101" s="58">
@@ -8282,17 +8301,17 @@
       <c r="K102" s="37"/>
       <c r="L102" s="37"/>
       <c r="M102" s="37"/>
-      <c r="N102" s="90" t="s">
-        <v>523</v>
-      </c>
-      <c r="O102" s="91"/>
-      <c r="P102" s="91"/>
+      <c r="N102" s="101" t="s">
+        <v>520</v>
+      </c>
+      <c r="O102" s="102"/>
+      <c r="P102" s="102"/>
       <c r="Q102" s="78">
         <f>SUM(Q10:Q101)</f>
-        <v>635.34769999999992</v>
-      </c>
-      <c r="R102" s="96"/>
-      <c r="S102" s="97"/>
+        <v>634.95269999999994</v>
+      </c>
+      <c r="R102" s="107"/>
+      <c r="S102" s="108"/>
     </row>
     <row r="103" spans="1:19" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A103" s="1"/>
@@ -8308,24 +8327,24 @@
       <c r="K103" s="10"/>
       <c r="L103" s="10"/>
       <c r="M103" s="10"/>
-      <c r="N103" s="90" t="s">
-        <v>524</v>
-      </c>
-      <c r="O103" s="91"/>
-      <c r="P103" s="91"/>
+      <c r="N103" s="101" t="s">
+        <v>521</v>
+      </c>
+      <c r="O103" s="102"/>
+      <c r="P103" s="102"/>
       <c r="Q103" s="79">
         <f>Q102/5</f>
-        <v>127.06953999999999</v>
-      </c>
-      <c r="R103" s="98"/>
-      <c r="S103" s="99"/>
+        <v>126.99053999999998</v>
+      </c>
+      <c r="R103" s="109"/>
+      <c r="S103" s="110"/>
     </row>
     <row r="104" spans="1:19" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="N104" s="90" t="s">
-        <v>525</v>
-      </c>
-      <c r="O104" s="91"/>
-      <c r="P104" s="91"/>
+      <c r="N104" s="101" t="s">
+        <v>522</v>
+      </c>
+      <c r="O104" s="102"/>
+      <c r="P104" s="102"/>
       <c r="Q104" s="79">
         <v>4</v>
       </c>
@@ -8353,80 +8372,80 @@
     <hyperlink ref="O21" r:id="rId11" xr:uid="{00000000-0004-0000-0000-00000A000000}"/>
     <hyperlink ref="O22" r:id="rId12" xr:uid="{00000000-0004-0000-0000-00000B000000}"/>
     <hyperlink ref="O23" r:id="rId13" xr:uid="{00000000-0004-0000-0000-00000C000000}"/>
-    <hyperlink ref="O25" r:id="rId14" xr:uid="{00000000-0004-0000-0000-00000D000000}"/>
-    <hyperlink ref="O27" r:id="rId15" xr:uid="{00000000-0004-0000-0000-00000E000000}"/>
-    <hyperlink ref="O36" r:id="rId16" xr:uid="{00000000-0004-0000-0000-00000F000000}"/>
-    <hyperlink ref="O37" r:id="rId17" xr:uid="{00000000-0004-0000-0000-000010000000}"/>
-    <hyperlink ref="O38" r:id="rId18" xr:uid="{00000000-0004-0000-0000-000011000000}"/>
-    <hyperlink ref="O40" r:id="rId19" xr:uid="{00000000-0004-0000-0000-000012000000}"/>
-    <hyperlink ref="O41" r:id="rId20" xr:uid="{00000000-0004-0000-0000-000013000000}"/>
-    <hyperlink ref="O42" r:id="rId21" xr:uid="{00000000-0004-0000-0000-000014000000}"/>
-    <hyperlink ref="O44" r:id="rId22" xr:uid="{00000000-0004-0000-0000-000015000000}"/>
-    <hyperlink ref="O45" r:id="rId23" xr:uid="{00000000-0004-0000-0000-000016000000}"/>
-    <hyperlink ref="O52" r:id="rId24" xr:uid="{00000000-0004-0000-0000-000017000000}"/>
-    <hyperlink ref="O54" r:id="rId25" xr:uid="{00000000-0004-0000-0000-000018000000}"/>
-    <hyperlink ref="O56" r:id="rId26" xr:uid="{00000000-0004-0000-0000-000019000000}"/>
-    <hyperlink ref="O57" r:id="rId27" xr:uid="{00000000-0004-0000-0000-00001A000000}"/>
-    <hyperlink ref="O58" r:id="rId28" xr:uid="{00000000-0004-0000-0000-00001B000000}"/>
-    <hyperlink ref="O59" r:id="rId29" xr:uid="{00000000-0004-0000-0000-00001C000000}"/>
-    <hyperlink ref="O60" r:id="rId30" xr:uid="{00000000-0004-0000-0000-00001D000000}"/>
-    <hyperlink ref="O61" r:id="rId31" xr:uid="{00000000-0004-0000-0000-00001E000000}"/>
-    <hyperlink ref="O62" r:id="rId32" xr:uid="{00000000-0004-0000-0000-00001F000000}"/>
-    <hyperlink ref="O63" r:id="rId33" xr:uid="{00000000-0004-0000-0000-000020000000}"/>
-    <hyperlink ref="O64" r:id="rId34" xr:uid="{00000000-0004-0000-0000-000021000000}"/>
-    <hyperlink ref="O65" r:id="rId35" xr:uid="{00000000-0004-0000-0000-000022000000}"/>
-    <hyperlink ref="O66" r:id="rId36" xr:uid="{00000000-0004-0000-0000-000023000000}"/>
-    <hyperlink ref="O68" r:id="rId37" xr:uid="{00000000-0004-0000-0000-000024000000}"/>
-    <hyperlink ref="O69" r:id="rId38" xr:uid="{00000000-0004-0000-0000-000025000000}"/>
-    <hyperlink ref="O70" r:id="rId39" xr:uid="{00000000-0004-0000-0000-000026000000}"/>
-    <hyperlink ref="O71" r:id="rId40" xr:uid="{00000000-0004-0000-0000-000027000000}"/>
-    <hyperlink ref="O72" r:id="rId41" xr:uid="{00000000-0004-0000-0000-000028000000}"/>
-    <hyperlink ref="O73" r:id="rId42" xr:uid="{00000000-0004-0000-0000-000029000000}"/>
-    <hyperlink ref="O75" r:id="rId43" xr:uid="{00000000-0004-0000-0000-00002A000000}"/>
-    <hyperlink ref="O76" r:id="rId44" xr:uid="{00000000-0004-0000-0000-00002B000000}"/>
-    <hyperlink ref="O77" r:id="rId45" xr:uid="{00000000-0004-0000-0000-00002C000000}"/>
-    <hyperlink ref="O79" r:id="rId46" xr:uid="{00000000-0004-0000-0000-00002D000000}"/>
-    <hyperlink ref="O80" r:id="rId47" xr:uid="{00000000-0004-0000-0000-00002E000000}"/>
-    <hyperlink ref="O81" r:id="rId48" xr:uid="{00000000-0004-0000-0000-00002F000000}"/>
-    <hyperlink ref="O82" r:id="rId49" xr:uid="{00000000-0004-0000-0000-000030000000}"/>
-    <hyperlink ref="O84" r:id="rId50" xr:uid="{00000000-0004-0000-0000-000031000000}"/>
-    <hyperlink ref="O87" r:id="rId51" xr:uid="{00000000-0004-0000-0000-000032000000}"/>
-    <hyperlink ref="O90" r:id="rId52" xr:uid="{00000000-0004-0000-0000-000033000000}"/>
-    <hyperlink ref="O91" r:id="rId53" xr:uid="{00000000-0004-0000-0000-000034000000}"/>
-    <hyperlink ref="O95" r:id="rId54" xr:uid="{00000000-0004-0000-0000-000035000000}"/>
-    <hyperlink ref="O96" r:id="rId55" xr:uid="{00000000-0004-0000-0000-000036000000}"/>
-    <hyperlink ref="O97" r:id="rId56" xr:uid="{00000000-0004-0000-0000-000037000000}"/>
-    <hyperlink ref="O98" r:id="rId57" xr:uid="{00000000-0004-0000-0000-000038000000}"/>
-    <hyperlink ref="O100" r:id="rId58" xr:uid="{00000000-0004-0000-0000-000039000000}"/>
-    <hyperlink ref="O101" r:id="rId59" xr:uid="{00000000-0004-0000-0000-00003A000000}"/>
-    <hyperlink ref="O24" r:id="rId60" xr:uid="{00000000-0004-0000-0000-00003B000000}"/>
-    <hyperlink ref="O26" r:id="rId61" xr:uid="{00000000-0004-0000-0000-00003C000000}"/>
-    <hyperlink ref="O28" r:id="rId62" xr:uid="{00000000-0004-0000-0000-00003D000000}"/>
-    <hyperlink ref="O29" r:id="rId63" xr:uid="{00000000-0004-0000-0000-00003E000000}"/>
-    <hyperlink ref="O31" r:id="rId64" xr:uid="{00000000-0004-0000-0000-00003F000000}"/>
-    <hyperlink ref="O39" r:id="rId65" xr:uid="{00000000-0004-0000-0000-000040000000}"/>
-    <hyperlink ref="O48" r:id="rId66" xr:uid="{00000000-0004-0000-0000-000041000000}"/>
-    <hyperlink ref="O47" r:id="rId67" xr:uid="{00000000-0004-0000-0000-000042000000}"/>
-    <hyperlink ref="O50" r:id="rId68" xr:uid="{00000000-0004-0000-0000-000043000000}"/>
-    <hyperlink ref="O51" r:id="rId69" xr:uid="{00000000-0004-0000-0000-000044000000}"/>
-    <hyperlink ref="O53" r:id="rId70" xr:uid="{00000000-0004-0000-0000-000045000000}"/>
-    <hyperlink ref="O55" r:id="rId71" xr:uid="{00000000-0004-0000-0000-000046000000}"/>
-    <hyperlink ref="O67" r:id="rId72" xr:uid="{00000000-0004-0000-0000-000047000000}"/>
-    <hyperlink ref="O83" r:id="rId73" xr:uid="{00000000-0004-0000-0000-000048000000}"/>
-    <hyperlink ref="O85" r:id="rId74" xr:uid="{00000000-0004-0000-0000-000049000000}"/>
-    <hyperlink ref="O43" r:id="rId75" xr:uid="{00000000-0004-0000-0000-00004A000000}"/>
-    <hyperlink ref="O49" r:id="rId76" xr:uid="{00000000-0004-0000-0000-00004B000000}"/>
-    <hyperlink ref="O74" r:id="rId77" xr:uid="{00000000-0004-0000-0000-00004C000000}"/>
-    <hyperlink ref="O78" r:id="rId78" xr:uid="{00000000-0004-0000-0000-00004D000000}"/>
-    <hyperlink ref="O89" r:id="rId79" xr:uid="{00000000-0004-0000-0000-00004E000000}"/>
-    <hyperlink ref="O94" r:id="rId80" xr:uid="{00000000-0004-0000-0000-00004F000000}"/>
-    <hyperlink ref="O33" r:id="rId81" xr:uid="{00000000-0004-0000-0000-000050000000}"/>
-    <hyperlink ref="O34" r:id="rId82" xr:uid="{00000000-0004-0000-0000-000051000000}"/>
-    <hyperlink ref="O35" r:id="rId83" xr:uid="{00000000-0004-0000-0000-000052000000}"/>
-    <hyperlink ref="O88" r:id="rId84" xr:uid="{00000000-0004-0000-0000-000053000000}"/>
-    <hyperlink ref="O16" r:id="rId85" xr:uid="{00000000-0004-0000-0000-000054000000}"/>
-    <hyperlink ref="O30" r:id="rId86" xr:uid="{00000000-0004-0000-0000-000055000000}"/>
-    <hyperlink ref="O99" r:id="rId87" xr:uid="{41DBDB4E-DF1C-471F-AD20-8FB2CA7D9E5E}"/>
+    <hyperlink ref="O27" r:id="rId14" xr:uid="{00000000-0004-0000-0000-00000E000000}"/>
+    <hyperlink ref="O36" r:id="rId15" xr:uid="{00000000-0004-0000-0000-00000F000000}"/>
+    <hyperlink ref="O37" r:id="rId16" xr:uid="{00000000-0004-0000-0000-000010000000}"/>
+    <hyperlink ref="O38" r:id="rId17" xr:uid="{00000000-0004-0000-0000-000011000000}"/>
+    <hyperlink ref="O40" r:id="rId18" xr:uid="{00000000-0004-0000-0000-000012000000}"/>
+    <hyperlink ref="O41" r:id="rId19" xr:uid="{00000000-0004-0000-0000-000013000000}"/>
+    <hyperlink ref="O42" r:id="rId20" xr:uid="{00000000-0004-0000-0000-000014000000}"/>
+    <hyperlink ref="O44" r:id="rId21" xr:uid="{00000000-0004-0000-0000-000015000000}"/>
+    <hyperlink ref="O45" r:id="rId22" xr:uid="{00000000-0004-0000-0000-000016000000}"/>
+    <hyperlink ref="O52" r:id="rId23" xr:uid="{00000000-0004-0000-0000-000017000000}"/>
+    <hyperlink ref="O54" r:id="rId24" xr:uid="{00000000-0004-0000-0000-000018000000}"/>
+    <hyperlink ref="O56" r:id="rId25" xr:uid="{00000000-0004-0000-0000-000019000000}"/>
+    <hyperlink ref="O57" r:id="rId26" xr:uid="{00000000-0004-0000-0000-00001A000000}"/>
+    <hyperlink ref="O58" r:id="rId27" xr:uid="{00000000-0004-0000-0000-00001B000000}"/>
+    <hyperlink ref="O59" r:id="rId28" xr:uid="{00000000-0004-0000-0000-00001C000000}"/>
+    <hyperlink ref="O60" r:id="rId29" xr:uid="{00000000-0004-0000-0000-00001D000000}"/>
+    <hyperlink ref="O61" r:id="rId30" xr:uid="{00000000-0004-0000-0000-00001E000000}"/>
+    <hyperlink ref="O62" r:id="rId31" xr:uid="{00000000-0004-0000-0000-00001F000000}"/>
+    <hyperlink ref="O63" r:id="rId32" xr:uid="{00000000-0004-0000-0000-000020000000}"/>
+    <hyperlink ref="O64" r:id="rId33" xr:uid="{00000000-0004-0000-0000-000021000000}"/>
+    <hyperlink ref="O65" r:id="rId34" xr:uid="{00000000-0004-0000-0000-000022000000}"/>
+    <hyperlink ref="O66" r:id="rId35" xr:uid="{00000000-0004-0000-0000-000023000000}"/>
+    <hyperlink ref="O68" r:id="rId36" xr:uid="{00000000-0004-0000-0000-000024000000}"/>
+    <hyperlink ref="O69" r:id="rId37" xr:uid="{00000000-0004-0000-0000-000025000000}"/>
+    <hyperlink ref="O70" r:id="rId38" xr:uid="{00000000-0004-0000-0000-000026000000}"/>
+    <hyperlink ref="O71" r:id="rId39" xr:uid="{00000000-0004-0000-0000-000027000000}"/>
+    <hyperlink ref="O72" r:id="rId40" xr:uid="{00000000-0004-0000-0000-000028000000}"/>
+    <hyperlink ref="O73" r:id="rId41" xr:uid="{00000000-0004-0000-0000-000029000000}"/>
+    <hyperlink ref="O75" r:id="rId42" xr:uid="{00000000-0004-0000-0000-00002A000000}"/>
+    <hyperlink ref="O76" r:id="rId43" xr:uid="{00000000-0004-0000-0000-00002B000000}"/>
+    <hyperlink ref="O77" r:id="rId44" xr:uid="{00000000-0004-0000-0000-00002C000000}"/>
+    <hyperlink ref="O79" r:id="rId45" xr:uid="{00000000-0004-0000-0000-00002D000000}"/>
+    <hyperlink ref="O80" r:id="rId46" xr:uid="{00000000-0004-0000-0000-00002E000000}"/>
+    <hyperlink ref="O81" r:id="rId47" xr:uid="{00000000-0004-0000-0000-00002F000000}"/>
+    <hyperlink ref="O82" r:id="rId48" xr:uid="{00000000-0004-0000-0000-000030000000}"/>
+    <hyperlink ref="O84" r:id="rId49" xr:uid="{00000000-0004-0000-0000-000031000000}"/>
+    <hyperlink ref="O87" r:id="rId50" xr:uid="{00000000-0004-0000-0000-000032000000}"/>
+    <hyperlink ref="O90" r:id="rId51" xr:uid="{00000000-0004-0000-0000-000033000000}"/>
+    <hyperlink ref="O91" r:id="rId52" xr:uid="{00000000-0004-0000-0000-000034000000}"/>
+    <hyperlink ref="O95" r:id="rId53" xr:uid="{00000000-0004-0000-0000-000035000000}"/>
+    <hyperlink ref="O96" r:id="rId54" xr:uid="{00000000-0004-0000-0000-000036000000}"/>
+    <hyperlink ref="O97" r:id="rId55" xr:uid="{00000000-0004-0000-0000-000037000000}"/>
+    <hyperlink ref="O98" r:id="rId56" xr:uid="{00000000-0004-0000-0000-000038000000}"/>
+    <hyperlink ref="O100" r:id="rId57" xr:uid="{00000000-0004-0000-0000-000039000000}"/>
+    <hyperlink ref="O101" r:id="rId58" xr:uid="{00000000-0004-0000-0000-00003A000000}"/>
+    <hyperlink ref="O24" r:id="rId59" xr:uid="{00000000-0004-0000-0000-00003B000000}"/>
+    <hyperlink ref="O26" r:id="rId60" xr:uid="{00000000-0004-0000-0000-00003C000000}"/>
+    <hyperlink ref="O28" r:id="rId61" xr:uid="{00000000-0004-0000-0000-00003D000000}"/>
+    <hyperlink ref="O29" r:id="rId62" xr:uid="{00000000-0004-0000-0000-00003E000000}"/>
+    <hyperlink ref="O31" r:id="rId63" xr:uid="{00000000-0004-0000-0000-00003F000000}"/>
+    <hyperlink ref="O39" r:id="rId64" xr:uid="{00000000-0004-0000-0000-000040000000}"/>
+    <hyperlink ref="O48" r:id="rId65" xr:uid="{00000000-0004-0000-0000-000041000000}"/>
+    <hyperlink ref="O47" r:id="rId66" xr:uid="{00000000-0004-0000-0000-000042000000}"/>
+    <hyperlink ref="O51" r:id="rId67" xr:uid="{00000000-0004-0000-0000-000044000000}"/>
+    <hyperlink ref="O53" r:id="rId68" xr:uid="{00000000-0004-0000-0000-000045000000}"/>
+    <hyperlink ref="O55" r:id="rId69" xr:uid="{00000000-0004-0000-0000-000046000000}"/>
+    <hyperlink ref="O67" r:id="rId70" xr:uid="{00000000-0004-0000-0000-000047000000}"/>
+    <hyperlink ref="O83" r:id="rId71" xr:uid="{00000000-0004-0000-0000-000048000000}"/>
+    <hyperlink ref="O85" r:id="rId72" xr:uid="{00000000-0004-0000-0000-000049000000}"/>
+    <hyperlink ref="O43" r:id="rId73" xr:uid="{00000000-0004-0000-0000-00004A000000}"/>
+    <hyperlink ref="O49" r:id="rId74" xr:uid="{00000000-0004-0000-0000-00004B000000}"/>
+    <hyperlink ref="O74" r:id="rId75" xr:uid="{00000000-0004-0000-0000-00004C000000}"/>
+    <hyperlink ref="O78" r:id="rId76" xr:uid="{00000000-0004-0000-0000-00004D000000}"/>
+    <hyperlink ref="O89" r:id="rId77" xr:uid="{00000000-0004-0000-0000-00004E000000}"/>
+    <hyperlink ref="O94" r:id="rId78" xr:uid="{00000000-0004-0000-0000-00004F000000}"/>
+    <hyperlink ref="O33" r:id="rId79" xr:uid="{00000000-0004-0000-0000-000050000000}"/>
+    <hyperlink ref="O34" r:id="rId80" xr:uid="{00000000-0004-0000-0000-000051000000}"/>
+    <hyperlink ref="O35" r:id="rId81" xr:uid="{00000000-0004-0000-0000-000052000000}"/>
+    <hyperlink ref="O88" r:id="rId82" xr:uid="{00000000-0004-0000-0000-000053000000}"/>
+    <hyperlink ref="O16" r:id="rId83" xr:uid="{00000000-0004-0000-0000-000054000000}"/>
+    <hyperlink ref="O30" r:id="rId84" xr:uid="{00000000-0004-0000-0000-000055000000}"/>
+    <hyperlink ref="O99" r:id="rId85" xr:uid="{41DBDB4E-DF1C-471F-AD20-8FB2CA7D9E5E}"/>
+    <hyperlink ref="O25" r:id="rId86" xr:uid="{DAC6EF1B-A44F-4325-8C76-4CC4A05529DD}"/>
+    <hyperlink ref="O50" r:id="rId87" xr:uid="{249CEE1C-EC12-47D3-9B5F-AD078E9DD01C}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId88"/>

--- a/BOM/GTV3_Board/eSpark_BOM.xlsx
+++ b/BOM/GTV3_Board/eSpark_BOM.xlsx
@@ -1,21 +1,20 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="25427"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
+  <fileVersion appName="xl" lastEdited="6" lowestEdited="6" rupBuild="14420"/>
   <workbookPr codeName="ThisWorkbook"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\GitHub\OliverStanton-WaterMonitor\BOM\GTV3_Board\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Faizan\GitHub\OliverStanton-WaterMonitor\BOM\GTV3_Board\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{29721828-455E-4D8A-81C6-4B1D2E0033E3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-5265" yWindow="2205" windowWidth="11790" windowHeight="15360" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-5265" yWindow="2205" windowWidth="11790" windowHeight="15360"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="181029"/>
+  <calcPr calcId="152511"/>
   <extLst>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
       <xcalcf:calcFeatures>
@@ -30,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="951" uniqueCount="545">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="952" uniqueCount="543">
   <si>
     <t>Component list</t>
   </si>
@@ -1584,12 +1583,6 @@
   </si>
   <si>
     <t>C441238</t>
-  </si>
-  <si>
-    <t>Aliexpress</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Is part ki Shipping Cost Add ni ha price me </t>
   </si>
   <si>
     <t xml:space="preserve">Total Component Cost </t>
@@ -1683,7 +1676,7 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <numFmts count="3">
     <numFmt numFmtId="164" formatCode="[$-409]h:mm:ss\ AM/PM;@"/>
     <numFmt numFmtId="165" formatCode="&quot;$&quot;#,##0.0000"/>
@@ -2217,7 +2210,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="20" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="112">
+  <cellXfs count="106">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
@@ -2387,21 +2380,6 @@
     <xf numFmtId="0" fontId="20" fillId="4" borderId="17" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="6" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="6" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="165" fontId="18" fillId="6" borderId="17" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="6" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="6" borderId="17" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="21" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -2436,9 +2414,6 @@
     <xf numFmtId="166" fontId="15" fillId="3" borderId="21" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="6" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="22" fillId="6" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -2451,9 +2426,6 @@
     <xf numFmtId="0" fontId="23" fillId="6" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="6" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="25" fillId="4" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -2490,14 +2462,14 @@
     <xf numFmtId="0" fontId="18" fillId="4" borderId="25" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="6" borderId="25" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="18" fillId="2" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="21" fillId="6" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="2" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="24" fillId="3" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="top"/>
@@ -2531,8 +2503,11 @@
     <xf numFmtId="0" fontId="17" fillId="3" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="2" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="0" fontId="20" fillId="2" borderId="17" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="4" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -2578,7 +2553,7 @@
         <xdr:cNvPr id="2" name="Picture 1">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000002000000}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{00000000-0008-0000-0000-000002000000}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -2874,7 +2849,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet1"/>
   <dimension ref="A1:T104"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
@@ -2916,15 +2891,15 @@
       <c r="H1" s="2"/>
       <c r="I1" s="2"/>
       <c r="J1" s="2"/>
-      <c r="K1" s="103"/>
-      <c r="L1" s="103"/>
-      <c r="M1" s="103"/>
-      <c r="N1" s="103"/>
-      <c r="O1" s="103"/>
-      <c r="P1" s="103"/>
-      <c r="Q1" s="103"/>
-      <c r="R1" s="103"/>
-      <c r="S1" s="104"/>
+      <c r="K1" s="96"/>
+      <c r="L1" s="96"/>
+      <c r="M1" s="96"/>
+      <c r="N1" s="96"/>
+      <c r="O1" s="96"/>
+      <c r="P1" s="96"/>
+      <c r="Q1" s="96"/>
+      <c r="R1" s="96"/>
+      <c r="S1" s="97"/>
     </row>
     <row r="2" spans="1:19" ht="32.25" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A2" s="1"/>
@@ -2935,7 +2910,7 @@
       </c>
       <c r="E2" s="11"/>
       <c r="F2" s="54" t="s">
-        <v>524</v>
+        <v>522</v>
       </c>
       <c r="G2" s="12"/>
       <c r="H2" s="12"/>
@@ -2960,7 +2935,7 @@
       </c>
       <c r="E3" s="13"/>
       <c r="F3" s="55" t="s">
-        <v>525</v>
+        <v>523</v>
       </c>
       <c r="G3" s="13"/>
       <c r="H3" s="13"/>
@@ -2974,7 +2949,7 @@
       <c r="P3" s="5"/>
       <c r="Q3" s="5"/>
       <c r="R3" s="5"/>
-      <c r="S3" s="105"/>
+      <c r="S3" s="98"/>
     </row>
     <row r="4" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A4" s="1"/>
@@ -2985,7 +2960,7 @@
       </c>
       <c r="E4" s="13"/>
       <c r="F4" s="56" t="s">
-        <v>525</v>
+        <v>523</v>
       </c>
       <c r="G4" s="14"/>
       <c r="H4" s="14"/>
@@ -2999,7 +2974,7 @@
       <c r="P4" s="6"/>
       <c r="Q4" s="6"/>
       <c r="R4" s="6"/>
-      <c r="S4" s="106"/>
+      <c r="S4" s="99"/>
     </row>
     <row r="5" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A5" s="1"/>
@@ -3024,7 +2999,7 @@
       <c r="P5" s="6"/>
       <c r="Q5" s="6"/>
       <c r="R5" s="6"/>
-      <c r="S5" s="106"/>
+      <c r="S5" s="99"/>
     </row>
     <row r="6" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A6" s="1"/>
@@ -3045,7 +3020,7 @@
       <c r="P6" s="6"/>
       <c r="Q6" s="6"/>
       <c r="R6" s="6"/>
-      <c r="S6" s="106"/>
+      <c r="S6" s="99"/>
     </row>
     <row r="7" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A7" s="1"/>
@@ -3066,7 +3041,7 @@
       <c r="P7" s="8"/>
       <c r="Q7" s="8"/>
       <c r="R7" s="8"/>
-      <c r="S7" s="106"/>
+      <c r="S7" s="99"/>
     </row>
     <row r="8" spans="1:19" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A8" s="1"/>
@@ -3087,7 +3062,7 @@
       <c r="P8" s="8"/>
       <c r="Q8" s="8"/>
       <c r="R8" s="8"/>
-      <c r="S8" s="106"/>
+      <c r="S8" s="99"/>
     </row>
     <row r="9" spans="1:19" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A9" s="1"/>
@@ -3118,7 +3093,7 @@
       <c r="J9" s="30" t="s">
         <v>400</v>
       </c>
-      <c r="K9" s="92" t="s">
+      <c r="K9" s="85" t="s">
         <v>412</v>
       </c>
       <c r="L9" s="30" t="s">
@@ -3152,7 +3127,7 @@
         <f t="shared" ref="B10:B41" si="0">ROW(B10) - ROW($B$9)</f>
         <v>1</v>
       </c>
-      <c r="C10" s="82" t="s">
+      <c r="C10" s="76" t="s">
         <v>385</v>
       </c>
       <c r="D10" s="46" t="s">
@@ -3176,7 +3151,7 @@
       <c r="J10" s="46" t="s">
         <v>413</v>
       </c>
-      <c r="K10" s="93" t="s">
+      <c r="K10" s="86" t="s">
         <v>338</v>
       </c>
       <c r="L10" s="46">
@@ -3208,7 +3183,7 @@
         <f t="shared" si="0"/>
         <v>2</v>
       </c>
-      <c r="C11" s="83" t="s">
+      <c r="C11" s="77" t="s">
         <v>385</v>
       </c>
       <c r="D11" s="50" t="s">
@@ -3232,7 +3207,7 @@
       <c r="J11" s="50" t="s">
         <v>415</v>
       </c>
-      <c r="K11" s="94" t="s">
+      <c r="K11" s="87" t="s">
         <v>339</v>
       </c>
       <c r="L11" s="50">
@@ -3264,7 +3239,7 @@
         <f t="shared" si="0"/>
         <v>3</v>
       </c>
-      <c r="C12" s="82" t="s">
+      <c r="C12" s="76" t="s">
         <v>385</v>
       </c>
       <c r="D12" s="46" t="s">
@@ -3288,7 +3263,7 @@
       <c r="J12" s="46" t="s">
         <v>416</v>
       </c>
-      <c r="K12" s="95" t="s">
+      <c r="K12" s="88" t="s">
         <v>340</v>
       </c>
       <c r="L12" s="46">
@@ -3320,7 +3295,7 @@
         <f t="shared" si="0"/>
         <v>4</v>
       </c>
-      <c r="C13" s="83" t="s">
+      <c r="C13" s="77" t="s">
         <v>385</v>
       </c>
       <c r="D13" s="50" t="s">
@@ -3344,7 +3319,7 @@
       <c r="J13" s="50" t="s">
         <v>417</v>
       </c>
-      <c r="K13" s="94" t="s">
+      <c r="K13" s="87" t="s">
         <v>341</v>
       </c>
       <c r="L13" s="50">
@@ -3376,7 +3351,7 @@
         <f t="shared" si="0"/>
         <v>5</v>
       </c>
-      <c r="C14" s="82" t="s">
+      <c r="C14" s="76" t="s">
         <v>385</v>
       </c>
       <c r="D14" s="46" t="s">
@@ -3400,7 +3375,7 @@
       <c r="J14" s="46" t="s">
         <v>418</v>
       </c>
-      <c r="K14" s="95" t="s">
+      <c r="K14" s="88" t="s">
         <v>342</v>
       </c>
       <c r="L14" s="46">
@@ -3423,8 +3398,8 @@
         <f t="shared" si="2"/>
         <v>1.3759999999999999</v>
       </c>
-      <c r="R14" s="81" t="s">
-        <v>539</v>
+      <c r="R14" s="75" t="s">
+        <v>537</v>
       </c>
       <c r="S14" s="48"/>
     </row>
@@ -3434,7 +3409,7 @@
         <f t="shared" si="0"/>
         <v>6</v>
       </c>
-      <c r="C15" s="83" t="s">
+      <c r="C15" s="77" t="s">
         <v>385</v>
       </c>
       <c r="D15" s="50" t="s">
@@ -3458,7 +3433,7 @@
       <c r="J15" s="50" t="s">
         <v>419</v>
       </c>
-      <c r="K15" s="94" t="s">
+      <c r="K15" s="87" t="s">
         <v>343</v>
       </c>
       <c r="L15" s="50">
@@ -3490,58 +3465,58 @@
         <f t="shared" si="0"/>
         <v>7</v>
       </c>
-      <c r="C16" s="84" t="s">
+      <c r="C16" s="78" t="s">
         <v>385</v>
       </c>
-      <c r="D16" s="73" t="s">
+      <c r="D16" s="68" t="s">
         <v>13</v>
       </c>
-      <c r="E16" s="74" t="s">
+      <c r="E16" s="69" t="s">
         <v>105</v>
       </c>
-      <c r="F16" s="73" t="s">
+      <c r="F16" s="68" t="s">
         <v>408</v>
       </c>
-      <c r="G16" s="100" t="s">
+      <c r="G16" s="92" t="s">
         <v>193</v>
       </c>
-      <c r="H16" s="73" t="s">
-        <v>526</v>
-      </c>
-      <c r="I16" s="73" t="s">
+      <c r="H16" s="68" t="s">
+        <v>524</v>
+      </c>
+      <c r="I16" s="68" t="s">
         <v>301</v>
       </c>
-      <c r="J16" s="73" t="s">
-        <v>527</v>
-      </c>
-      <c r="K16" s="96" t="s">
+      <c r="J16" s="68" t="s">
+        <v>525</v>
+      </c>
+      <c r="K16" s="89" t="s">
         <v>340</v>
       </c>
-      <c r="L16" s="73">
+      <c r="L16" s="68">
         <v>1</v>
       </c>
-      <c r="M16" s="73">
+      <c r="M16" s="68">
         <f t="shared" si="1"/>
         <v>5</v>
       </c>
-      <c r="N16" s="73">
+      <c r="N16" s="68">
         <v>10</v>
       </c>
-      <c r="O16" s="89" t="s">
-        <v>414</v>
-      </c>
-      <c r="P16" s="75">
+      <c r="O16" s="82" t="s">
+        <v>414</v>
+      </c>
+      <c r="P16" s="70">
         <v>0.187</v>
       </c>
-      <c r="Q16" s="75">
+      <c r="Q16" s="70">
         <f t="shared" si="2"/>
         <v>1.87</v>
       </c>
-      <c r="R16" s="81" t="s">
-        <v>538</v>
-      </c>
-      <c r="S16" s="76" t="s">
-        <v>528</v>
+      <c r="R16" s="75" t="s">
+        <v>536</v>
+      </c>
+      <c r="S16" s="71" t="s">
+        <v>526</v>
       </c>
     </row>
     <row r="17" spans="1:19" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
@@ -3550,7 +3525,7 @@
         <f t="shared" si="0"/>
         <v>8</v>
       </c>
-      <c r="C17" s="83" t="s">
+      <c r="C17" s="77" t="s">
         <v>385</v>
       </c>
       <c r="D17" s="50" t="s">
@@ -3574,7 +3549,7 @@
       <c r="J17" s="50" t="s">
         <v>420</v>
       </c>
-      <c r="K17" s="94" t="s">
+      <c r="K17" s="87" t="s">
         <v>344</v>
       </c>
       <c r="L17" s="50">
@@ -3606,7 +3581,7 @@
         <f t="shared" si="0"/>
         <v>9</v>
       </c>
-      <c r="C18" s="82" t="s">
+      <c r="C18" s="76" t="s">
         <v>385</v>
       </c>
       <c r="D18" s="46" t="s">
@@ -3630,7 +3605,7 @@
       <c r="J18" s="46" t="s">
         <v>421</v>
       </c>
-      <c r="K18" s="95" t="s">
+      <c r="K18" s="88" t="s">
         <v>345</v>
       </c>
       <c r="L18" s="46">
@@ -3662,7 +3637,7 @@
         <f t="shared" si="0"/>
         <v>10</v>
       </c>
-      <c r="C19" s="83" t="s">
+      <c r="C19" s="77" t="s">
         <v>385</v>
       </c>
       <c r="D19" s="50" t="s">
@@ -3686,7 +3661,7 @@
       <c r="J19" s="50" t="s">
         <v>422</v>
       </c>
-      <c r="K19" s="94" t="s">
+      <c r="K19" s="87" t="s">
         <v>339</v>
       </c>
       <c r="L19" s="50">
@@ -3718,7 +3693,7 @@
         <f t="shared" si="0"/>
         <v>11</v>
       </c>
-      <c r="C20" s="82" t="s">
+      <c r="C20" s="76" t="s">
         <v>385</v>
       </c>
       <c r="D20" s="46" t="s">
@@ -3742,7 +3717,7 @@
       <c r="J20" s="46" t="s">
         <v>423</v>
       </c>
-      <c r="K20" s="95" t="s">
+      <c r="K20" s="88" t="s">
         <v>346</v>
       </c>
       <c r="L20" s="46">
@@ -3774,7 +3749,7 @@
         <f t="shared" si="0"/>
         <v>12</v>
       </c>
-      <c r="C21" s="83" t="s">
+      <c r="C21" s="77" t="s">
         <v>385</v>
       </c>
       <c r="D21" s="50" t="s">
@@ -3798,7 +3773,7 @@
       <c r="J21" s="50" t="s">
         <v>424</v>
       </c>
-      <c r="K21" s="94" t="s">
+      <c r="K21" s="87" t="s">
         <v>347</v>
       </c>
       <c r="L21" s="50">
@@ -3830,7 +3805,7 @@
         <f t="shared" si="0"/>
         <v>13</v>
       </c>
-      <c r="C22" s="82" t="s">
+      <c r="C22" s="76" t="s">
         <v>385</v>
       </c>
       <c r="D22" s="46" t="s">
@@ -3854,7 +3829,7 @@
       <c r="J22" s="46" t="s">
         <v>425</v>
       </c>
-      <c r="K22" s="95" t="s">
+      <c r="K22" s="88" t="s">
         <v>348</v>
       </c>
       <c r="L22" s="46">
@@ -3886,7 +3861,7 @@
         <f t="shared" si="0"/>
         <v>14</v>
       </c>
-      <c r="C23" s="83" t="s">
+      <c r="C23" s="77" t="s">
         <v>385</v>
       </c>
       <c r="D23" s="50" t="s">
@@ -3910,7 +3885,7 @@
       <c r="J23" s="50" t="s">
         <v>426</v>
       </c>
-      <c r="K23" s="94" t="s">
+      <c r="K23" s="87" t="s">
         <v>349</v>
       </c>
       <c r="L23" s="50">
@@ -3942,7 +3917,7 @@
         <f t="shared" si="0"/>
         <v>15</v>
       </c>
-      <c r="C24" s="82" t="s">
+      <c r="C24" s="76" t="s">
         <v>385</v>
       </c>
       <c r="D24" s="46" t="s">
@@ -3954,7 +3929,7 @@
       <c r="F24" s="46" t="s">
         <v>190</v>
       </c>
-      <c r="G24" s="68" t="s">
+      <c r="G24" s="63" t="s">
         <v>248</v>
       </c>
       <c r="H24" s="46" t="s">
@@ -3966,7 +3941,7 @@
       <c r="J24" s="46" t="s">
         <v>475</v>
       </c>
-      <c r="K24" s="95" t="s">
+      <c r="K24" s="88" t="s">
         <v>350</v>
       </c>
       <c r="L24" s="46">
@@ -3998,7 +3973,7 @@
         <f t="shared" si="0"/>
         <v>16</v>
       </c>
-      <c r="C25" s="83" t="s">
+      <c r="C25" s="77" t="s">
         <v>385</v>
       </c>
       <c r="D25" s="50" t="s">
@@ -4010,19 +3985,19 @@
       <c r="F25" s="50" t="s">
         <v>190</v>
       </c>
-      <c r="G25" s="69" t="s">
+      <c r="G25" s="64" t="s">
         <v>249</v>
       </c>
       <c r="H25" s="50" t="s">
-        <v>540</v>
+        <v>538</v>
       </c>
       <c r="I25" s="50" t="s">
         <v>298</v>
       </c>
       <c r="J25" s="50" t="s">
-        <v>541</v>
-      </c>
-      <c r="K25" s="94" t="s">
+        <v>539</v>
+      </c>
+      <c r="K25" s="87" t="s">
         <v>351</v>
       </c>
       <c r="L25" s="50">
@@ -4054,7 +4029,7 @@
         <f t="shared" si="0"/>
         <v>17</v>
       </c>
-      <c r="C26" s="82" t="s">
+      <c r="C26" s="76" t="s">
         <v>386</v>
       </c>
       <c r="D26" s="46" t="s">
@@ -4078,7 +4053,7 @@
       <c r="J26" s="46" t="s">
         <v>476</v>
       </c>
-      <c r="K26" s="95" t="s">
+      <c r="K26" s="88" t="s">
         <v>410</v>
       </c>
       <c r="L26" s="46">
@@ -4110,7 +4085,7 @@
         <f t="shared" si="0"/>
         <v>18</v>
       </c>
-      <c r="C27" s="83" t="s">
+      <c r="C27" s="77" t="s">
         <v>386</v>
       </c>
       <c r="D27" s="50" t="s">
@@ -4134,7 +4109,7 @@
       <c r="J27" s="50" t="s">
         <v>427</v>
       </c>
-      <c r="K27" s="94" t="s">
+      <c r="K27" s="87" t="s">
         <v>410</v>
       </c>
       <c r="L27" s="50">
@@ -4166,7 +4141,7 @@
         <f t="shared" si="0"/>
         <v>19</v>
       </c>
-      <c r="C28" s="82" t="s">
+      <c r="C28" s="76" t="s">
         <v>386</v>
       </c>
       <c r="D28" s="46" t="s">
@@ -4190,7 +4165,7 @@
       <c r="J28" s="46" t="s">
         <v>479</v>
       </c>
-      <c r="K28" s="95" t="s">
+      <c r="K28" s="88" t="s">
         <v>410</v>
       </c>
       <c r="L28" s="46">
@@ -4222,7 +4197,7 @@
         <f t="shared" si="0"/>
         <v>20</v>
       </c>
-      <c r="C29" s="83" t="s">
+      <c r="C29" s="77" t="s">
         <v>386</v>
       </c>
       <c r="D29" s="50" t="s">
@@ -4246,7 +4221,7 @@
       <c r="J29" s="50" t="s">
         <v>428</v>
       </c>
-      <c r="K29" s="94" t="s">
+      <c r="K29" s="87" t="s">
         <v>410</v>
       </c>
       <c r="L29" s="50">
@@ -4278,58 +4253,58 @@
         <f t="shared" si="0"/>
         <v>21</v>
       </c>
-      <c r="C30" s="84" t="s">
+      <c r="C30" s="78" t="s">
         <v>386</v>
       </c>
-      <c r="D30" s="73" t="s">
+      <c r="D30" s="68" t="s">
         <v>27</v>
       </c>
-      <c r="E30" s="74" t="s">
+      <c r="E30" s="69" t="s">
         <v>119</v>
       </c>
-      <c r="F30" s="73" t="s">
+      <c r="F30" s="68" t="s">
         <v>196</v>
       </c>
-      <c r="G30" s="100" t="s">
+      <c r="G30" s="92" t="s">
         <v>252</v>
       </c>
-      <c r="H30" s="73" t="s">
-        <v>529</v>
-      </c>
-      <c r="I30" s="73" t="s">
+      <c r="H30" s="68" t="s">
+        <v>527</v>
+      </c>
+      <c r="I30" s="68" t="s">
         <v>305</v>
       </c>
-      <c r="J30" s="73" t="s">
-        <v>530</v>
-      </c>
-      <c r="K30" s="96" t="s">
-        <v>410</v>
-      </c>
-      <c r="L30" s="73">
+      <c r="J30" s="68" t="s">
+        <v>528</v>
+      </c>
+      <c r="K30" s="89" t="s">
+        <v>410</v>
+      </c>
+      <c r="L30" s="68">
         <v>1</v>
       </c>
-      <c r="M30" s="73">
+      <c r="M30" s="68">
         <f t="shared" si="1"/>
         <v>5</v>
       </c>
-      <c r="N30" s="73">
+      <c r="N30" s="68">
         <v>10</v>
       </c>
-      <c r="O30" s="89" t="s">
-        <v>414</v>
-      </c>
-      <c r="P30" s="75">
+      <c r="O30" s="82" t="s">
+        <v>414</v>
+      </c>
+      <c r="P30" s="70">
         <v>6.9000000000000006E-2</v>
       </c>
-      <c r="Q30" s="75">
+      <c r="Q30" s="70">
         <f t="shared" si="2"/>
         <v>0.69000000000000006</v>
       </c>
-      <c r="R30" s="81" t="s">
-        <v>538</v>
-      </c>
-      <c r="S30" s="76" t="s">
-        <v>531</v>
+      <c r="R30" s="75" t="s">
+        <v>536</v>
+      </c>
+      <c r="S30" s="71" t="s">
+        <v>529</v>
       </c>
     </row>
     <row r="31" spans="1:19" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
@@ -4338,7 +4313,7 @@
         <f t="shared" si="0"/>
         <v>22</v>
       </c>
-      <c r="C31" s="83" t="s">
+      <c r="C31" s="77" t="s">
         <v>386</v>
       </c>
       <c r="D31" s="50" t="s">
@@ -4362,7 +4337,7 @@
       <c r="J31" s="50" t="s">
         <v>481</v>
       </c>
-      <c r="K31" s="94" t="s">
+      <c r="K31" s="87" t="s">
         <v>410</v>
       </c>
       <c r="L31" s="50">
@@ -4394,7 +4369,7 @@
         <f t="shared" si="0"/>
         <v>23</v>
       </c>
-      <c r="C32" s="82" t="s">
+      <c r="C32" s="76" t="s">
         <v>387</v>
       </c>
       <c r="D32" s="46" t="s">
@@ -4414,7 +4389,7 @@
         <v>307</v>
       </c>
       <c r="J32" s="46"/>
-      <c r="K32" s="95" t="s">
+      <c r="K32" s="88" t="s">
         <v>410</v>
       </c>
       <c r="L32" s="46">
@@ -4440,7 +4415,7 @@
         <f t="shared" si="0"/>
         <v>24</v>
       </c>
-      <c r="C33" s="83" t="s">
+      <c r="C33" s="77" t="s">
         <v>388</v>
       </c>
       <c r="D33" s="50" t="s">
@@ -4452,7 +4427,7 @@
       <c r="F33" s="50" t="s">
         <v>408</v>
       </c>
-      <c r="G33" s="69" t="s">
+      <c r="G33" s="64" t="s">
         <v>199</v>
       </c>
       <c r="H33" s="50" t="s">
@@ -4464,7 +4439,7 @@
       <c r="J33" s="50" t="s">
         <v>513</v>
       </c>
-      <c r="K33" s="94" t="s">
+      <c r="K33" s="87" t="s">
         <v>410</v>
       </c>
       <c r="L33" s="50">
@@ -4496,7 +4471,7 @@
         <f t="shared" si="0"/>
         <v>25</v>
       </c>
-      <c r="C34" s="82" t="s">
+      <c r="C34" s="76" t="s">
         <v>388</v>
       </c>
       <c r="D34" s="46" t="s">
@@ -4508,7 +4483,7 @@
       <c r="F34" s="46" t="s">
         <v>408</v>
       </c>
-      <c r="G34" s="68" t="s">
+      <c r="G34" s="63" t="s">
         <v>200</v>
       </c>
       <c r="H34" s="46" t="s">
@@ -4520,7 +4495,7 @@
       <c r="J34" s="46" t="s">
         <v>515</v>
       </c>
-      <c r="K34" s="95" t="s">
+      <c r="K34" s="88" t="s">
         <v>410</v>
       </c>
       <c r="L34" s="46">
@@ -4552,7 +4527,7 @@
         <f t="shared" si="0"/>
         <v>26</v>
       </c>
-      <c r="C35" s="83" t="s">
+      <c r="C35" s="77" t="s">
         <v>388</v>
       </c>
       <c r="D35" s="50" t="s">
@@ -4564,7 +4539,7 @@
       <c r="F35" s="50" t="s">
         <v>408</v>
       </c>
-      <c r="G35" s="69" t="s">
+      <c r="G35" s="64" t="s">
         <v>201</v>
       </c>
       <c r="H35" s="50" t="s">
@@ -4576,7 +4551,7 @@
       <c r="J35" s="50" t="s">
         <v>517</v>
       </c>
-      <c r="K35" s="97" t="s">
+      <c r="K35" s="90" t="s">
         <v>411</v>
       </c>
       <c r="L35" s="50">
@@ -4608,7 +4583,7 @@
         <f t="shared" si="0"/>
         <v>27</v>
       </c>
-      <c r="C36" s="82" t="s">
+      <c r="C36" s="76" t="s">
         <v>387</v>
       </c>
       <c r="D36" s="46" t="s">
@@ -4632,7 +4607,7 @@
       <c r="J36" s="46" t="s">
         <v>429</v>
       </c>
-      <c r="K36" s="95" t="s">
+      <c r="K36" s="88" t="s">
         <v>410</v>
       </c>
       <c r="L36" s="46">
@@ -4664,7 +4639,7 @@
         <f t="shared" si="0"/>
         <v>28</v>
       </c>
-      <c r="C37" s="83" t="s">
+      <c r="C37" s="77" t="s">
         <v>389</v>
       </c>
       <c r="D37" s="50" t="s">
@@ -4688,7 +4663,7 @@
       <c r="J37" s="50" t="s">
         <v>430</v>
       </c>
-      <c r="K37" s="94" t="s">
+      <c r="K37" s="87" t="s">
         <v>410</v>
       </c>
       <c r="L37" s="50">
@@ -4720,7 +4695,7 @@
         <f t="shared" si="0"/>
         <v>29</v>
       </c>
-      <c r="C38" s="82" t="s">
+      <c r="C38" s="76" t="s">
         <v>387</v>
       </c>
       <c r="D38" s="46" t="s">
@@ -4744,7 +4719,7 @@
       <c r="J38" s="46" t="s">
         <v>431</v>
       </c>
-      <c r="K38" s="95" t="s">
+      <c r="K38" s="88" t="s">
         <v>410</v>
       </c>
       <c r="L38" s="46">
@@ -4776,7 +4751,7 @@
         <f t="shared" si="0"/>
         <v>30</v>
       </c>
-      <c r="C39" s="83" t="s">
+      <c r="C39" s="77" t="s">
         <v>390</v>
       </c>
       <c r="D39" s="50" t="s">
@@ -4800,7 +4775,7 @@
       <c r="J39" s="50" t="s">
         <v>483</v>
       </c>
-      <c r="K39" s="94" t="s">
+      <c r="K39" s="87" t="s">
         <v>353</v>
       </c>
       <c r="L39" s="50">
@@ -4832,7 +4807,7 @@
         <f t="shared" si="0"/>
         <v>31</v>
       </c>
-      <c r="C40" s="82" t="s">
+      <c r="C40" s="76" t="s">
         <v>390</v>
       </c>
       <c r="D40" s="46" t="s">
@@ -4856,7 +4831,7 @@
       <c r="J40" s="46" t="s">
         <v>432</v>
       </c>
-      <c r="K40" s="95" t="s">
+      <c r="K40" s="88" t="s">
         <v>354</v>
       </c>
       <c r="L40" s="46">
@@ -4888,7 +4863,7 @@
         <f t="shared" si="0"/>
         <v>32</v>
       </c>
-      <c r="C41" s="83" t="s">
+      <c r="C41" s="77" t="s">
         <v>390</v>
       </c>
       <c r="D41" s="50" t="s">
@@ -4912,7 +4887,7 @@
       <c r="J41" s="50" t="s">
         <v>433</v>
       </c>
-      <c r="K41" s="94" t="s">
+      <c r="K41" s="87" t="s">
         <v>355</v>
       </c>
       <c r="L41" s="50">
@@ -4944,7 +4919,7 @@
         <f t="shared" ref="B42:B73" si="3">ROW(B42) - ROW($B$9)</f>
         <v>33</v>
       </c>
-      <c r="C42" s="82" t="s">
+      <c r="C42" s="76" t="s">
         <v>390</v>
       </c>
       <c r="D42" s="46" t="s">
@@ -4968,7 +4943,7 @@
       <c r="J42" s="46" t="s">
         <v>434</v>
       </c>
-      <c r="K42" s="95" t="s">
+      <c r="K42" s="88" t="s">
         <v>356</v>
       </c>
       <c r="L42" s="46">
@@ -5000,7 +4975,7 @@
         <f t="shared" si="3"/>
         <v>34</v>
       </c>
-      <c r="C43" s="83" t="s">
+      <c r="C43" s="77" t="s">
         <v>391</v>
       </c>
       <c r="D43" s="50" t="s">
@@ -5012,7 +4987,7 @@
       <c r="F43" s="50" t="s">
         <v>209</v>
       </c>
-      <c r="G43" s="69" t="s">
+      <c r="G43" s="64" t="s">
         <v>255</v>
       </c>
       <c r="H43" s="50" t="s">
@@ -5024,7 +4999,7 @@
       <c r="J43" s="50" t="s">
         <v>500</v>
       </c>
-      <c r="K43" s="94" t="s">
+      <c r="K43" s="87" t="s">
         <v>410</v>
       </c>
       <c r="L43" s="50">
@@ -5056,7 +5031,7 @@
         <f t="shared" si="3"/>
         <v>35</v>
       </c>
-      <c r="C44" s="82" t="s">
+      <c r="C44" s="76" t="s">
         <v>391</v>
       </c>
       <c r="D44" s="46" t="s">
@@ -5080,7 +5055,7 @@
       <c r="J44" s="46" t="s">
         <v>435</v>
       </c>
-      <c r="K44" s="95" t="s">
+      <c r="K44" s="88" t="s">
         <v>410</v>
       </c>
       <c r="L44" s="46">
@@ -5112,7 +5087,7 @@
         <f t="shared" si="3"/>
         <v>36</v>
       </c>
-      <c r="C45" s="83" t="s">
+      <c r="C45" s="77" t="s">
         <v>392</v>
       </c>
       <c r="D45" s="50" t="s">
@@ -5136,7 +5111,7 @@
       <c r="J45" s="50" t="s">
         <v>436</v>
       </c>
-      <c r="K45" s="94" t="s">
+      <c r="K45" s="87" t="s">
         <v>410</v>
       </c>
       <c r="L45" s="50">
@@ -5168,7 +5143,7 @@
         <f t="shared" si="3"/>
         <v>37</v>
       </c>
-      <c r="C46" s="82" t="s">
+      <c r="C46" s="76" t="s">
         <v>357</v>
       </c>
       <c r="D46" s="46" t="s">
@@ -5192,7 +5167,7 @@
       <c r="J46" s="46" t="s">
         <v>410</v>
       </c>
-      <c r="K46" s="95" t="s">
+      <c r="K46" s="88" t="s">
         <v>410</v>
       </c>
       <c r="L46" s="46">
@@ -5214,8 +5189,8 @@
       <c r="Q46" s="60" t="s">
         <v>410</v>
       </c>
-      <c r="R46" s="87" t="s">
-        <v>523</v>
+      <c r="R46" s="80" t="s">
+        <v>521</v>
       </c>
       <c r="S46" s="48" t="s">
         <v>410</v>
@@ -5227,7 +5202,7 @@
         <f t="shared" si="3"/>
         <v>38</v>
       </c>
-      <c r="C47" s="83" t="s">
+      <c r="C47" s="77" t="s">
         <v>389</v>
       </c>
       <c r="D47" s="50" t="s">
@@ -5239,7 +5214,7 @@
       <c r="F47" s="50" t="s">
         <v>211</v>
       </c>
-      <c r="G47" s="69">
+      <c r="G47" s="64">
         <v>61300311121</v>
       </c>
       <c r="H47" s="50" t="s">
@@ -5251,7 +5226,7 @@
       <c r="J47" s="50" t="s">
         <v>487</v>
       </c>
-      <c r="K47" s="94" t="s">
+      <c r="K47" s="87" t="s">
         <v>410</v>
       </c>
       <c r="L47" s="50">
@@ -5283,7 +5258,7 @@
         <f t="shared" si="3"/>
         <v>39</v>
       </c>
-      <c r="C48" s="82" t="s">
+      <c r="C48" s="76" t="s">
         <v>389</v>
       </c>
       <c r="D48" s="46" t="s">
@@ -5295,7 +5270,7 @@
       <c r="F48" s="46" t="s">
         <v>212</v>
       </c>
-      <c r="G48" s="68">
+      <c r="G48" s="63">
         <v>61300611121</v>
       </c>
       <c r="H48" s="46" t="s">
@@ -5307,7 +5282,7 @@
       <c r="J48" s="46" t="s">
         <v>485</v>
       </c>
-      <c r="K48" s="95" t="s">
+      <c r="K48" s="88" t="s">
         <v>410</v>
       </c>
       <c r="L48" s="46">
@@ -5339,7 +5314,7 @@
         <f t="shared" si="3"/>
         <v>40</v>
       </c>
-      <c r="C49" s="83" t="s">
+      <c r="C49" s="77" t="s">
         <v>389</v>
       </c>
       <c r="D49" s="50" t="s">
@@ -5351,7 +5326,7 @@
       <c r="F49" s="50" t="s">
         <v>213</v>
       </c>
-      <c r="G49" s="69" t="s">
+      <c r="G49" s="64" t="s">
         <v>257</v>
       </c>
       <c r="H49" s="50" t="s">
@@ -5363,7 +5338,7 @@
       <c r="J49" s="50" t="s">
         <v>501</v>
       </c>
-      <c r="K49" s="94" t="s">
+      <c r="K49" s="87" t="s">
         <v>410</v>
       </c>
       <c r="L49" s="50">
@@ -5395,7 +5370,7 @@
         <f t="shared" si="3"/>
         <v>41</v>
       </c>
-      <c r="C50" s="82" t="s">
+      <c r="C50" s="76" t="s">
         <v>389</v>
       </c>
       <c r="D50" s="46" t="s">
@@ -5407,19 +5382,19 @@
       <c r="F50" s="46" t="s">
         <v>214</v>
       </c>
-      <c r="G50" s="68">
+      <c r="G50" s="63">
         <v>61300211121</v>
       </c>
-      <c r="H50" s="111" t="s">
-        <v>542</v>
+      <c r="H50" s="93" t="s">
+        <v>540</v>
       </c>
       <c r="I50" s="46" t="s">
         <v>319</v>
       </c>
       <c r="J50" s="46" t="s">
-        <v>543</v>
-      </c>
-      <c r="K50" s="95" t="s">
+        <v>541</v>
+      </c>
+      <c r="K50" s="88" t="s">
         <v>410</v>
       </c>
       <c r="L50" s="46">
@@ -5451,7 +5426,7 @@
         <f t="shared" si="3"/>
         <v>42</v>
       </c>
-      <c r="C51" s="83" t="s">
+      <c r="C51" s="77" t="s">
         <v>389</v>
       </c>
       <c r="D51" s="50" t="s">
@@ -5463,7 +5438,7 @@
       <c r="F51" s="50" t="s">
         <v>215</v>
       </c>
-      <c r="G51" s="69">
+      <c r="G51" s="64">
         <v>61300411121</v>
       </c>
       <c r="H51" s="50" t="s">
@@ -5475,7 +5450,7 @@
       <c r="J51" s="50" t="s">
         <v>489</v>
       </c>
-      <c r="K51" s="94" t="s">
+      <c r="K51" s="87" t="s">
         <v>410</v>
       </c>
       <c r="L51" s="50">
@@ -5507,7 +5482,7 @@
         <f t="shared" si="3"/>
         <v>43</v>
       </c>
-      <c r="C52" s="82" t="s">
+      <c r="C52" s="76" t="s">
         <v>393</v>
       </c>
       <c r="D52" s="46" t="s">
@@ -5531,7 +5506,7 @@
       <c r="J52" s="46" t="s">
         <v>437</v>
       </c>
-      <c r="K52" s="95" t="s">
+      <c r="K52" s="88" t="s">
         <v>410</v>
       </c>
       <c r="L52" s="46">
@@ -5563,7 +5538,7 @@
         <f t="shared" si="3"/>
         <v>44</v>
       </c>
-      <c r="C53" s="83" t="s">
+      <c r="C53" s="77" t="s">
         <v>393</v>
       </c>
       <c r="D53" s="50" t="s">
@@ -5587,7 +5562,7 @@
       <c r="J53" s="50" t="s">
         <v>491</v>
       </c>
-      <c r="K53" s="94" t="s">
+      <c r="K53" s="87" t="s">
         <v>410</v>
       </c>
       <c r="L53" s="50">
@@ -5619,7 +5594,7 @@
         <f t="shared" si="3"/>
         <v>45</v>
       </c>
-      <c r="C54" s="82" t="s">
+      <c r="C54" s="76" t="s">
         <v>393</v>
       </c>
       <c r="D54" s="46" t="s">
@@ -5643,7 +5618,7 @@
       <c r="J54" s="46" t="s">
         <v>438</v>
       </c>
-      <c r="K54" s="95" t="s">
+      <c r="K54" s="88" t="s">
         <v>410</v>
       </c>
       <c r="L54" s="46">
@@ -5675,7 +5650,7 @@
         <f t="shared" si="3"/>
         <v>46</v>
       </c>
-      <c r="C55" s="83" t="s">
+      <c r="C55" s="77" t="s">
         <v>393</v>
       </c>
       <c r="D55" s="50" t="s">
@@ -5687,7 +5662,7 @@
       <c r="F55" s="50" t="s">
         <v>217</v>
       </c>
-      <c r="G55" s="70" t="s">
+      <c r="G55" s="65" t="s">
         <v>261</v>
       </c>
       <c r="H55" s="50" t="s">
@@ -5699,7 +5674,7 @@
       <c r="J55" s="50" t="s">
         <v>492</v>
       </c>
-      <c r="K55" s="94" t="s">
+      <c r="K55" s="87" t="s">
         <v>410</v>
       </c>
       <c r="L55" s="50">
@@ -5731,7 +5706,7 @@
         <f t="shared" si="3"/>
         <v>47</v>
       </c>
-      <c r="C56" s="82" t="s">
+      <c r="C56" s="76" t="s">
         <v>393</v>
       </c>
       <c r="D56" s="46" t="s">
@@ -5753,7 +5728,7 @@
       <c r="J56" s="46" t="s">
         <v>439</v>
       </c>
-      <c r="K56" s="95" t="s">
+      <c r="K56" s="88" t="s">
         <v>410</v>
       </c>
       <c r="L56" s="46">
@@ -5785,7 +5760,7 @@
         <f t="shared" si="3"/>
         <v>48</v>
       </c>
-      <c r="C57" s="83" t="s">
+      <c r="C57" s="77" t="s">
         <v>393</v>
       </c>
       <c r="D57" s="50" t="s">
@@ -5809,7 +5784,7 @@
       <c r="J57" s="50" t="s">
         <v>440</v>
       </c>
-      <c r="K57" s="94" t="s">
+      <c r="K57" s="87" t="s">
         <v>410</v>
       </c>
       <c r="L57" s="50">
@@ -5841,7 +5816,7 @@
         <f t="shared" si="3"/>
         <v>49</v>
       </c>
-      <c r="C58" s="82" t="s">
+      <c r="C58" s="76" t="s">
         <v>393</v>
       </c>
       <c r="D58" s="46" t="s">
@@ -5865,7 +5840,7 @@
       <c r="J58" s="46" t="s">
         <v>441</v>
       </c>
-      <c r="K58" s="95" t="s">
+      <c r="K58" s="88" t="s">
         <v>410</v>
       </c>
       <c r="L58" s="46">
@@ -5897,7 +5872,7 @@
         <f t="shared" si="3"/>
         <v>50</v>
       </c>
-      <c r="C59" s="83" t="s">
+      <c r="C59" s="77" t="s">
         <v>393</v>
       </c>
       <c r="D59" s="50" t="s">
@@ -5921,7 +5896,7 @@
       <c r="J59" s="50" t="s">
         <v>442</v>
       </c>
-      <c r="K59" s="94" t="s">
+      <c r="K59" s="87" t="s">
         <v>410</v>
       </c>
       <c r="L59" s="50">
@@ -5953,7 +5928,7 @@
         <f t="shared" si="3"/>
         <v>51</v>
       </c>
-      <c r="C60" s="82" t="s">
+      <c r="C60" s="76" t="s">
         <v>394</v>
       </c>
       <c r="D60" s="46" t="s">
@@ -5963,7 +5938,7 @@
         <v>147</v>
       </c>
       <c r="F60" s="46" t="s">
-        <v>544</v>
+        <v>542</v>
       </c>
       <c r="G60" s="47" t="s">
         <v>265</v>
@@ -5977,7 +5952,7 @@
       <c r="J60" s="46" t="s">
         <v>443</v>
       </c>
-      <c r="K60" s="95" t="s">
+      <c r="K60" s="88" t="s">
         <v>358</v>
       </c>
       <c r="L60" s="46">
@@ -6009,7 +5984,7 @@
         <f t="shared" si="3"/>
         <v>52</v>
       </c>
-      <c r="C61" s="83" t="s">
+      <c r="C61" s="77" t="s">
         <v>394</v>
       </c>
       <c r="D61" s="50" t="s">
@@ -6031,7 +6006,7 @@
       <c r="J61" s="50" t="s">
         <v>444</v>
       </c>
-      <c r="K61" s="94" t="s">
+      <c r="K61" s="87" t="s">
         <v>359</v>
       </c>
       <c r="L61" s="50">
@@ -6063,7 +6038,7 @@
         <f t="shared" si="3"/>
         <v>53</v>
       </c>
-      <c r="C62" s="82" t="s">
+      <c r="C62" s="76" t="s">
         <v>394</v>
       </c>
       <c r="D62" s="46" t="s">
@@ -6087,7 +6062,7 @@
       <c r="J62" s="46" t="s">
         <v>473</v>
       </c>
-      <c r="K62" s="95" t="s">
+      <c r="K62" s="88" t="s">
         <v>360</v>
       </c>
       <c r="L62" s="46">
@@ -6119,11 +6094,11 @@
         <f t="shared" si="3"/>
         <v>54</v>
       </c>
-      <c r="C63" s="83" t="s">
+      <c r="C63" s="77" t="s">
         <v>394</v>
       </c>
       <c r="D63" s="50" t="s">
-        <v>537</v>
+        <v>535</v>
       </c>
       <c r="E63" s="51" t="s">
         <v>150</v>
@@ -6143,7 +6118,7 @@
       <c r="J63" s="50" t="s">
         <v>445</v>
       </c>
-      <c r="K63" s="94" t="s">
+      <c r="K63" s="87" t="s">
         <v>361</v>
       </c>
       <c r="L63" s="50">
@@ -6175,7 +6150,7 @@
         <f t="shared" si="3"/>
         <v>55</v>
       </c>
-      <c r="C64" s="82" t="s">
+      <c r="C64" s="76" t="s">
         <v>394</v>
       </c>
       <c r="D64" s="46" t="s">
@@ -6199,7 +6174,7 @@
       <c r="J64" s="46" t="s">
         <v>446</v>
       </c>
-      <c r="K64" s="95" t="s">
+      <c r="K64" s="88" t="s">
         <v>362</v>
       </c>
       <c r="L64" s="46">
@@ -6231,7 +6206,7 @@
         <f t="shared" si="3"/>
         <v>56</v>
       </c>
-      <c r="C65" s="83" t="s">
+      <c r="C65" s="77" t="s">
         <v>394</v>
       </c>
       <c r="D65" s="50" t="s">
@@ -6253,7 +6228,7 @@
       <c r="J65" s="50" t="s">
         <v>447</v>
       </c>
-      <c r="K65" s="94" t="s">
+      <c r="K65" s="87" t="s">
         <v>363</v>
       </c>
       <c r="L65" s="50">
@@ -6285,7 +6260,7 @@
         <f t="shared" si="3"/>
         <v>57</v>
       </c>
-      <c r="C66" s="82" t="s">
+      <c r="C66" s="76" t="s">
         <v>394</v>
       </c>
       <c r="D66" s="46" t="s">
@@ -6309,7 +6284,7 @@
       <c r="J66" s="46" t="s">
         <v>448</v>
       </c>
-      <c r="K66" s="95" t="s">
+      <c r="K66" s="88" t="s">
         <v>364</v>
       </c>
       <c r="L66" s="46">
@@ -6341,7 +6316,7 @@
         <f t="shared" si="3"/>
         <v>58</v>
       </c>
-      <c r="C67" s="83" t="s">
+      <c r="C67" s="77" t="s">
         <v>394</v>
       </c>
       <c r="D67" s="50" t="s">
@@ -6353,7 +6328,7 @@
       <c r="F67" s="50" t="s">
         <v>220</v>
       </c>
-      <c r="G67" s="69" t="s">
+      <c r="G67" s="64" t="s">
         <v>271</v>
       </c>
       <c r="H67" s="50" t="s">
@@ -6365,7 +6340,7 @@
       <c r="J67" s="50" t="s">
         <v>494</v>
       </c>
-      <c r="K67" s="94" t="s">
+      <c r="K67" s="87" t="s">
         <v>365</v>
       </c>
       <c r="L67" s="50">
@@ -6397,7 +6372,7 @@
         <f t="shared" si="3"/>
         <v>59</v>
       </c>
-      <c r="C68" s="82" t="s">
+      <c r="C68" s="76" t="s">
         <v>394</v>
       </c>
       <c r="D68" s="46" t="s">
@@ -6421,7 +6396,7 @@
       <c r="J68" s="46" t="s">
         <v>449</v>
       </c>
-      <c r="K68" s="95" t="s">
+      <c r="K68" s="88" t="s">
         <v>366</v>
       </c>
       <c r="L68" s="46">
@@ -6453,7 +6428,7 @@
         <f t="shared" si="3"/>
         <v>60</v>
       </c>
-      <c r="C69" s="83" t="s">
+      <c r="C69" s="77" t="s">
         <v>394</v>
       </c>
       <c r="D69" s="50" t="s">
@@ -6477,7 +6452,7 @@
       <c r="J69" s="50" t="s">
         <v>450</v>
       </c>
-      <c r="K69" s="94" t="s">
+      <c r="K69" s="87" t="s">
         <v>367</v>
       </c>
       <c r="L69" s="50">
@@ -6509,7 +6484,7 @@
         <f t="shared" si="3"/>
         <v>61</v>
       </c>
-      <c r="C70" s="82" t="s">
+      <c r="C70" s="76" t="s">
         <v>394</v>
       </c>
       <c r="D70" s="46" t="s">
@@ -6533,7 +6508,7 @@
       <c r="J70" s="46" t="s">
         <v>451</v>
       </c>
-      <c r="K70" s="95" t="s">
+      <c r="K70" s="88" t="s">
         <v>368</v>
       </c>
       <c r="L70" s="46">
@@ -6565,7 +6540,7 @@
         <f t="shared" si="3"/>
         <v>62</v>
       </c>
-      <c r="C71" s="83" t="s">
+      <c r="C71" s="77" t="s">
         <v>394</v>
       </c>
       <c r="D71" s="50" t="s">
@@ -6589,7 +6564,7 @@
       <c r="J71" s="50" t="s">
         <v>452</v>
       </c>
-      <c r="K71" s="94" t="s">
+      <c r="K71" s="87" t="s">
         <v>369</v>
       </c>
       <c r="L71" s="50">
@@ -6621,7 +6596,7 @@
         <f t="shared" si="3"/>
         <v>63</v>
       </c>
-      <c r="C72" s="82" t="s">
+      <c r="C72" s="76" t="s">
         <v>394</v>
       </c>
       <c r="D72" s="46" t="s">
@@ -6645,7 +6620,7 @@
       <c r="J72" s="46" t="s">
         <v>453</v>
       </c>
-      <c r="K72" s="95" t="s">
+      <c r="K72" s="88" t="s">
         <v>370</v>
       </c>
       <c r="L72" s="46">
@@ -6677,7 +6652,7 @@
         <f t="shared" si="3"/>
         <v>64</v>
       </c>
-      <c r="C73" s="83" t="s">
+      <c r="C73" s="77" t="s">
         <v>394</v>
       </c>
       <c r="D73" s="50" t="s">
@@ -6701,7 +6676,7 @@
       <c r="J73" s="50" t="s">
         <v>454</v>
       </c>
-      <c r="K73" s="94" t="s">
+      <c r="K73" s="87" t="s">
         <v>371</v>
       </c>
       <c r="L73" s="50">
@@ -6733,7 +6708,7 @@
         <f t="shared" ref="B74:B101" si="4">ROW(B74) - ROW($B$9)</f>
         <v>65</v>
       </c>
-      <c r="C74" s="82" t="s">
+      <c r="C74" s="76" t="s">
         <v>394</v>
       </c>
       <c r="D74" s="46" t="s">
@@ -6757,7 +6732,7 @@
       <c r="J74" s="46" t="s">
         <v>506</v>
       </c>
-      <c r="K74" s="95" t="s">
+      <c r="K74" s="88" t="s">
         <v>503</v>
       </c>
       <c r="L74" s="46">
@@ -6780,7 +6755,7 @@
         <f t="shared" si="2"/>
         <v>0.16</v>
       </c>
-      <c r="R74" s="88"/>
+      <c r="R74" s="81"/>
       <c r="S74" s="48"/>
     </row>
     <row r="75" spans="1:19" ht="36.75" thickBot="1" x14ac:dyDescent="0.3">
@@ -6789,7 +6764,7 @@
         <f t="shared" si="4"/>
         <v>66</v>
       </c>
-      <c r="C75" s="83" t="s">
+      <c r="C75" s="77" t="s">
         <v>394</v>
       </c>
       <c r="D75" s="50" t="s">
@@ -6813,7 +6788,7 @@
       <c r="J75" s="50" t="s">
         <v>455</v>
       </c>
-      <c r="K75" s="94" t="s">
+      <c r="K75" s="87" t="s">
         <v>372</v>
       </c>
       <c r="L75" s="50">
@@ -6845,7 +6820,7 @@
         <f t="shared" si="4"/>
         <v>67</v>
       </c>
-      <c r="C76" s="82" t="s">
+      <c r="C76" s="76" t="s">
         <v>394</v>
       </c>
       <c r="D76" s="46" t="s">
@@ -6869,7 +6844,7 @@
       <c r="J76" s="46" t="s">
         <v>456</v>
       </c>
-      <c r="K76" s="95" t="s">
+      <c r="K76" s="88" t="s">
         <v>373</v>
       </c>
       <c r="L76" s="46">
@@ -6901,7 +6876,7 @@
         <f t="shared" si="4"/>
         <v>68</v>
       </c>
-      <c r="C77" s="83" t="s">
+      <c r="C77" s="77" t="s">
         <v>394</v>
       </c>
       <c r="D77" s="50" t="s">
@@ -6925,7 +6900,7 @@
       <c r="J77" s="50" t="s">
         <v>457</v>
       </c>
-      <c r="K77" s="94" t="s">
+      <c r="K77" s="87" t="s">
         <v>374</v>
       </c>
       <c r="L77" s="50">
@@ -6957,7 +6932,7 @@
         <f t="shared" si="4"/>
         <v>69</v>
       </c>
-      <c r="C78" s="82" t="s">
+      <c r="C78" s="76" t="s">
         <v>394</v>
       </c>
       <c r="D78" s="46" t="s">
@@ -6969,7 +6944,7 @@
       <c r="F78" s="46" t="s">
         <v>221</v>
       </c>
-      <c r="G78" s="68" t="s">
+      <c r="G78" s="63" t="s">
         <v>281</v>
       </c>
       <c r="H78" s="46" t="s">
@@ -6981,7 +6956,7 @@
       <c r="J78" s="46" t="s">
         <v>508</v>
       </c>
-      <c r="K78" s="95" t="s">
+      <c r="K78" s="88" t="s">
         <v>375</v>
       </c>
       <c r="L78" s="46">
@@ -7013,7 +6988,7 @@
         <f t="shared" si="4"/>
         <v>70</v>
       </c>
-      <c r="C79" s="83" t="s">
+      <c r="C79" s="77" t="s">
         <v>394</v>
       </c>
       <c r="D79" s="50" t="s">
@@ -7037,7 +7012,7 @@
       <c r="J79" s="50" t="s">
         <v>458</v>
       </c>
-      <c r="K79" s="94" t="s">
+      <c r="K79" s="87" t="s">
         <v>376</v>
       </c>
       <c r="L79" s="50">
@@ -7069,7 +7044,7 @@
         <f t="shared" si="4"/>
         <v>71</v>
       </c>
-      <c r="C80" s="82" t="s">
+      <c r="C80" s="76" t="s">
         <v>394</v>
       </c>
       <c r="D80" s="46" t="s">
@@ -7093,7 +7068,7 @@
       <c r="J80" s="46" t="s">
         <v>459</v>
       </c>
-      <c r="K80" s="95" t="s">
+      <c r="K80" s="88" t="s">
         <v>377</v>
       </c>
       <c r="L80" s="46">
@@ -7125,7 +7100,7 @@
         <f t="shared" si="4"/>
         <v>72</v>
       </c>
-      <c r="C81" s="82" t="s">
+      <c r="C81" s="76" t="s">
         <v>394</v>
       </c>
       <c r="D81" s="46" t="s">
@@ -7149,7 +7124,7 @@
       <c r="J81" s="46" t="s">
         <v>460</v>
       </c>
-      <c r="K81" s="95" t="s">
+      <c r="K81" s="88" t="s">
         <v>378</v>
       </c>
       <c r="L81" s="46">
@@ -7181,7 +7156,7 @@
         <f t="shared" si="4"/>
         <v>73</v>
       </c>
-      <c r="C82" s="83" t="s">
+      <c r="C82" s="77" t="s">
         <v>394</v>
       </c>
       <c r="D82" s="50" t="s">
@@ -7205,7 +7180,7 @@
       <c r="J82" s="50" t="s">
         <v>461</v>
       </c>
-      <c r="K82" s="94" t="s">
+      <c r="K82" s="87" t="s">
         <v>379</v>
       </c>
       <c r="L82" s="50">
@@ -7237,7 +7212,7 @@
         <f t="shared" si="4"/>
         <v>74</v>
       </c>
-      <c r="C83" s="82" t="s">
+      <c r="C83" s="76" t="s">
         <v>394</v>
       </c>
       <c r="D83" s="46" t="s">
@@ -7261,7 +7236,7 @@
       <c r="J83" s="46" t="s">
         <v>496</v>
       </c>
-      <c r="K83" s="95" t="s">
+      <c r="K83" s="88" t="s">
         <v>380</v>
       </c>
       <c r="L83" s="46">
@@ -7293,7 +7268,7 @@
         <f t="shared" si="4"/>
         <v>75</v>
       </c>
-      <c r="C84" s="83" t="s">
+      <c r="C84" s="77" t="s">
         <v>394</v>
       </c>
       <c r="D84" s="50" t="s">
@@ -7317,7 +7292,7 @@
       <c r="J84" s="50" t="s">
         <v>462</v>
       </c>
-      <c r="K84" s="94" t="s">
+      <c r="K84" s="87" t="s">
         <v>381</v>
       </c>
       <c r="L84" s="50">
@@ -7349,7 +7324,7 @@
         <f t="shared" si="4"/>
         <v>76</v>
       </c>
-      <c r="C85" s="82" t="s">
+      <c r="C85" s="76" t="s">
         <v>394</v>
       </c>
       <c r="D85" s="46" t="s">
@@ -7361,7 +7336,7 @@
       <c r="F85" s="46" t="s">
         <v>223</v>
       </c>
-      <c r="G85" s="68" t="s">
+      <c r="G85" s="63" t="s">
         <v>287</v>
       </c>
       <c r="H85" s="46" t="s">
@@ -7373,7 +7348,7 @@
       <c r="J85" s="46" t="s">
         <v>498</v>
       </c>
-      <c r="K85" s="95" t="s">
+      <c r="K85" s="88" t="s">
         <v>362</v>
       </c>
       <c r="L85" s="46">
@@ -7405,7 +7380,7 @@
         <f t="shared" si="4"/>
         <v>77</v>
       </c>
-      <c r="C86" s="83" t="s">
+      <c r="C86" s="77" t="s">
         <v>224</v>
       </c>
       <c r="D86" s="50" t="s">
@@ -7429,7 +7404,7 @@
       <c r="J86" s="50" t="s">
         <v>410</v>
       </c>
-      <c r="K86" s="94" t="s">
+      <c r="K86" s="87" t="s">
         <v>410</v>
       </c>
       <c r="L86" s="50">
@@ -7439,22 +7414,22 @@
         <f t="shared" si="5"/>
         <v>90</v>
       </c>
-      <c r="N86" s="71" t="s">
-        <v>410</v>
-      </c>
-      <c r="O86" s="72" t="s">
-        <v>410</v>
-      </c>
-      <c r="P86" s="71" t="s">
-        <v>410</v>
-      </c>
-      <c r="Q86" s="72" t="s">
-        <v>410</v>
-      </c>
-      <c r="R86" s="86" t="s">
-        <v>523</v>
-      </c>
-      <c r="S86" s="72" t="s">
+      <c r="N86" s="66" t="s">
+        <v>410</v>
+      </c>
+      <c r="O86" s="67" t="s">
+        <v>410</v>
+      </c>
+      <c r="P86" s="66" t="s">
+        <v>410</v>
+      </c>
+      <c r="Q86" s="67" t="s">
+        <v>410</v>
+      </c>
+      <c r="R86" s="79" t="s">
+        <v>521</v>
+      </c>
+      <c r="S86" s="67" t="s">
         <v>410</v>
       </c>
     </row>
@@ -7464,7 +7439,7 @@
         <f t="shared" si="4"/>
         <v>78</v>
       </c>
-      <c r="C87" s="82" t="s">
+      <c r="C87" s="76" t="s">
         <v>395</v>
       </c>
       <c r="D87" s="46" t="s">
@@ -7488,7 +7463,7 @@
       <c r="J87" s="46" t="s">
         <v>463</v>
       </c>
-      <c r="K87" s="95" t="s">
+      <c r="K87" s="88" t="s">
         <v>410</v>
       </c>
       <c r="L87" s="46">
@@ -7514,64 +7489,62 @@
       <c r="R87" s="48"/>
       <c r="S87" s="48"/>
     </row>
-    <row r="88" spans="1:20" ht="36.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="88" spans="1:20" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A88" s="1"/>
       <c r="B88" s="38">
         <f t="shared" si="4"/>
         <v>79</v>
       </c>
-      <c r="C88" s="85" t="s">
+      <c r="C88" s="77" t="s">
         <v>396</v>
       </c>
-      <c r="D88" s="63" t="s">
+      <c r="D88" s="50" t="s">
         <v>84</v>
       </c>
-      <c r="E88" s="64" t="s">
+      <c r="E88" s="51" t="s">
         <v>175</v>
       </c>
-      <c r="F88" s="63" t="s">
+      <c r="F88" s="50" t="s">
         <v>226</v>
       </c>
-      <c r="G88" s="64" t="s">
+      <c r="G88" s="51" t="s">
         <v>288</v>
       </c>
-      <c r="H88" s="63" t="s">
-        <v>410</v>
-      </c>
-      <c r="I88" s="63" t="s">
+      <c r="H88" s="50" t="s">
+        <v>410</v>
+      </c>
+      <c r="I88" s="50" t="s">
         <v>331</v>
       </c>
-      <c r="J88" s="63" t="s">
-        <v>410</v>
-      </c>
-      <c r="K88" s="98" t="s">
-        <v>410</v>
-      </c>
-      <c r="L88" s="63">
+      <c r="J88" s="50" t="s">
+        <v>410</v>
+      </c>
+      <c r="K88" s="87" t="s">
+        <v>410</v>
+      </c>
+      <c r="L88" s="50">
         <v>2</v>
       </c>
-      <c r="M88" s="63">
+      <c r="M88" s="50">
         <f t="shared" si="5"/>
         <v>10</v>
       </c>
-      <c r="N88" s="63">
-        <v>10</v>
-      </c>
-      <c r="O88" s="67" t="s">
-        <v>518</v>
-      </c>
-      <c r="P88" s="65">
-        <v>8</v>
-      </c>
-      <c r="Q88" s="65">
+      <c r="N88" s="50">
+        <v>12</v>
+      </c>
+      <c r="O88" s="62" t="s">
+        <v>408</v>
+      </c>
+      <c r="P88" s="61">
+        <v>10.59</v>
+      </c>
+      <c r="Q88" s="61">
         <f t="shared" si="6"/>
-        <v>80</v>
-      </c>
-      <c r="R88" s="80" t="s">
-        <v>519</v>
-      </c>
-      <c r="S88" s="66"/>
-      <c r="T88" s="77"/>
+        <v>127.08</v>
+      </c>
+      <c r="R88" s="105"/>
+      <c r="S88" s="52"/>
+      <c r="T88" s="72"/>
     </row>
     <row r="89" spans="1:20" ht="36.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A89" s="1"/>
@@ -7579,7 +7552,7 @@
         <f t="shared" si="4"/>
         <v>80</v>
       </c>
-      <c r="C89" s="82" t="s">
+      <c r="C89" s="76" t="s">
         <v>396</v>
       </c>
       <c r="D89" s="46" t="s">
@@ -7603,7 +7576,7 @@
       <c r="J89" s="46" t="s">
         <v>509</v>
       </c>
-      <c r="K89" s="95" t="s">
+      <c r="K89" s="88" t="s">
         <v>410</v>
       </c>
       <c r="L89" s="46">
@@ -7635,7 +7608,7 @@
         <f t="shared" si="4"/>
         <v>81</v>
       </c>
-      <c r="C90" s="83" t="s">
+      <c r="C90" s="77" t="s">
         <v>396</v>
       </c>
       <c r="D90" s="50" t="s">
@@ -7659,7 +7632,7 @@
       <c r="J90" s="50" t="s">
         <v>464</v>
       </c>
-      <c r="K90" s="94" t="s">
+      <c r="K90" s="87" t="s">
         <v>410</v>
       </c>
       <c r="L90" s="50">
@@ -7691,7 +7664,7 @@
         <f t="shared" si="4"/>
         <v>82</v>
       </c>
-      <c r="C91" s="82" t="s">
+      <c r="C91" s="76" t="s">
         <v>396</v>
       </c>
       <c r="D91" s="46" t="s">
@@ -7715,7 +7688,7 @@
       <c r="J91" s="46" t="s">
         <v>465</v>
       </c>
-      <c r="K91" s="95" t="s">
+      <c r="K91" s="88" t="s">
         <v>410</v>
       </c>
       <c r="L91" s="46">
@@ -7747,49 +7720,53 @@
         <f t="shared" si="4"/>
         <v>83</v>
       </c>
-      <c r="C92" s="85" t="s">
+      <c r="C92" s="77" t="s">
         <v>396</v>
       </c>
-      <c r="D92" s="63" t="s">
+      <c r="D92" s="50" t="s">
         <v>88</v>
       </c>
-      <c r="E92" s="64" t="s">
+      <c r="E92" s="51" t="s">
         <v>179</v>
       </c>
-      <c r="F92" s="63" t="s">
+      <c r="F92" s="50" t="s">
         <v>226</v>
       </c>
-      <c r="G92" s="64" t="s">
+      <c r="G92" s="51" t="s">
         <v>292</v>
       </c>
-      <c r="H92" s="63" t="s">
-        <v>410</v>
-      </c>
-      <c r="I92" s="63" t="s">
+      <c r="H92" s="50" t="s">
+        <v>410</v>
+      </c>
+      <c r="I92" s="50" t="s">
         <v>304</v>
       </c>
-      <c r="J92" s="63"/>
-      <c r="K92" s="98" t="s">
-        <v>410</v>
-      </c>
-      <c r="L92" s="63">
+      <c r="J92" s="50"/>
+      <c r="K92" s="87" t="s">
+        <v>410</v>
+      </c>
+      <c r="L92" s="50">
         <v>1</v>
       </c>
-      <c r="M92" s="63">
+      <c r="M92" s="50">
         <f t="shared" si="5"/>
         <v>5</v>
       </c>
-      <c r="N92" s="63">
+      <c r="N92" s="50">
         <v>6</v>
       </c>
-      <c r="O92" s="67"/>
-      <c r="P92" s="65"/>
-      <c r="Q92" s="65">
+      <c r="O92" s="62" t="s">
+        <v>408</v>
+      </c>
+      <c r="P92" s="61">
+        <v>1.48</v>
+      </c>
+      <c r="Q92" s="61">
         <f t="shared" si="6"/>
-        <v>0</v>
-      </c>
-      <c r="R92" s="66"/>
-      <c r="S92" s="66"/>
+        <v>8.879999999999999</v>
+      </c>
+      <c r="R92" s="52"/>
+      <c r="S92" s="52"/>
     </row>
     <row r="93" spans="1:20" ht="24.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A93" s="1"/>
@@ -7797,47 +7774,53 @@
         <f t="shared" si="4"/>
         <v>84</v>
       </c>
-      <c r="C93" s="84" t="s">
+      <c r="C93" s="76" t="s">
         <v>396</v>
       </c>
-      <c r="D93" s="73" t="s">
+      <c r="D93" s="46" t="s">
         <v>89</v>
       </c>
-      <c r="E93" s="74" t="s">
+      <c r="E93" s="47" t="s">
         <v>180</v>
       </c>
-      <c r="F93" s="73" t="s">
+      <c r="F93" s="46" t="s">
         <v>409</v>
       </c>
-      <c r="G93" s="74" t="s">
+      <c r="G93" s="47" t="s">
         <v>229</v>
       </c>
-      <c r="H93" s="73" t="s">
-        <v>410</v>
-      </c>
-      <c r="I93" s="73" t="s">
+      <c r="H93" s="46" t="s">
+        <v>410</v>
+      </c>
+      <c r="I93" s="46" t="s">
         <v>334</v>
       </c>
-      <c r="J93" s="73"/>
-      <c r="K93" s="96" t="s">
-        <v>410</v>
-      </c>
-      <c r="L93" s="73">
+      <c r="J93" s="46"/>
+      <c r="K93" s="88" t="s">
+        <v>410</v>
+      </c>
+      <c r="L93" s="46">
         <v>1</v>
       </c>
-      <c r="M93" s="73">
+      <c r="M93" s="46">
         <f t="shared" si="5"/>
         <v>5</v>
       </c>
-      <c r="N93" s="73"/>
-      <c r="O93" s="73"/>
-      <c r="P93" s="75"/>
-      <c r="Q93" s="75">
+      <c r="N93" s="46">
+        <v>6</v>
+      </c>
+      <c r="O93" s="104" t="s">
+        <v>408</v>
+      </c>
+      <c r="P93" s="60">
+        <v>4.42</v>
+      </c>
+      <c r="Q93" s="60">
         <f t="shared" si="6"/>
-        <v>0</v>
-      </c>
-      <c r="R93" s="76"/>
-      <c r="S93" s="76"/>
+        <v>26.52</v>
+      </c>
+      <c r="R93" s="48"/>
+      <c r="S93" s="48"/>
     </row>
     <row r="94" spans="1:20" ht="36.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A94" s="1"/>
@@ -7845,7 +7828,7 @@
         <f t="shared" si="4"/>
         <v>85</v>
       </c>
-      <c r="C94" s="83" t="s">
+      <c r="C94" s="77" t="s">
         <v>396</v>
       </c>
       <c r="D94" s="50" t="s">
@@ -7869,7 +7852,7 @@
       <c r="J94" s="50" t="s">
         <v>510</v>
       </c>
-      <c r="K94" s="94" t="s">
+      <c r="K94" s="87" t="s">
         <v>410</v>
       </c>
       <c r="L94" s="50">
@@ -7901,7 +7884,7 @@
         <f t="shared" si="4"/>
         <v>86</v>
       </c>
-      <c r="C95" s="82" t="s">
+      <c r="C95" s="76" t="s">
         <v>396</v>
       </c>
       <c r="D95" s="46" t="s">
@@ -7925,7 +7908,7 @@
       <c r="J95" s="46" t="s">
         <v>466</v>
       </c>
-      <c r="K95" s="95" t="s">
+      <c r="K95" s="88" t="s">
         <v>410</v>
       </c>
       <c r="L95" s="46">
@@ -7957,7 +7940,7 @@
         <f t="shared" si="4"/>
         <v>87</v>
       </c>
-      <c r="C96" s="83" t="s">
+      <c r="C96" s="77" t="s">
         <v>396</v>
       </c>
       <c r="D96" s="50" t="s">
@@ -7981,7 +7964,7 @@
       <c r="J96" s="50" t="s">
         <v>467</v>
       </c>
-      <c r="K96" s="94" t="s">
+      <c r="K96" s="87" t="s">
         <v>410</v>
       </c>
       <c r="L96" s="50">
@@ -8013,7 +7996,7 @@
         <f t="shared" si="4"/>
         <v>88</v>
       </c>
-      <c r="C97" s="82" t="s">
+      <c r="C97" s="76" t="s">
         <v>396</v>
       </c>
       <c r="D97" s="46" t="s">
@@ -8037,7 +8020,7 @@
       <c r="J97" s="46" t="s">
         <v>468</v>
       </c>
-      <c r="K97" s="95" t="s">
+      <c r="K97" s="88" t="s">
         <v>410</v>
       </c>
       <c r="L97" s="46">
@@ -8069,7 +8052,7 @@
         <f t="shared" si="4"/>
         <v>89</v>
       </c>
-      <c r="C98" s="83" t="s">
+      <c r="C98" s="77" t="s">
         <v>396</v>
       </c>
       <c r="D98" s="50" t="s">
@@ -8093,7 +8076,7 @@
       <c r="J98" s="50" t="s">
         <v>469</v>
       </c>
-      <c r="K98" s="94" t="s">
+      <c r="K98" s="87" t="s">
         <v>410</v>
       </c>
       <c r="L98" s="50">
@@ -8125,32 +8108,32 @@
         <f t="shared" si="4"/>
         <v>90</v>
       </c>
-      <c r="C99" s="82" t="s">
+      <c r="C99" s="76" t="s">
         <v>397</v>
       </c>
       <c r="D99" s="46" t="s">
         <v>95</v>
       </c>
       <c r="E99" s="47" t="s">
-        <v>535</v>
+        <v>533</v>
       </c>
       <c r="F99" s="46" t="s">
         <v>408</v>
       </c>
       <c r="G99" s="47" t="s">
+        <v>530</v>
+      </c>
+      <c r="H99" s="83" t="s">
+        <v>410</v>
+      </c>
+      <c r="I99" s="46" t="s">
+        <v>531</v>
+      </c>
+      <c r="J99" s="46" t="s">
+        <v>534</v>
+      </c>
+      <c r="K99" s="47" t="s">
         <v>532</v>
-      </c>
-      <c r="H99" s="90" t="s">
-        <v>410</v>
-      </c>
-      <c r="I99" s="46" t="s">
-        <v>533</v>
-      </c>
-      <c r="J99" s="46" t="s">
-        <v>536</v>
-      </c>
-      <c r="K99" s="47" t="s">
-        <v>534</v>
       </c>
       <c r="L99" s="46">
         <v>1</v>
@@ -8172,7 +8155,7 @@
         <f t="shared" si="6"/>
         <v>1.2804</v>
       </c>
-      <c r="R99" s="91"/>
+      <c r="R99" s="84"/>
       <c r="S99" s="48"/>
     </row>
     <row r="100" spans="1:19" ht="36.75" thickBot="1" x14ac:dyDescent="0.3">
@@ -8181,7 +8164,7 @@
         <f t="shared" si="4"/>
         <v>91</v>
       </c>
-      <c r="C100" s="83" t="s">
+      <c r="C100" s="77" t="s">
         <v>397</v>
       </c>
       <c r="D100" s="50" t="s">
@@ -8205,7 +8188,7 @@
       <c r="J100" s="50" t="s">
         <v>470</v>
       </c>
-      <c r="K100" s="94" t="s">
+      <c r="K100" s="87" t="s">
         <v>382</v>
       </c>
       <c r="L100" s="50">
@@ -8237,7 +8220,7 @@
         <f t="shared" si="4"/>
         <v>92</v>
       </c>
-      <c r="C101" s="82" t="s">
+      <c r="C101" s="76" t="s">
         <v>397</v>
       </c>
       <c r="D101" s="46" t="s">
@@ -8261,7 +8244,7 @@
       <c r="J101" s="46" t="s">
         <v>471</v>
       </c>
-      <c r="K101" s="99" t="s">
+      <c r="K101" s="91" t="s">
         <v>383</v>
       </c>
       <c r="L101" s="58">
@@ -8301,17 +8284,17 @@
       <c r="K102" s="37"/>
       <c r="L102" s="37"/>
       <c r="M102" s="37"/>
-      <c r="N102" s="101" t="s">
-        <v>520</v>
-      </c>
-      <c r="O102" s="102"/>
-      <c r="P102" s="102"/>
-      <c r="Q102" s="78">
+      <c r="N102" s="94" t="s">
+        <v>518</v>
+      </c>
+      <c r="O102" s="95"/>
+      <c r="P102" s="95"/>
+      <c r="Q102" s="73">
         <f>SUM(Q10:Q101)</f>
-        <v>634.95269999999994</v>
-      </c>
-      <c r="R102" s="107"/>
-      <c r="S102" s="108"/>
+        <v>717.43269999999995</v>
+      </c>
+      <c r="R102" s="100"/>
+      <c r="S102" s="101"/>
     </row>
     <row r="103" spans="1:19" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A103" s="1"/>
@@ -8327,27 +8310,25 @@
       <c r="K103" s="10"/>
       <c r="L103" s="10"/>
       <c r="M103" s="10"/>
-      <c r="N103" s="101" t="s">
-        <v>521</v>
-      </c>
-      <c r="O103" s="102"/>
-      <c r="P103" s="102"/>
-      <c r="Q103" s="79">
+      <c r="N103" s="94" t="s">
+        <v>519</v>
+      </c>
+      <c r="O103" s="95"/>
+      <c r="P103" s="95"/>
+      <c r="Q103" s="74">
         <f>Q102/5</f>
-        <v>126.99053999999998</v>
-      </c>
-      <c r="R103" s="109"/>
-      <c r="S103" s="110"/>
+        <v>143.48653999999999</v>
+      </c>
+      <c r="R103" s="102"/>
+      <c r="S103" s="103"/>
     </row>
     <row r="104" spans="1:19" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="N104" s="101" t="s">
-        <v>522</v>
-      </c>
-      <c r="O104" s="102"/>
-      <c r="P104" s="102"/>
-      <c r="Q104" s="79">
-        <v>4</v>
-      </c>
+      <c r="N104" s="94" t="s">
+        <v>520</v>
+      </c>
+      <c r="O104" s="95"/>
+      <c r="P104" s="95"/>
+      <c r="Q104" s="74"/>
     </row>
   </sheetData>
   <mergeCells count="6">
@@ -8359,93 +8340,93 @@
     <mergeCell ref="N103:P103"/>
   </mergeCells>
   <hyperlinks>
-    <hyperlink ref="O10" r:id="rId1" xr:uid="{00000000-0004-0000-0000-000000000000}"/>
-    <hyperlink ref="O11" r:id="rId2" xr:uid="{00000000-0004-0000-0000-000001000000}"/>
-    <hyperlink ref="O12" r:id="rId3" xr:uid="{00000000-0004-0000-0000-000002000000}"/>
-    <hyperlink ref="O13" r:id="rId4" xr:uid="{00000000-0004-0000-0000-000003000000}"/>
-    <hyperlink ref="O14" r:id="rId5" xr:uid="{00000000-0004-0000-0000-000004000000}"/>
-    <hyperlink ref="O15" r:id="rId6" xr:uid="{00000000-0004-0000-0000-000005000000}"/>
-    <hyperlink ref="O17" r:id="rId7" xr:uid="{00000000-0004-0000-0000-000006000000}"/>
-    <hyperlink ref="O18" r:id="rId8" xr:uid="{00000000-0004-0000-0000-000007000000}"/>
-    <hyperlink ref="O19" r:id="rId9" xr:uid="{00000000-0004-0000-0000-000008000000}"/>
-    <hyperlink ref="O20" r:id="rId10" xr:uid="{00000000-0004-0000-0000-000009000000}"/>
-    <hyperlink ref="O21" r:id="rId11" xr:uid="{00000000-0004-0000-0000-00000A000000}"/>
-    <hyperlink ref="O22" r:id="rId12" xr:uid="{00000000-0004-0000-0000-00000B000000}"/>
-    <hyperlink ref="O23" r:id="rId13" xr:uid="{00000000-0004-0000-0000-00000C000000}"/>
-    <hyperlink ref="O27" r:id="rId14" xr:uid="{00000000-0004-0000-0000-00000E000000}"/>
-    <hyperlink ref="O36" r:id="rId15" xr:uid="{00000000-0004-0000-0000-00000F000000}"/>
-    <hyperlink ref="O37" r:id="rId16" xr:uid="{00000000-0004-0000-0000-000010000000}"/>
-    <hyperlink ref="O38" r:id="rId17" xr:uid="{00000000-0004-0000-0000-000011000000}"/>
-    <hyperlink ref="O40" r:id="rId18" xr:uid="{00000000-0004-0000-0000-000012000000}"/>
-    <hyperlink ref="O41" r:id="rId19" xr:uid="{00000000-0004-0000-0000-000013000000}"/>
-    <hyperlink ref="O42" r:id="rId20" xr:uid="{00000000-0004-0000-0000-000014000000}"/>
-    <hyperlink ref="O44" r:id="rId21" xr:uid="{00000000-0004-0000-0000-000015000000}"/>
-    <hyperlink ref="O45" r:id="rId22" xr:uid="{00000000-0004-0000-0000-000016000000}"/>
-    <hyperlink ref="O52" r:id="rId23" xr:uid="{00000000-0004-0000-0000-000017000000}"/>
-    <hyperlink ref="O54" r:id="rId24" xr:uid="{00000000-0004-0000-0000-000018000000}"/>
-    <hyperlink ref="O56" r:id="rId25" xr:uid="{00000000-0004-0000-0000-000019000000}"/>
-    <hyperlink ref="O57" r:id="rId26" xr:uid="{00000000-0004-0000-0000-00001A000000}"/>
-    <hyperlink ref="O58" r:id="rId27" xr:uid="{00000000-0004-0000-0000-00001B000000}"/>
-    <hyperlink ref="O59" r:id="rId28" xr:uid="{00000000-0004-0000-0000-00001C000000}"/>
-    <hyperlink ref="O60" r:id="rId29" xr:uid="{00000000-0004-0000-0000-00001D000000}"/>
-    <hyperlink ref="O61" r:id="rId30" xr:uid="{00000000-0004-0000-0000-00001E000000}"/>
-    <hyperlink ref="O62" r:id="rId31" xr:uid="{00000000-0004-0000-0000-00001F000000}"/>
-    <hyperlink ref="O63" r:id="rId32" xr:uid="{00000000-0004-0000-0000-000020000000}"/>
-    <hyperlink ref="O64" r:id="rId33" xr:uid="{00000000-0004-0000-0000-000021000000}"/>
-    <hyperlink ref="O65" r:id="rId34" xr:uid="{00000000-0004-0000-0000-000022000000}"/>
-    <hyperlink ref="O66" r:id="rId35" xr:uid="{00000000-0004-0000-0000-000023000000}"/>
-    <hyperlink ref="O68" r:id="rId36" xr:uid="{00000000-0004-0000-0000-000024000000}"/>
-    <hyperlink ref="O69" r:id="rId37" xr:uid="{00000000-0004-0000-0000-000025000000}"/>
-    <hyperlink ref="O70" r:id="rId38" xr:uid="{00000000-0004-0000-0000-000026000000}"/>
-    <hyperlink ref="O71" r:id="rId39" xr:uid="{00000000-0004-0000-0000-000027000000}"/>
-    <hyperlink ref="O72" r:id="rId40" xr:uid="{00000000-0004-0000-0000-000028000000}"/>
-    <hyperlink ref="O73" r:id="rId41" xr:uid="{00000000-0004-0000-0000-000029000000}"/>
-    <hyperlink ref="O75" r:id="rId42" xr:uid="{00000000-0004-0000-0000-00002A000000}"/>
-    <hyperlink ref="O76" r:id="rId43" xr:uid="{00000000-0004-0000-0000-00002B000000}"/>
-    <hyperlink ref="O77" r:id="rId44" xr:uid="{00000000-0004-0000-0000-00002C000000}"/>
-    <hyperlink ref="O79" r:id="rId45" xr:uid="{00000000-0004-0000-0000-00002D000000}"/>
-    <hyperlink ref="O80" r:id="rId46" xr:uid="{00000000-0004-0000-0000-00002E000000}"/>
-    <hyperlink ref="O81" r:id="rId47" xr:uid="{00000000-0004-0000-0000-00002F000000}"/>
-    <hyperlink ref="O82" r:id="rId48" xr:uid="{00000000-0004-0000-0000-000030000000}"/>
-    <hyperlink ref="O84" r:id="rId49" xr:uid="{00000000-0004-0000-0000-000031000000}"/>
-    <hyperlink ref="O87" r:id="rId50" xr:uid="{00000000-0004-0000-0000-000032000000}"/>
-    <hyperlink ref="O90" r:id="rId51" xr:uid="{00000000-0004-0000-0000-000033000000}"/>
-    <hyperlink ref="O91" r:id="rId52" xr:uid="{00000000-0004-0000-0000-000034000000}"/>
-    <hyperlink ref="O95" r:id="rId53" xr:uid="{00000000-0004-0000-0000-000035000000}"/>
-    <hyperlink ref="O96" r:id="rId54" xr:uid="{00000000-0004-0000-0000-000036000000}"/>
-    <hyperlink ref="O97" r:id="rId55" xr:uid="{00000000-0004-0000-0000-000037000000}"/>
-    <hyperlink ref="O98" r:id="rId56" xr:uid="{00000000-0004-0000-0000-000038000000}"/>
-    <hyperlink ref="O100" r:id="rId57" xr:uid="{00000000-0004-0000-0000-000039000000}"/>
-    <hyperlink ref="O101" r:id="rId58" xr:uid="{00000000-0004-0000-0000-00003A000000}"/>
-    <hyperlink ref="O24" r:id="rId59" xr:uid="{00000000-0004-0000-0000-00003B000000}"/>
-    <hyperlink ref="O26" r:id="rId60" xr:uid="{00000000-0004-0000-0000-00003C000000}"/>
-    <hyperlink ref="O28" r:id="rId61" xr:uid="{00000000-0004-0000-0000-00003D000000}"/>
-    <hyperlink ref="O29" r:id="rId62" xr:uid="{00000000-0004-0000-0000-00003E000000}"/>
-    <hyperlink ref="O31" r:id="rId63" xr:uid="{00000000-0004-0000-0000-00003F000000}"/>
-    <hyperlink ref="O39" r:id="rId64" xr:uid="{00000000-0004-0000-0000-000040000000}"/>
-    <hyperlink ref="O48" r:id="rId65" xr:uid="{00000000-0004-0000-0000-000041000000}"/>
-    <hyperlink ref="O47" r:id="rId66" xr:uid="{00000000-0004-0000-0000-000042000000}"/>
-    <hyperlink ref="O51" r:id="rId67" xr:uid="{00000000-0004-0000-0000-000044000000}"/>
-    <hyperlink ref="O53" r:id="rId68" xr:uid="{00000000-0004-0000-0000-000045000000}"/>
-    <hyperlink ref="O55" r:id="rId69" xr:uid="{00000000-0004-0000-0000-000046000000}"/>
-    <hyperlink ref="O67" r:id="rId70" xr:uid="{00000000-0004-0000-0000-000047000000}"/>
-    <hyperlink ref="O83" r:id="rId71" xr:uid="{00000000-0004-0000-0000-000048000000}"/>
-    <hyperlink ref="O85" r:id="rId72" xr:uid="{00000000-0004-0000-0000-000049000000}"/>
-    <hyperlink ref="O43" r:id="rId73" xr:uid="{00000000-0004-0000-0000-00004A000000}"/>
-    <hyperlink ref="O49" r:id="rId74" xr:uid="{00000000-0004-0000-0000-00004B000000}"/>
-    <hyperlink ref="O74" r:id="rId75" xr:uid="{00000000-0004-0000-0000-00004C000000}"/>
-    <hyperlink ref="O78" r:id="rId76" xr:uid="{00000000-0004-0000-0000-00004D000000}"/>
-    <hyperlink ref="O89" r:id="rId77" xr:uid="{00000000-0004-0000-0000-00004E000000}"/>
-    <hyperlink ref="O94" r:id="rId78" xr:uid="{00000000-0004-0000-0000-00004F000000}"/>
-    <hyperlink ref="O33" r:id="rId79" xr:uid="{00000000-0004-0000-0000-000050000000}"/>
-    <hyperlink ref="O34" r:id="rId80" xr:uid="{00000000-0004-0000-0000-000051000000}"/>
-    <hyperlink ref="O35" r:id="rId81" xr:uid="{00000000-0004-0000-0000-000052000000}"/>
-    <hyperlink ref="O88" r:id="rId82" xr:uid="{00000000-0004-0000-0000-000053000000}"/>
-    <hyperlink ref="O16" r:id="rId83" xr:uid="{00000000-0004-0000-0000-000054000000}"/>
-    <hyperlink ref="O30" r:id="rId84" xr:uid="{00000000-0004-0000-0000-000055000000}"/>
-    <hyperlink ref="O99" r:id="rId85" xr:uid="{41DBDB4E-DF1C-471F-AD20-8FB2CA7D9E5E}"/>
-    <hyperlink ref="O25" r:id="rId86" xr:uid="{DAC6EF1B-A44F-4325-8C76-4CC4A05529DD}"/>
-    <hyperlink ref="O50" r:id="rId87" xr:uid="{249CEE1C-EC12-47D3-9B5F-AD078E9DD01C}"/>
+    <hyperlink ref="O10" r:id="rId1"/>
+    <hyperlink ref="O11" r:id="rId2"/>
+    <hyperlink ref="O12" r:id="rId3"/>
+    <hyperlink ref="O13" r:id="rId4"/>
+    <hyperlink ref="O14" r:id="rId5"/>
+    <hyperlink ref="O15" r:id="rId6"/>
+    <hyperlink ref="O17" r:id="rId7"/>
+    <hyperlink ref="O18" r:id="rId8"/>
+    <hyperlink ref="O19" r:id="rId9"/>
+    <hyperlink ref="O20" r:id="rId10"/>
+    <hyperlink ref="O21" r:id="rId11"/>
+    <hyperlink ref="O22" r:id="rId12"/>
+    <hyperlink ref="O23" r:id="rId13"/>
+    <hyperlink ref="O27" r:id="rId14"/>
+    <hyperlink ref="O36" r:id="rId15"/>
+    <hyperlink ref="O37" r:id="rId16"/>
+    <hyperlink ref="O38" r:id="rId17"/>
+    <hyperlink ref="O40" r:id="rId18"/>
+    <hyperlink ref="O41" r:id="rId19"/>
+    <hyperlink ref="O42" r:id="rId20"/>
+    <hyperlink ref="O44" r:id="rId21"/>
+    <hyperlink ref="O45" r:id="rId22"/>
+    <hyperlink ref="O52" r:id="rId23"/>
+    <hyperlink ref="O54" r:id="rId24"/>
+    <hyperlink ref="O56" r:id="rId25"/>
+    <hyperlink ref="O57" r:id="rId26"/>
+    <hyperlink ref="O58" r:id="rId27"/>
+    <hyperlink ref="O59" r:id="rId28"/>
+    <hyperlink ref="O60" r:id="rId29"/>
+    <hyperlink ref="O61" r:id="rId30"/>
+    <hyperlink ref="O62" r:id="rId31"/>
+    <hyperlink ref="O63" r:id="rId32"/>
+    <hyperlink ref="O64" r:id="rId33"/>
+    <hyperlink ref="O65" r:id="rId34"/>
+    <hyperlink ref="O66" r:id="rId35"/>
+    <hyperlink ref="O68" r:id="rId36"/>
+    <hyperlink ref="O69" r:id="rId37"/>
+    <hyperlink ref="O70" r:id="rId38"/>
+    <hyperlink ref="O71" r:id="rId39"/>
+    <hyperlink ref="O72" r:id="rId40"/>
+    <hyperlink ref="O73" r:id="rId41"/>
+    <hyperlink ref="O75" r:id="rId42"/>
+    <hyperlink ref="O76" r:id="rId43"/>
+    <hyperlink ref="O77" r:id="rId44"/>
+    <hyperlink ref="O79" r:id="rId45"/>
+    <hyperlink ref="O80" r:id="rId46"/>
+    <hyperlink ref="O81" r:id="rId47"/>
+    <hyperlink ref="O82" r:id="rId48"/>
+    <hyperlink ref="O84" r:id="rId49"/>
+    <hyperlink ref="O87" r:id="rId50"/>
+    <hyperlink ref="O90" r:id="rId51"/>
+    <hyperlink ref="O91" r:id="rId52"/>
+    <hyperlink ref="O95" r:id="rId53"/>
+    <hyperlink ref="O96" r:id="rId54"/>
+    <hyperlink ref="O97" r:id="rId55"/>
+    <hyperlink ref="O98" r:id="rId56"/>
+    <hyperlink ref="O100" r:id="rId57"/>
+    <hyperlink ref="O101" r:id="rId58"/>
+    <hyperlink ref="O24" r:id="rId59"/>
+    <hyperlink ref="O26" r:id="rId60"/>
+    <hyperlink ref="O28" r:id="rId61"/>
+    <hyperlink ref="O29" r:id="rId62"/>
+    <hyperlink ref="O31" r:id="rId63"/>
+    <hyperlink ref="O39" r:id="rId64"/>
+    <hyperlink ref="O48" r:id="rId65"/>
+    <hyperlink ref="O47" r:id="rId66"/>
+    <hyperlink ref="O51" r:id="rId67"/>
+    <hyperlink ref="O53" r:id="rId68"/>
+    <hyperlink ref="O55" r:id="rId69"/>
+    <hyperlink ref="O67" r:id="rId70"/>
+    <hyperlink ref="O83" r:id="rId71"/>
+    <hyperlink ref="O85" r:id="rId72"/>
+    <hyperlink ref="O43" r:id="rId73"/>
+    <hyperlink ref="O49" r:id="rId74"/>
+    <hyperlink ref="O74" r:id="rId75"/>
+    <hyperlink ref="O78" r:id="rId76"/>
+    <hyperlink ref="O89" r:id="rId77"/>
+    <hyperlink ref="O94" r:id="rId78"/>
+    <hyperlink ref="O33" r:id="rId79"/>
+    <hyperlink ref="O34" r:id="rId80"/>
+    <hyperlink ref="O35" r:id="rId81"/>
+    <hyperlink ref="O88" r:id="rId82" display="Aliexpress"/>
+    <hyperlink ref="O16" r:id="rId83"/>
+    <hyperlink ref="O30" r:id="rId84"/>
+    <hyperlink ref="O99" r:id="rId85"/>
+    <hyperlink ref="O25" r:id="rId86"/>
+    <hyperlink ref="O50" r:id="rId87"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId88"/>

--- a/BOM/GTV3_Board/eSpark_BOM.xlsx
+++ b/BOM/GTV3_Board/eSpark_BOM.xlsx
@@ -1,20 +1,21 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
-  <fileVersion appName="xl" lastEdited="6" lowestEdited="6" rupBuild="14420"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="25629"/>
   <workbookPr codeName="ThisWorkbook"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Faizan\GitHub\OliverStanton-WaterMonitor\BOM\GTV3_Board\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\GitHub\OliverStanton-WaterMonitor\BOM\GTV3_Board\"/>
     </mc:Choice>
   </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E35DA53F-C4EB-48AB-A80C-55F773FF2804}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-5265" yWindow="2205" windowWidth="11790" windowHeight="15360"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="152511"/>
+  <calcPr calcId="181029"/>
   <extLst>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
       <xcalcf:calcFeatures>
@@ -29,7 +30,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="952" uniqueCount="543">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="952" uniqueCount="542">
   <si>
     <t>Component list</t>
   </si>
@@ -1396,9 +1397,6 @@
     <t>C325658</t>
   </si>
   <si>
-    <t>C228019</t>
-  </si>
-  <si>
     <t>C144654</t>
   </si>
   <si>
@@ -1591,9 +1589,6 @@
     <t>Single Board Cost</t>
   </si>
   <si>
-    <t>Aliexpress Shipping</t>
-  </si>
-  <si>
     <t>DO NOT MOUNT</t>
   </si>
   <si>
@@ -1609,21 +1604,6 @@
     <t>C123716</t>
   </si>
   <si>
-    <r>
-      <t xml:space="preserve">Alternate added. </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="9"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>Design change needed</t>
-    </r>
-  </si>
-  <si>
     <t>SMBJ70A/TR13</t>
   </si>
   <si>
@@ -1652,9 +1632,6 @@
   </si>
   <si>
     <t xml:space="preserve">Part added in design </t>
-  </si>
-  <si>
-    <t xml:space="preserve">Less Stock </t>
   </si>
   <si>
     <t>0603CG1R5C500NT</t>
@@ -1671,18 +1648,27 @@
   </si>
   <si>
     <t xml:space="preserve">   </t>
+  </si>
+  <si>
+    <t>SCR0603F69K8</t>
+  </si>
+  <si>
+    <t>C3016381</t>
+  </si>
+  <si>
+    <t>Alternate added. Design change needed</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="3">
     <numFmt numFmtId="164" formatCode="[$-409]h:mm:ss\ AM/PM;@"/>
     <numFmt numFmtId="165" formatCode="&quot;$&quot;#,##0.0000"/>
     <numFmt numFmtId="166" formatCode="&quot;$&quot;#,##0.00"/>
   </numFmts>
-  <fonts count="27" x14ac:knownFonts="1">
+  <fonts count="25" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1838,13 +1824,6 @@
     </font>
     <font>
       <b/>
-      <sz val="9"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
       <sz val="10"/>
       <name val="Calibri"/>
       <family val="2"/>
@@ -1859,14 +1838,6 @@
     </font>
     <font>
       <b/>
-      <sz val="9"/>
-      <color rgb="FFFF0000"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
       <sz val="10"/>
       <color rgb="FFFF0000"/>
       <name val="Calibri"/>
@@ -1874,7 +1845,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="7">
+  <fills count="6">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -1905,14 +1876,8 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
   </fills>
-  <borders count="26">
+  <borders count="25">
     <border>
       <left/>
       <right/>
@@ -2172,17 +2137,6 @@
       <left style="medium">
         <color indexed="64"/>
       </left>
-      <right style="medium">
-        <color indexed="64"/>
-      </right>
-      <top/>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="medium">
-        <color indexed="64"/>
-      </left>
       <right/>
       <top style="medium">
         <color indexed="64"/>
@@ -2210,7 +2164,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="20" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="106">
+  <cellXfs count="84">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
@@ -2365,9 +2319,6 @@
     <xf numFmtId="0" fontId="11" fillId="3" borderId="5" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="2" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="20" fillId="2" borderId="16" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -2386,27 +2337,6 @@
     <xf numFmtId="0" fontId="21" fillId="4" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="4" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="4" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="4" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="6" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="6" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="165" fontId="18" fillId="6" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="6" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="166" fontId="15" fillId="3" borderId="15" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -2414,68 +2344,32 @@
     <xf numFmtId="166" fontId="15" fillId="3" borderId="21" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="6" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="22" fillId="2" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="2" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="22" fillId="4" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="4" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="6" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="4" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="2" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="2" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="6" borderId="16" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="2" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="2" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="24" fillId="2" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="17" fillId="5" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="2" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="18" fillId="2" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="4" borderId="25" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="18" fillId="4" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="18" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="6" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="4" borderId="25" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="2" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="6" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="2" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="3" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="23" fillId="3" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="top"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="24" fillId="3" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="23" fillId="3" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="top"/>
       <protection locked="0"/>
     </xf>
@@ -2501,12 +2395,6 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="17" fillId="3" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="2" borderId="17" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="4" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -2553,7 +2441,7 @@
         <xdr:cNvPr id="2" name="Picture 1">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{00000000-0008-0000-0000-000002000000}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000002000000}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -2849,9 +2737,9 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <sheetPr codeName="Sheet1"/>
-  <dimension ref="A1:T104"/>
+  <dimension ref="A1:T103"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="2" max="2" width="3.140625" style="26" customWidth="1"/>
@@ -2891,15 +2779,15 @@
       <c r="H1" s="2"/>
       <c r="I1" s="2"/>
       <c r="J1" s="2"/>
-      <c r="K1" s="96"/>
-      <c r="L1" s="96"/>
-      <c r="M1" s="96"/>
-      <c r="N1" s="96"/>
-      <c r="O1" s="96"/>
-      <c r="P1" s="96"/>
-      <c r="Q1" s="96"/>
-      <c r="R1" s="96"/>
-      <c r="S1" s="97"/>
+      <c r="K1" s="76"/>
+      <c r="L1" s="76"/>
+      <c r="M1" s="76"/>
+      <c r="N1" s="76"/>
+      <c r="O1" s="76"/>
+      <c r="P1" s="76"/>
+      <c r="Q1" s="76"/>
+      <c r="R1" s="76"/>
+      <c r="S1" s="77"/>
     </row>
     <row r="2" spans="1:19" ht="32.25" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A2" s="1"/>
@@ -2910,7 +2798,7 @@
       </c>
       <c r="E2" s="11"/>
       <c r="F2" s="54" t="s">
-        <v>522</v>
+        <v>520</v>
       </c>
       <c r="G2" s="12"/>
       <c r="H2" s="12"/>
@@ -2935,7 +2823,7 @@
       </c>
       <c r="E3" s="13"/>
       <c r="F3" s="55" t="s">
-        <v>523</v>
+        <v>521</v>
       </c>
       <c r="G3" s="13"/>
       <c r="H3" s="13"/>
@@ -2949,7 +2837,7 @@
       <c r="P3" s="5"/>
       <c r="Q3" s="5"/>
       <c r="R3" s="5"/>
-      <c r="S3" s="98"/>
+      <c r="S3" s="78"/>
     </row>
     <row r="4" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A4" s="1"/>
@@ -2960,7 +2848,7 @@
       </c>
       <c r="E4" s="13"/>
       <c r="F4" s="56" t="s">
-        <v>523</v>
+        <v>521</v>
       </c>
       <c r="G4" s="14"/>
       <c r="H4" s="14"/>
@@ -2974,7 +2862,7 @@
       <c r="P4" s="6"/>
       <c r="Q4" s="6"/>
       <c r="R4" s="6"/>
-      <c r="S4" s="99"/>
+      <c r="S4" s="79"/>
     </row>
     <row r="5" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A5" s="1"/>
@@ -2999,7 +2887,7 @@
       <c r="P5" s="6"/>
       <c r="Q5" s="6"/>
       <c r="R5" s="6"/>
-      <c r="S5" s="99"/>
+      <c r="S5" s="79"/>
     </row>
     <row r="6" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A6" s="1"/>
@@ -3020,7 +2908,7 @@
       <c r="P6" s="6"/>
       <c r="Q6" s="6"/>
       <c r="R6" s="6"/>
-      <c r="S6" s="99"/>
+      <c r="S6" s="79"/>
     </row>
     <row r="7" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A7" s="1"/>
@@ -3041,7 +2929,7 @@
       <c r="P7" s="8"/>
       <c r="Q7" s="8"/>
       <c r="R7" s="8"/>
-      <c r="S7" s="99"/>
+      <c r="S7" s="79"/>
     </row>
     <row r="8" spans="1:19" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A8" s="1"/>
@@ -3062,7 +2950,7 @@
       <c r="P8" s="8"/>
       <c r="Q8" s="8"/>
       <c r="R8" s="8"/>
-      <c r="S8" s="99"/>
+      <c r="S8" s="79"/>
     </row>
     <row r="9" spans="1:19" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A9" s="1"/>
@@ -3093,7 +2981,7 @@
       <c r="J9" s="30" t="s">
         <v>400</v>
       </c>
-      <c r="K9" s="85" t="s">
+      <c r="K9" s="70" t="s">
         <v>412</v>
       </c>
       <c r="L9" s="30" t="s">
@@ -3127,7 +3015,7 @@
         <f t="shared" ref="B10:B41" si="0">ROW(B10) - ROW($B$9)</f>
         <v>1</v>
       </c>
-      <c r="C10" s="76" t="s">
+      <c r="C10" s="67" t="s">
         <v>385</v>
       </c>
       <c r="D10" s="46" t="s">
@@ -3151,7 +3039,7 @@
       <c r="J10" s="46" t="s">
         <v>413</v>
       </c>
-      <c r="K10" s="86" t="s">
+      <c r="K10" s="71" t="s">
         <v>338</v>
       </c>
       <c r="L10" s="46">
@@ -3164,15 +3052,15 @@
       <c r="N10" s="46">
         <v>80</v>
       </c>
-      <c r="O10" s="59" t="s">
-        <v>414</v>
-      </c>
-      <c r="P10" s="60">
-        <v>2.47E-2</v>
-      </c>
-      <c r="Q10" s="60">
+      <c r="O10" s="58" t="s">
+        <v>414</v>
+      </c>
+      <c r="P10" s="59">
+        <v>2.2100000000000002E-2</v>
+      </c>
+      <c r="Q10" s="59">
         <f>P10*N10</f>
-        <v>1.976</v>
+        <v>1.7680000000000002</v>
       </c>
       <c r="R10" s="48"/>
       <c r="S10" s="49"/>
@@ -3183,7 +3071,7 @@
         <f t="shared" si="0"/>
         <v>2</v>
       </c>
-      <c r="C11" s="77" t="s">
+      <c r="C11" s="68" t="s">
         <v>385</v>
       </c>
       <c r="D11" s="50" t="s">
@@ -3207,7 +3095,7 @@
       <c r="J11" s="50" t="s">
         <v>415</v>
       </c>
-      <c r="K11" s="87" t="s">
+      <c r="K11" s="72" t="s">
         <v>339</v>
       </c>
       <c r="L11" s="50">
@@ -3220,15 +3108,15 @@
       <c r="N11" s="50">
         <v>200</v>
       </c>
-      <c r="O11" s="62" t="s">
-        <v>414</v>
-      </c>
-      <c r="P11" s="61">
-        <v>3.3999999999999998E-3</v>
-      </c>
-      <c r="Q11" s="61">
+      <c r="O11" s="61" t="s">
+        <v>414</v>
+      </c>
+      <c r="P11" s="60">
+        <v>2.7000000000000001E-3</v>
+      </c>
+      <c r="Q11" s="60">
         <f t="shared" ref="Q11:Q74" si="2">P11*N11</f>
-        <v>0.67999999999999994</v>
+        <v>0.54</v>
       </c>
       <c r="R11" s="52"/>
       <c r="S11" s="53"/>
@@ -3239,7 +3127,7 @@
         <f t="shared" si="0"/>
         <v>3</v>
       </c>
-      <c r="C12" s="76" t="s">
+      <c r="C12" s="67" t="s">
         <v>385</v>
       </c>
       <c r="D12" s="46" t="s">
@@ -3263,7 +3151,7 @@
       <c r="J12" s="46" t="s">
         <v>416</v>
       </c>
-      <c r="K12" s="88" t="s">
+      <c r="K12" s="73" t="s">
         <v>340</v>
       </c>
       <c r="L12" s="46">
@@ -3274,17 +3162,17 @@
         <v>35</v>
       </c>
       <c r="N12" s="46">
-        <v>50</v>
-      </c>
-      <c r="O12" s="59" t="s">
-        <v>414</v>
-      </c>
-      <c r="P12" s="60">
-        <v>5.8999999999999999E-3</v>
-      </c>
-      <c r="Q12" s="60">
+        <v>100</v>
+      </c>
+      <c r="O12" s="58" t="s">
+        <v>414</v>
+      </c>
+      <c r="P12" s="59">
+        <v>5.4999999999999997E-3</v>
+      </c>
+      <c r="Q12" s="59">
         <f t="shared" si="2"/>
-        <v>0.29499999999999998</v>
+        <v>0.54999999999999993</v>
       </c>
       <c r="R12" s="48"/>
       <c r="S12" s="48"/>
@@ -3295,7 +3183,7 @@
         <f t="shared" si="0"/>
         <v>4</v>
       </c>
-      <c r="C13" s="77" t="s">
+      <c r="C13" s="68" t="s">
         <v>385</v>
       </c>
       <c r="D13" s="50" t="s">
@@ -3307,7 +3195,7 @@
       <c r="F13" s="50" t="s">
         <v>408</v>
       </c>
-      <c r="G13" s="50" t="s">
+      <c r="G13" s="51" t="s">
         <v>191</v>
       </c>
       <c r="H13" s="50" t="s">
@@ -3319,7 +3207,7 @@
       <c r="J13" s="50" t="s">
         <v>417</v>
       </c>
-      <c r="K13" s="87" t="s">
+      <c r="K13" s="72" t="s">
         <v>341</v>
       </c>
       <c r="L13" s="50">
@@ -3332,18 +3220,18 @@
       <c r="N13" s="50">
         <v>27</v>
       </c>
-      <c r="O13" s="62" t="s">
-        <v>414</v>
-      </c>
-      <c r="P13" s="61">
-        <v>0.43640000000000001</v>
-      </c>
-      <c r="Q13" s="61">
+      <c r="O13" s="61" t="s">
+        <v>414</v>
+      </c>
+      <c r="P13" s="60">
+        <v>0.33410000000000001</v>
+      </c>
+      <c r="Q13" s="60">
         <f t="shared" si="2"/>
-        <v>11.7828</v>
+        <v>9.0206999999999997</v>
       </c>
       <c r="R13" s="52"/>
-      <c r="S13" s="52"/>
+      <c r="S13" s="53"/>
     </row>
     <row r="14" spans="1:19" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A14" s="1"/>
@@ -3351,7 +3239,7 @@
         <f t="shared" si="0"/>
         <v>5</v>
       </c>
-      <c r="C14" s="76" t="s">
+      <c r="C14" s="67" t="s">
         <v>385</v>
       </c>
       <c r="D14" s="46" t="s">
@@ -3375,7 +3263,7 @@
       <c r="J14" s="46" t="s">
         <v>418</v>
       </c>
-      <c r="K14" s="88" t="s">
+      <c r="K14" s="73" t="s">
         <v>342</v>
       </c>
       <c r="L14" s="46">
@@ -3388,19 +3276,17 @@
       <c r="N14" s="46">
         <v>10</v>
       </c>
-      <c r="O14" s="59" t="s">
-        <v>414</v>
-      </c>
-      <c r="P14" s="60">
-        <v>0.1376</v>
-      </c>
-      <c r="Q14" s="60">
+      <c r="O14" s="58" t="s">
+        <v>414</v>
+      </c>
+      <c r="P14" s="59">
+        <v>0.1237</v>
+      </c>
+      <c r="Q14" s="59">
         <f t="shared" si="2"/>
-        <v>1.3759999999999999</v>
-      </c>
-      <c r="R14" s="75" t="s">
-        <v>537</v>
-      </c>
+        <v>1.2370000000000001</v>
+      </c>
+      <c r="R14" s="48"/>
       <c r="S14" s="48"/>
     </row>
     <row r="15" spans="1:19" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
@@ -3409,7 +3295,7 @@
         <f t="shared" si="0"/>
         <v>6</v>
       </c>
-      <c r="C15" s="77" t="s">
+      <c r="C15" s="68" t="s">
         <v>385</v>
       </c>
       <c r="D15" s="50" t="s">
@@ -3433,7 +3319,7 @@
       <c r="J15" s="50" t="s">
         <v>419</v>
       </c>
-      <c r="K15" s="87" t="s">
+      <c r="K15" s="72" t="s">
         <v>343</v>
       </c>
       <c r="L15" s="50">
@@ -3446,77 +3332,77 @@
       <c r="N15" s="50">
         <v>100</v>
       </c>
-      <c r="O15" s="62" t="s">
-        <v>414</v>
-      </c>
-      <c r="P15" s="61">
-        <v>3.0999999999999999E-3</v>
-      </c>
-      <c r="Q15" s="61">
+      <c r="O15" s="61" t="s">
+        <v>414</v>
+      </c>
+      <c r="P15" s="60">
+        <v>2.3999999999999998E-3</v>
+      </c>
+      <c r="Q15" s="60">
         <f t="shared" si="2"/>
-        <v>0.31</v>
+        <v>0.24</v>
       </c>
       <c r="R15" s="52"/>
-      <c r="S15" s="52"/>
-    </row>
-    <row r="16" spans="1:19" ht="24.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="S15" s="53"/>
+    </row>
+    <row r="16" spans="1:19" ht="26.25" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A16" s="1"/>
       <c r="B16" s="38">
         <f t="shared" si="0"/>
         <v>7</v>
       </c>
-      <c r="C16" s="78" t="s">
+      <c r="C16" s="67" t="s">
         <v>385</v>
       </c>
-      <c r="D16" s="68" t="s">
+      <c r="D16" s="46" t="s">
         <v>13</v>
       </c>
-      <c r="E16" s="69" t="s">
+      <c r="E16" s="47" t="s">
         <v>105</v>
       </c>
-      <c r="F16" s="68" t="s">
+      <c r="F16" s="46" t="s">
         <v>408</v>
       </c>
-      <c r="G16" s="92" t="s">
+      <c r="G16" s="62" t="s">
         <v>193</v>
       </c>
-      <c r="H16" s="68" t="s">
-        <v>524</v>
-      </c>
-      <c r="I16" s="68" t="s">
+      <c r="H16" s="46" t="s">
+        <v>522</v>
+      </c>
+      <c r="I16" s="46" t="s">
         <v>301</v>
       </c>
-      <c r="J16" s="68" t="s">
-        <v>525</v>
-      </c>
-      <c r="K16" s="89" t="s">
+      <c r="J16" s="46" t="s">
+        <v>523</v>
+      </c>
+      <c r="K16" s="73" t="s">
         <v>340</v>
       </c>
-      <c r="L16" s="68">
+      <c r="L16" s="46">
         <v>1</v>
       </c>
-      <c r="M16" s="68">
+      <c r="M16" s="46">
         <f t="shared" si="1"/>
         <v>5</v>
       </c>
-      <c r="N16" s="68">
-        <v>10</v>
-      </c>
-      <c r="O16" s="82" t="s">
-        <v>414</v>
-      </c>
-      <c r="P16" s="70">
-        <v>0.187</v>
-      </c>
-      <c r="Q16" s="70">
+      <c r="N16" s="46">
+        <v>7</v>
+      </c>
+      <c r="O16" s="58" t="s">
+        <v>414</v>
+      </c>
+      <c r="P16" s="59">
+        <v>0.1686</v>
+      </c>
+      <c r="Q16" s="59">
         <f t="shared" si="2"/>
-        <v>1.87</v>
-      </c>
-      <c r="R16" s="75" t="s">
-        <v>536</v>
-      </c>
-      <c r="S16" s="71" t="s">
-        <v>526</v>
+        <v>1.1801999999999999</v>
+      </c>
+      <c r="R16" s="69" t="s">
+        <v>533</v>
+      </c>
+      <c r="S16" s="69" t="s">
+        <v>541</v>
       </c>
     </row>
     <row r="17" spans="1:19" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
@@ -3525,7 +3411,7 @@
         <f t="shared" si="0"/>
         <v>8</v>
       </c>
-      <c r="C17" s="77" t="s">
+      <c r="C17" s="68" t="s">
         <v>385</v>
       </c>
       <c r="D17" s="50" t="s">
@@ -3549,7 +3435,7 @@
       <c r="J17" s="50" t="s">
         <v>420</v>
       </c>
-      <c r="K17" s="87" t="s">
+      <c r="K17" s="72" t="s">
         <v>344</v>
       </c>
       <c r="L17" s="50">
@@ -3562,18 +3448,18 @@
       <c r="N17" s="50">
         <v>100</v>
       </c>
-      <c r="O17" s="62" t="s">
-        <v>414</v>
-      </c>
-      <c r="P17" s="61">
-        <v>3.3999999999999998E-3</v>
-      </c>
-      <c r="Q17" s="61">
+      <c r="O17" s="61" t="s">
+        <v>414</v>
+      </c>
+      <c r="P17" s="60">
+        <v>2.5999999999999999E-3</v>
+      </c>
+      <c r="Q17" s="60">
         <f t="shared" si="2"/>
-        <v>0.33999999999999997</v>
+        <v>0.26</v>
       </c>
       <c r="R17" s="52"/>
-      <c r="S17" s="52"/>
+      <c r="S17" s="53"/>
     </row>
     <row r="18" spans="1:19" ht="24.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A18" s="1"/>
@@ -3581,7 +3467,7 @@
         <f t="shared" si="0"/>
         <v>9</v>
       </c>
-      <c r="C18" s="76" t="s">
+      <c r="C18" s="67" t="s">
         <v>385</v>
       </c>
       <c r="D18" s="46" t="s">
@@ -3605,7 +3491,7 @@
       <c r="J18" s="46" t="s">
         <v>421</v>
       </c>
-      <c r="K18" s="88" t="s">
+      <c r="K18" s="73" t="s">
         <v>345</v>
       </c>
       <c r="L18" s="46">
@@ -3618,13 +3504,13 @@
       <c r="N18" s="46">
         <v>100</v>
       </c>
-      <c r="O18" s="59" t="s">
-        <v>414</v>
-      </c>
-      <c r="P18" s="60">
+      <c r="O18" s="58" t="s">
+        <v>414</v>
+      </c>
+      <c r="P18" s="59">
         <v>3.3999999999999998E-3</v>
       </c>
-      <c r="Q18" s="60">
+      <c r="Q18" s="59">
         <f t="shared" si="2"/>
         <v>0.33999999999999997</v>
       </c>
@@ -3637,7 +3523,7 @@
         <f t="shared" si="0"/>
         <v>10</v>
       </c>
-      <c r="C19" s="77" t="s">
+      <c r="C19" s="68" t="s">
         <v>385</v>
       </c>
       <c r="D19" s="50" t="s">
@@ -3661,7 +3547,7 @@
       <c r="J19" s="50" t="s">
         <v>422</v>
       </c>
-      <c r="K19" s="87" t="s">
+      <c r="K19" s="72" t="s">
         <v>339</v>
       </c>
       <c r="L19" s="50">
@@ -3674,18 +3560,18 @@
       <c r="N19" s="50">
         <v>50</v>
       </c>
-      <c r="O19" s="62" t="s">
-        <v>414</v>
-      </c>
-      <c r="P19" s="61">
+      <c r="O19" s="61" t="s">
+        <v>414</v>
+      </c>
+      <c r="P19" s="60">
         <v>8.0999999999999996E-3</v>
       </c>
-      <c r="Q19" s="61">
+      <c r="Q19" s="60">
         <f t="shared" si="2"/>
         <v>0.40499999999999997</v>
       </c>
       <c r="R19" s="52"/>
-      <c r="S19" s="52"/>
+      <c r="S19" s="53"/>
     </row>
     <row r="20" spans="1:19" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A20" s="1"/>
@@ -3693,7 +3579,7 @@
         <f t="shared" si="0"/>
         <v>11</v>
       </c>
-      <c r="C20" s="76" t="s">
+      <c r="C20" s="67" t="s">
         <v>385</v>
       </c>
       <c r="D20" s="46" t="s">
@@ -3717,7 +3603,7 @@
       <c r="J20" s="46" t="s">
         <v>423</v>
       </c>
-      <c r="K20" s="88" t="s">
+      <c r="K20" s="73" t="s">
         <v>346</v>
       </c>
       <c r="L20" s="46">
@@ -3730,13 +3616,13 @@
       <c r="N20" s="46">
         <v>100</v>
       </c>
-      <c r="O20" s="59" t="s">
-        <v>414</v>
-      </c>
-      <c r="P20" s="60">
+      <c r="O20" s="58" t="s">
+        <v>414</v>
+      </c>
+      <c r="P20" s="59">
         <v>3.5999999999999999E-3</v>
       </c>
-      <c r="Q20" s="60">
+      <c r="Q20" s="59">
         <f t="shared" si="2"/>
         <v>0.36</v>
       </c>
@@ -3749,7 +3635,7 @@
         <f t="shared" si="0"/>
         <v>12</v>
       </c>
-      <c r="C21" s="77" t="s">
+      <c r="C21" s="68" t="s">
         <v>385</v>
       </c>
       <c r="D21" s="50" t="s">
@@ -3773,7 +3659,7 @@
       <c r="J21" s="50" t="s">
         <v>424</v>
       </c>
-      <c r="K21" s="87" t="s">
+      <c r="K21" s="72" t="s">
         <v>347</v>
       </c>
       <c r="L21" s="50">
@@ -3786,18 +3672,18 @@
       <c r="N21" s="50">
         <v>50</v>
       </c>
-      <c r="O21" s="62" t="s">
-        <v>414</v>
-      </c>
-      <c r="P21" s="61">
+      <c r="O21" s="61" t="s">
+        <v>414</v>
+      </c>
+      <c r="P21" s="60">
         <v>1.1900000000000001E-2</v>
       </c>
-      <c r="Q21" s="61">
+      <c r="Q21" s="60">
         <f t="shared" si="2"/>
         <v>0.59500000000000008</v>
       </c>
       <c r="R21" s="52"/>
-      <c r="S21" s="52"/>
+      <c r="S21" s="53"/>
     </row>
     <row r="22" spans="1:19" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A22" s="1"/>
@@ -3805,7 +3691,7 @@
         <f t="shared" si="0"/>
         <v>13</v>
       </c>
-      <c r="C22" s="76" t="s">
+      <c r="C22" s="67" t="s">
         <v>385</v>
       </c>
       <c r="D22" s="46" t="s">
@@ -3829,7 +3715,7 @@
       <c r="J22" s="46" t="s">
         <v>425</v>
       </c>
-      <c r="K22" s="88" t="s">
+      <c r="K22" s="73" t="s">
         <v>348</v>
       </c>
       <c r="L22" s="46">
@@ -3842,13 +3728,13 @@
       <c r="N22" s="46">
         <v>20</v>
       </c>
-      <c r="O22" s="59" t="s">
-        <v>414</v>
-      </c>
-      <c r="P22" s="60">
+      <c r="O22" s="58" t="s">
+        <v>414</v>
+      </c>
+      <c r="P22" s="59">
         <v>3.49E-2</v>
       </c>
-      <c r="Q22" s="60">
+      <c r="Q22" s="59">
         <f t="shared" si="2"/>
         <v>0.69799999999999995</v>
       </c>
@@ -3861,7 +3747,7 @@
         <f t="shared" si="0"/>
         <v>14</v>
       </c>
-      <c r="C23" s="77" t="s">
+      <c r="C23" s="68" t="s">
         <v>385</v>
       </c>
       <c r="D23" s="50" t="s">
@@ -3885,7 +3771,7 @@
       <c r="J23" s="50" t="s">
         <v>426</v>
       </c>
-      <c r="K23" s="87" t="s">
+      <c r="K23" s="72" t="s">
         <v>349</v>
       </c>
       <c r="L23" s="50">
@@ -3898,18 +3784,18 @@
       <c r="N23" s="50">
         <v>100</v>
       </c>
-      <c r="O23" s="62" t="s">
-        <v>414</v>
-      </c>
-      <c r="P23" s="61">
+      <c r="O23" s="61" t="s">
+        <v>414</v>
+      </c>
+      <c r="P23" s="60">
         <v>3.7000000000000002E-3</v>
       </c>
-      <c r="Q23" s="61">
+      <c r="Q23" s="60">
         <f t="shared" si="2"/>
         <v>0.37</v>
       </c>
       <c r="R23" s="52"/>
-      <c r="S23" s="52"/>
+      <c r="S23" s="53"/>
     </row>
     <row r="24" spans="1:19" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A24" s="1"/>
@@ -3917,7 +3803,7 @@
         <f t="shared" si="0"/>
         <v>15</v>
       </c>
-      <c r="C24" s="76" t="s">
+      <c r="C24" s="67" t="s">
         <v>385</v>
       </c>
       <c r="D24" s="46" t="s">
@@ -3929,19 +3815,19 @@
       <c r="F24" s="46" t="s">
         <v>190</v>
       </c>
-      <c r="G24" s="63" t="s">
+      <c r="G24" s="62" t="s">
         <v>248</v>
       </c>
       <c r="H24" s="46" t="s">
-        <v>474</v>
+        <v>473</v>
       </c>
       <c r="I24" s="46" t="s">
         <v>303</v>
       </c>
       <c r="J24" s="46" t="s">
-        <v>475</v>
-      </c>
-      <c r="K24" s="88" t="s">
+        <v>474</v>
+      </c>
+      <c r="K24" s="73" t="s">
         <v>350</v>
       </c>
       <c r="L24" s="46">
@@ -3954,13 +3840,13 @@
       <c r="N24" s="46">
         <v>20</v>
       </c>
-      <c r="O24" s="59" t="s">
-        <v>414</v>
-      </c>
-      <c r="P24" s="60">
+      <c r="O24" s="58" t="s">
+        <v>414</v>
+      </c>
+      <c r="P24" s="59">
         <v>3.5999999999999997E-2</v>
       </c>
-      <c r="Q24" s="60">
+      <c r="Q24" s="59">
         <f t="shared" si="2"/>
         <v>0.72</v>
       </c>
@@ -3973,7 +3859,7 @@
         <f t="shared" si="0"/>
         <v>16</v>
       </c>
-      <c r="C25" s="77" t="s">
+      <c r="C25" s="68" t="s">
         <v>385</v>
       </c>
       <c r="D25" s="50" t="s">
@@ -3985,19 +3871,19 @@
       <c r="F25" s="50" t="s">
         <v>190</v>
       </c>
-      <c r="G25" s="64" t="s">
+      <c r="G25" s="63" t="s">
         <v>249</v>
       </c>
       <c r="H25" s="50" t="s">
-        <v>538</v>
+        <v>534</v>
       </c>
       <c r="I25" s="50" t="s">
         <v>298</v>
       </c>
       <c r="J25" s="50" t="s">
-        <v>539</v>
-      </c>
-      <c r="K25" s="87" t="s">
+        <v>535</v>
+      </c>
+      <c r="K25" s="72" t="s">
         <v>351</v>
       </c>
       <c r="L25" s="50">
@@ -4010,18 +3896,18 @@
       <c r="N25" s="50">
         <v>100</v>
       </c>
-      <c r="O25" s="62" t="s">
-        <v>414</v>
-      </c>
-      <c r="P25" s="61">
+      <c r="O25" s="61" t="s">
+        <v>414</v>
+      </c>
+      <c r="P25" s="60">
         <v>3.5000000000000001E-3</v>
       </c>
-      <c r="Q25" s="61">
+      <c r="Q25" s="60">
         <f t="shared" si="2"/>
         <v>0.35000000000000003</v>
       </c>
       <c r="R25" s="52"/>
-      <c r="S25" s="52"/>
+      <c r="S25" s="53"/>
     </row>
     <row r="26" spans="1:19" ht="24.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A26" s="1"/>
@@ -4029,7 +3915,7 @@
         <f t="shared" si="0"/>
         <v>17</v>
       </c>
-      <c r="C26" s="76" t="s">
+      <c r="C26" s="67" t="s">
         <v>386</v>
       </c>
       <c r="D26" s="46" t="s">
@@ -4041,19 +3927,19 @@
       <c r="F26" s="46" t="s">
         <v>194</v>
       </c>
-      <c r="G26" s="46" t="s">
+      <c r="G26" s="47" t="s">
         <v>352</v>
       </c>
       <c r="H26" s="46" t="s">
         <v>410</v>
       </c>
       <c r="I26" s="46" t="s">
-        <v>477</v>
+        <v>476</v>
       </c>
       <c r="J26" s="46" t="s">
-        <v>476</v>
-      </c>
-      <c r="K26" s="88" t="s">
+        <v>475</v>
+      </c>
+      <c r="K26" s="73" t="s">
         <v>410</v>
       </c>
       <c r="L26" s="46">
@@ -4066,13 +3952,13 @@
       <c r="N26" s="46">
         <v>20</v>
       </c>
-      <c r="O26" s="59" t="s">
-        <v>414</v>
-      </c>
-      <c r="P26" s="60">
+      <c r="O26" s="58" t="s">
+        <v>414</v>
+      </c>
+      <c r="P26" s="59">
         <v>2.98E-2</v>
       </c>
-      <c r="Q26" s="60">
+      <c r="Q26" s="59">
         <f t="shared" si="2"/>
         <v>0.59599999999999997</v>
       </c>
@@ -4085,7 +3971,7 @@
         <f t="shared" si="0"/>
         <v>18</v>
       </c>
-      <c r="C27" s="77" t="s">
+      <c r="C27" s="68" t="s">
         <v>386</v>
       </c>
       <c r="D27" s="50" t="s">
@@ -4109,7 +3995,7 @@
       <c r="J27" s="50" t="s">
         <v>427</v>
       </c>
-      <c r="K27" s="87" t="s">
+      <c r="K27" s="72" t="s">
         <v>410</v>
       </c>
       <c r="L27" s="50">
@@ -4122,18 +4008,18 @@
       <c r="N27" s="50">
         <v>6</v>
       </c>
-      <c r="O27" s="62" t="s">
-        <v>414</v>
-      </c>
-      <c r="P27" s="61">
+      <c r="O27" s="61" t="s">
+        <v>414</v>
+      </c>
+      <c r="P27" s="60">
         <v>0.84399999999999997</v>
       </c>
-      <c r="Q27" s="61">
+      <c r="Q27" s="60">
         <f t="shared" si="2"/>
         <v>5.0640000000000001</v>
       </c>
       <c r="R27" s="52"/>
-      <c r="S27" s="52"/>
+      <c r="S27" s="53"/>
     </row>
     <row r="28" spans="1:19" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A28" s="1"/>
@@ -4141,7 +4027,7 @@
         <f t="shared" si="0"/>
         <v>19</v>
       </c>
-      <c r="C28" s="76" t="s">
+      <c r="C28" s="67" t="s">
         <v>386</v>
       </c>
       <c r="D28" s="46" t="s">
@@ -4160,12 +4046,12 @@
         <v>410</v>
       </c>
       <c r="I28" s="46" t="s">
+        <v>477</v>
+      </c>
+      <c r="J28" s="46" t="s">
         <v>478</v>
       </c>
-      <c r="J28" s="46" t="s">
-        <v>479</v>
-      </c>
-      <c r="K28" s="88" t="s">
+      <c r="K28" s="73" t="s">
         <v>410</v>
       </c>
       <c r="L28" s="46">
@@ -4178,13 +4064,13 @@
       <c r="N28" s="46">
         <v>20</v>
       </c>
-      <c r="O28" s="59" t="s">
-        <v>414</v>
-      </c>
-      <c r="P28" s="60">
+      <c r="O28" s="58" t="s">
+        <v>414</v>
+      </c>
+      <c r="P28" s="59">
         <v>3.5000000000000003E-2</v>
       </c>
-      <c r="Q28" s="60">
+      <c r="Q28" s="59">
         <f t="shared" si="2"/>
         <v>0.70000000000000007</v>
       </c>
@@ -4197,7 +4083,7 @@
         <f t="shared" si="0"/>
         <v>20</v>
       </c>
-      <c r="C29" s="77" t="s">
+      <c r="C29" s="68" t="s">
         <v>386</v>
       </c>
       <c r="D29" s="50" t="s">
@@ -4209,19 +4095,19 @@
       <c r="F29" s="50" t="s">
         <v>408</v>
       </c>
-      <c r="G29" s="50" t="s">
+      <c r="G29" s="51" t="s">
         <v>195</v>
       </c>
       <c r="H29" s="50" t="s">
         <v>410</v>
       </c>
       <c r="I29" s="50" t="s">
-        <v>480</v>
+        <v>479</v>
       </c>
       <c r="J29" s="50" t="s">
         <v>428</v>
       </c>
-      <c r="K29" s="87" t="s">
+      <c r="K29" s="72" t="s">
         <v>410</v>
       </c>
       <c r="L29" s="50">
@@ -4234,77 +4120,77 @@
       <c r="N29" s="50">
         <v>12</v>
       </c>
-      <c r="O29" s="62" t="s">
-        <v>414</v>
-      </c>
-      <c r="P29" s="61">
+      <c r="O29" s="61" t="s">
+        <v>414</v>
+      </c>
+      <c r="P29" s="60">
         <v>0.69610000000000005</v>
       </c>
-      <c r="Q29" s="61">
+      <c r="Q29" s="60">
         <f t="shared" si="2"/>
         <v>8.3532000000000011</v>
       </c>
       <c r="R29" s="52"/>
-      <c r="S29" s="52"/>
-    </row>
-    <row r="30" spans="1:19" ht="36.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="S29" s="53"/>
+    </row>
+    <row r="30" spans="1:19" ht="39" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A30" s="1"/>
       <c r="B30" s="38">
         <f t="shared" si="0"/>
         <v>21</v>
       </c>
-      <c r="C30" s="78" t="s">
+      <c r="C30" s="67" t="s">
         <v>386</v>
       </c>
-      <c r="D30" s="68" t="s">
+      <c r="D30" s="46" t="s">
         <v>27</v>
       </c>
-      <c r="E30" s="69" t="s">
+      <c r="E30" s="47" t="s">
         <v>119</v>
       </c>
-      <c r="F30" s="68" t="s">
+      <c r="F30" s="46" t="s">
         <v>196</v>
       </c>
-      <c r="G30" s="92" t="s">
+      <c r="G30" s="62" t="s">
         <v>252</v>
       </c>
-      <c r="H30" s="68" t="s">
-        <v>527</v>
-      </c>
-      <c r="I30" s="68" t="s">
+      <c r="H30" s="46" t="s">
+        <v>524</v>
+      </c>
+      <c r="I30" s="46" t="s">
         <v>305</v>
       </c>
-      <c r="J30" s="68" t="s">
-        <v>528</v>
-      </c>
-      <c r="K30" s="89" t="s">
-        <v>410</v>
-      </c>
-      <c r="L30" s="68">
+      <c r="J30" s="46" t="s">
+        <v>525</v>
+      </c>
+      <c r="K30" s="73" t="s">
+        <v>410</v>
+      </c>
+      <c r="L30" s="46">
         <v>1</v>
       </c>
-      <c r="M30" s="68">
+      <c r="M30" s="46">
         <f t="shared" si="1"/>
         <v>5</v>
       </c>
-      <c r="N30" s="68">
+      <c r="N30" s="46">
         <v>10</v>
       </c>
-      <c r="O30" s="82" t="s">
-        <v>414</v>
-      </c>
-      <c r="P30" s="70">
+      <c r="O30" s="58" t="s">
+        <v>414</v>
+      </c>
+      <c r="P30" s="59">
         <v>6.9000000000000006E-2</v>
       </c>
-      <c r="Q30" s="70">
+      <c r="Q30" s="59">
         <f t="shared" si="2"/>
         <v>0.69000000000000006</v>
       </c>
-      <c r="R30" s="75" t="s">
-        <v>536</v>
-      </c>
-      <c r="S30" s="71" t="s">
-        <v>529</v>
+      <c r="R30" s="69" t="s">
+        <v>533</v>
+      </c>
+      <c r="S30" s="69" t="s">
+        <v>526</v>
       </c>
     </row>
     <row r="31" spans="1:19" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
@@ -4313,7 +4199,7 @@
         <f t="shared" si="0"/>
         <v>22</v>
       </c>
-      <c r="C31" s="77" t="s">
+      <c r="C31" s="68" t="s">
         <v>386</v>
       </c>
       <c r="D31" s="50" t="s">
@@ -4325,7 +4211,7 @@
       <c r="F31" s="50" t="s">
         <v>196</v>
       </c>
-      <c r="G31" s="50" t="s">
+      <c r="G31" s="51" t="s">
         <v>197</v>
       </c>
       <c r="H31" s="50" t="s">
@@ -4335,9 +4221,9 @@
         <v>306</v>
       </c>
       <c r="J31" s="50" t="s">
-        <v>481</v>
-      </c>
-      <c r="K31" s="87" t="s">
+        <v>480</v>
+      </c>
+      <c r="K31" s="72" t="s">
         <v>410</v>
       </c>
       <c r="L31" s="50">
@@ -4350,18 +4236,18 @@
       <c r="N31" s="50">
         <v>10</v>
       </c>
-      <c r="O31" s="62" t="s">
-        <v>414</v>
-      </c>
-      <c r="P31" s="61">
+      <c r="O31" s="61" t="s">
+        <v>414</v>
+      </c>
+      <c r="P31" s="60">
         <v>6.2399999999999997E-2</v>
       </c>
-      <c r="Q31" s="61">
+      <c r="Q31" s="60">
         <f t="shared" si="2"/>
         <v>0.624</v>
       </c>
       <c r="R31" s="52"/>
-      <c r="S31" s="52"/>
+      <c r="S31" s="53"/>
     </row>
     <row r="32" spans="1:19" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A32" s="1"/>
@@ -4369,7 +4255,7 @@
         <f t="shared" si="0"/>
         <v>23</v>
       </c>
-      <c r="C32" s="76" t="s">
+      <c r="C32" s="67" t="s">
         <v>387</v>
       </c>
       <c r="D32" s="46" t="s">
@@ -4389,7 +4275,7 @@
         <v>307</v>
       </c>
       <c r="J32" s="46"/>
-      <c r="K32" s="88" t="s">
+      <c r="K32" s="73" t="s">
         <v>410</v>
       </c>
       <c r="L32" s="46">
@@ -4400,9 +4286,9 @@
         <v>5</v>
       </c>
       <c r="N32" s="46"/>
-      <c r="O32" s="46"/>
-      <c r="P32" s="60"/>
-      <c r="Q32" s="60">
+      <c r="O32" s="58"/>
+      <c r="P32" s="59"/>
+      <c r="Q32" s="59">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
@@ -4415,7 +4301,7 @@
         <f t="shared" si="0"/>
         <v>24</v>
       </c>
-      <c r="C33" s="77" t="s">
+      <c r="C33" s="68" t="s">
         <v>388</v>
       </c>
       <c r="D33" s="50" t="s">
@@ -4427,19 +4313,19 @@
       <c r="F33" s="50" t="s">
         <v>408</v>
       </c>
-      <c r="G33" s="64" t="s">
+      <c r="G33" s="63" t="s">
         <v>199</v>
       </c>
       <c r="H33" s="50" t="s">
-        <v>512</v>
+        <v>511</v>
       </c>
       <c r="I33" s="50" t="s">
         <v>308</v>
       </c>
       <c r="J33" s="50" t="s">
-        <v>513</v>
-      </c>
-      <c r="K33" s="87" t="s">
+        <v>512</v>
+      </c>
+      <c r="K33" s="72" t="s">
         <v>410</v>
       </c>
       <c r="L33" s="50">
@@ -4452,18 +4338,18 @@
       <c r="N33" s="50">
         <v>50</v>
       </c>
-      <c r="O33" s="62" t="s">
-        <v>414</v>
-      </c>
-      <c r="P33" s="61">
+      <c r="O33" s="61" t="s">
+        <v>414</v>
+      </c>
+      <c r="P33" s="60">
         <v>7.0999999999999994E-2</v>
       </c>
-      <c r="Q33" s="61">
+      <c r="Q33" s="60">
         <f t="shared" si="2"/>
         <v>3.55</v>
       </c>
       <c r="R33" s="52"/>
-      <c r="S33" s="52"/>
+      <c r="S33" s="53"/>
     </row>
     <row r="34" spans="1:19" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A34" s="1"/>
@@ -4471,7 +4357,7 @@
         <f t="shared" si="0"/>
         <v>25</v>
       </c>
-      <c r="C34" s="76" t="s">
+      <c r="C34" s="67" t="s">
         <v>388</v>
       </c>
       <c r="D34" s="46" t="s">
@@ -4483,19 +4369,19 @@
       <c r="F34" s="46" t="s">
         <v>408</v>
       </c>
-      <c r="G34" s="63" t="s">
+      <c r="G34" s="62" t="s">
         <v>200</v>
       </c>
       <c r="H34" s="46" t="s">
-        <v>514</v>
+        <v>513</v>
       </c>
       <c r="I34" s="46" t="s">
         <v>308</v>
       </c>
       <c r="J34" s="46" t="s">
-        <v>515</v>
-      </c>
-      <c r="K34" s="88" t="s">
+        <v>514</v>
+      </c>
+      <c r="K34" s="73" t="s">
         <v>410</v>
       </c>
       <c r="L34" s="46">
@@ -4508,13 +4394,13 @@
       <c r="N34" s="46">
         <v>30</v>
       </c>
-      <c r="O34" s="59" t="s">
-        <v>414</v>
-      </c>
-      <c r="P34" s="60">
+      <c r="O34" s="58" t="s">
+        <v>414</v>
+      </c>
+      <c r="P34" s="59">
         <v>0.1221</v>
       </c>
-      <c r="Q34" s="60">
+      <c r="Q34" s="59">
         <f t="shared" si="2"/>
         <v>3.6629999999999998</v>
       </c>
@@ -4527,7 +4413,7 @@
         <f t="shared" si="0"/>
         <v>26</v>
       </c>
-      <c r="C35" s="77" t="s">
+      <c r="C35" s="68" t="s">
         <v>388</v>
       </c>
       <c r="D35" s="50" t="s">
@@ -4539,19 +4425,19 @@
       <c r="F35" s="50" t="s">
         <v>408</v>
       </c>
-      <c r="G35" s="64" t="s">
+      <c r="G35" s="63" t="s">
         <v>201</v>
       </c>
       <c r="H35" s="50" t="s">
-        <v>516</v>
+        <v>515</v>
       </c>
       <c r="I35" s="50" t="s">
         <v>308</v>
       </c>
       <c r="J35" s="50" t="s">
-        <v>517</v>
-      </c>
-      <c r="K35" s="90" t="s">
+        <v>516</v>
+      </c>
+      <c r="K35" s="72" t="s">
         <v>411</v>
       </c>
       <c r="L35" s="50">
@@ -4564,18 +4450,18 @@
       <c r="N35" s="50">
         <v>10</v>
       </c>
-      <c r="O35" s="62" t="s">
-        <v>414</v>
-      </c>
-      <c r="P35" s="61">
+      <c r="O35" s="61" t="s">
+        <v>414</v>
+      </c>
+      <c r="P35" s="60">
         <v>0.1225</v>
       </c>
-      <c r="Q35" s="61">
+      <c r="Q35" s="60">
         <f t="shared" si="2"/>
         <v>1.2250000000000001</v>
       </c>
       <c r="R35" s="52"/>
-      <c r="S35" s="52"/>
+      <c r="S35" s="53"/>
     </row>
     <row r="36" spans="1:19" ht="36.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A36" s="1"/>
@@ -4583,7 +4469,7 @@
         <f t="shared" si="0"/>
         <v>27</v>
       </c>
-      <c r="C36" s="76" t="s">
+      <c r="C36" s="67" t="s">
         <v>387</v>
       </c>
       <c r="D36" s="46" t="s">
@@ -4607,7 +4493,7 @@
       <c r="J36" s="46" t="s">
         <v>429</v>
       </c>
-      <c r="K36" s="88" t="s">
+      <c r="K36" s="73" t="s">
         <v>410</v>
       </c>
       <c r="L36" s="46">
@@ -4620,13 +4506,13 @@
       <c r="N36" s="46">
         <v>6</v>
       </c>
-      <c r="O36" s="59" t="s">
-        <v>414</v>
-      </c>
-      <c r="P36" s="60">
+      <c r="O36" s="58" t="s">
+        <v>414</v>
+      </c>
+      <c r="P36" s="59">
         <v>0.83430000000000004</v>
       </c>
-      <c r="Q36" s="60">
+      <c r="Q36" s="59">
         <f t="shared" si="2"/>
         <v>5.0058000000000007</v>
       </c>
@@ -4639,7 +4525,7 @@
         <f t="shared" si="0"/>
         <v>28</v>
       </c>
-      <c r="C37" s="77" t="s">
+      <c r="C37" s="68" t="s">
         <v>389</v>
       </c>
       <c r="D37" s="50" t="s">
@@ -4651,7 +4537,7 @@
       <c r="F37" s="50" t="s">
         <v>408</v>
       </c>
-      <c r="G37" s="50" t="s">
+      <c r="G37" s="51" t="s">
         <v>203</v>
       </c>
       <c r="H37" s="50" t="s">
@@ -4663,7 +4549,7 @@
       <c r="J37" s="50" t="s">
         <v>430</v>
       </c>
-      <c r="K37" s="87" t="s">
+      <c r="K37" s="72" t="s">
         <v>410</v>
       </c>
       <c r="L37" s="50">
@@ -4676,18 +4562,18 @@
       <c r="N37" s="50">
         <v>10</v>
       </c>
-      <c r="O37" s="62" t="s">
-        <v>414</v>
-      </c>
-      <c r="P37" s="61">
+      <c r="O37" s="61" t="s">
+        <v>414</v>
+      </c>
+      <c r="P37" s="60">
         <v>6.7199999999999996E-2</v>
       </c>
-      <c r="Q37" s="61">
+      <c r="Q37" s="60">
         <f t="shared" si="2"/>
         <v>0.67199999999999993</v>
       </c>
       <c r="R37" s="52"/>
-      <c r="S37" s="52"/>
+      <c r="S37" s="53"/>
     </row>
     <row r="38" spans="1:19" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A38" s="1"/>
@@ -4695,7 +4581,7 @@
         <f t="shared" si="0"/>
         <v>29</v>
       </c>
-      <c r="C38" s="76" t="s">
+      <c r="C38" s="67" t="s">
         <v>387</v>
       </c>
       <c r="D38" s="46" t="s">
@@ -4719,7 +4605,7 @@
       <c r="J38" s="46" t="s">
         <v>431</v>
       </c>
-      <c r="K38" s="88" t="s">
+      <c r="K38" s="73" t="s">
         <v>410</v>
       </c>
       <c r="L38" s="46">
@@ -4732,13 +4618,13 @@
       <c r="N38" s="46">
         <v>6</v>
       </c>
-      <c r="O38" s="59" t="s">
-        <v>414</v>
-      </c>
-      <c r="P38" s="60">
+      <c r="O38" s="58" t="s">
+        <v>414</v>
+      </c>
+      <c r="P38" s="59">
         <v>0.2482</v>
       </c>
-      <c r="Q38" s="60">
+      <c r="Q38" s="59">
         <f t="shared" si="2"/>
         <v>1.4892000000000001</v>
       </c>
@@ -4751,7 +4637,7 @@
         <f t="shared" si="0"/>
         <v>30</v>
       </c>
-      <c r="C39" s="77" t="s">
+      <c r="C39" s="68" t="s">
         <v>390</v>
       </c>
       <c r="D39" s="50" t="s">
@@ -4764,7 +4650,7 @@
         <v>205</v>
       </c>
       <c r="G39" s="51" t="s">
-        <v>482</v>
+        <v>481</v>
       </c>
       <c r="H39" s="50" t="s">
         <v>410</v>
@@ -4773,9 +4659,9 @@
         <v>312</v>
       </c>
       <c r="J39" s="50" t="s">
-        <v>483</v>
-      </c>
-      <c r="K39" s="87" t="s">
+        <v>482</v>
+      </c>
+      <c r="K39" s="72" t="s">
         <v>353</v>
       </c>
       <c r="L39" s="50">
@@ -4788,18 +4674,18 @@
       <c r="N39" s="50">
         <v>10</v>
       </c>
-      <c r="O39" s="62" t="s">
-        <v>414</v>
-      </c>
-      <c r="P39" s="61">
+      <c r="O39" s="61" t="s">
+        <v>414</v>
+      </c>
+      <c r="P39" s="60">
         <v>4.4600000000000001E-2</v>
       </c>
-      <c r="Q39" s="61">
+      <c r="Q39" s="60">
         <f t="shared" si="2"/>
         <v>0.44600000000000001</v>
       </c>
       <c r="R39" s="52"/>
-      <c r="S39" s="52"/>
+      <c r="S39" s="53"/>
     </row>
     <row r="40" spans="1:19" ht="36.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A40" s="1"/>
@@ -4807,7 +4693,7 @@
         <f t="shared" si="0"/>
         <v>31</v>
       </c>
-      <c r="C40" s="76" t="s">
+      <c r="C40" s="67" t="s">
         <v>390</v>
       </c>
       <c r="D40" s="46" t="s">
@@ -4831,7 +4717,7 @@
       <c r="J40" s="46" t="s">
         <v>432</v>
       </c>
-      <c r="K40" s="88" t="s">
+      <c r="K40" s="73" t="s">
         <v>354</v>
       </c>
       <c r="L40" s="46">
@@ -4844,13 +4730,13 @@
       <c r="N40" s="46">
         <v>6</v>
       </c>
-      <c r="O40" s="59" t="s">
-        <v>414</v>
-      </c>
-      <c r="P40" s="60">
+      <c r="O40" s="58" t="s">
+        <v>414</v>
+      </c>
+      <c r="P40" s="59">
         <v>0.54279999999999995</v>
       </c>
-      <c r="Q40" s="60">
+      <c r="Q40" s="59">
         <f t="shared" si="2"/>
         <v>3.2567999999999997</v>
       </c>
@@ -4863,7 +4749,7 @@
         <f t="shared" si="0"/>
         <v>32</v>
       </c>
-      <c r="C41" s="77" t="s">
+      <c r="C41" s="68" t="s">
         <v>390</v>
       </c>
       <c r="D41" s="50" t="s">
@@ -4887,7 +4773,7 @@
       <c r="J41" s="50" t="s">
         <v>433</v>
       </c>
-      <c r="K41" s="87" t="s">
+      <c r="K41" s="72" t="s">
         <v>355</v>
       </c>
       <c r="L41" s="50">
@@ -4900,18 +4786,18 @@
       <c r="N41" s="50">
         <v>10</v>
       </c>
-      <c r="O41" s="62" t="s">
-        <v>414</v>
-      </c>
-      <c r="P41" s="61">
+      <c r="O41" s="61" t="s">
+        <v>414</v>
+      </c>
+      <c r="P41" s="60">
         <v>8.9399999999999993E-2</v>
       </c>
-      <c r="Q41" s="61">
+      <c r="Q41" s="60">
         <f t="shared" si="2"/>
         <v>0.89399999999999991</v>
       </c>
       <c r="R41" s="52"/>
-      <c r="S41" s="52"/>
+      <c r="S41" s="53"/>
     </row>
     <row r="42" spans="1:19" ht="36.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A42" s="1"/>
@@ -4919,7 +4805,7 @@
         <f t="shared" ref="B42:B73" si="3">ROW(B42) - ROW($B$9)</f>
         <v>33</v>
       </c>
-      <c r="C42" s="76" t="s">
+      <c r="C42" s="67" t="s">
         <v>390</v>
       </c>
       <c r="D42" s="46" t="s">
@@ -4943,7 +4829,7 @@
       <c r="J42" s="46" t="s">
         <v>434</v>
       </c>
-      <c r="K42" s="88" t="s">
+      <c r="K42" s="73" t="s">
         <v>356</v>
       </c>
       <c r="L42" s="46">
@@ -4956,13 +4842,13 @@
       <c r="N42" s="46">
         <v>10</v>
       </c>
-      <c r="O42" s="59" t="s">
-        <v>414</v>
-      </c>
-      <c r="P42" s="60">
+      <c r="O42" s="58" t="s">
+        <v>414</v>
+      </c>
+      <c r="P42" s="59">
         <v>1.01E-2</v>
       </c>
-      <c r="Q42" s="60">
+      <c r="Q42" s="59">
         <f t="shared" si="2"/>
         <v>0.10099999999999999</v>
       </c>
@@ -4975,7 +4861,7 @@
         <f t="shared" si="3"/>
         <v>34</v>
       </c>
-      <c r="C43" s="77" t="s">
+      <c r="C43" s="68" t="s">
         <v>391</v>
       </c>
       <c r="D43" s="50" t="s">
@@ -4987,19 +4873,19 @@
       <c r="F43" s="50" t="s">
         <v>209</v>
       </c>
-      <c r="G43" s="64" t="s">
+      <c r="G43" s="63" t="s">
         <v>255</v>
       </c>
       <c r="H43" s="50" t="s">
-        <v>499</v>
+        <v>498</v>
       </c>
       <c r="I43" s="50" t="s">
         <v>316</v>
       </c>
       <c r="J43" s="50" t="s">
-        <v>500</v>
-      </c>
-      <c r="K43" s="87" t="s">
+        <v>499</v>
+      </c>
+      <c r="K43" s="72" t="s">
         <v>410</v>
       </c>
       <c r="L43" s="50">
@@ -5012,18 +4898,18 @@
       <c r="N43" s="50">
         <v>40</v>
       </c>
-      <c r="O43" s="62" t="s">
-        <v>414</v>
-      </c>
-      <c r="P43" s="61">
+      <c r="O43" s="61" t="s">
+        <v>414</v>
+      </c>
+      <c r="P43" s="60">
         <v>3.6799999999999999E-2</v>
       </c>
-      <c r="Q43" s="61">
+      <c r="Q43" s="60">
         <f t="shared" si="2"/>
         <v>1.472</v>
       </c>
       <c r="R43" s="52"/>
-      <c r="S43" s="52"/>
+      <c r="S43" s="53"/>
     </row>
     <row r="44" spans="1:19" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A44" s="1"/>
@@ -5031,7 +4917,7 @@
         <f t="shared" si="3"/>
         <v>35</v>
       </c>
-      <c r="C44" s="76" t="s">
+      <c r="C44" s="67" t="s">
         <v>391</v>
       </c>
       <c r="D44" s="46" t="s">
@@ -5055,7 +4941,7 @@
       <c r="J44" s="46" t="s">
         <v>435</v>
       </c>
-      <c r="K44" s="88" t="s">
+      <c r="K44" s="73" t="s">
         <v>410</v>
       </c>
       <c r="L44" s="46">
@@ -5068,13 +4954,13 @@
       <c r="N44" s="46">
         <v>10</v>
       </c>
-      <c r="O44" s="59" t="s">
-        <v>414</v>
-      </c>
-      <c r="P44" s="60">
+      <c r="O44" s="58" t="s">
+        <v>414</v>
+      </c>
+      <c r="P44" s="59">
         <v>0.1363</v>
       </c>
-      <c r="Q44" s="60">
+      <c r="Q44" s="59">
         <f t="shared" si="2"/>
         <v>1.363</v>
       </c>
@@ -5087,7 +4973,7 @@
         <f t="shared" si="3"/>
         <v>36</v>
       </c>
-      <c r="C45" s="77" t="s">
+      <c r="C45" s="68" t="s">
         <v>392</v>
       </c>
       <c r="D45" s="50" t="s">
@@ -5099,7 +4985,7 @@
       <c r="F45" s="50" t="s">
         <v>408</v>
       </c>
-      <c r="G45" s="50" t="s">
+      <c r="G45" s="51" t="s">
         <v>210</v>
       </c>
       <c r="H45" s="50" t="s">
@@ -5111,7 +4997,7 @@
       <c r="J45" s="50" t="s">
         <v>436</v>
       </c>
-      <c r="K45" s="87" t="s">
+      <c r="K45" s="72" t="s">
         <v>410</v>
       </c>
       <c r="L45" s="50">
@@ -5124,18 +5010,18 @@
       <c r="N45" s="50">
         <v>6</v>
       </c>
-      <c r="O45" s="62" t="s">
-        <v>414</v>
-      </c>
-      <c r="P45" s="61">
+      <c r="O45" s="61" t="s">
+        <v>414</v>
+      </c>
+      <c r="P45" s="60">
         <v>0.46300000000000002</v>
       </c>
-      <c r="Q45" s="61">
+      <c r="Q45" s="60">
         <f t="shared" si="2"/>
         <v>2.778</v>
       </c>
       <c r="R45" s="52"/>
-      <c r="S45" s="52"/>
+      <c r="S45" s="53"/>
     </row>
     <row r="46" spans="1:19" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A46" s="1"/>
@@ -5143,7 +5029,7 @@
         <f t="shared" si="3"/>
         <v>37</v>
       </c>
-      <c r="C46" s="76" t="s">
+      <c r="C46" s="67" t="s">
         <v>357</v>
       </c>
       <c r="D46" s="46" t="s">
@@ -5167,7 +5053,7 @@
       <c r="J46" s="46" t="s">
         <v>410</v>
       </c>
-      <c r="K46" s="88" t="s">
+      <c r="K46" s="73" t="s">
         <v>410</v>
       </c>
       <c r="L46" s="46">
@@ -5180,17 +5066,17 @@
       <c r="N46" s="46" t="s">
         <v>410</v>
       </c>
-      <c r="O46" s="46" t="s">
-        <v>410</v>
-      </c>
-      <c r="P46" s="60" t="s">
-        <v>410</v>
-      </c>
-      <c r="Q46" s="60" t="s">
-        <v>410</v>
-      </c>
-      <c r="R46" s="80" t="s">
-        <v>521</v>
+      <c r="O46" s="58" t="s">
+        <v>410</v>
+      </c>
+      <c r="P46" s="59" t="s">
+        <v>410</v>
+      </c>
+      <c r="Q46" s="59" t="s">
+        <v>410</v>
+      </c>
+      <c r="R46" s="69" t="s">
+        <v>519</v>
       </c>
       <c r="S46" s="48" t="s">
         <v>410</v>
@@ -5202,7 +5088,7 @@
         <f t="shared" si="3"/>
         <v>38</v>
       </c>
-      <c r="C47" s="77" t="s">
+      <c r="C47" s="68" t="s">
         <v>389</v>
       </c>
       <c r="D47" s="50" t="s">
@@ -5214,19 +5100,19 @@
       <c r="F47" s="50" t="s">
         <v>211</v>
       </c>
-      <c r="G47" s="64">
+      <c r="G47" s="63">
         <v>61300311121</v>
       </c>
       <c r="H47" s="50" t="s">
-        <v>486</v>
+        <v>485</v>
       </c>
       <c r="I47" s="50" t="s">
         <v>319</v>
       </c>
       <c r="J47" s="50" t="s">
-        <v>487</v>
-      </c>
-      <c r="K47" s="87" t="s">
+        <v>486</v>
+      </c>
+      <c r="K47" s="72" t="s">
         <v>410</v>
       </c>
       <c r="L47" s="50">
@@ -5239,18 +5125,18 @@
       <c r="N47" s="50">
         <v>20</v>
       </c>
-      <c r="O47" s="62" t="s">
-        <v>414</v>
-      </c>
-      <c r="P47" s="61">
+      <c r="O47" s="61" t="s">
+        <v>414</v>
+      </c>
+      <c r="P47" s="60">
         <v>6.0699999999999997E-2</v>
       </c>
-      <c r="Q47" s="61">
+      <c r="Q47" s="60">
         <f t="shared" si="2"/>
         <v>1.214</v>
       </c>
       <c r="R47" s="52"/>
-      <c r="S47" s="52"/>
+      <c r="S47" s="53"/>
     </row>
     <row r="48" spans="1:19" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A48" s="1"/>
@@ -5258,7 +5144,7 @@
         <f t="shared" si="3"/>
         <v>39</v>
       </c>
-      <c r="C48" s="76" t="s">
+      <c r="C48" s="67" t="s">
         <v>389</v>
       </c>
       <c r="D48" s="46" t="s">
@@ -5270,19 +5156,19 @@
       <c r="F48" s="46" t="s">
         <v>212</v>
       </c>
-      <c r="G48" s="63">
+      <c r="G48" s="62">
         <v>61300611121</v>
       </c>
       <c r="H48" s="46" t="s">
-        <v>484</v>
+        <v>483</v>
       </c>
       <c r="I48" s="46" t="s">
         <v>319</v>
       </c>
       <c r="J48" s="46" t="s">
-        <v>485</v>
-      </c>
-      <c r="K48" s="88" t="s">
+        <v>484</v>
+      </c>
+      <c r="K48" s="73" t="s">
         <v>410</v>
       </c>
       <c r="L48" s="46">
@@ -5295,13 +5181,13 @@
       <c r="N48" s="46">
         <v>40</v>
       </c>
-      <c r="O48" s="59" t="s">
-        <v>414</v>
-      </c>
-      <c r="P48" s="60">
+      <c r="O48" s="58" t="s">
+        <v>414</v>
+      </c>
+      <c r="P48" s="59">
         <v>3.5499999999999997E-2</v>
       </c>
-      <c r="Q48" s="60">
+      <c r="Q48" s="59">
         <f t="shared" si="2"/>
         <v>1.42</v>
       </c>
@@ -5314,7 +5200,7 @@
         <f t="shared" si="3"/>
         <v>40</v>
       </c>
-      <c r="C49" s="77" t="s">
+      <c r="C49" s="68" t="s">
         <v>389</v>
       </c>
       <c r="D49" s="50" t="s">
@@ -5326,19 +5212,19 @@
       <c r="F49" s="50" t="s">
         <v>213</v>
       </c>
-      <c r="G49" s="64" t="s">
+      <c r="G49" s="63" t="s">
         <v>257</v>
       </c>
       <c r="H49" s="50" t="s">
+        <v>500</v>
+      </c>
+      <c r="I49" s="50" t="s">
         <v>501</v>
       </c>
-      <c r="I49" s="50" t="s">
-        <v>502</v>
-      </c>
       <c r="J49" s="50" t="s">
-        <v>501</v>
-      </c>
-      <c r="K49" s="87" t="s">
+        <v>500</v>
+      </c>
+      <c r="K49" s="72" t="s">
         <v>410</v>
       </c>
       <c r="L49" s="50">
@@ -5351,26 +5237,26 @@
       <c r="N49" s="50">
         <v>10</v>
       </c>
-      <c r="O49" s="62" t="s">
-        <v>414</v>
-      </c>
-      <c r="P49" s="61">
+      <c r="O49" s="61" t="s">
+        <v>414</v>
+      </c>
+      <c r="P49" s="60">
         <v>0.12429999999999999</v>
       </c>
-      <c r="Q49" s="61">
+      <c r="Q49" s="60">
         <f t="shared" si="2"/>
         <v>1.2429999999999999</v>
       </c>
       <c r="R49" s="52"/>
-      <c r="S49" s="52"/>
-    </row>
-    <row r="50" spans="1:19" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="S49" s="53"/>
+    </row>
+    <row r="50" spans="1:19" ht="24.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A50" s="1"/>
       <c r="B50" s="38">
         <f t="shared" si="3"/>
         <v>41</v>
       </c>
-      <c r="C50" s="76" t="s">
+      <c r="C50" s="67" t="s">
         <v>389</v>
       </c>
       <c r="D50" s="46" t="s">
@@ -5382,19 +5268,19 @@
       <c r="F50" s="46" t="s">
         <v>214</v>
       </c>
-      <c r="G50" s="63">
+      <c r="G50" s="62">
         <v>61300211121</v>
       </c>
-      <c r="H50" s="93" t="s">
-        <v>540</v>
+      <c r="H50" s="46" t="s">
+        <v>536</v>
       </c>
       <c r="I50" s="46" t="s">
         <v>319</v>
       </c>
       <c r="J50" s="46" t="s">
-        <v>541</v>
-      </c>
-      <c r="K50" s="88" t="s">
+        <v>537</v>
+      </c>
+      <c r="K50" s="73" t="s">
         <v>410</v>
       </c>
       <c r="L50" s="46">
@@ -5407,13 +5293,13 @@
       <c r="N50" s="46">
         <v>50</v>
       </c>
-      <c r="O50" s="59" t="s">
-        <v>414</v>
-      </c>
-      <c r="P50" s="60">
+      <c r="O50" s="58" t="s">
+        <v>414</v>
+      </c>
+      <c r="P50" s="59">
         <v>1.2E-2</v>
       </c>
-      <c r="Q50" s="60">
+      <c r="Q50" s="59">
         <f t="shared" si="2"/>
         <v>0.6</v>
       </c>
@@ -5426,7 +5312,7 @@
         <f t="shared" si="3"/>
         <v>42</v>
       </c>
-      <c r="C51" s="77" t="s">
+      <c r="C51" s="68" t="s">
         <v>389</v>
       </c>
       <c r="D51" s="50" t="s">
@@ -5438,19 +5324,19 @@
       <c r="F51" s="50" t="s">
         <v>215</v>
       </c>
-      <c r="G51" s="64">
+      <c r="G51" s="63">
         <v>61300411121</v>
       </c>
       <c r="H51" s="50" t="s">
-        <v>488</v>
+        <v>487</v>
       </c>
       <c r="I51" s="50" t="s">
         <v>319</v>
       </c>
       <c r="J51" s="50" t="s">
-        <v>489</v>
-      </c>
-      <c r="K51" s="87" t="s">
+        <v>488</v>
+      </c>
+      <c r="K51" s="72" t="s">
         <v>410</v>
       </c>
       <c r="L51" s="50">
@@ -5463,18 +5349,18 @@
       <c r="N51" s="50">
         <v>20</v>
       </c>
-      <c r="O51" s="62" t="s">
-        <v>414</v>
-      </c>
-      <c r="P51" s="61">
+      <c r="O51" s="61" t="s">
+        <v>414</v>
+      </c>
+      <c r="P51" s="60">
         <v>2.29E-2</v>
       </c>
-      <c r="Q51" s="61">
+      <c r="Q51" s="60">
         <f t="shared" si="2"/>
         <v>0.45800000000000002</v>
       </c>
       <c r="R51" s="52"/>
-      <c r="S51" s="52"/>
+      <c r="S51" s="53"/>
     </row>
     <row r="52" spans="1:19" ht="24.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A52" s="1"/>
@@ -5482,7 +5368,7 @@
         <f t="shared" si="3"/>
         <v>43</v>
       </c>
-      <c r="C52" s="76" t="s">
+      <c r="C52" s="67" t="s">
         <v>393</v>
       </c>
       <c r="D52" s="46" t="s">
@@ -5506,7 +5392,7 @@
       <c r="J52" s="46" t="s">
         <v>437</v>
       </c>
-      <c r="K52" s="88" t="s">
+      <c r="K52" s="73" t="s">
         <v>410</v>
       </c>
       <c r="L52" s="46">
@@ -5519,13 +5405,13 @@
       <c r="N52" s="46">
         <v>48</v>
       </c>
-      <c r="O52" s="59" t="s">
-        <v>414</v>
-      </c>
-      <c r="P52" s="60">
+      <c r="O52" s="58" t="s">
+        <v>414</v>
+      </c>
+      <c r="P52" s="59">
         <v>0.311</v>
       </c>
-      <c r="Q52" s="60">
+      <c r="Q52" s="59">
         <f t="shared" si="2"/>
         <v>14.928000000000001</v>
       </c>
@@ -5538,7 +5424,7 @@
         <f t="shared" si="3"/>
         <v>44</v>
       </c>
-      <c r="C53" s="77" t="s">
+      <c r="C53" s="68" t="s">
         <v>393</v>
       </c>
       <c r="D53" s="50" t="s">
@@ -5557,12 +5443,12 @@
         <v>410</v>
       </c>
       <c r="I53" s="50" t="s">
+        <v>489</v>
+      </c>
+      <c r="J53" s="50" t="s">
         <v>490</v>
       </c>
-      <c r="J53" s="50" t="s">
-        <v>491</v>
-      </c>
-      <c r="K53" s="87" t="s">
+      <c r="K53" s="72" t="s">
         <v>410</v>
       </c>
       <c r="L53" s="50">
@@ -5575,18 +5461,18 @@
       <c r="N53" s="50">
         <v>10</v>
       </c>
-      <c r="O53" s="62" t="s">
-        <v>414</v>
-      </c>
-      <c r="P53" s="61">
+      <c r="O53" s="61" t="s">
+        <v>414</v>
+      </c>
+      <c r="P53" s="60">
         <v>7.51E-2</v>
       </c>
-      <c r="Q53" s="61">
+      <c r="Q53" s="60">
         <f t="shared" si="2"/>
         <v>0.751</v>
       </c>
       <c r="R53" s="52"/>
-      <c r="S53" s="52"/>
+      <c r="S53" s="53"/>
     </row>
     <row r="54" spans="1:19" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A54" s="1"/>
@@ -5594,7 +5480,7 @@
         <f t="shared" si="3"/>
         <v>45</v>
       </c>
-      <c r="C54" s="76" t="s">
+      <c r="C54" s="67" t="s">
         <v>393</v>
       </c>
       <c r="D54" s="46" t="s">
@@ -5618,7 +5504,7 @@
       <c r="J54" s="46" t="s">
         <v>438</v>
       </c>
-      <c r="K54" s="88" t="s">
+      <c r="K54" s="73" t="s">
         <v>410</v>
       </c>
       <c r="L54" s="46">
@@ -5631,13 +5517,13 @@
       <c r="N54" s="46">
         <v>12</v>
       </c>
-      <c r="O54" s="59" t="s">
-        <v>414</v>
-      </c>
-      <c r="P54" s="60">
+      <c r="O54" s="58" t="s">
+        <v>414</v>
+      </c>
+      <c r="P54" s="59">
         <v>3.6715</v>
       </c>
-      <c r="Q54" s="60">
+      <c r="Q54" s="59">
         <f t="shared" si="2"/>
         <v>44.058</v>
       </c>
@@ -5650,7 +5536,7 @@
         <f t="shared" si="3"/>
         <v>46</v>
       </c>
-      <c r="C55" s="77" t="s">
+      <c r="C55" s="68" t="s">
         <v>393</v>
       </c>
       <c r="D55" s="50" t="s">
@@ -5662,19 +5548,19 @@
       <c r="F55" s="50" t="s">
         <v>217</v>
       </c>
-      <c r="G55" s="65" t="s">
+      <c r="G55" s="51" t="s">
         <v>261</v>
       </c>
       <c r="H55" s="50" t="s">
         <v>410</v>
       </c>
       <c r="I55" s="50" t="s">
-        <v>490</v>
+        <v>489</v>
       </c>
       <c r="J55" s="50" t="s">
-        <v>492</v>
-      </c>
-      <c r="K55" s="87" t="s">
+        <v>491</v>
+      </c>
+      <c r="K55" s="72" t="s">
         <v>410</v>
       </c>
       <c r="L55" s="50">
@@ -5687,18 +5573,18 @@
       <c r="N55" s="50">
         <v>15</v>
       </c>
-      <c r="O55" s="62" t="s">
-        <v>414</v>
-      </c>
-      <c r="P55" s="61">
+      <c r="O55" s="61" t="s">
+        <v>414</v>
+      </c>
+      <c r="P55" s="60">
         <v>7.2599999999999998E-2</v>
       </c>
-      <c r="Q55" s="61">
+      <c r="Q55" s="60">
         <f t="shared" si="2"/>
         <v>1.089</v>
       </c>
       <c r="R55" s="52"/>
-      <c r="S55" s="52"/>
+      <c r="S55" s="53"/>
     </row>
     <row r="56" spans="1:19" ht="24.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A56" s="1"/>
@@ -5706,7 +5592,7 @@
         <f t="shared" si="3"/>
         <v>47</v>
       </c>
-      <c r="C56" s="76" t="s">
+      <c r="C56" s="67" t="s">
         <v>393</v>
       </c>
       <c r="D56" s="46" t="s">
@@ -5728,7 +5614,7 @@
       <c r="J56" s="46" t="s">
         <v>439</v>
       </c>
-      <c r="K56" s="88" t="s">
+      <c r="K56" s="73" t="s">
         <v>410</v>
       </c>
       <c r="L56" s="46">
@@ -5741,13 +5627,13 @@
       <c r="N56" s="46">
         <v>60</v>
       </c>
-      <c r="O56" s="59" t="s">
-        <v>414</v>
-      </c>
-      <c r="P56" s="60">
+      <c r="O56" s="58" t="s">
+        <v>414</v>
+      </c>
+      <c r="P56" s="59">
         <v>2.1000000000000001E-2</v>
       </c>
-      <c r="Q56" s="60">
+      <c r="Q56" s="59">
         <f t="shared" si="2"/>
         <v>1.26</v>
       </c>
@@ -5760,7 +5646,7 @@
         <f t="shared" si="3"/>
         <v>48</v>
       </c>
-      <c r="C57" s="77" t="s">
+      <c r="C57" s="68" t="s">
         <v>393</v>
       </c>
       <c r="D57" s="50" t="s">
@@ -5784,7 +5670,7 @@
       <c r="J57" s="50" t="s">
         <v>440</v>
       </c>
-      <c r="K57" s="87" t="s">
+      <c r="K57" s="72" t="s">
         <v>410</v>
       </c>
       <c r="L57" s="50">
@@ -5797,18 +5683,18 @@
       <c r="N57" s="50">
         <v>20</v>
       </c>
-      <c r="O57" s="62" t="s">
-        <v>414</v>
-      </c>
-      <c r="P57" s="61">
+      <c r="O57" s="61" t="s">
+        <v>414</v>
+      </c>
+      <c r="P57" s="60">
         <v>2.29E-2</v>
       </c>
-      <c r="Q57" s="61">
+      <c r="Q57" s="60">
         <f t="shared" si="2"/>
         <v>0.45800000000000002</v>
       </c>
       <c r="R57" s="52"/>
-      <c r="S57" s="52"/>
+      <c r="S57" s="53"/>
     </row>
     <row r="58" spans="1:19" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A58" s="1"/>
@@ -5816,7 +5702,7 @@
         <f t="shared" si="3"/>
         <v>49</v>
       </c>
-      <c r="C58" s="76" t="s">
+      <c r="C58" s="67" t="s">
         <v>393</v>
       </c>
       <c r="D58" s="46" t="s">
@@ -5840,7 +5726,7 @@
       <c r="J58" s="46" t="s">
         <v>441</v>
       </c>
-      <c r="K58" s="88" t="s">
+      <c r="K58" s="73" t="s">
         <v>410</v>
       </c>
       <c r="L58" s="46">
@@ -5853,13 +5739,13 @@
       <c r="N58" s="46">
         <v>20</v>
       </c>
-      <c r="O58" s="59" t="s">
-        <v>414</v>
-      </c>
-      <c r="P58" s="60">
+      <c r="O58" s="58" t="s">
+        <v>414</v>
+      </c>
+      <c r="P58" s="59">
         <v>3.3399999999999999E-2</v>
       </c>
-      <c r="Q58" s="60">
+      <c r="Q58" s="59">
         <f t="shared" si="2"/>
         <v>0.66799999999999993</v>
       </c>
@@ -5872,7 +5758,7 @@
         <f t="shared" si="3"/>
         <v>50</v>
       </c>
-      <c r="C59" s="77" t="s">
+      <c r="C59" s="68" t="s">
         <v>393</v>
       </c>
       <c r="D59" s="50" t="s">
@@ -5884,7 +5770,7 @@
       <c r="F59" s="50" t="s">
         <v>408</v>
       </c>
-      <c r="G59" s="50" t="s">
+      <c r="G59" s="51" t="s">
         <v>219</v>
       </c>
       <c r="H59" s="50" t="s">
@@ -5896,7 +5782,7 @@
       <c r="J59" s="50" t="s">
         <v>442</v>
       </c>
-      <c r="K59" s="87" t="s">
+      <c r="K59" s="72" t="s">
         <v>410</v>
       </c>
       <c r="L59" s="50">
@@ -5909,18 +5795,18 @@
       <c r="N59" s="50">
         <v>6</v>
       </c>
-      <c r="O59" s="62" t="s">
-        <v>414</v>
-      </c>
-      <c r="P59" s="61">
+      <c r="O59" s="61" t="s">
+        <v>414</v>
+      </c>
+      <c r="P59" s="60">
         <v>0.40760000000000002</v>
       </c>
-      <c r="Q59" s="61">
+      <c r="Q59" s="60">
         <f t="shared" si="2"/>
         <v>2.4456000000000002</v>
       </c>
       <c r="R59" s="52"/>
-      <c r="S59" s="52"/>
+      <c r="S59" s="53"/>
     </row>
     <row r="60" spans="1:19" ht="36.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A60" s="1"/>
@@ -5928,7 +5814,7 @@
         <f t="shared" si="3"/>
         <v>51</v>
       </c>
-      <c r="C60" s="76" t="s">
+      <c r="C60" s="67" t="s">
         <v>394</v>
       </c>
       <c r="D60" s="46" t="s">
@@ -5938,7 +5824,7 @@
         <v>147</v>
       </c>
       <c r="F60" s="46" t="s">
-        <v>542</v>
+        <v>538</v>
       </c>
       <c r="G60" s="47" t="s">
         <v>265</v>
@@ -5952,7 +5838,7 @@
       <c r="J60" s="46" t="s">
         <v>443</v>
       </c>
-      <c r="K60" s="88" t="s">
+      <c r="K60" s="73" t="s">
         <v>358</v>
       </c>
       <c r="L60" s="46">
@@ -5965,13 +5851,13 @@
       <c r="N60" s="46">
         <v>100</v>
       </c>
-      <c r="O60" s="59" t="s">
-        <v>414</v>
-      </c>
-      <c r="P60" s="60">
+      <c r="O60" s="58" t="s">
+        <v>414</v>
+      </c>
+      <c r="P60" s="59">
         <v>2.3999999999999998E-3</v>
       </c>
-      <c r="Q60" s="60">
+      <c r="Q60" s="59">
         <f t="shared" si="2"/>
         <v>0.24</v>
       </c>
@@ -5984,7 +5870,7 @@
         <f t="shared" si="3"/>
         <v>52</v>
       </c>
-      <c r="C61" s="77" t="s">
+      <c r="C61" s="68" t="s">
         <v>394</v>
       </c>
       <c r="D61" s="50" t="s">
@@ -6006,7 +5892,7 @@
       <c r="J61" s="50" t="s">
         <v>444</v>
       </c>
-      <c r="K61" s="87" t="s">
+      <c r="K61" s="72" t="s">
         <v>359</v>
       </c>
       <c r="L61" s="50">
@@ -6019,18 +5905,18 @@
       <c r="N61" s="50">
         <v>100</v>
       </c>
-      <c r="O61" s="62" t="s">
-        <v>414</v>
-      </c>
-      <c r="P61" s="61">
+      <c r="O61" s="61" t="s">
+        <v>414</v>
+      </c>
+      <c r="P61" s="60">
         <v>1.2999999999999999E-3</v>
       </c>
-      <c r="Q61" s="61">
+      <c r="Q61" s="60">
         <f t="shared" si="2"/>
         <v>0.13</v>
       </c>
       <c r="R61" s="52"/>
-      <c r="S61" s="52"/>
+      <c r="S61" s="53"/>
     </row>
     <row r="62" spans="1:19" ht="36.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A62" s="1"/>
@@ -6038,7 +5924,7 @@
         <f t="shared" si="3"/>
         <v>53</v>
       </c>
-      <c r="C62" s="76" t="s">
+      <c r="C62" s="67" t="s">
         <v>394</v>
       </c>
       <c r="D62" s="46" t="s">
@@ -6051,7 +5937,7 @@
         <v>220</v>
       </c>
       <c r="G62" s="47" t="s">
-        <v>472</v>
+        <v>471</v>
       </c>
       <c r="H62" s="46" t="s">
         <v>410</v>
@@ -6060,9 +5946,9 @@
         <v>323</v>
       </c>
       <c r="J62" s="46" t="s">
-        <v>473</v>
-      </c>
-      <c r="K62" s="88" t="s">
+        <v>472</v>
+      </c>
+      <c r="K62" s="73" t="s">
         <v>360</v>
       </c>
       <c r="L62" s="46">
@@ -6075,13 +5961,13 @@
       <c r="N62" s="46">
         <v>50</v>
       </c>
-      <c r="O62" s="59" t="s">
-        <v>414</v>
-      </c>
-      <c r="P62" s="60">
+      <c r="O62" s="58" t="s">
+        <v>414</v>
+      </c>
+      <c r="P62" s="59">
         <v>4.3E-3</v>
       </c>
-      <c r="Q62" s="60">
+      <c r="Q62" s="59">
         <f t="shared" si="2"/>
         <v>0.215</v>
       </c>
@@ -6094,11 +5980,11 @@
         <f t="shared" si="3"/>
         <v>54</v>
       </c>
-      <c r="C63" s="77" t="s">
+      <c r="C63" s="68" t="s">
         <v>394</v>
       </c>
       <c r="D63" s="50" t="s">
-        <v>535</v>
+        <v>532</v>
       </c>
       <c r="E63" s="51" t="s">
         <v>150</v>
@@ -6118,7 +6004,7 @@
       <c r="J63" s="50" t="s">
         <v>445</v>
       </c>
-      <c r="K63" s="87" t="s">
+      <c r="K63" s="72" t="s">
         <v>361</v>
       </c>
       <c r="L63" s="50">
@@ -6131,18 +6017,18 @@
       <c r="N63" s="50">
         <v>200</v>
       </c>
-      <c r="O63" s="62" t="s">
-        <v>414</v>
-      </c>
-      <c r="P63" s="61">
+      <c r="O63" s="61" t="s">
+        <v>414</v>
+      </c>
+      <c r="P63" s="60">
         <v>2E-3</v>
       </c>
-      <c r="Q63" s="61">
+      <c r="Q63" s="60">
         <f t="shared" si="2"/>
         <v>0.4</v>
       </c>
       <c r="R63" s="52"/>
-      <c r="S63" s="52"/>
+      <c r="S63" s="53"/>
     </row>
     <row r="64" spans="1:19" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A64" s="1"/>
@@ -6150,7 +6036,7 @@
         <f t="shared" si="3"/>
         <v>55</v>
       </c>
-      <c r="C64" s="76" t="s">
+      <c r="C64" s="67" t="s">
         <v>394</v>
       </c>
       <c r="D64" s="46" t="s">
@@ -6174,7 +6060,7 @@
       <c r="J64" s="46" t="s">
         <v>446</v>
       </c>
-      <c r="K64" s="88" t="s">
+      <c r="K64" s="73" t="s">
         <v>362</v>
       </c>
       <c r="L64" s="46">
@@ -6187,13 +6073,13 @@
       <c r="N64" s="46">
         <v>100</v>
       </c>
-      <c r="O64" s="59" t="s">
-        <v>414</v>
-      </c>
-      <c r="P64" s="60">
+      <c r="O64" s="58" t="s">
+        <v>414</v>
+      </c>
+      <c r="P64" s="59">
         <v>1.1999999999999999E-3</v>
       </c>
-      <c r="Q64" s="60">
+      <c r="Q64" s="59">
         <f t="shared" si="2"/>
         <v>0.12</v>
       </c>
@@ -6206,7 +6092,7 @@
         <f t="shared" si="3"/>
         <v>56</v>
       </c>
-      <c r="C65" s="77" t="s">
+      <c r="C65" s="68" t="s">
         <v>394</v>
       </c>
       <c r="D65" s="50" t="s">
@@ -6228,7 +6114,7 @@
       <c r="J65" s="50" t="s">
         <v>447</v>
       </c>
-      <c r="K65" s="87" t="s">
+      <c r="K65" s="72" t="s">
         <v>363</v>
       </c>
       <c r="L65" s="50">
@@ -6241,18 +6127,18 @@
       <c r="N65" s="50">
         <v>100</v>
       </c>
-      <c r="O65" s="62" t="s">
-        <v>414</v>
-      </c>
-      <c r="P65" s="61">
+      <c r="O65" s="61" t="s">
+        <v>414</v>
+      </c>
+      <c r="P65" s="60">
         <v>1.9E-3</v>
       </c>
-      <c r="Q65" s="61">
+      <c r="Q65" s="60">
         <f t="shared" si="2"/>
         <v>0.19</v>
       </c>
       <c r="R65" s="52"/>
-      <c r="S65" s="52"/>
+      <c r="S65" s="53"/>
     </row>
     <row r="66" spans="1:19" ht="36.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A66" s="1"/>
@@ -6260,7 +6146,7 @@
         <f t="shared" si="3"/>
         <v>57</v>
       </c>
-      <c r="C66" s="76" t="s">
+      <c r="C66" s="67" t="s">
         <v>394</v>
       </c>
       <c r="D66" s="46" t="s">
@@ -6284,7 +6170,7 @@
       <c r="J66" s="46" t="s">
         <v>448</v>
       </c>
-      <c r="K66" s="88" t="s">
+      <c r="K66" s="73" t="s">
         <v>364</v>
       </c>
       <c r="L66" s="46">
@@ -6297,13 +6183,13 @@
       <c r="N66" s="46">
         <v>100</v>
       </c>
-      <c r="O66" s="59" t="s">
-        <v>414</v>
-      </c>
-      <c r="P66" s="60">
+      <c r="O66" s="58" t="s">
+        <v>414</v>
+      </c>
+      <c r="P66" s="59">
         <v>1.6999999999999999E-3</v>
       </c>
-      <c r="Q66" s="60">
+      <c r="Q66" s="59">
         <f t="shared" si="2"/>
         <v>0.16999999999999998</v>
       </c>
@@ -6316,7 +6202,7 @@
         <f t="shared" si="3"/>
         <v>58</v>
       </c>
-      <c r="C67" s="77" t="s">
+      <c r="C67" s="68" t="s">
         <v>394</v>
       </c>
       <c r="D67" s="50" t="s">
@@ -6328,19 +6214,19 @@
       <c r="F67" s="50" t="s">
         <v>220</v>
       </c>
-      <c r="G67" s="64" t="s">
+      <c r="G67" s="63" t="s">
         <v>271</v>
       </c>
       <c r="H67" s="50" t="s">
-        <v>493</v>
+        <v>492</v>
       </c>
       <c r="I67" s="50" t="s">
         <v>325</v>
       </c>
       <c r="J67" s="50" t="s">
-        <v>494</v>
-      </c>
-      <c r="K67" s="87" t="s">
+        <v>493</v>
+      </c>
+      <c r="K67" s="72" t="s">
         <v>365</v>
       </c>
       <c r="L67" s="50">
@@ -6353,18 +6239,18 @@
       <c r="N67" s="50">
         <v>20</v>
       </c>
-      <c r="O67" s="62" t="s">
-        <v>414</v>
-      </c>
-      <c r="P67" s="61">
+      <c r="O67" s="61" t="s">
+        <v>414</v>
+      </c>
+      <c r="P67" s="60">
         <v>2.93E-2</v>
       </c>
-      <c r="Q67" s="61">
+      <c r="Q67" s="60">
         <f t="shared" si="2"/>
         <v>0.58599999999999997</v>
       </c>
       <c r="R67" s="52"/>
-      <c r="S67" s="52"/>
+      <c r="S67" s="53"/>
     </row>
     <row r="68" spans="1:19" ht="24.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A68" s="1"/>
@@ -6372,7 +6258,7 @@
         <f t="shared" si="3"/>
         <v>59</v>
       </c>
-      <c r="C68" s="76" t="s">
+      <c r="C68" s="67" t="s">
         <v>394</v>
       </c>
       <c r="D68" s="46" t="s">
@@ -6396,7 +6282,7 @@
       <c r="J68" s="46" t="s">
         <v>449</v>
       </c>
-      <c r="K68" s="88" t="s">
+      <c r="K68" s="73" t="s">
         <v>366</v>
       </c>
       <c r="L68" s="46">
@@ -6409,13 +6295,13 @@
       <c r="N68" s="46">
         <v>100</v>
       </c>
-      <c r="O68" s="59" t="s">
-        <v>414</v>
-      </c>
-      <c r="P68" s="60">
+      <c r="O68" s="58" t="s">
+        <v>414</v>
+      </c>
+      <c r="P68" s="59">
         <v>1.4E-3</v>
       </c>
-      <c r="Q68" s="60">
+      <c r="Q68" s="59">
         <f t="shared" si="2"/>
         <v>0.13999999999999999</v>
       </c>
@@ -6428,7 +6314,7 @@
         <f t="shared" si="3"/>
         <v>60</v>
       </c>
-      <c r="C69" s="77" t="s">
+      <c r="C69" s="68" t="s">
         <v>394</v>
       </c>
       <c r="D69" s="50" t="s">
@@ -6452,7 +6338,7 @@
       <c r="J69" s="50" t="s">
         <v>450</v>
       </c>
-      <c r="K69" s="87" t="s">
+      <c r="K69" s="72" t="s">
         <v>367</v>
       </c>
       <c r="L69" s="50">
@@ -6465,18 +6351,18 @@
       <c r="N69" s="50">
         <v>100</v>
       </c>
-      <c r="O69" s="62" t="s">
-        <v>414</v>
-      </c>
-      <c r="P69" s="61">
+      <c r="O69" s="61" t="s">
+        <v>414</v>
+      </c>
+      <c r="P69" s="60">
         <v>1.5E-3</v>
       </c>
-      <c r="Q69" s="61">
+      <c r="Q69" s="60">
         <f t="shared" si="2"/>
         <v>0.15</v>
       </c>
       <c r="R69" s="52"/>
-      <c r="S69" s="52"/>
+      <c r="S69" s="53"/>
     </row>
     <row r="70" spans="1:19" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A70" s="1"/>
@@ -6484,7 +6370,7 @@
         <f t="shared" si="3"/>
         <v>61</v>
       </c>
-      <c r="C70" s="76" t="s">
+      <c r="C70" s="67" t="s">
         <v>394</v>
       </c>
       <c r="D70" s="46" t="s">
@@ -6508,7 +6394,7 @@
       <c r="J70" s="46" t="s">
         <v>451</v>
       </c>
-      <c r="K70" s="88" t="s">
+      <c r="K70" s="73" t="s">
         <v>368</v>
       </c>
       <c r="L70" s="46">
@@ -6521,13 +6407,13 @@
       <c r="N70" s="46">
         <v>100</v>
       </c>
-      <c r="O70" s="59" t="s">
-        <v>414</v>
-      </c>
-      <c r="P70" s="60">
+      <c r="O70" s="58" t="s">
+        <v>414</v>
+      </c>
+      <c r="P70" s="59">
         <v>1.4E-3</v>
       </c>
-      <c r="Q70" s="60">
+      <c r="Q70" s="59">
         <f t="shared" si="2"/>
         <v>0.13999999999999999</v>
       </c>
@@ -6540,7 +6426,7 @@
         <f t="shared" si="3"/>
         <v>62</v>
       </c>
-      <c r="C71" s="77" t="s">
+      <c r="C71" s="68" t="s">
         <v>394</v>
       </c>
       <c r="D71" s="50" t="s">
@@ -6564,7 +6450,7 @@
       <c r="J71" s="50" t="s">
         <v>452</v>
       </c>
-      <c r="K71" s="87" t="s">
+      <c r="K71" s="72" t="s">
         <v>369</v>
       </c>
       <c r="L71" s="50">
@@ -6577,18 +6463,18 @@
       <c r="N71" s="50">
         <v>100</v>
       </c>
-      <c r="O71" s="62" t="s">
-        <v>414</v>
-      </c>
-      <c r="P71" s="61">
+      <c r="O71" s="61" t="s">
+        <v>414</v>
+      </c>
+      <c r="P71" s="60">
         <v>1.2999999999999999E-3</v>
       </c>
-      <c r="Q71" s="61">
+      <c r="Q71" s="60">
         <f t="shared" si="2"/>
         <v>0.13</v>
       </c>
       <c r="R71" s="52"/>
-      <c r="S71" s="52"/>
+      <c r="S71" s="53"/>
     </row>
     <row r="72" spans="1:19" ht="24.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A72" s="1"/>
@@ -6596,7 +6482,7 @@
         <f t="shared" si="3"/>
         <v>63</v>
       </c>
-      <c r="C72" s="76" t="s">
+      <c r="C72" s="67" t="s">
         <v>394</v>
       </c>
       <c r="D72" s="46" t="s">
@@ -6620,7 +6506,7 @@
       <c r="J72" s="46" t="s">
         <v>453</v>
       </c>
-      <c r="K72" s="88" t="s">
+      <c r="K72" s="73" t="s">
         <v>370</v>
       </c>
       <c r="L72" s="46">
@@ -6633,13 +6519,13 @@
       <c r="N72" s="46">
         <v>100</v>
       </c>
-      <c r="O72" s="59" t="s">
-        <v>414</v>
-      </c>
-      <c r="P72" s="60">
+      <c r="O72" s="58" t="s">
+        <v>414</v>
+      </c>
+      <c r="P72" s="59">
         <v>1.1999999999999999E-3</v>
       </c>
-      <c r="Q72" s="60">
+      <c r="Q72" s="59">
         <f t="shared" si="2"/>
         <v>0.12</v>
       </c>
@@ -6652,7 +6538,7 @@
         <f t="shared" si="3"/>
         <v>64</v>
       </c>
-      <c r="C73" s="77" t="s">
+      <c r="C73" s="68" t="s">
         <v>394</v>
       </c>
       <c r="D73" s="50" t="s">
@@ -6676,7 +6562,7 @@
       <c r="J73" s="50" t="s">
         <v>454</v>
       </c>
-      <c r="K73" s="87" t="s">
+      <c r="K73" s="72" t="s">
         <v>371</v>
       </c>
       <c r="L73" s="50">
@@ -6689,18 +6575,18 @@
       <c r="N73" s="50">
         <v>100</v>
       </c>
-      <c r="O73" s="62" t="s">
-        <v>414</v>
-      </c>
-      <c r="P73" s="61">
+      <c r="O73" s="61" t="s">
+        <v>414</v>
+      </c>
+      <c r="P73" s="60">
         <v>4.0000000000000001E-3</v>
       </c>
-      <c r="Q73" s="61">
+      <c r="Q73" s="60">
         <f t="shared" si="2"/>
         <v>0.4</v>
       </c>
       <c r="R73" s="52"/>
-      <c r="S73" s="52"/>
+      <c r="S73" s="53"/>
     </row>
     <row r="74" spans="1:19" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A74" s="1"/>
@@ -6708,7 +6594,7 @@
         <f t="shared" ref="B74:B101" si="4">ROW(B74) - ROW($B$9)</f>
         <v>65</v>
       </c>
-      <c r="C74" s="76" t="s">
+      <c r="C74" s="67" t="s">
         <v>394</v>
       </c>
       <c r="D74" s="46" t="s">
@@ -6721,19 +6607,19 @@
         <v>220</v>
       </c>
       <c r="G74" s="47" t="s">
+        <v>503</v>
+      </c>
+      <c r="H74" s="46" t="s">
+        <v>410</v>
+      </c>
+      <c r="I74" s="46" t="s">
         <v>504</v>
       </c>
-      <c r="H74" s="46" t="s">
-        <v>410</v>
-      </c>
-      <c r="I74" s="46" t="s">
+      <c r="J74" s="46" t="s">
         <v>505</v>
       </c>
-      <c r="J74" s="46" t="s">
-        <v>506</v>
-      </c>
-      <c r="K74" s="88" t="s">
-        <v>503</v>
+      <c r="K74" s="73" t="s">
+        <v>502</v>
       </c>
       <c r="L74" s="46">
         <v>1</v>
@@ -6745,17 +6631,17 @@
       <c r="N74" s="46">
         <v>100</v>
       </c>
-      <c r="O74" s="59" t="s">
-        <v>414</v>
-      </c>
-      <c r="P74" s="60">
+      <c r="O74" s="58" t="s">
+        <v>414</v>
+      </c>
+      <c r="P74" s="59">
         <v>1.6000000000000001E-3</v>
       </c>
-      <c r="Q74" s="60">
+      <c r="Q74" s="59">
         <f t="shared" si="2"/>
         <v>0.16</v>
       </c>
-      <c r="R74" s="81"/>
+      <c r="R74" s="48"/>
       <c r="S74" s="48"/>
     </row>
     <row r="75" spans="1:19" ht="36.75" thickBot="1" x14ac:dyDescent="0.3">
@@ -6764,7 +6650,7 @@
         <f t="shared" si="4"/>
         <v>66</v>
       </c>
-      <c r="C75" s="77" t="s">
+      <c r="C75" s="68" t="s">
         <v>394</v>
       </c>
       <c r="D75" s="50" t="s">
@@ -6776,19 +6662,19 @@
       <c r="F75" s="50" t="s">
         <v>220</v>
       </c>
-      <c r="G75" s="51" t="s">
+      <c r="G75" s="63" t="s">
         <v>278</v>
       </c>
       <c r="H75" s="50" t="s">
-        <v>410</v>
+        <v>539</v>
       </c>
       <c r="I75" s="50" t="s">
         <v>298</v>
       </c>
       <c r="J75" s="50" t="s">
-        <v>455</v>
-      </c>
-      <c r="K75" s="87" t="s">
+        <v>540</v>
+      </c>
+      <c r="K75" s="72" t="s">
         <v>372</v>
       </c>
       <c r="L75" s="50">
@@ -6801,18 +6687,18 @@
       <c r="N75" s="50">
         <v>100</v>
       </c>
-      <c r="O75" s="62" t="s">
-        <v>414</v>
-      </c>
-      <c r="P75" s="61">
-        <v>2.5999999999999999E-3</v>
-      </c>
-      <c r="Q75" s="61">
+      <c r="O75" s="61" t="s">
+        <v>414</v>
+      </c>
+      <c r="P75" s="60">
+        <v>8.9999999999999998E-4</v>
+      </c>
+      <c r="Q75" s="60">
         <f t="shared" ref="Q75:Q101" si="6">P75*N75</f>
-        <v>0.26</v>
+        <v>0.09</v>
       </c>
       <c r="R75" s="52"/>
-      <c r="S75" s="52"/>
+      <c r="S75" s="53"/>
     </row>
     <row r="76" spans="1:19" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A76" s="1"/>
@@ -6820,7 +6706,7 @@
         <f t="shared" si="4"/>
         <v>67</v>
       </c>
-      <c r="C76" s="76" t="s">
+      <c r="C76" s="67" t="s">
         <v>394</v>
       </c>
       <c r="D76" s="46" t="s">
@@ -6842,9 +6728,9 @@
         <v>298</v>
       </c>
       <c r="J76" s="46" t="s">
-        <v>456</v>
-      </c>
-      <c r="K76" s="88" t="s">
+        <v>455</v>
+      </c>
+      <c r="K76" s="73" t="s">
         <v>373</v>
       </c>
       <c r="L76" s="46">
@@ -6857,13 +6743,13 @@
       <c r="N76" s="46">
         <v>100</v>
       </c>
-      <c r="O76" s="59" t="s">
-        <v>414</v>
-      </c>
-      <c r="P76" s="60">
+      <c r="O76" s="58" t="s">
+        <v>414</v>
+      </c>
+      <c r="P76" s="59">
         <v>2.2000000000000001E-3</v>
       </c>
-      <c r="Q76" s="60">
+      <c r="Q76" s="59">
         <f t="shared" si="6"/>
         <v>0.22</v>
       </c>
@@ -6876,7 +6762,7 @@
         <f t="shared" si="4"/>
         <v>68</v>
       </c>
-      <c r="C77" s="77" t="s">
+      <c r="C77" s="68" t="s">
         <v>394</v>
       </c>
       <c r="D77" s="50" t="s">
@@ -6898,9 +6784,9 @@
         <v>298</v>
       </c>
       <c r="J77" s="50" t="s">
-        <v>457</v>
-      </c>
-      <c r="K77" s="87" t="s">
+        <v>456</v>
+      </c>
+      <c r="K77" s="72" t="s">
         <v>374</v>
       </c>
       <c r="L77" s="50">
@@ -6913,18 +6799,18 @@
       <c r="N77" s="50">
         <v>100</v>
       </c>
-      <c r="O77" s="62" t="s">
-        <v>414</v>
-      </c>
-      <c r="P77" s="61">
+      <c r="O77" s="61" t="s">
+        <v>414</v>
+      </c>
+      <c r="P77" s="60">
         <v>1.5E-3</v>
       </c>
-      <c r="Q77" s="61">
+      <c r="Q77" s="60">
         <f t="shared" si="6"/>
         <v>0.15</v>
       </c>
       <c r="R77" s="52"/>
-      <c r="S77" s="52"/>
+      <c r="S77" s="53"/>
     </row>
     <row r="78" spans="1:19" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A78" s="1"/>
@@ -6932,7 +6818,7 @@
         <f t="shared" si="4"/>
         <v>69</v>
       </c>
-      <c r="C78" s="76" t="s">
+      <c r="C78" s="67" t="s">
         <v>394</v>
       </c>
       <c r="D78" s="46" t="s">
@@ -6944,19 +6830,19 @@
       <c r="F78" s="46" t="s">
         <v>221</v>
       </c>
-      <c r="G78" s="63" t="s">
+      <c r="G78" s="47" t="s">
         <v>281</v>
       </c>
       <c r="H78" s="46" t="s">
-        <v>507</v>
+        <v>506</v>
       </c>
       <c r="I78" s="46" t="s">
         <v>325</v>
       </c>
       <c r="J78" s="46" t="s">
-        <v>508</v>
-      </c>
-      <c r="K78" s="88" t="s">
+        <v>507</v>
+      </c>
+      <c r="K78" s="73" t="s">
         <v>375</v>
       </c>
       <c r="L78" s="46">
@@ -6969,13 +6855,13 @@
       <c r="N78" s="46">
         <v>50</v>
       </c>
-      <c r="O78" s="59" t="s">
-        <v>414</v>
-      </c>
-      <c r="P78" s="60">
+      <c r="O78" s="58" t="s">
+        <v>414</v>
+      </c>
+      <c r="P78" s="59">
         <v>6.4000000000000003E-3</v>
       </c>
-      <c r="Q78" s="60">
+      <c r="Q78" s="59">
         <f t="shared" si="6"/>
         <v>0.32</v>
       </c>
@@ -6988,7 +6874,7 @@
         <f t="shared" si="4"/>
         <v>70</v>
       </c>
-      <c r="C79" s="77" t="s">
+      <c r="C79" s="68" t="s">
         <v>394</v>
       </c>
       <c r="D79" s="50" t="s">
@@ -7010,9 +6896,9 @@
         <v>298</v>
       </c>
       <c r="J79" s="50" t="s">
-        <v>458</v>
-      </c>
-      <c r="K79" s="87" t="s">
+        <v>457</v>
+      </c>
+      <c r="K79" s="72" t="s">
         <v>376</v>
       </c>
       <c r="L79" s="50">
@@ -7025,18 +6911,18 @@
       <c r="N79" s="50">
         <v>100</v>
       </c>
-      <c r="O79" s="62" t="s">
-        <v>414</v>
-      </c>
-      <c r="P79" s="61">
+      <c r="O79" s="61" t="s">
+        <v>414</v>
+      </c>
+      <c r="P79" s="60">
         <v>1.4E-3</v>
       </c>
-      <c r="Q79" s="61">
+      <c r="Q79" s="60">
         <f t="shared" si="6"/>
         <v>0.13999999999999999</v>
       </c>
       <c r="R79" s="52"/>
-      <c r="S79" s="52"/>
+      <c r="S79" s="53"/>
     </row>
     <row r="80" spans="1:19" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A80" s="1"/>
@@ -7044,7 +6930,7 @@
         <f t="shared" si="4"/>
         <v>71</v>
       </c>
-      <c r="C80" s="76" t="s">
+      <c r="C80" s="67" t="s">
         <v>394</v>
       </c>
       <c r="D80" s="46" t="s">
@@ -7066,9 +6952,9 @@
         <v>298</v>
       </c>
       <c r="J80" s="46" t="s">
-        <v>459</v>
-      </c>
-      <c r="K80" s="88" t="s">
+        <v>458</v>
+      </c>
+      <c r="K80" s="73" t="s">
         <v>377</v>
       </c>
       <c r="L80" s="46">
@@ -7081,13 +6967,13 @@
       <c r="N80" s="46">
         <v>100</v>
       </c>
-      <c r="O80" s="59" t="s">
-        <v>414</v>
-      </c>
-      <c r="P80" s="60">
+      <c r="O80" s="58" t="s">
+        <v>414</v>
+      </c>
+      <c r="P80" s="59">
         <v>1.5E-3</v>
       </c>
-      <c r="Q80" s="60">
+      <c r="Q80" s="59">
         <f t="shared" si="6"/>
         <v>0.15</v>
       </c>
@@ -7100,44 +6986,44 @@
         <f t="shared" si="4"/>
         <v>72</v>
       </c>
-      <c r="C81" s="76" t="s">
+      <c r="C81" s="68" t="s">
         <v>394</v>
       </c>
-      <c r="D81" s="46" t="s">
+      <c r="D81" s="50" t="s">
         <v>77</v>
       </c>
-      <c r="E81" s="47" t="s">
+      <c r="E81" s="51" t="s">
         <v>168</v>
       </c>
-      <c r="F81" s="46" t="s">
+      <c r="F81" s="50" t="s">
         <v>220</v>
       </c>
-      <c r="G81" s="47" t="s">
+      <c r="G81" s="51" t="s">
         <v>284</v>
       </c>
-      <c r="H81" s="46" t="s">
-        <v>410</v>
-      </c>
-      <c r="I81" s="46" t="s">
+      <c r="H81" s="50" t="s">
+        <v>410</v>
+      </c>
+      <c r="I81" s="50" t="s">
         <v>298</v>
       </c>
-      <c r="J81" s="46" t="s">
-        <v>460</v>
-      </c>
-      <c r="K81" s="88" t="s">
+      <c r="J81" s="50" t="s">
+        <v>459</v>
+      </c>
+      <c r="K81" s="72" t="s">
         <v>378</v>
       </c>
-      <c r="L81" s="46">
+      <c r="L81" s="50">
         <v>2</v>
       </c>
-      <c r="M81" s="46">
+      <c r="M81" s="50">
         <f t="shared" si="5"/>
         <v>10</v>
       </c>
-      <c r="N81" s="46">
+      <c r="N81" s="50">
         <v>100</v>
       </c>
-      <c r="O81" s="59" t="s">
+      <c r="O81" s="61" t="s">
         <v>414</v>
       </c>
       <c r="P81" s="60">
@@ -7147,8 +7033,8 @@
         <f t="shared" si="6"/>
         <v>0.13999999999999999</v>
       </c>
-      <c r="R81" s="48"/>
-      <c r="S81" s="48"/>
+      <c r="R81" s="52"/>
+      <c r="S81" s="53"/>
     </row>
     <row r="82" spans="1:20" ht="24.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A82" s="1"/>
@@ -7156,55 +7042,55 @@
         <f t="shared" si="4"/>
         <v>73</v>
       </c>
-      <c r="C82" s="77" t="s">
+      <c r="C82" s="67" t="s">
         <v>394</v>
       </c>
-      <c r="D82" s="50" t="s">
+      <c r="D82" s="46" t="s">
         <v>78</v>
       </c>
-      <c r="E82" s="51" t="s">
+      <c r="E82" s="47" t="s">
         <v>169</v>
       </c>
-      <c r="F82" s="50" t="s">
+      <c r="F82" s="46" t="s">
         <v>220</v>
       </c>
-      <c r="G82" s="51" t="s">
+      <c r="G82" s="47" t="s">
         <v>285</v>
       </c>
-      <c r="H82" s="50" t="s">
-        <v>410</v>
-      </c>
-      <c r="I82" s="50" t="s">
+      <c r="H82" s="46" t="s">
+        <v>410</v>
+      </c>
+      <c r="I82" s="46" t="s">
         <v>298</v>
       </c>
-      <c r="J82" s="50" t="s">
-        <v>461</v>
-      </c>
-      <c r="K82" s="87" t="s">
+      <c r="J82" s="46" t="s">
+        <v>460</v>
+      </c>
+      <c r="K82" s="73" t="s">
         <v>379</v>
       </c>
-      <c r="L82" s="50">
+      <c r="L82" s="46">
         <v>2</v>
       </c>
-      <c r="M82" s="50">
+      <c r="M82" s="46">
         <f t="shared" si="5"/>
         <v>10</v>
       </c>
-      <c r="N82" s="50">
+      <c r="N82" s="46">
         <v>100</v>
       </c>
-      <c r="O82" s="62" t="s">
-        <v>414</v>
-      </c>
-      <c r="P82" s="61">
+      <c r="O82" s="58" t="s">
+        <v>414</v>
+      </c>
+      <c r="P82" s="59">
         <v>1.5E-3</v>
       </c>
-      <c r="Q82" s="61">
+      <c r="Q82" s="59">
         <f t="shared" si="6"/>
         <v>0.15</v>
       </c>
-      <c r="R82" s="52"/>
-      <c r="S82" s="52"/>
+      <c r="R82" s="48"/>
+      <c r="S82" s="48"/>
     </row>
     <row r="83" spans="1:20" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A83" s="1"/>
@@ -7212,44 +7098,44 @@
         <f t="shared" si="4"/>
         <v>74</v>
       </c>
-      <c r="C83" s="76" t="s">
+      <c r="C83" s="68" t="s">
         <v>394</v>
       </c>
-      <c r="D83" s="46" t="s">
+      <c r="D83" s="50" t="s">
         <v>79</v>
       </c>
-      <c r="E83" s="47" t="s">
+      <c r="E83" s="51" t="s">
         <v>170</v>
       </c>
-      <c r="F83" s="46" t="s">
+      <c r="F83" s="50" t="s">
         <v>222</v>
       </c>
-      <c r="G83" s="47" t="s">
+      <c r="G83" s="51" t="s">
+        <v>494</v>
+      </c>
+      <c r="H83" s="50" t="s">
+        <v>410</v>
+      </c>
+      <c r="I83" s="50" t="s">
+        <v>328</v>
+      </c>
+      <c r="J83" s="50" t="s">
         <v>495</v>
       </c>
-      <c r="H83" s="46" t="s">
-        <v>410</v>
-      </c>
-      <c r="I83" s="46" t="s">
-        <v>328</v>
-      </c>
-      <c r="J83" s="46" t="s">
-        <v>496</v>
-      </c>
-      <c r="K83" s="88" t="s">
+      <c r="K83" s="72" t="s">
         <v>380</v>
       </c>
-      <c r="L83" s="46">
+      <c r="L83" s="50">
         <v>2</v>
       </c>
-      <c r="M83" s="46">
+      <c r="M83" s="50">
         <f t="shared" si="5"/>
         <v>10</v>
       </c>
-      <c r="N83" s="46">
+      <c r="N83" s="50">
         <v>50</v>
       </c>
-      <c r="O83" s="59" t="s">
+      <c r="O83" s="61" t="s">
         <v>414</v>
       </c>
       <c r="P83" s="60">
@@ -7259,8 +7145,8 @@
         <f t="shared" si="6"/>
         <v>0.56499999999999995</v>
       </c>
-      <c r="R83" s="48"/>
-      <c r="S83" s="48"/>
+      <c r="R83" s="52"/>
+      <c r="S83" s="53"/>
     </row>
     <row r="84" spans="1:20" ht="24.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A84" s="1"/>
@@ -7268,55 +7154,55 @@
         <f t="shared" si="4"/>
         <v>75</v>
       </c>
-      <c r="C84" s="77" t="s">
+      <c r="C84" s="67" t="s">
         <v>394</v>
       </c>
-      <c r="D84" s="50" t="s">
+      <c r="D84" s="46" t="s">
         <v>80</v>
       </c>
-      <c r="E84" s="51" t="s">
+      <c r="E84" s="47" t="s">
         <v>171</v>
       </c>
-      <c r="F84" s="50" t="s">
+      <c r="F84" s="46" t="s">
         <v>220</v>
       </c>
-      <c r="G84" s="51" t="s">
+      <c r="G84" s="47" t="s">
         <v>286</v>
       </c>
-      <c r="H84" s="50" t="s">
-        <v>410</v>
-      </c>
-      <c r="I84" s="50" t="s">
+      <c r="H84" s="46" t="s">
+        <v>410</v>
+      </c>
+      <c r="I84" s="46" t="s">
         <v>298</v>
       </c>
-      <c r="J84" s="50" t="s">
-        <v>462</v>
-      </c>
-      <c r="K84" s="87" t="s">
+      <c r="J84" s="46" t="s">
+        <v>461</v>
+      </c>
+      <c r="K84" s="73" t="s">
         <v>381</v>
       </c>
-      <c r="L84" s="50">
+      <c r="L84" s="46">
         <v>2</v>
       </c>
-      <c r="M84" s="50">
+      <c r="M84" s="46">
         <f t="shared" si="5"/>
         <v>10</v>
       </c>
-      <c r="N84" s="50">
+      <c r="N84" s="46">
         <v>100</v>
       </c>
-      <c r="O84" s="62" t="s">
-        <v>414</v>
-      </c>
-      <c r="P84" s="61">
+      <c r="O84" s="58" t="s">
+        <v>414</v>
+      </c>
+      <c r="P84" s="59">
         <v>1.2999999999999999E-3</v>
       </c>
-      <c r="Q84" s="61">
+      <c r="Q84" s="59">
         <f t="shared" si="6"/>
         <v>0.13</v>
       </c>
-      <c r="R84" s="52"/>
-      <c r="S84" s="52"/>
+      <c r="R84" s="48"/>
+      <c r="S84" s="48"/>
     </row>
     <row r="85" spans="1:20" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A85" s="1"/>
@@ -7324,44 +7210,44 @@
         <f t="shared" si="4"/>
         <v>76</v>
       </c>
-      <c r="C85" s="76" t="s">
+      <c r="C85" s="68" t="s">
         <v>394</v>
       </c>
-      <c r="D85" s="46" t="s">
+      <c r="D85" s="50" t="s">
         <v>81</v>
       </c>
-      <c r="E85" s="47" t="s">
+      <c r="E85" s="51" t="s">
         <v>172</v>
       </c>
-      <c r="F85" s="46" t="s">
+      <c r="F85" s="50" t="s">
         <v>223</v>
       </c>
       <c r="G85" s="63" t="s">
         <v>287</v>
       </c>
-      <c r="H85" s="46" t="s">
+      <c r="H85" s="50" t="s">
+        <v>496</v>
+      </c>
+      <c r="I85" s="50" t="s">
+        <v>329</v>
+      </c>
+      <c r="J85" s="50" t="s">
         <v>497</v>
       </c>
-      <c r="I85" s="46" t="s">
-        <v>329</v>
-      </c>
-      <c r="J85" s="46" t="s">
-        <v>498</v>
-      </c>
-      <c r="K85" s="88" t="s">
+      <c r="K85" s="72" t="s">
         <v>362</v>
       </c>
-      <c r="L85" s="46">
+      <c r="L85" s="50">
         <v>1</v>
       </c>
-      <c r="M85" s="46">
+      <c r="M85" s="50">
         <f t="shared" si="5"/>
         <v>5</v>
       </c>
-      <c r="N85" s="46">
+      <c r="N85" s="50">
         <v>20</v>
       </c>
-      <c r="O85" s="59" t="s">
+      <c r="O85" s="61" t="s">
         <v>414</v>
       </c>
       <c r="P85" s="60">
@@ -7371,8 +7257,8 @@
         <f t="shared" si="6"/>
         <v>0.65</v>
       </c>
-      <c r="R85" s="48"/>
-      <c r="S85" s="48"/>
+      <c r="R85" s="52"/>
+      <c r="S85" s="53"/>
     </row>
     <row r="86" spans="1:20" ht="36.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A86" s="1"/>
@@ -7380,56 +7266,56 @@
         <f t="shared" si="4"/>
         <v>77</v>
       </c>
-      <c r="C86" s="77" t="s">
+      <c r="C86" s="67" t="s">
         <v>224</v>
       </c>
-      <c r="D86" s="50" t="s">
+      <c r="D86" s="46" t="s">
         <v>82</v>
       </c>
-      <c r="E86" s="51" t="s">
+      <c r="E86" s="47" t="s">
         <v>173</v>
       </c>
-      <c r="F86" s="50" t="s">
+      <c r="F86" s="46" t="s">
         <v>408</v>
       </c>
-      <c r="G86" s="51" t="s">
-        <v>410</v>
-      </c>
-      <c r="H86" s="50" t="s">
-        <v>410</v>
-      </c>
-      <c r="I86" s="51" t="s">
-        <v>410</v>
-      </c>
-      <c r="J86" s="50" t="s">
-        <v>410</v>
-      </c>
-      <c r="K86" s="87" t="s">
-        <v>410</v>
-      </c>
-      <c r="L86" s="50">
+      <c r="G86" s="47" t="s">
+        <v>410</v>
+      </c>
+      <c r="H86" s="46" t="s">
+        <v>410</v>
+      </c>
+      <c r="I86" s="46" t="s">
+        <v>410</v>
+      </c>
+      <c r="J86" s="46" t="s">
+        <v>410</v>
+      </c>
+      <c r="K86" s="73" t="s">
+        <v>410</v>
+      </c>
+      <c r="L86" s="46">
         <v>18</v>
       </c>
-      <c r="M86" s="50">
+      <c r="M86" s="46">
         <f t="shared" si="5"/>
         <v>90</v>
       </c>
-      <c r="N86" s="66" t="s">
-        <v>410</v>
-      </c>
-      <c r="O86" s="67" t="s">
-        <v>410</v>
-      </c>
-      <c r="P86" s="66" t="s">
-        <v>410</v>
-      </c>
-      <c r="Q86" s="67" t="s">
-        <v>410</v>
-      </c>
-      <c r="R86" s="79" t="s">
-        <v>521</v>
-      </c>
-      <c r="S86" s="67" t="s">
+      <c r="N86" s="46" t="s">
+        <v>410</v>
+      </c>
+      <c r="O86" s="58" t="s">
+        <v>410</v>
+      </c>
+      <c r="P86" s="59" t="s">
+        <v>410</v>
+      </c>
+      <c r="Q86" s="59" t="s">
+        <v>410</v>
+      </c>
+      <c r="R86" s="69" t="s">
+        <v>519</v>
+      </c>
+      <c r="S86" s="48" t="s">
         <v>410</v>
       </c>
     </row>
@@ -7439,44 +7325,44 @@
         <f t="shared" si="4"/>
         <v>78</v>
       </c>
-      <c r="C87" s="76" t="s">
+      <c r="C87" s="68" t="s">
         <v>395</v>
       </c>
-      <c r="D87" s="46" t="s">
+      <c r="D87" s="50" t="s">
         <v>83</v>
       </c>
-      <c r="E87" s="47" t="s">
+      <c r="E87" s="51" t="s">
         <v>174</v>
       </c>
-      <c r="F87" s="46" t="s">
+      <c r="F87" s="50" t="s">
         <v>408</v>
       </c>
-      <c r="G87" s="47" t="s">
+      <c r="G87" s="51" t="s">
         <v>225</v>
       </c>
-      <c r="H87" s="46" t="s">
-        <v>410</v>
-      </c>
-      <c r="I87" s="46" t="s">
+      <c r="H87" s="50" t="s">
+        <v>410</v>
+      </c>
+      <c r="I87" s="50" t="s">
         <v>330</v>
       </c>
-      <c r="J87" s="46" t="s">
-        <v>463</v>
-      </c>
-      <c r="K87" s="88" t="s">
-        <v>410</v>
-      </c>
-      <c r="L87" s="46">
+      <c r="J87" s="50" t="s">
+        <v>462</v>
+      </c>
+      <c r="K87" s="72" t="s">
+        <v>410</v>
+      </c>
+      <c r="L87" s="50">
         <v>7</v>
       </c>
-      <c r="M87" s="46">
+      <c r="M87" s="50">
         <f t="shared" si="5"/>
         <v>35</v>
       </c>
-      <c r="N87" s="46">
+      <c r="N87" s="50">
         <v>37</v>
       </c>
-      <c r="O87" s="59" t="s">
+      <c r="O87" s="61" t="s">
         <v>414</v>
       </c>
       <c r="P87" s="60">
@@ -7486,8 +7372,8 @@
         <f t="shared" si="6"/>
         <v>27.557600000000001</v>
       </c>
-      <c r="R87" s="48"/>
-      <c r="S87" s="48"/>
+      <c r="R87" s="52"/>
+      <c r="S87" s="53"/>
     </row>
     <row r="88" spans="1:20" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A88" s="1"/>
@@ -7495,56 +7381,56 @@
         <f t="shared" si="4"/>
         <v>79</v>
       </c>
-      <c r="C88" s="77" t="s">
+      <c r="C88" s="67" t="s">
         <v>396</v>
       </c>
-      <c r="D88" s="50" t="s">
+      <c r="D88" s="46" t="s">
         <v>84</v>
       </c>
-      <c r="E88" s="51" t="s">
+      <c r="E88" s="47" t="s">
         <v>175</v>
       </c>
-      <c r="F88" s="50" t="s">
+      <c r="F88" s="46" t="s">
         <v>226</v>
       </c>
-      <c r="G88" s="51" t="s">
+      <c r="G88" s="47" t="s">
         <v>288</v>
       </c>
-      <c r="H88" s="50" t="s">
-        <v>410</v>
-      </c>
-      <c r="I88" s="50" t="s">
+      <c r="H88" s="46" t="s">
+        <v>410</v>
+      </c>
+      <c r="I88" s="46" t="s">
         <v>331</v>
       </c>
-      <c r="J88" s="50" t="s">
-        <v>410</v>
-      </c>
-      <c r="K88" s="87" t="s">
-        <v>410</v>
-      </c>
-      <c r="L88" s="50">
+      <c r="J88" s="46" t="s">
+        <v>410</v>
+      </c>
+      <c r="K88" s="73" t="s">
+        <v>410</v>
+      </c>
+      <c r="L88" s="46">
         <v>2</v>
       </c>
-      <c r="M88" s="50">
+      <c r="M88" s="46">
         <f t="shared" si="5"/>
         <v>10</v>
       </c>
-      <c r="N88" s="50">
+      <c r="N88" s="46">
         <v>12</v>
       </c>
-      <c r="O88" s="62" t="s">
+      <c r="O88" s="58" t="s">
         <v>408</v>
       </c>
-      <c r="P88" s="61">
+      <c r="P88" s="59">
         <v>10.59</v>
       </c>
-      <c r="Q88" s="61">
+      <c r="Q88" s="59">
         <f t="shared" si="6"/>
         <v>127.08</v>
       </c>
-      <c r="R88" s="105"/>
-      <c r="S88" s="52"/>
-      <c r="T88" s="72"/>
+      <c r="R88" s="48"/>
+      <c r="S88" s="48"/>
+      <c r="T88" s="64"/>
     </row>
     <row r="89" spans="1:20" ht="36.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A89" s="1"/>
@@ -7552,44 +7438,44 @@
         <f t="shared" si="4"/>
         <v>80</v>
       </c>
-      <c r="C89" s="76" t="s">
+      <c r="C89" s="68" t="s">
         <v>396</v>
       </c>
-      <c r="D89" s="46" t="s">
+      <c r="D89" s="50" t="s">
         <v>85</v>
       </c>
-      <c r="E89" s="47" t="s">
+      <c r="E89" s="51" t="s">
         <v>176</v>
       </c>
-      <c r="F89" s="46" t="s">
+      <c r="F89" s="50" t="s">
         <v>226</v>
       </c>
-      <c r="G89" s="47" t="s">
+      <c r="G89" s="51" t="s">
         <v>289</v>
       </c>
-      <c r="H89" s="46" t="s">
-        <v>410</v>
-      </c>
-      <c r="I89" s="46" t="s">
+      <c r="H89" s="50" t="s">
+        <v>410</v>
+      </c>
+      <c r="I89" s="50" t="s">
         <v>332</v>
       </c>
-      <c r="J89" s="46" t="s">
-        <v>509</v>
-      </c>
-      <c r="K89" s="88" t="s">
-        <v>410</v>
-      </c>
-      <c r="L89" s="46">
+      <c r="J89" s="50" t="s">
+        <v>508</v>
+      </c>
+      <c r="K89" s="72" t="s">
+        <v>410</v>
+      </c>
+      <c r="L89" s="50">
         <v>1</v>
       </c>
-      <c r="M89" s="46">
+      <c r="M89" s="50">
         <f t="shared" si="5"/>
         <v>5</v>
       </c>
-      <c r="N89" s="46">
+      <c r="N89" s="50">
         <v>6</v>
       </c>
-      <c r="O89" s="59" t="s">
+      <c r="O89" s="61" t="s">
         <v>414</v>
       </c>
       <c r="P89" s="60">
@@ -7599,8 +7485,8 @@
         <f t="shared" si="6"/>
         <v>2.8242000000000003</v>
       </c>
-      <c r="R89" s="48"/>
-      <c r="S89" s="48"/>
+      <c r="R89" s="52"/>
+      <c r="S89" s="53"/>
     </row>
     <row r="90" spans="1:20" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A90" s="1"/>
@@ -7608,55 +7494,55 @@
         <f t="shared" si="4"/>
         <v>81</v>
       </c>
-      <c r="C90" s="77" t="s">
+      <c r="C90" s="67" t="s">
         <v>396</v>
       </c>
-      <c r="D90" s="50" t="s">
+      <c r="D90" s="46" t="s">
         <v>86</v>
       </c>
-      <c r="E90" s="51" t="s">
+      <c r="E90" s="47" t="s">
         <v>177</v>
       </c>
-      <c r="F90" s="50" t="s">
+      <c r="F90" s="46" t="s">
         <v>227</v>
       </c>
-      <c r="G90" s="51" t="s">
+      <c r="G90" s="47" t="s">
         <v>290</v>
       </c>
-      <c r="H90" s="50" t="s">
-        <v>410</v>
-      </c>
-      <c r="I90" s="50" t="s">
+      <c r="H90" s="46" t="s">
+        <v>410</v>
+      </c>
+      <c r="I90" s="46" t="s">
         <v>332</v>
       </c>
-      <c r="J90" s="50" t="s">
-        <v>464</v>
-      </c>
-      <c r="K90" s="87" t="s">
-        <v>410</v>
-      </c>
-      <c r="L90" s="50">
+      <c r="J90" s="46" t="s">
+        <v>463</v>
+      </c>
+      <c r="K90" s="73" t="s">
+        <v>410</v>
+      </c>
+      <c r="L90" s="46">
         <v>1</v>
       </c>
-      <c r="M90" s="50">
+      <c r="M90" s="46">
         <f t="shared" si="5"/>
         <v>5</v>
       </c>
-      <c r="N90" s="50">
+      <c r="N90" s="46">
         <v>6</v>
       </c>
-      <c r="O90" s="62" t="s">
-        <v>414</v>
-      </c>
-      <c r="P90" s="61">
+      <c r="O90" s="58" t="s">
+        <v>414</v>
+      </c>
+      <c r="P90" s="59">
         <v>1.0368999999999999</v>
       </c>
-      <c r="Q90" s="61">
+      <c r="Q90" s="59">
         <f t="shared" si="6"/>
         <v>6.2213999999999992</v>
       </c>
-      <c r="R90" s="52"/>
-      <c r="S90" s="52"/>
+      <c r="R90" s="48"/>
+      <c r="S90" s="48"/>
     </row>
     <row r="91" spans="1:20" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A91" s="1"/>
@@ -7664,44 +7550,44 @@
         <f t="shared" si="4"/>
         <v>82</v>
       </c>
-      <c r="C91" s="76" t="s">
+      <c r="C91" s="68" t="s">
         <v>396</v>
       </c>
-      <c r="D91" s="46" t="s">
+      <c r="D91" s="50" t="s">
         <v>87</v>
       </c>
-      <c r="E91" s="47" t="s">
+      <c r="E91" s="51" t="s">
         <v>178</v>
       </c>
-      <c r="F91" s="46" t="s">
+      <c r="F91" s="50" t="s">
         <v>228</v>
       </c>
-      <c r="G91" s="47" t="s">
+      <c r="G91" s="51" t="s">
         <v>291</v>
       </c>
-      <c r="H91" s="46" t="s">
-        <v>410</v>
-      </c>
-      <c r="I91" s="46" t="s">
+      <c r="H91" s="50" t="s">
+        <v>410</v>
+      </c>
+      <c r="I91" s="50" t="s">
         <v>333</v>
       </c>
-      <c r="J91" s="46" t="s">
-        <v>465</v>
-      </c>
-      <c r="K91" s="88" t="s">
-        <v>410</v>
-      </c>
-      <c r="L91" s="46">
+      <c r="J91" s="50" t="s">
+        <v>464</v>
+      </c>
+      <c r="K91" s="72" t="s">
+        <v>410</v>
+      </c>
+      <c r="L91" s="50">
         <v>1</v>
       </c>
-      <c r="M91" s="46">
+      <c r="M91" s="50">
         <f t="shared" si="5"/>
         <v>5</v>
       </c>
-      <c r="N91" s="46">
+      <c r="N91" s="50">
         <v>6</v>
       </c>
-      <c r="O91" s="59" t="s">
+      <c r="O91" s="61" t="s">
         <v>414</v>
       </c>
       <c r="P91" s="60">
@@ -7711,8 +7597,8 @@
         <f t="shared" si="6"/>
         <v>176.7936</v>
       </c>
-      <c r="R91" s="48"/>
-      <c r="S91" s="48"/>
+      <c r="R91" s="52"/>
+      <c r="S91" s="53"/>
     </row>
     <row r="92" spans="1:20" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A92" s="1"/>
@@ -7720,53 +7606,55 @@
         <f t="shared" si="4"/>
         <v>83</v>
       </c>
-      <c r="C92" s="77" t="s">
+      <c r="C92" s="67" t="s">
         <v>396</v>
       </c>
-      <c r="D92" s="50" t="s">
+      <c r="D92" s="46" t="s">
         <v>88</v>
       </c>
-      <c r="E92" s="51" t="s">
+      <c r="E92" s="47" t="s">
         <v>179</v>
       </c>
-      <c r="F92" s="50" t="s">
+      <c r="F92" s="46" t="s">
         <v>226</v>
       </c>
-      <c r="G92" s="51" t="s">
+      <c r="G92" s="47" t="s">
         <v>292</v>
       </c>
-      <c r="H92" s="50" t="s">
-        <v>410</v>
-      </c>
-      <c r="I92" s="50" t="s">
+      <c r="H92" s="46" t="s">
+        <v>410</v>
+      </c>
+      <c r="I92" s="46" t="s">
         <v>304</v>
       </c>
-      <c r="J92" s="50"/>
-      <c r="K92" s="87" t="s">
-        <v>410</v>
-      </c>
-      <c r="L92" s="50">
+      <c r="J92" s="46" t="s">
+        <v>410</v>
+      </c>
+      <c r="K92" s="73" t="s">
+        <v>410</v>
+      </c>
+      <c r="L92" s="46">
         <v>1</v>
       </c>
-      <c r="M92" s="50">
+      <c r="M92" s="46">
         <f t="shared" si="5"/>
         <v>5</v>
       </c>
-      <c r="N92" s="50">
+      <c r="N92" s="46">
         <v>6</v>
       </c>
-      <c r="O92" s="62" t="s">
+      <c r="O92" s="58" t="s">
         <v>408</v>
       </c>
-      <c r="P92" s="61">
+      <c r="P92" s="59">
         <v>1.48</v>
       </c>
-      <c r="Q92" s="61">
+      <c r="Q92" s="59">
         <f t="shared" si="6"/>
         <v>8.879999999999999</v>
       </c>
-      <c r="R92" s="52"/>
-      <c r="S92" s="52"/>
+      <c r="R92" s="48"/>
+      <c r="S92" s="48"/>
     </row>
     <row r="93" spans="1:20" ht="24.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A93" s="1"/>
@@ -7774,42 +7662,44 @@
         <f t="shared" si="4"/>
         <v>84</v>
       </c>
-      <c r="C93" s="76" t="s">
+      <c r="C93" s="68" t="s">
         <v>396</v>
       </c>
-      <c r="D93" s="46" t="s">
+      <c r="D93" s="50" t="s">
         <v>89</v>
       </c>
-      <c r="E93" s="47" t="s">
+      <c r="E93" s="51" t="s">
         <v>180</v>
       </c>
-      <c r="F93" s="46" t="s">
+      <c r="F93" s="50" t="s">
         <v>409</v>
       </c>
-      <c r="G93" s="47" t="s">
+      <c r="G93" s="51" t="s">
         <v>229</v>
       </c>
-      <c r="H93" s="46" t="s">
-        <v>410</v>
-      </c>
-      <c r="I93" s="46" t="s">
+      <c r="H93" s="50" t="s">
+        <v>410</v>
+      </c>
+      <c r="I93" s="50" t="s">
         <v>334</v>
       </c>
-      <c r="J93" s="46"/>
-      <c r="K93" s="88" t="s">
-        <v>410</v>
-      </c>
-      <c r="L93" s="46">
+      <c r="J93" s="50" t="s">
+        <v>410</v>
+      </c>
+      <c r="K93" s="72" t="s">
+        <v>410</v>
+      </c>
+      <c r="L93" s="50">
         <v>1</v>
       </c>
-      <c r="M93" s="46">
+      <c r="M93" s="50">
         <f t="shared" si="5"/>
         <v>5</v>
       </c>
-      <c r="N93" s="46">
+      <c r="N93" s="50">
         <v>6</v>
       </c>
-      <c r="O93" s="104" t="s">
+      <c r="O93" s="61" t="s">
         <v>408</v>
       </c>
       <c r="P93" s="60">
@@ -7819,8 +7709,8 @@
         <f t="shared" si="6"/>
         <v>26.52</v>
       </c>
-      <c r="R93" s="48"/>
-      <c r="S93" s="48"/>
+      <c r="R93" s="52"/>
+      <c r="S93" s="53"/>
     </row>
     <row r="94" spans="1:20" ht="36.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A94" s="1"/>
@@ -7828,55 +7718,55 @@
         <f t="shared" si="4"/>
         <v>85</v>
       </c>
-      <c r="C94" s="77" t="s">
+      <c r="C94" s="67" t="s">
         <v>396</v>
       </c>
-      <c r="D94" s="50" t="s">
+      <c r="D94" s="46" t="s">
         <v>90</v>
       </c>
-      <c r="E94" s="51" t="s">
+      <c r="E94" s="47" t="s">
         <v>181</v>
       </c>
-      <c r="F94" s="50" t="s">
+      <c r="F94" s="46" t="s">
         <v>408</v>
       </c>
-      <c r="G94" s="51" t="s">
+      <c r="G94" s="47" t="s">
         <v>230</v>
       </c>
-      <c r="H94" s="50" t="s">
-        <v>410</v>
-      </c>
-      <c r="I94" s="50" t="s">
-        <v>511</v>
-      </c>
-      <c r="J94" s="50" t="s">
+      <c r="H94" s="46" t="s">
+        <v>410</v>
+      </c>
+      <c r="I94" s="46" t="s">
         <v>510</v>
       </c>
-      <c r="K94" s="87" t="s">
-        <v>410</v>
-      </c>
-      <c r="L94" s="50">
+      <c r="J94" s="46" t="s">
+        <v>509</v>
+      </c>
+      <c r="K94" s="73" t="s">
+        <v>410</v>
+      </c>
+      <c r="L94" s="46">
         <v>4</v>
       </c>
-      <c r="M94" s="50">
+      <c r="M94" s="46">
         <f t="shared" si="5"/>
         <v>20</v>
       </c>
-      <c r="N94" s="50">
+      <c r="N94" s="46">
         <v>22</v>
       </c>
-      <c r="O94" s="62" t="s">
-        <v>414</v>
-      </c>
-      <c r="P94" s="61">
+      <c r="O94" s="58" t="s">
+        <v>414</v>
+      </c>
+      <c r="P94" s="59">
         <v>0.51759999999999995</v>
       </c>
-      <c r="Q94" s="61">
+      <c r="Q94" s="59">
         <f t="shared" si="6"/>
         <v>11.387199999999998</v>
       </c>
-      <c r="R94" s="52"/>
-      <c r="S94" s="52"/>
+      <c r="R94" s="48"/>
+      <c r="S94" s="48"/>
     </row>
     <row r="95" spans="1:20" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A95" s="1"/>
@@ -7884,44 +7774,44 @@
         <f t="shared" si="4"/>
         <v>86</v>
       </c>
-      <c r="C95" s="76" t="s">
+      <c r="C95" s="68" t="s">
         <v>396</v>
       </c>
-      <c r="D95" s="46" t="s">
+      <c r="D95" s="50" t="s">
         <v>91</v>
       </c>
-      <c r="E95" s="47" t="s">
+      <c r="E95" s="51" t="s">
         <v>182</v>
       </c>
-      <c r="F95" s="46" t="s">
+      <c r="F95" s="50" t="s">
         <v>231</v>
       </c>
-      <c r="G95" s="47" t="s">
+      <c r="G95" s="51" t="s">
         <v>293</v>
       </c>
-      <c r="H95" s="46" t="s">
-        <v>410</v>
-      </c>
-      <c r="I95" s="46" t="s">
+      <c r="H95" s="50" t="s">
+        <v>410</v>
+      </c>
+      <c r="I95" s="50" t="s">
         <v>332</v>
       </c>
-      <c r="J95" s="46" t="s">
-        <v>466</v>
-      </c>
-      <c r="K95" s="88" t="s">
-        <v>410</v>
-      </c>
-      <c r="L95" s="46">
+      <c r="J95" s="50" t="s">
+        <v>465</v>
+      </c>
+      <c r="K95" s="72" t="s">
+        <v>410</v>
+      </c>
+      <c r="L95" s="50">
         <v>3</v>
       </c>
-      <c r="M95" s="46">
+      <c r="M95" s="50">
         <f t="shared" si="5"/>
         <v>15</v>
       </c>
-      <c r="N95" s="46">
+      <c r="N95" s="50">
         <v>17</v>
       </c>
-      <c r="O95" s="59" t="s">
+      <c r="O95" s="61" t="s">
         <v>414</v>
       </c>
       <c r="P95" s="60">
@@ -7931,8 +7821,8 @@
         <f t="shared" si="6"/>
         <v>5.6729000000000003</v>
       </c>
-      <c r="R95" s="48"/>
-      <c r="S95" s="48"/>
+      <c r="R95" s="52"/>
+      <c r="S95" s="53"/>
     </row>
     <row r="96" spans="1:20" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A96" s="1"/>
@@ -7940,55 +7830,55 @@
         <f t="shared" si="4"/>
         <v>87</v>
       </c>
-      <c r="C96" s="77" t="s">
+      <c r="C96" s="67" t="s">
         <v>396</v>
       </c>
-      <c r="D96" s="50" t="s">
+      <c r="D96" s="46" t="s">
         <v>92</v>
       </c>
-      <c r="E96" s="51" t="s">
+      <c r="E96" s="47" t="s">
         <v>183</v>
       </c>
-      <c r="F96" s="50" t="s">
+      <c r="F96" s="46" t="s">
         <v>232</v>
       </c>
-      <c r="G96" s="51" t="s">
+      <c r="G96" s="47" t="s">
         <v>294</v>
       </c>
-      <c r="H96" s="50" t="s">
-        <v>410</v>
-      </c>
-      <c r="I96" s="50" t="s">
+      <c r="H96" s="46" t="s">
+        <v>410</v>
+      </c>
+      <c r="I96" s="46" t="s">
         <v>332</v>
       </c>
-      <c r="J96" s="50" t="s">
-        <v>467</v>
-      </c>
-      <c r="K96" s="87" t="s">
-        <v>410</v>
-      </c>
-      <c r="L96" s="50">
+      <c r="J96" s="46" t="s">
+        <v>466</v>
+      </c>
+      <c r="K96" s="73" t="s">
+        <v>410</v>
+      </c>
+      <c r="L96" s="46">
         <v>1</v>
       </c>
-      <c r="M96" s="50">
+      <c r="M96" s="46">
         <f t="shared" si="5"/>
         <v>5</v>
       </c>
-      <c r="N96" s="50">
+      <c r="N96" s="46">
         <v>6</v>
       </c>
-      <c r="O96" s="62" t="s">
-        <v>414</v>
-      </c>
-      <c r="P96" s="61">
+      <c r="O96" s="58" t="s">
+        <v>414</v>
+      </c>
+      <c r="P96" s="59">
         <v>24.546299999999999</v>
       </c>
-      <c r="Q96" s="61">
+      <c r="Q96" s="59">
         <f t="shared" si="6"/>
         <v>147.27779999999998</v>
       </c>
-      <c r="R96" s="52"/>
-      <c r="S96" s="52"/>
+      <c r="R96" s="48"/>
+      <c r="S96" s="48"/>
     </row>
     <row r="97" spans="1:19" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A97" s="1"/>
@@ -7996,44 +7886,44 @@
         <f t="shared" si="4"/>
         <v>88</v>
       </c>
-      <c r="C97" s="76" t="s">
+      <c r="C97" s="68" t="s">
         <v>396</v>
       </c>
-      <c r="D97" s="46" t="s">
+      <c r="D97" s="50" t="s">
         <v>93</v>
       </c>
-      <c r="E97" s="47" t="s">
+      <c r="E97" s="51" t="s">
         <v>184</v>
       </c>
-      <c r="F97" s="46" t="s">
+      <c r="F97" s="50" t="s">
         <v>233</v>
       </c>
-      <c r="G97" s="47" t="s">
+      <c r="G97" s="51" t="s">
         <v>295</v>
       </c>
-      <c r="H97" s="46" t="s">
-        <v>410</v>
-      </c>
-      <c r="I97" s="46" t="s">
+      <c r="H97" s="50" t="s">
+        <v>410</v>
+      </c>
+      <c r="I97" s="50" t="s">
         <v>335</v>
       </c>
-      <c r="J97" s="46" t="s">
-        <v>468</v>
-      </c>
-      <c r="K97" s="88" t="s">
-        <v>410</v>
-      </c>
-      <c r="L97" s="46">
+      <c r="J97" s="50" t="s">
+        <v>467</v>
+      </c>
+      <c r="K97" s="72" t="s">
+        <v>410</v>
+      </c>
+      <c r="L97" s="50">
         <v>1</v>
       </c>
-      <c r="M97" s="46">
+      <c r="M97" s="50">
         <f t="shared" si="5"/>
         <v>5</v>
       </c>
-      <c r="N97" s="46">
+      <c r="N97" s="50">
         <v>6</v>
       </c>
-      <c r="O97" s="59" t="s">
+      <c r="O97" s="61" t="s">
         <v>414</v>
       </c>
       <c r="P97" s="60">
@@ -8043,8 +7933,8 @@
         <f t="shared" si="6"/>
         <v>25.142400000000002</v>
       </c>
-      <c r="R97" s="48"/>
-      <c r="S97" s="48"/>
+      <c r="R97" s="52"/>
+      <c r="S97" s="53"/>
     </row>
     <row r="98" spans="1:19" ht="24.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A98" s="1"/>
@@ -8052,55 +7942,55 @@
         <f t="shared" si="4"/>
         <v>89</v>
       </c>
-      <c r="C98" s="77" t="s">
+      <c r="C98" s="67" t="s">
         <v>396</v>
       </c>
-      <c r="D98" s="50" t="s">
+      <c r="D98" s="46" t="s">
         <v>94</v>
       </c>
-      <c r="E98" s="51" t="s">
+      <c r="E98" s="47" t="s">
         <v>185</v>
       </c>
-      <c r="F98" s="50" t="s">
+      <c r="F98" s="46" t="s">
         <v>408</v>
       </c>
-      <c r="G98" s="51" t="s">
+      <c r="G98" s="47" t="s">
         <v>234</v>
       </c>
-      <c r="H98" s="50" t="s">
-        <v>410</v>
-      </c>
-      <c r="I98" s="50" t="s">
+      <c r="H98" s="46" t="s">
+        <v>410</v>
+      </c>
+      <c r="I98" s="46" t="s">
         <v>336</v>
       </c>
-      <c r="J98" s="50" t="s">
-        <v>469</v>
-      </c>
-      <c r="K98" s="87" t="s">
-        <v>410</v>
-      </c>
-      <c r="L98" s="50">
+      <c r="J98" s="46" t="s">
+        <v>468</v>
+      </c>
+      <c r="K98" s="73" t="s">
+        <v>410</v>
+      </c>
+      <c r="L98" s="46">
         <v>1</v>
       </c>
-      <c r="M98" s="50">
+      <c r="M98" s="46">
         <f t="shared" si="5"/>
         <v>5</v>
       </c>
-      <c r="N98" s="50">
+      <c r="N98" s="46">
         <v>6</v>
       </c>
-      <c r="O98" s="62" t="s">
-        <v>414</v>
-      </c>
-      <c r="P98" s="61">
+      <c r="O98" s="58" t="s">
+        <v>414</v>
+      </c>
+      <c r="P98" s="59">
         <v>1.1451</v>
       </c>
-      <c r="Q98" s="61">
+      <c r="Q98" s="59">
         <f t="shared" si="6"/>
         <v>6.8705999999999996</v>
       </c>
-      <c r="R98" s="52"/>
-      <c r="S98" s="52"/>
+      <c r="R98" s="48"/>
+      <c r="S98" s="48"/>
     </row>
     <row r="99" spans="1:19" ht="36.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A99" s="1"/>
@@ -8108,44 +7998,44 @@
         <f t="shared" si="4"/>
         <v>90</v>
       </c>
-      <c r="C99" s="76" t="s">
+      <c r="C99" s="68" t="s">
         <v>397</v>
       </c>
-      <c r="D99" s="46" t="s">
+      <c r="D99" s="50" t="s">
         <v>95</v>
       </c>
-      <c r="E99" s="47" t="s">
-        <v>533</v>
-      </c>
-      <c r="F99" s="46" t="s">
+      <c r="E99" s="51" t="s">
+        <v>530</v>
+      </c>
+      <c r="F99" s="50" t="s">
         <v>408</v>
       </c>
-      <c r="G99" s="47" t="s">
-        <v>530</v>
-      </c>
-      <c r="H99" s="83" t="s">
-        <v>410</v>
-      </c>
-      <c r="I99" s="46" t="s">
+      <c r="G99" s="51" t="s">
+        <v>527</v>
+      </c>
+      <c r="H99" s="50" t="s">
+        <v>410</v>
+      </c>
+      <c r="I99" s="50" t="s">
+        <v>528</v>
+      </c>
+      <c r="J99" s="50" t="s">
         <v>531</v>
       </c>
-      <c r="J99" s="46" t="s">
-        <v>534</v>
-      </c>
-      <c r="K99" s="47" t="s">
-        <v>532</v>
-      </c>
-      <c r="L99" s="46">
+      <c r="K99" s="72" t="s">
+        <v>529</v>
+      </c>
+      <c r="L99" s="50">
         <v>1</v>
       </c>
-      <c r="M99" s="46">
+      <c r="M99" s="50">
         <f t="shared" si="5"/>
         <v>5</v>
       </c>
-      <c r="N99" s="46">
+      <c r="N99" s="50">
         <v>6</v>
       </c>
-      <c r="O99" s="59" t="s">
+      <c r="O99" s="61" t="s">
         <v>414</v>
       </c>
       <c r="P99" s="60">
@@ -8155,8 +8045,8 @@
         <f t="shared" si="6"/>
         <v>1.2804</v>
       </c>
-      <c r="R99" s="84"/>
-      <c r="S99" s="48"/>
+      <c r="R99" s="52"/>
+      <c r="S99" s="53"/>
     </row>
     <row r="100" spans="1:19" ht="36.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A100" s="1"/>
@@ -8164,55 +8054,55 @@
         <f t="shared" si="4"/>
         <v>91</v>
       </c>
-      <c r="C100" s="77" t="s">
+      <c r="C100" s="67" t="s">
         <v>397</v>
       </c>
-      <c r="D100" s="50" t="s">
+      <c r="D100" s="46" t="s">
         <v>96</v>
       </c>
-      <c r="E100" s="51" t="s">
+      <c r="E100" s="47" t="s">
         <v>186</v>
       </c>
-      <c r="F100" s="50" t="s">
+      <c r="F100" s="46" t="s">
         <v>408</v>
       </c>
-      <c r="G100" s="51" t="s">
+      <c r="G100" s="47" t="s">
         <v>235</v>
       </c>
-      <c r="H100" s="50" t="s">
-        <v>410</v>
-      </c>
-      <c r="I100" s="50" t="s">
+      <c r="H100" s="46" t="s">
+        <v>410</v>
+      </c>
+      <c r="I100" s="46" t="s">
         <v>322</v>
       </c>
-      <c r="J100" s="50" t="s">
-        <v>470</v>
-      </c>
-      <c r="K100" s="87" t="s">
+      <c r="J100" s="46" t="s">
+        <v>469</v>
+      </c>
+      <c r="K100" s="73" t="s">
         <v>382</v>
       </c>
-      <c r="L100" s="50">
+      <c r="L100" s="46">
         <v>1</v>
       </c>
-      <c r="M100" s="50">
+      <c r="M100" s="46">
         <f t="shared" si="5"/>
         <v>5</v>
       </c>
-      <c r="N100" s="50">
+      <c r="N100" s="46">
         <v>6</v>
       </c>
-      <c r="O100" s="62" t="s">
-        <v>414</v>
-      </c>
-      <c r="P100" s="61">
+      <c r="O100" s="58" t="s">
+        <v>414</v>
+      </c>
+      <c r="P100" s="59">
         <v>0.107</v>
       </c>
-      <c r="Q100" s="61">
+      <c r="Q100" s="59">
         <f t="shared" si="6"/>
         <v>0.64200000000000002</v>
       </c>
-      <c r="R100" s="52"/>
-      <c r="S100" s="52"/>
+      <c r="R100" s="48"/>
+      <c r="S100" s="48"/>
     </row>
     <row r="101" spans="1:19" ht="36.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A101" s="1"/>
@@ -8220,44 +8110,44 @@
         <f t="shared" si="4"/>
         <v>92</v>
       </c>
-      <c r="C101" s="76" t="s">
+      <c r="C101" s="68" t="s">
         <v>397</v>
       </c>
-      <c r="D101" s="46" t="s">
+      <c r="D101" s="50" t="s">
         <v>97</v>
       </c>
-      <c r="E101" s="47" t="s">
+      <c r="E101" s="51" t="s">
         <v>187</v>
       </c>
-      <c r="F101" s="46" t="s">
+      <c r="F101" s="50" t="s">
         <v>408</v>
       </c>
-      <c r="G101" s="47" t="s">
+      <c r="G101" s="51" t="s">
         <v>236</v>
       </c>
-      <c r="H101" s="46" t="s">
-        <v>410</v>
-      </c>
-      <c r="I101" s="46" t="s">
+      <c r="H101" s="50" t="s">
+        <v>410</v>
+      </c>
+      <c r="I101" s="50" t="s">
         <v>337</v>
       </c>
-      <c r="J101" s="46" t="s">
-        <v>471</v>
-      </c>
-      <c r="K101" s="91" t="s">
+      <c r="J101" s="50" t="s">
+        <v>470</v>
+      </c>
+      <c r="K101" s="72" t="s">
         <v>383</v>
       </c>
-      <c r="L101" s="58">
+      <c r="L101" s="50">
         <v>1</v>
       </c>
-      <c r="M101" s="46">
+      <c r="M101" s="50">
         <f t="shared" si="5"/>
         <v>5</v>
       </c>
-      <c r="N101" s="46">
+      <c r="N101" s="50">
         <v>6</v>
       </c>
-      <c r="O101" s="59" t="s">
+      <c r="O101" s="61" t="s">
         <v>414</v>
       </c>
       <c r="P101" s="60">
@@ -8267,8 +8157,8 @@
         <f t="shared" si="6"/>
         <v>2.1132</v>
       </c>
-      <c r="R101" s="48"/>
-      <c r="S101" s="48"/>
+      <c r="R101" s="52"/>
+      <c r="S101" s="53"/>
     </row>
     <row r="102" spans="1:19" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A102" s="1"/>
@@ -8284,17 +8174,17 @@
       <c r="K102" s="37"/>
       <c r="L102" s="37"/>
       <c r="M102" s="37"/>
-      <c r="N102" s="94" t="s">
-        <v>518</v>
-      </c>
-      <c r="O102" s="95"/>
-      <c r="P102" s="95"/>
-      <c r="Q102" s="73">
+      <c r="N102" s="74" t="s">
+        <v>517</v>
+      </c>
+      <c r="O102" s="75"/>
+      <c r="P102" s="75"/>
+      <c r="Q102" s="65">
         <f>SUM(Q10:Q101)</f>
-        <v>717.43269999999995</v>
-      </c>
-      <c r="R102" s="100"/>
-      <c r="S102" s="101"/>
+        <v>713.42879999999991</v>
+      </c>
+      <c r="R102" s="80"/>
+      <c r="S102" s="81"/>
     </row>
     <row r="103" spans="1:19" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A103" s="1"/>
@@ -8310,29 +8200,20 @@
       <c r="K103" s="10"/>
       <c r="L103" s="10"/>
       <c r="M103" s="10"/>
-      <c r="N103" s="94" t="s">
-        <v>519</v>
-      </c>
-      <c r="O103" s="95"/>
-      <c r="P103" s="95"/>
-      <c r="Q103" s="74">
+      <c r="N103" s="74" t="s">
+        <v>518</v>
+      </c>
+      <c r="O103" s="75"/>
+      <c r="P103" s="75"/>
+      <c r="Q103" s="66">
         <f>Q102/5</f>
-        <v>143.48653999999999</v>
-      </c>
-      <c r="R103" s="102"/>
-      <c r="S103" s="103"/>
-    </row>
-    <row r="104" spans="1:19" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="N104" s="94" t="s">
-        <v>520</v>
-      </c>
-      <c r="O104" s="95"/>
-      <c r="P104" s="95"/>
-      <c r="Q104" s="74"/>
+        <v>142.68575999999999</v>
+      </c>
+      <c r="R103" s="82"/>
+      <c r="S103" s="83"/>
     </row>
   </sheetData>
-  <mergeCells count="6">
-    <mergeCell ref="N104:P104"/>
+  <mergeCells count="5">
     <mergeCell ref="K1:S1"/>
     <mergeCell ref="S3:S8"/>
     <mergeCell ref="R102:S103"/>
@@ -8340,93 +8221,93 @@
     <mergeCell ref="N103:P103"/>
   </mergeCells>
   <hyperlinks>
-    <hyperlink ref="O10" r:id="rId1"/>
-    <hyperlink ref="O11" r:id="rId2"/>
-    <hyperlink ref="O12" r:id="rId3"/>
-    <hyperlink ref="O13" r:id="rId4"/>
-    <hyperlink ref="O14" r:id="rId5"/>
-    <hyperlink ref="O15" r:id="rId6"/>
-    <hyperlink ref="O17" r:id="rId7"/>
-    <hyperlink ref="O18" r:id="rId8"/>
-    <hyperlink ref="O19" r:id="rId9"/>
-    <hyperlink ref="O20" r:id="rId10"/>
-    <hyperlink ref="O21" r:id="rId11"/>
-    <hyperlink ref="O22" r:id="rId12"/>
-    <hyperlink ref="O23" r:id="rId13"/>
-    <hyperlink ref="O27" r:id="rId14"/>
-    <hyperlink ref="O36" r:id="rId15"/>
-    <hyperlink ref="O37" r:id="rId16"/>
-    <hyperlink ref="O38" r:id="rId17"/>
-    <hyperlink ref="O40" r:id="rId18"/>
-    <hyperlink ref="O41" r:id="rId19"/>
-    <hyperlink ref="O42" r:id="rId20"/>
-    <hyperlink ref="O44" r:id="rId21"/>
-    <hyperlink ref="O45" r:id="rId22"/>
-    <hyperlink ref="O52" r:id="rId23"/>
-    <hyperlink ref="O54" r:id="rId24"/>
-    <hyperlink ref="O56" r:id="rId25"/>
-    <hyperlink ref="O57" r:id="rId26"/>
-    <hyperlink ref="O58" r:id="rId27"/>
-    <hyperlink ref="O59" r:id="rId28"/>
-    <hyperlink ref="O60" r:id="rId29"/>
-    <hyperlink ref="O61" r:id="rId30"/>
-    <hyperlink ref="O62" r:id="rId31"/>
-    <hyperlink ref="O63" r:id="rId32"/>
-    <hyperlink ref="O64" r:id="rId33"/>
-    <hyperlink ref="O65" r:id="rId34"/>
-    <hyperlink ref="O66" r:id="rId35"/>
-    <hyperlink ref="O68" r:id="rId36"/>
-    <hyperlink ref="O69" r:id="rId37"/>
-    <hyperlink ref="O70" r:id="rId38"/>
-    <hyperlink ref="O71" r:id="rId39"/>
-    <hyperlink ref="O72" r:id="rId40"/>
-    <hyperlink ref="O73" r:id="rId41"/>
-    <hyperlink ref="O75" r:id="rId42"/>
-    <hyperlink ref="O76" r:id="rId43"/>
-    <hyperlink ref="O77" r:id="rId44"/>
-    <hyperlink ref="O79" r:id="rId45"/>
-    <hyperlink ref="O80" r:id="rId46"/>
-    <hyperlink ref="O81" r:id="rId47"/>
-    <hyperlink ref="O82" r:id="rId48"/>
-    <hyperlink ref="O84" r:id="rId49"/>
-    <hyperlink ref="O87" r:id="rId50"/>
-    <hyperlink ref="O90" r:id="rId51"/>
-    <hyperlink ref="O91" r:id="rId52"/>
-    <hyperlink ref="O95" r:id="rId53"/>
-    <hyperlink ref="O96" r:id="rId54"/>
-    <hyperlink ref="O97" r:id="rId55"/>
-    <hyperlink ref="O98" r:id="rId56"/>
-    <hyperlink ref="O100" r:id="rId57"/>
-    <hyperlink ref="O101" r:id="rId58"/>
-    <hyperlink ref="O24" r:id="rId59"/>
-    <hyperlink ref="O26" r:id="rId60"/>
-    <hyperlink ref="O28" r:id="rId61"/>
-    <hyperlink ref="O29" r:id="rId62"/>
-    <hyperlink ref="O31" r:id="rId63"/>
-    <hyperlink ref="O39" r:id="rId64"/>
-    <hyperlink ref="O48" r:id="rId65"/>
-    <hyperlink ref="O47" r:id="rId66"/>
-    <hyperlink ref="O51" r:id="rId67"/>
-    <hyperlink ref="O53" r:id="rId68"/>
-    <hyperlink ref="O55" r:id="rId69"/>
-    <hyperlink ref="O67" r:id="rId70"/>
-    <hyperlink ref="O83" r:id="rId71"/>
-    <hyperlink ref="O85" r:id="rId72"/>
-    <hyperlink ref="O43" r:id="rId73"/>
-    <hyperlink ref="O49" r:id="rId74"/>
-    <hyperlink ref="O74" r:id="rId75"/>
-    <hyperlink ref="O78" r:id="rId76"/>
-    <hyperlink ref="O89" r:id="rId77"/>
-    <hyperlink ref="O94" r:id="rId78"/>
-    <hyperlink ref="O33" r:id="rId79"/>
-    <hyperlink ref="O34" r:id="rId80"/>
-    <hyperlink ref="O35" r:id="rId81"/>
-    <hyperlink ref="O88" r:id="rId82" display="Aliexpress"/>
-    <hyperlink ref="O16" r:id="rId83"/>
-    <hyperlink ref="O30" r:id="rId84"/>
-    <hyperlink ref="O99" r:id="rId85"/>
-    <hyperlink ref="O25" r:id="rId86"/>
-    <hyperlink ref="O50" r:id="rId87"/>
+    <hyperlink ref="O10" r:id="rId1" xr:uid="{00000000-0004-0000-0000-000000000000}"/>
+    <hyperlink ref="O11" r:id="rId2" xr:uid="{00000000-0004-0000-0000-000001000000}"/>
+    <hyperlink ref="O12" r:id="rId3" xr:uid="{00000000-0004-0000-0000-000002000000}"/>
+    <hyperlink ref="O13" r:id="rId4" xr:uid="{00000000-0004-0000-0000-000003000000}"/>
+    <hyperlink ref="O14" r:id="rId5" xr:uid="{00000000-0004-0000-0000-000004000000}"/>
+    <hyperlink ref="O15" r:id="rId6" xr:uid="{00000000-0004-0000-0000-000005000000}"/>
+    <hyperlink ref="O17" r:id="rId7" xr:uid="{00000000-0004-0000-0000-000006000000}"/>
+    <hyperlink ref="O18" r:id="rId8" xr:uid="{00000000-0004-0000-0000-000007000000}"/>
+    <hyperlink ref="O19" r:id="rId9" xr:uid="{00000000-0004-0000-0000-000008000000}"/>
+    <hyperlink ref="O20" r:id="rId10" xr:uid="{00000000-0004-0000-0000-000009000000}"/>
+    <hyperlink ref="O21" r:id="rId11" xr:uid="{00000000-0004-0000-0000-00000A000000}"/>
+    <hyperlink ref="O22" r:id="rId12" xr:uid="{00000000-0004-0000-0000-00000B000000}"/>
+    <hyperlink ref="O23" r:id="rId13" xr:uid="{00000000-0004-0000-0000-00000C000000}"/>
+    <hyperlink ref="O27" r:id="rId14" xr:uid="{00000000-0004-0000-0000-00000D000000}"/>
+    <hyperlink ref="O36" r:id="rId15" xr:uid="{00000000-0004-0000-0000-00000E000000}"/>
+    <hyperlink ref="O37" r:id="rId16" xr:uid="{00000000-0004-0000-0000-00000F000000}"/>
+    <hyperlink ref="O38" r:id="rId17" xr:uid="{00000000-0004-0000-0000-000010000000}"/>
+    <hyperlink ref="O40" r:id="rId18" xr:uid="{00000000-0004-0000-0000-000011000000}"/>
+    <hyperlink ref="O41" r:id="rId19" xr:uid="{00000000-0004-0000-0000-000012000000}"/>
+    <hyperlink ref="O42" r:id="rId20" xr:uid="{00000000-0004-0000-0000-000013000000}"/>
+    <hyperlink ref="O44" r:id="rId21" xr:uid="{00000000-0004-0000-0000-000014000000}"/>
+    <hyperlink ref="O45" r:id="rId22" xr:uid="{00000000-0004-0000-0000-000015000000}"/>
+    <hyperlink ref="O52" r:id="rId23" xr:uid="{00000000-0004-0000-0000-000016000000}"/>
+    <hyperlink ref="O54" r:id="rId24" xr:uid="{00000000-0004-0000-0000-000017000000}"/>
+    <hyperlink ref="O56" r:id="rId25" xr:uid="{00000000-0004-0000-0000-000018000000}"/>
+    <hyperlink ref="O57" r:id="rId26" xr:uid="{00000000-0004-0000-0000-000019000000}"/>
+    <hyperlink ref="O58" r:id="rId27" xr:uid="{00000000-0004-0000-0000-00001A000000}"/>
+    <hyperlink ref="O59" r:id="rId28" xr:uid="{00000000-0004-0000-0000-00001B000000}"/>
+    <hyperlink ref="O60" r:id="rId29" xr:uid="{00000000-0004-0000-0000-00001C000000}"/>
+    <hyperlink ref="O61" r:id="rId30" xr:uid="{00000000-0004-0000-0000-00001D000000}"/>
+    <hyperlink ref="O62" r:id="rId31" xr:uid="{00000000-0004-0000-0000-00001E000000}"/>
+    <hyperlink ref="O63" r:id="rId32" xr:uid="{00000000-0004-0000-0000-00001F000000}"/>
+    <hyperlink ref="O64" r:id="rId33" xr:uid="{00000000-0004-0000-0000-000020000000}"/>
+    <hyperlink ref="O65" r:id="rId34" xr:uid="{00000000-0004-0000-0000-000021000000}"/>
+    <hyperlink ref="O66" r:id="rId35" xr:uid="{00000000-0004-0000-0000-000022000000}"/>
+    <hyperlink ref="O68" r:id="rId36" xr:uid="{00000000-0004-0000-0000-000023000000}"/>
+    <hyperlink ref="O69" r:id="rId37" xr:uid="{00000000-0004-0000-0000-000024000000}"/>
+    <hyperlink ref="O70" r:id="rId38" xr:uid="{00000000-0004-0000-0000-000025000000}"/>
+    <hyperlink ref="O71" r:id="rId39" xr:uid="{00000000-0004-0000-0000-000026000000}"/>
+    <hyperlink ref="O72" r:id="rId40" xr:uid="{00000000-0004-0000-0000-000027000000}"/>
+    <hyperlink ref="O73" r:id="rId41" xr:uid="{00000000-0004-0000-0000-000028000000}"/>
+    <hyperlink ref="O76" r:id="rId42" xr:uid="{00000000-0004-0000-0000-00002A000000}"/>
+    <hyperlink ref="O77" r:id="rId43" xr:uid="{00000000-0004-0000-0000-00002B000000}"/>
+    <hyperlink ref="O79" r:id="rId44" xr:uid="{00000000-0004-0000-0000-00002C000000}"/>
+    <hyperlink ref="O80" r:id="rId45" xr:uid="{00000000-0004-0000-0000-00002D000000}"/>
+    <hyperlink ref="O81" r:id="rId46" xr:uid="{00000000-0004-0000-0000-00002E000000}"/>
+    <hyperlink ref="O82" r:id="rId47" xr:uid="{00000000-0004-0000-0000-00002F000000}"/>
+    <hyperlink ref="O84" r:id="rId48" xr:uid="{00000000-0004-0000-0000-000030000000}"/>
+    <hyperlink ref="O87" r:id="rId49" xr:uid="{00000000-0004-0000-0000-000031000000}"/>
+    <hyperlink ref="O90" r:id="rId50" xr:uid="{00000000-0004-0000-0000-000032000000}"/>
+    <hyperlink ref="O91" r:id="rId51" xr:uid="{00000000-0004-0000-0000-000033000000}"/>
+    <hyperlink ref="O95" r:id="rId52" xr:uid="{00000000-0004-0000-0000-000034000000}"/>
+    <hyperlink ref="O96" r:id="rId53" xr:uid="{00000000-0004-0000-0000-000035000000}"/>
+    <hyperlink ref="O97" r:id="rId54" xr:uid="{00000000-0004-0000-0000-000036000000}"/>
+    <hyperlink ref="O98" r:id="rId55" xr:uid="{00000000-0004-0000-0000-000037000000}"/>
+    <hyperlink ref="O100" r:id="rId56" xr:uid="{00000000-0004-0000-0000-000038000000}"/>
+    <hyperlink ref="O101" r:id="rId57" xr:uid="{00000000-0004-0000-0000-000039000000}"/>
+    <hyperlink ref="O24" r:id="rId58" xr:uid="{00000000-0004-0000-0000-00003A000000}"/>
+    <hyperlink ref="O26" r:id="rId59" xr:uid="{00000000-0004-0000-0000-00003B000000}"/>
+    <hyperlink ref="O28" r:id="rId60" xr:uid="{00000000-0004-0000-0000-00003C000000}"/>
+    <hyperlink ref="O29" r:id="rId61" xr:uid="{00000000-0004-0000-0000-00003D000000}"/>
+    <hyperlink ref="O31" r:id="rId62" xr:uid="{00000000-0004-0000-0000-00003E000000}"/>
+    <hyperlink ref="O39" r:id="rId63" xr:uid="{00000000-0004-0000-0000-00003F000000}"/>
+    <hyperlink ref="O48" r:id="rId64" xr:uid="{00000000-0004-0000-0000-000040000000}"/>
+    <hyperlink ref="O47" r:id="rId65" xr:uid="{00000000-0004-0000-0000-000041000000}"/>
+    <hyperlink ref="O51" r:id="rId66" xr:uid="{00000000-0004-0000-0000-000042000000}"/>
+    <hyperlink ref="O53" r:id="rId67" xr:uid="{00000000-0004-0000-0000-000043000000}"/>
+    <hyperlink ref="O55" r:id="rId68" xr:uid="{00000000-0004-0000-0000-000044000000}"/>
+    <hyperlink ref="O67" r:id="rId69" xr:uid="{00000000-0004-0000-0000-000045000000}"/>
+    <hyperlink ref="O83" r:id="rId70" xr:uid="{00000000-0004-0000-0000-000046000000}"/>
+    <hyperlink ref="O85" r:id="rId71" xr:uid="{00000000-0004-0000-0000-000047000000}"/>
+    <hyperlink ref="O43" r:id="rId72" xr:uid="{00000000-0004-0000-0000-000048000000}"/>
+    <hyperlink ref="O49" r:id="rId73" xr:uid="{00000000-0004-0000-0000-000049000000}"/>
+    <hyperlink ref="O74" r:id="rId74" xr:uid="{00000000-0004-0000-0000-00004A000000}"/>
+    <hyperlink ref="O78" r:id="rId75" xr:uid="{00000000-0004-0000-0000-00004B000000}"/>
+    <hyperlink ref="O89" r:id="rId76" xr:uid="{00000000-0004-0000-0000-00004C000000}"/>
+    <hyperlink ref="O94" r:id="rId77" xr:uid="{00000000-0004-0000-0000-00004D000000}"/>
+    <hyperlink ref="O33" r:id="rId78" xr:uid="{00000000-0004-0000-0000-00004E000000}"/>
+    <hyperlink ref="O34" r:id="rId79" xr:uid="{00000000-0004-0000-0000-00004F000000}"/>
+    <hyperlink ref="O35" r:id="rId80" xr:uid="{00000000-0004-0000-0000-000050000000}"/>
+    <hyperlink ref="O88" r:id="rId81" display="Aliexpress" xr:uid="{00000000-0004-0000-0000-000051000000}"/>
+    <hyperlink ref="O16" r:id="rId82" xr:uid="{00000000-0004-0000-0000-000052000000}"/>
+    <hyperlink ref="O30" r:id="rId83" xr:uid="{00000000-0004-0000-0000-000053000000}"/>
+    <hyperlink ref="O99" r:id="rId84" xr:uid="{00000000-0004-0000-0000-000054000000}"/>
+    <hyperlink ref="O25" r:id="rId85" xr:uid="{00000000-0004-0000-0000-000055000000}"/>
+    <hyperlink ref="O50" r:id="rId86" xr:uid="{00000000-0004-0000-0000-000056000000}"/>
+    <hyperlink ref="O75" r:id="rId87" xr:uid="{303610F2-634A-46C3-8C9B-440AB18F1615}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId88"/>
